--- a/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_O2_mean" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_Amp_std" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_O2_mean_final" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_Amp_std_final" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,3051 +545,2007 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.75068493150685</v>
+        <v>9.65</v>
       </c>
       <c r="C2" t="n">
-        <v>35.34189189189189</v>
+        <v>15.46110913916118</v>
       </c>
       <c r="D2" t="n">
-        <v>24.67945205479452</v>
+        <v>18.54935926913667</v>
       </c>
       <c r="E2" t="n">
-        <v>23.87866666666666</v>
+        <v>21.78694941568939</v>
       </c>
       <c r="F2" t="n">
-        <v>24.7445945945946</v>
+        <v>25.15555954722332</v>
       </c>
       <c r="G2" t="n">
-        <v>29.98493150684931</v>
+        <v>28.81458085605667</v>
       </c>
       <c r="H2" t="n">
-        <v>40.67733333333334</v>
+        <v>32.45646831177407</v>
       </c>
       <c r="I2" t="n">
-        <v>50.71095890410958</v>
+        <v>35.8670826286396</v>
       </c>
       <c r="J2" t="n">
-        <v>60.99295774647887</v>
+        <v>38.74707821881903</v>
       </c>
       <c r="K2" t="n">
-        <v>60.28493150684932</v>
+        <v>40.85599750600296</v>
       </c>
       <c r="L2" t="n">
-        <v>61.28219178082193</v>
+        <v>42.37063537461099</v>
       </c>
       <c r="M2" t="n">
-        <v>61.01986301369864</v>
+        <v>43.54229004790477</v>
       </c>
       <c r="N2" t="n">
-        <v>60.75753424657535</v>
+        <v>44.76148005009369</v>
       </c>
       <c r="O2" t="n">
-        <v>62.16805555555556</v>
+        <v>46.20238965044202</v>
       </c>
       <c r="P2" t="n">
-        <v>61.99428571428572</v>
+        <v>47.9041287907293</v>
       </c>
       <c r="Q2" t="n">
-        <v>62.02972972972974</v>
+        <v>49.87108999373954</v>
       </c>
       <c r="R2" t="n">
-        <v>61.8625</v>
+        <v>52.16859961243863</v>
       </c>
       <c r="S2" t="n">
-        <v>62.17837837837838</v>
+        <v>54.88922832528763</v>
       </c>
       <c r="T2" t="n">
-        <v>62.175</v>
+        <v>57.8843165076551</v>
       </c>
       <c r="U2" t="n">
-        <v>62.26351351351352</v>
+        <v>60.91656520343245</v>
       </c>
       <c r="V2" t="n">
-        <v>62.92328767123287</v>
+        <v>63.87146863663083</v>
       </c>
       <c r="W2" t="n">
-        <v>62.79999999999998</v>
+        <v>66.6177309795255</v>
       </c>
       <c r="X2" t="n">
-        <v>63.85945945945945</v>
+        <v>68.87214829232791</v>
       </c>
       <c r="Y2" t="n">
-        <v>65.71891891891892</v>
+        <v>70.6225074454231</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.83879279279279</v>
+        <v>72.04269128413308</v>
       </c>
       <c r="AA2" t="n">
-        <v>67.95866666666666</v>
+        <v>73.25190249284908</v>
       </c>
       <c r="AB2" t="n">
-        <v>70.21917808219177</v>
+        <v>74.08856250605247</v>
       </c>
       <c r="AC2" t="n">
-        <v>72.08904109589041</v>
+        <v>74.70540537820682</v>
       </c>
       <c r="AD2" t="n">
-        <v>73.37534246575342</v>
+        <v>75.3486755601544</v>
       </c>
       <c r="AE2" t="n">
-        <v>73.11527777777776</v>
+        <v>75.93489385348214</v>
       </c>
       <c r="AF2" t="n">
-        <v>73.75675675675676</v>
+        <v>76.44435227314752</v>
       </c>
       <c r="AG2" t="n">
-        <v>74.11917808219179</v>
+        <v>76.96859512627096</v>
       </c>
       <c r="AH2" t="n">
-        <v>74.57361111111112</v>
+        <v>77.45978897757188</v>
       </c>
       <c r="AI2" t="n">
-        <v>74.89305555555556</v>
+        <v>77.78183462950511</v>
       </c>
       <c r="AJ2" t="n">
-        <v>73.97671232876712</v>
+        <v>77.97730360276522</v>
       </c>
       <c r="AK2" t="n">
-        <v>74.48732394366198</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>78.17191704180813</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>78.34836182488422</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.058108108108108</v>
+        <v>8.12973</v>
       </c>
       <c r="C3" t="n">
-        <v>30.24202898550725</v>
+        <v>3.25228039473922</v>
       </c>
       <c r="D3" t="n">
-        <v>27.64782608695652</v>
+        <v>3.364212683650287</v>
       </c>
       <c r="E3" t="n">
-        <v>32.85142857142857</v>
+        <v>3.48287177355173</v>
       </c>
       <c r="F3" t="n">
-        <v>36.16857142857143</v>
+        <v>3.605471173249272</v>
       </c>
       <c r="G3" t="n">
-        <v>42.56764705882352</v>
+        <v>3.729644358550961</v>
       </c>
       <c r="H3" t="n">
-        <v>48.63810924369748</v>
+        <v>3.864440643052854</v>
       </c>
       <c r="I3" t="n">
-        <v>54.70857142857143</v>
+        <v>3.989227608506113</v>
       </c>
       <c r="J3" t="n">
-        <v>59.18695652173913</v>
+        <v>4.02578611658015</v>
       </c>
       <c r="K3" t="n">
-        <v>64.18285714285716</v>
+        <v>3.983985999999987</v>
       </c>
       <c r="L3" t="n">
-        <v>65.53043478260869</v>
+        <v>24.827226</v>
       </c>
       <c r="M3" t="n">
-        <v>66.07777777777777</v>
+        <v>42.64999999999974</v>
       </c>
       <c r="N3" t="n">
-        <v>67.99117647058823</v>
+        <v>43.92647158240941</v>
       </c>
       <c r="O3" t="n">
-        <v>69.31029411764706</v>
+        <v>45.62294152566175</v>
       </c>
       <c r="P3" t="n">
-        <v>67.9014705882353</v>
+        <v>47.39843074614056</v>
       </c>
       <c r="Q3" t="n">
-        <v>66.17720588235295</v>
+        <v>48.86377706684392</v>
       </c>
       <c r="R3" t="n">
-        <v>64.45294117647059</v>
+        <v>50.14980627566681</v>
       </c>
       <c r="S3" t="n">
-        <v>64.35428571428572</v>
+        <v>51.33238789059841</v>
       </c>
       <c r="T3" t="n">
-        <v>63.72608695652175</v>
+        <v>52.25815007245286</v>
       </c>
       <c r="U3" t="n">
-        <v>63.16428571428571</v>
+        <v>53.08098689436493</v>
       </c>
       <c r="V3" t="n">
-        <v>63.05</v>
+        <v>53.97803545431091</v>
       </c>
       <c r="W3" t="n">
-        <v>63.00142857142856</v>
+        <v>54.89395080360104</v>
       </c>
       <c r="X3" t="n">
-        <v>63.36000000000001</v>
+        <v>55.80648646616048</v>
       </c>
       <c r="Y3" t="n">
-        <v>64.31000000000002</v>
+        <v>56.71785604204922</v>
       </c>
       <c r="Z3" t="n">
-        <v>63.38088235294117</v>
+        <v>57.54661289204992</v>
       </c>
       <c r="AA3" t="n">
-        <v>77.13999999999999</v>
+        <v>58.33333228214769</v>
       </c>
       <c r="AB3" t="n">
-        <v>77.70289855072464</v>
+        <v>59.13217009365904</v>
       </c>
       <c r="AC3" t="n">
-        <v>78.56911764705882</v>
+        <v>59.90738148721586</v>
       </c>
       <c r="AD3" t="n">
-        <v>77.45882352941177</v>
+        <v>60.64849323320785</v>
       </c>
       <c r="AE3" t="n">
-        <v>79.5913043478261</v>
+        <v>61.34033651290144</v>
       </c>
       <c r="AF3" t="n">
-        <v>77.85882352941177</v>
+        <v>61.9017322318532</v>
       </c>
       <c r="AG3" t="n">
-        <v>78.07428571428571</v>
+        <v>62.28692040464059</v>
       </c>
       <c r="AH3" t="n">
-        <v>79.36666666666665</v>
+        <v>62.60854203504828</v>
       </c>
       <c r="AI3" t="n">
-        <v>78.91323529411764</v>
+        <v>62.86005339944435</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78.32499999999999</v>
+        <v>62.93339635309037</v>
       </c>
       <c r="AK3" t="n">
-        <v>78.73964285714285</v>
+        <v>63.01839617799696</v>
       </c>
       <c r="AL3" t="n">
-        <v>79.15428571428572</v>
+        <v>63.10295976546545</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.0.1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.136</v>
+        <v>2.964865</v>
       </c>
       <c r="C4" t="n">
-        <v>19.54583333333333</v>
+        <v>5.291480936428114</v>
       </c>
       <c r="D4" t="n">
-        <v>6.693243243243242</v>
+        <v>6.005287715968212</v>
       </c>
       <c r="E4" t="n">
-        <v>6.47638888888889</v>
+        <v>6.747712947322447</v>
       </c>
       <c r="F4" t="n">
-        <v>6.806756756756758</v>
+        <v>7.512599396201913</v>
       </c>
       <c r="G4" t="n">
-        <v>7.841095890410958</v>
+        <v>8.451296166220136</v>
       </c>
       <c r="H4" t="n">
-        <v>9.416438356164385</v>
+        <v>10.02086437468918</v>
       </c>
       <c r="I4" t="n">
-        <v>10.97027027027027</v>
+        <v>11.8499214661563</v>
       </c>
       <c r="J4" t="n">
-        <v>13.84266666666667</v>
+        <v>13.80431178721747</v>
       </c>
       <c r="K4" t="n">
-        <v>87.62972972972972</v>
+        <v>15.96766516001771</v>
       </c>
       <c r="L4" t="n">
-        <v>23.59166666666667</v>
+        <v>18.86985630983473</v>
       </c>
       <c r="M4" t="n">
-        <v>30.87464788732395</v>
+        <v>21.8939564354245</v>
       </c>
       <c r="N4" t="n">
-        <v>40.06849315068493</v>
+        <v>24.75827965141584</v>
       </c>
       <c r="O4" t="n">
-        <v>42.07222222222222</v>
+        <v>27.5324244252263</v>
       </c>
       <c r="P4" t="n">
-        <v>44.23150684931506</v>
+        <v>30.13699462737576</v>
       </c>
       <c r="Q4" t="n">
-        <v>45.54722222222222</v>
+        <v>32.47017922929259</v>
       </c>
       <c r="R4" t="n">
-        <v>47.26</v>
+        <v>34.66086440229379</v>
       </c>
       <c r="S4" t="n">
-        <v>49.23135135135135</v>
+        <v>36.7697131490673</v>
       </c>
       <c r="T4" t="n">
-        <v>51.2027027027027</v>
+        <v>38.81949447505011</v>
       </c>
       <c r="U4" t="n">
-        <v>52.53150684931506</v>
+        <v>40.89437154318029</v>
       </c>
       <c r="V4" t="n">
-        <v>53.16301369863013</v>
+        <v>43.01014518092033</v>
       </c>
       <c r="W4" t="n">
-        <v>53.83013698630137</v>
+        <v>44.88084969938217</v>
       </c>
       <c r="X4" t="n">
-        <v>54.64400000000001</v>
+        <v>46.62280267369698</v>
       </c>
       <c r="Y4" t="n">
-        <v>55.18513513513513</v>
+        <v>48.32061970748242</v>
       </c>
       <c r="Z4" t="n">
-        <v>56.54861111111112</v>
+        <v>49.78862127591312</v>
       </c>
       <c r="AA4" t="n">
-        <v>57.85138888888888</v>
+        <v>50.85833357902915</v>
       </c>
       <c r="AB4" t="n">
-        <v>58.16351351351351</v>
+        <v>51.84194334783509</v>
       </c>
       <c r="AC4" t="n">
-        <v>59.62297297297297</v>
+        <v>52.82985333431148</v>
       </c>
       <c r="AD4" t="n">
-        <v>60.80810810810811</v>
+        <v>53.80128445200702</v>
       </c>
       <c r="AE4" t="n">
-        <v>61.9486111111111</v>
+        <v>54.69168281959904</v>
       </c>
       <c r="AF4" t="n">
-        <v>63.11830985915493</v>
+        <v>55.50763305461435</v>
       </c>
       <c r="AG4" t="n">
-        <v>63.44931506849314</v>
+        <v>56.27939891994482</v>
       </c>
       <c r="AH4" t="n">
-        <v>64.5</v>
+        <v>56.98025894804638</v>
       </c>
       <c r="AI4" t="n">
-        <v>64.48219178082192</v>
+        <v>57.5771197432014</v>
       </c>
       <c r="AJ4" t="n">
-        <v>64.90405405405406</v>
+        <v>58.02048210560845</v>
       </c>
       <c r="AK4" t="n">
-        <v>65.33287671232877</v>
+        <v>58.46286756062535</v>
       </c>
       <c r="AL4" t="n">
-        <v>65.09178082191779</v>
+        <v>58.89995906154616</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.0.2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.894366197183099</v>
+        <v>18.26316</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39428571428571</v>
+        <v>31.17857346319187</v>
       </c>
       <c r="D5" t="n">
-        <v>15.46901408450704</v>
+        <v>32.26250208622808</v>
       </c>
       <c r="E5" t="n">
-        <v>20.21780821917808</v>
+        <v>33.32991287739645</v>
       </c>
       <c r="F5" t="n">
-        <v>25.49324324324324</v>
+        <v>34.39722039667004</v>
       </c>
       <c r="G5" t="n">
-        <v>112.1544117647059</v>
+        <v>35.4749546446668</v>
       </c>
       <c r="H5" t="n">
-        <v>34.21506849315069</v>
+        <v>36.57949487038102</v>
       </c>
       <c r="I5" t="n">
-        <v>38.84931506849315</v>
+        <v>37.79706652334375</v>
       </c>
       <c r="J5" t="n">
-        <v>44.37027027027028</v>
+        <v>39.16912191224822</v>
       </c>
       <c r="K5" t="n">
-        <v>48.31111111111112</v>
+        <v>40.66986513912704</v>
       </c>
       <c r="L5" t="n">
-        <v>50.81066666666667</v>
+        <v>42.19084908835267</v>
       </c>
       <c r="M5" t="n">
-        <v>52.74787064676617</v>
+        <v>43.63692739943872</v>
       </c>
       <c r="N5" t="n">
-        <v>54.68507462686567</v>
+        <v>44.98147496385357</v>
       </c>
       <c r="O5" t="n">
-        <v>56.12191780821919</v>
+        <v>46.37808707089665</v>
       </c>
       <c r="P5" t="n">
-        <v>57.38513513513512</v>
+        <v>47.92156009815821</v>
       </c>
       <c r="Q5" t="n">
-        <v>58.1394366197183</v>
+        <v>49.60578792040895</v>
       </c>
       <c r="R5" t="n">
-        <v>59.11527777777777</v>
+        <v>51.60223125562006</v>
       </c>
       <c r="S5" t="n">
-        <v>60.92162162162162</v>
+        <v>53.76953866639514</v>
       </c>
       <c r="T5" t="n">
-        <v>60.59189189189188</v>
+        <v>55.94906170297703</v>
       </c>
       <c r="U5" t="n">
-        <v>61.17083333333332</v>
+        <v>57.90654274549994</v>
       </c>
       <c r="V5" t="n">
-        <v>60.77887323943662</v>
+        <v>59.51218192325025</v>
       </c>
       <c r="W5" t="n">
-        <v>61.29178082191781</v>
+        <v>60.90270396031817</v>
       </c>
       <c r="X5" t="n">
-        <v>61.87602739726027</v>
+        <v>62.05252006905096</v>
       </c>
       <c r="Y5" t="n">
-        <v>62.46027397260274</v>
+        <v>62.89991614844624</v>
       </c>
       <c r="Z5" t="n">
-        <v>61.63333333333333</v>
+        <v>63.61611797321594</v>
       </c>
       <c r="AA5" t="n">
-        <v>61.0768115942029</v>
+        <v>64.42028391329363</v>
       </c>
       <c r="AB5" t="n">
-        <v>60.52318840579711</v>
+        <v>65.4450012103994</v>
       </c>
       <c r="AC5" t="n">
-        <v>61.93529411764706</v>
+        <v>66.55031682088253</v>
       </c>
       <c r="AD5" t="n">
-        <v>62.01176470588236</v>
+        <v>67.65515516977804</v>
       </c>
       <c r="AE5" t="n">
-        <v>61.24285714285713</v>
+        <v>68.79383731445751</v>
       </c>
       <c r="AF5" t="n">
-        <v>61.46351351351352</v>
+        <v>69.81835003071336</v>
       </c>
       <c r="AG5" t="n">
-        <v>62.40555555555555</v>
+        <v>70.67677604046037</v>
       </c>
       <c r="AH5" t="n">
-        <v>63.35972222222223</v>
+        <v>71.55734703730126</v>
       </c>
       <c r="AI5" t="n">
-        <v>64.82112676056337</v>
+        <v>72.45225632336499</v>
       </c>
       <c r="AJ5" t="n">
-        <v>64.32089552238806</v>
+        <v>73.27684608656055</v>
       </c>
       <c r="AK5" t="n">
-        <v>62.87058823529412</v>
+        <v>74.11589180760028</v>
       </c>
       <c r="AL5" t="n">
-        <v>64.42028985507247</v>
+        <v>74.95057841386782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.020547945205479</v>
+        <v>7.447945</v>
       </c>
       <c r="C6" t="n">
-        <v>2.117741935483872</v>
+        <v>10.87932119499448</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9164383561643834</v>
+        <v>10.62255451165437</v>
       </c>
       <c r="E6" t="n">
-        <v>1.011111111111111</v>
+        <v>10.38178658784931</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>10.1673609688286</v>
       </c>
       <c r="G6" t="n">
-        <v>1.608450704225352</v>
+        <v>10.09564592782764</v>
       </c>
       <c r="H6" t="n">
-        <v>1.956164383561644</v>
+        <v>10.01051957256907</v>
       </c>
       <c r="I6" t="n">
-        <v>2.753424657534247</v>
+        <v>9.947244983539671</v>
       </c>
       <c r="J6" t="n">
-        <v>3.871830985915494</v>
+        <v>9.935498443367919</v>
       </c>
       <c r="K6" t="n">
-        <v>6.247222222222222</v>
+        <v>9.6991296133096</v>
       </c>
       <c r="L6" t="n">
-        <v>9.263013698630136</v>
+        <v>14.84064669291528</v>
       </c>
       <c r="M6" t="n">
-        <v>12.94520547945206</v>
+        <v>18.67259963438416</v>
       </c>
       <c r="N6" t="n">
-        <v>17.83285714285715</v>
+        <v>22.51448075</v>
       </c>
       <c r="O6" t="n">
-        <v>98.37397260273973</v>
+        <v>26.76249999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>26.56986301369863</v>
+        <v>31.29764980334756</v>
       </c>
       <c r="Q6" t="n">
-        <v>29.79726027397261</v>
+        <v>35.33052154499513</v>
       </c>
       <c r="R6" t="n">
-        <v>29.84383561643835</v>
+        <v>39.37702086242754</v>
       </c>
       <c r="S6" t="n">
-        <v>30.67916666666667</v>
+        <v>43.65819448388204</v>
       </c>
       <c r="T6" t="n">
-        <v>30.86986301369863</v>
+        <v>44.6383525742102</v>
       </c>
       <c r="U6" t="n">
-        <v>108.3527027027027</v>
+        <v>45.40621800145292</v>
       </c>
       <c r="V6" t="n">
-        <v>25.80972222222222</v>
+        <v>46.21110092166333</v>
       </c>
       <c r="W6" t="n">
-        <v>26.51944444444445</v>
+        <v>47.0079973771416</v>
       </c>
       <c r="X6" t="n">
-        <v>27.22222222222222</v>
+        <v>47.76854883649862</v>
       </c>
       <c r="Y6" t="n">
-        <v>27.52432432432432</v>
+        <v>48.42665519268038</v>
       </c>
       <c r="Z6" t="n">
-        <v>26.10277777777777</v>
+        <v>48.85840642801567</v>
       </c>
       <c r="AA6" t="n">
-        <v>24.79594594594595</v>
+        <v>49.01927951332792</v>
       </c>
       <c r="AB6" t="n">
-        <v>24.96056338028169</v>
+        <v>49.02501382215354</v>
       </c>
       <c r="AC6" t="n">
-        <v>24.36301369863014</v>
+        <v>48.91264397950726</v>
       </c>
       <c r="AD6" t="n">
-        <v>21.57123287671233</v>
+        <v>48.71771074394292</v>
       </c>
       <c r="AE6" t="n">
-        <v>22.3013698630137</v>
+        <v>48.51745056374924</v>
       </c>
       <c r="AF6" t="n">
-        <v>21.04383561643836</v>
+        <v>48.31418086816166</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.74933333333333</v>
+        <v>48.09153937573616</v>
       </c>
       <c r="AH6" t="n">
-        <v>19.33918918918919</v>
+        <v>47.95575740780998</v>
       </c>
       <c r="AI6" t="n">
-        <v>19.09583333333333</v>
+        <v>47.94500382251788</v>
       </c>
       <c r="AJ6" t="n">
-        <v>19.62876712328768</v>
+        <v>47.97430429169253</v>
       </c>
       <c r="AK6" t="n">
-        <v>19.25135135135135</v>
+        <v>48.00138578905763</v>
       </c>
       <c r="AL6" t="n">
-        <v>19.32191780821918</v>
+        <v>48.02681467784694</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5.1</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>10.17286</v>
+      </c>
       <c r="C7" t="n">
-        <v>14.08333333333333</v>
+        <v>14.26105904580309</v>
       </c>
       <c r="D7" t="n">
-        <v>9.776092896174864</v>
+        <v>13.9098926239275</v>
       </c>
       <c r="E7" t="n">
-        <v>5.468852459016393</v>
+        <v>13.63958475458608</v>
       </c>
       <c r="F7" t="n">
-        <v>5.346478873239437</v>
+        <v>13.3793951841015</v>
       </c>
       <c r="G7" t="n">
-        <v>6.561971830985915</v>
+        <v>13.74553710014854</v>
       </c>
       <c r="H7" t="n">
-        <v>8.139726027397261</v>
+        <v>14.63412983260628</v>
       </c>
       <c r="I7" t="n">
-        <v>9.515277777777778</v>
+        <v>15.88968721298384</v>
       </c>
       <c r="J7" t="n">
-        <v>75.61095890410959</v>
+        <v>17.32711236962222</v>
       </c>
       <c r="K7" t="n">
-        <v>16.73918918918919</v>
+        <v>18.66309845644065</v>
       </c>
       <c r="L7" t="n">
-        <v>21.8225352112676</v>
+        <v>19.79191914522078</v>
       </c>
       <c r="M7" t="n">
-        <v>27.42028985507246</v>
+        <v>20.67627948137896</v>
       </c>
       <c r="N7" t="n">
-        <v>33.77534246575343</v>
+        <v>20.8945724092169</v>
       </c>
       <c r="O7" t="n">
-        <v>39.55068493150685</v>
+        <v>23.08931156937978</v>
       </c>
       <c r="P7" t="n">
-        <v>43.90405405405405</v>
+        <v>25.11694134468588</v>
       </c>
       <c r="Q7" t="n">
-        <v>46.27866666666667</v>
+        <v>27.0974690811125</v>
       </c>
       <c r="R7" t="n">
-        <v>46.90547945205478</v>
+        <v>29.15068089416545</v>
       </c>
       <c r="S7" t="n">
-        <v>47.79726027397261</v>
+        <v>32.3430172107745</v>
       </c>
       <c r="T7" t="n">
-        <v>48.71486486486487</v>
+        <v>34.8419967413932</v>
       </c>
       <c r="U7" t="n">
-        <v>49.84007132132132</v>
+        <v>36.8384549667144</v>
       </c>
       <c r="V7" t="n">
-        <v>50.96527777777778</v>
+        <v>38.26071725307348</v>
       </c>
       <c r="W7" t="n">
-        <v>51.63513513513514</v>
+        <v>39.12605162192885</v>
       </c>
       <c r="X7" t="n">
-        <v>51.71095890410959</v>
+        <v>39.58161980686216</v>
       </c>
       <c r="Y7" t="n">
-        <v>52.27500000000001</v>
+        <v>39.83633275672819</v>
       </c>
       <c r="Z7" t="n">
-        <v>52.47432432432432</v>
+        <v>40.06263848002204</v>
       </c>
       <c r="AA7" t="n">
-        <v>52.59726027397261</v>
+        <v>40.26531049485698</v>
       </c>
       <c r="AB7" t="n">
-        <v>52.66986301369863</v>
+        <v>40.38486767371072</v>
       </c>
       <c r="AC7" t="n">
-        <v>53.1958904109589</v>
+        <v>40.49607321798293</v>
       </c>
       <c r="AD7" t="n">
-        <v>53.65000000000001</v>
+        <v>40.6024921865476</v>
       </c>
       <c r="AE7" t="n">
-        <v>53.82054794520548</v>
+        <v>40.60570580932152</v>
       </c>
       <c r="AF7" t="n">
-        <v>54.22777777777778</v>
+        <v>40.65024278760167</v>
       </c>
       <c r="AG7" t="n">
-        <v>54.30945945945946</v>
+        <v>40.89626372446228</v>
       </c>
       <c r="AH7" t="n">
-        <v>54.19305555555556</v>
+        <v>41.18905413735824</v>
       </c>
       <c r="AI7" t="n">
-        <v>54.3418918918919</v>
+        <v>41.41143692408546</v>
       </c>
       <c r="AJ7" t="n">
-        <v>54.84931506849316</v>
+        <v>41.73075645691105</v>
       </c>
       <c r="AK7" t="n">
-        <v>54.75466666666667</v>
-      </c>
-      <c r="AL7" t="inlineStr"/>
+        <v>42.05026733983939</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>42.34643011921254</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.880000000000001</v>
+        <v>9.697297000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>6.554189189189191</v>
+        <v>13.67713470146214</v>
       </c>
       <c r="D8" t="n">
-        <v>8.22837837837838</v>
+        <v>12.89350048452637</v>
       </c>
       <c r="E8" t="n">
-        <v>67.13108108108109</v>
+        <v>12.09915254278754</v>
       </c>
       <c r="F8" t="n">
-        <v>8.246478873239434</v>
+        <v>11.31554998191995</v>
       </c>
       <c r="G8" t="n">
-        <v>9.016438356164382</v>
+        <v>10.61955486923859</v>
       </c>
       <c r="H8" t="n">
-        <v>10.70266666666667</v>
+        <v>9.782709853460464</v>
       </c>
       <c r="I8" t="n">
-        <v>13.45820895522388</v>
+        <v>14.20933544710776</v>
       </c>
       <c r="J8" t="n">
-        <v>14.85416666666667</v>
+        <v>17.40971531627517</v>
       </c>
       <c r="K8" t="n">
-        <v>17.75342465753425</v>
+        <v>20.59368515001883</v>
       </c>
       <c r="L8" t="n">
-        <v>21.31095890410959</v>
+        <v>24.26756999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>23.3625</v>
+        <v>28.55634500000001</v>
       </c>
       <c r="N8" t="n">
-        <v>26.52297297297297</v>
+        <v>32.21032942811716</v>
       </c>
       <c r="O8" t="n">
-        <v>29.34864864864865</v>
+        <v>35.78679678100372</v>
       </c>
       <c r="P8" t="n">
-        <v>31.68873239436619</v>
+        <v>40.80029413258546</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.51267605633802</v>
+        <v>40.00443083845147</v>
       </c>
       <c r="R8" t="n">
-        <v>37.44324324324324</v>
+        <v>39.95327148181164</v>
       </c>
       <c r="S8" t="n">
-        <v>42.24347826086957</v>
+        <v>40.16595467106236</v>
       </c>
       <c r="T8" t="n">
-        <v>45.95479452054794</v>
+        <v>40.52264385778156</v>
       </c>
       <c r="U8" t="n">
-        <v>48.09066666666667</v>
+        <v>40.79862627433637</v>
       </c>
       <c r="V8" t="n">
-        <v>51.2945205479452</v>
+        <v>40.93317272396174</v>
       </c>
       <c r="W8" t="n">
-        <v>53.78591549295774</v>
+        <v>41.08654993420453</v>
       </c>
       <c r="X8" t="n">
-        <v>55.0945205479452</v>
+        <v>41.24807645862219</v>
       </c>
       <c r="Y8" t="n">
-        <v>56.96891891891892</v>
+        <v>41.6947028537048</v>
       </c>
       <c r="Z8" t="n">
-        <v>57.05068493150684</v>
+        <v>42.47085508650417</v>
       </c>
       <c r="AA8" t="n">
-        <v>58.16486486486486</v>
+        <v>43.19849073169033</v>
       </c>
       <c r="AB8" t="n">
-        <v>58.49577464788734</v>
+        <v>43.69798399412674</v>
       </c>
       <c r="AC8" t="n">
-        <v>59.83108108108108</v>
+        <v>44.05896294838508</v>
       </c>
       <c r="AD8" t="n">
-        <v>58.43380281690141</v>
+        <v>44.13926233224553</v>
       </c>
       <c r="AE8" t="n">
-        <v>59.72957746478873</v>
+        <v>43.91222607511288</v>
       </c>
       <c r="AF8" t="n">
-        <v>59.26712328767123</v>
+        <v>43.5279372362061</v>
       </c>
       <c r="AG8" t="n">
-        <v>59.22027027027027</v>
+        <v>42.98449487888816</v>
       </c>
       <c r="AH8" t="n">
-        <v>59.88493150684932</v>
+        <v>42.32975792441082</v>
       </c>
       <c r="AI8" t="n">
-        <v>60.20945945945946</v>
+        <v>41.72962476766737</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60.14109589041096</v>
+        <v>41.16779353473536</v>
       </c>
       <c r="AK8" t="n">
-        <v>60.14794520547945</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>40.59263209708094</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>40.05178745089067</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.375409836065574</v>
+        <v>4.394521</v>
       </c>
       <c r="C9" t="n">
-        <v>21.86981132075472</v>
+        <v>3.547632805503286</v>
       </c>
       <c r="D9" t="n">
-        <v>77.52027027027027</v>
+        <v>5.116186109467545</v>
       </c>
       <c r="E9" t="n">
-        <v>76.91199999999999</v>
+        <v>6.707166621569808</v>
       </c>
       <c r="F9" t="n">
-        <v>15.2054794520548</v>
+        <v>8.314975876545873</v>
       </c>
       <c r="G9" t="n">
-        <v>17.57333333333333</v>
+        <v>9.955183979858829</v>
       </c>
       <c r="H9" t="n">
-        <v>20.97837837837838</v>
+        <v>11.78586005404437</v>
       </c>
       <c r="I9" t="n">
-        <v>24.87638888888889</v>
+        <v>13.91460591102136</v>
       </c>
       <c r="J9" t="n">
-        <v>28.76164383561644</v>
+        <v>15.83764208034098</v>
       </c>
       <c r="K9" t="n">
-        <v>32.51506849315069</v>
+        <v>17.66332277221579</v>
       </c>
       <c r="L9" t="n">
-        <v>37.05890410958904</v>
+        <v>19.44413970039853</v>
       </c>
       <c r="M9" t="n">
-        <v>40.54864864864864</v>
+        <v>20.9417282410296</v>
       </c>
       <c r="N9" t="n">
-        <v>44.27162162162162</v>
+        <v>22.08821553717624</v>
       </c>
       <c r="O9" t="n">
-        <v>46.04864864864864</v>
+        <v>23.24176443031644</v>
       </c>
       <c r="P9" t="n">
-        <v>46.57183098591549</v>
+        <v>24.39336897765064</v>
       </c>
       <c r="Q9" t="n">
-        <v>46.19583333333333</v>
+        <v>25.60626136258676</v>
       </c>
       <c r="R9" t="n">
-        <v>47.45270270270271</v>
+        <v>26.82601833338154</v>
       </c>
       <c r="S9" t="n">
-        <v>47.61066666666666</v>
+        <v>27.96829323963454</v>
       </c>
       <c r="T9" t="n">
-        <v>48.39305555555555</v>
+        <v>28.92506949133712</v>
       </c>
       <c r="U9" t="n">
-        <v>49.08219178082192</v>
+        <v>29.72754885901848</v>
       </c>
       <c r="V9" t="n">
-        <v>49.48767123287671</v>
+        <v>30.39115449439561</v>
       </c>
       <c r="W9" t="n">
-        <v>49.76621621621621</v>
+        <v>30.88902683833037</v>
       </c>
       <c r="X9" t="n">
-        <v>50.42972972972973</v>
+        <v>31.24750116043358</v>
       </c>
       <c r="Y9" t="n">
-        <v>50.88591549295774</v>
+        <v>31.56214838075532</v>
       </c>
       <c r="Z9" t="n">
-        <v>51.11369863013699</v>
+        <v>31.84953919821209</v>
       </c>
       <c r="AA9" t="n">
-        <v>50.94383561643836</v>
+        <v>31.96873280366306</v>
       </c>
       <c r="AB9" t="n">
-        <v>51.28219178082192</v>
+        <v>31.83468056276029</v>
       </c>
       <c r="AC9" t="n">
-        <v>50.76756756756756</v>
+        <v>31.58123692663064</v>
       </c>
       <c r="AD9" t="n">
-        <v>50.92894736842106</v>
+        <v>31.23312174998874</v>
       </c>
       <c r="AE9" t="n">
-        <v>51.55972222222223</v>
+        <v>30.76940806717779</v>
       </c>
       <c r="AF9" t="n">
-        <v>51.45416666666667</v>
+        <v>30.3273181490677</v>
       </c>
       <c r="AG9" t="n">
-        <v>51.67260273972602</v>
+        <v>30.02109314794908</v>
       </c>
       <c r="AH9" t="n">
-        <v>51.55753424657534</v>
+        <v>29.80703127866024</v>
       </c>
       <c r="AI9" t="n">
-        <v>51.40277777777778</v>
+        <v>29.6522776816847</v>
       </c>
       <c r="AJ9" t="n">
-        <v>51.84428571428572</v>
+        <v>29.50803029598542</v>
       </c>
       <c r="AK9" t="n">
-        <v>51.57432432432432</v>
+        <v>29.366838706493</v>
       </c>
       <c r="AL9" t="n">
-        <v>51.24444444444445</v>
+        <v>29.21978108793043</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.25.1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>8.539726</v>
+      </c>
+      <c r="C10" t="n">
+        <v>16.87027323955277</v>
+      </c>
       <c r="D10" t="n">
-        <v>4.733333333333333</v>
+        <v>17.74286052750478</v>
       </c>
       <c r="E10" t="n">
-        <v>5.066666666666666</v>
+        <v>18.64183833232763</v>
       </c>
       <c r="F10" t="n">
-        <v>5.920833333333333</v>
+        <v>19.55610832529299</v>
       </c>
       <c r="G10" t="n">
-        <v>7.10945945945946</v>
+        <v>20.52438796514669</v>
       </c>
       <c r="H10" t="n">
-        <v>7.638356164383564</v>
+        <v>21.76018544975185</v>
       </c>
       <c r="I10" t="n">
-        <v>8.820270270270271</v>
+        <v>23.64627591583746</v>
       </c>
       <c r="J10" t="n">
-        <v>10.1056338028169</v>
+        <v>25.43883211228479</v>
       </c>
       <c r="K10" t="n">
-        <v>11.4013698630137</v>
+        <v>27.12989518237</v>
       </c>
       <c r="L10" t="n">
-        <v>13.35068493150685</v>
+        <v>28.76206289815297</v>
       </c>
       <c r="M10" t="n">
-        <v>15.87808219178082</v>
+        <v>30.3616995831565</v>
       </c>
       <c r="N10" t="n">
-        <v>17.96351351351351</v>
+        <v>32.19355835170914</v>
       </c>
       <c r="O10" t="n">
-        <v>20.86438356164384</v>
+        <v>34.43443980166904</v>
       </c>
       <c r="P10" t="n">
-        <v>24.18356164383562</v>
+        <v>36.9335056915852</v>
       </c>
       <c r="Q10" t="n">
-        <v>27.09861111111111</v>
+        <v>39.60830582349993</v>
       </c>
       <c r="R10" t="n">
-        <v>31.49041095890411</v>
+        <v>42.25222764231462</v>
       </c>
       <c r="S10" t="n">
-        <v>35.92972972972973</v>
+        <v>44.54851695805557</v>
       </c>
       <c r="T10" t="n">
-        <v>40.32083333333334</v>
+        <v>46.53803300442479</v>
       </c>
       <c r="U10" t="n">
-        <v>43.17206050228311</v>
+        <v>48.15203867215413</v>
       </c>
       <c r="V10" t="n">
-        <v>46.02328767123288</v>
+        <v>49.3110699439448</v>
       </c>
       <c r="W10" t="n">
-        <v>47.05675675675676</v>
+        <v>50.22228042295586</v>
       </c>
       <c r="X10" t="n">
-        <v>47.88918918918919</v>
+        <v>51.01247782870399</v>
       </c>
       <c r="Y10" t="n">
-        <v>48.04729729729729</v>
+        <v>51.56806359694946</v>
       </c>
       <c r="Z10" t="n">
-        <v>48.21506849315068</v>
+        <v>51.89859225284453</v>
       </c>
       <c r="AA10" t="n">
-        <v>48.31733333333335</v>
+        <v>52.09730832112618</v>
       </c>
       <c r="AB10" t="n">
-        <v>48.42916666666666</v>
+        <v>52.14017712163138</v>
       </c>
       <c r="AC10" t="n">
-        <v>47.93098591549296</v>
+        <v>52.00762828612966</v>
       </c>
       <c r="AD10" t="n">
-        <v>48.16760563380281</v>
+        <v>51.69738174902004</v>
       </c>
       <c r="AE10" t="n">
-        <v>47.71804939224387</v>
+        <v>51.28743231991752</v>
       </c>
       <c r="AF10" t="n">
-        <v>47.26849315068493</v>
+        <v>50.89913859478774</v>
       </c>
       <c r="AG10" t="n">
-        <v>47.01805555555556</v>
+        <v>50.53856435734566</v>
       </c>
       <c r="AH10" t="n">
-        <v>46.43972602739726</v>
+        <v>50.14604475555712</v>
       </c>
       <c r="AI10" t="n">
-        <v>45.89583333333334</v>
+        <v>49.769139677822</v>
       </c>
       <c r="AJ10" t="n">
-        <v>45.88800000000001</v>
+        <v>49.39305643040008</v>
       </c>
       <c r="AK10" t="n">
-        <v>45.31486486486487</v>
+        <v>49.00426572308648</v>
       </c>
       <c r="AL10" t="n">
-        <v>44.96805555555555</v>
+        <v>48.60333310097825</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.63</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>18.47838</v>
+      </c>
       <c r="C11" t="n">
-        <v>13.6433962264151</v>
+        <v>30.34358452631288</v>
       </c>
       <c r="D11" t="n">
-        <v>9.111111111111111</v>
+        <v>32.04622690339809</v>
       </c>
       <c r="E11" t="n">
-        <v>9.149910394265234</v>
+        <v>33.79929860742717</v>
       </c>
       <c r="F11" t="n">
-        <v>9.188709677419356</v>
+        <v>35.5893516805206</v>
       </c>
       <c r="G11" t="n">
-        <v>10.08082191780822</v>
+        <v>37.47224545662907</v>
       </c>
       <c r="H11" t="n">
-        <v>10.55</v>
+        <v>39.38138502684003</v>
       </c>
       <c r="I11" t="n">
-        <v>11.55915492957746</v>
+        <v>41.29573687911231</v>
       </c>
       <c r="J11" t="n">
-        <v>13.1554054054054</v>
+        <v>43.09933421160717</v>
       </c>
       <c r="K11" t="n">
-        <v>15.6527027027027</v>
+        <v>44.70725170199128</v>
       </c>
       <c r="L11" t="n">
-        <v>17.08493150684932</v>
+        <v>46.12392027064128</v>
       </c>
       <c r="M11" t="n">
-        <v>18.42957746478873</v>
+        <v>47.36102223691622</v>
       </c>
       <c r="N11" t="n">
-        <v>18.90684931506849</v>
+        <v>48.41170103060246</v>
       </c>
       <c r="O11" t="n">
-        <v>19.01408450704225</v>
+        <v>49.36723650836419</v>
       </c>
       <c r="P11" t="n">
-        <v>21.0375</v>
+        <v>50.25668852532555</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.90547945205479</v>
+        <v>51.09619397818028</v>
       </c>
       <c r="R11" t="n">
-        <v>25.79594594594595</v>
+        <v>51.92718188635356</v>
       </c>
       <c r="S11" t="n">
-        <v>32.29014084507042</v>
+        <v>52.71202844753101</v>
       </c>
       <c r="T11" t="n">
-        <v>36.6945205479452</v>
+        <v>53.47013369550854</v>
       </c>
       <c r="U11" t="n">
-        <v>39.98356164383562</v>
+        <v>54.1986703494188</v>
       </c>
       <c r="V11" t="n">
-        <v>44.93287671232876</v>
+        <v>54.87934718975951</v>
       </c>
       <c r="W11" t="n">
-        <v>48.09027777777778</v>
+        <v>55.46608988690353</v>
       </c>
       <c r="X11" t="n">
-        <v>50.57361111111111</v>
+        <v>55.76899541360326</v>
       </c>
       <c r="Y11" t="n">
-        <v>52.5445945945946</v>
+        <v>55.82022272656231</v>
       </c>
       <c r="Z11" t="n">
-        <v>52.72361111111111</v>
+        <v>55.78938684636199</v>
       </c>
       <c r="AA11" t="n">
-        <v>52.91081081081082</v>
+        <v>55.7222399693989</v>
       </c>
       <c r="AB11" t="n">
-        <v>52.62027027027027</v>
+        <v>55.60937375482213</v>
       </c>
       <c r="AC11" t="n">
-        <v>52.33783783783785</v>
+        <v>55.4019274314695</v>
       </c>
       <c r="AD11" t="n">
-        <v>52.43</v>
+        <v>55.13742003194418</v>
       </c>
       <c r="AE11" t="n">
-        <v>52.16891891891893</v>
+        <v>54.82172735318736</v>
       </c>
       <c r="AF11" t="n">
-        <v>52.30972222222223</v>
+        <v>54.45686498578919</v>
       </c>
       <c r="AG11" t="n">
-        <v>51.87671232876712</v>
+        <v>54.14406749637669</v>
       </c>
       <c r="AH11" t="n">
-        <v>52.1125</v>
+        <v>53.92903072515974</v>
       </c>
       <c r="AI11" t="n">
-        <v>51.04657534246576</v>
+        <v>53.78471707708577</v>
       </c>
       <c r="AJ11" t="n">
-        <v>51.41095890410959</v>
+        <v>53.63774674993581</v>
       </c>
       <c r="AK11" t="n">
-        <v>50.90000000000001</v>
+        <v>53.48329775490136</v>
       </c>
       <c r="AL11" t="n">
-        <v>50.54054054054054</v>
+        <v>53.33202545464782</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.63.1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.880821917808218</v>
+        <v>85.85890000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>21.28767123287671</v>
+        <v>26.84247</v>
       </c>
       <c r="D12" t="n">
-        <v>16.88513513513514</v>
+        <v>24.09718</v>
       </c>
       <c r="E12" t="n">
-        <v>17.57808219178082</v>
+        <v>23.81644</v>
       </c>
       <c r="F12" t="n">
-        <v>19.61388888888889</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>22.15753424657534</v>
+        <v>33.04324</v>
       </c>
       <c r="H12" t="n">
-        <v>24.75068493150685</v>
+        <v>27.55079999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>27.77123287671233</v>
+        <v>30.80308725869812</v>
       </c>
       <c r="J12" t="n">
-        <v>30.52054794520548</v>
+        <v>33.10799437487991</v>
       </c>
       <c r="K12" t="n">
-        <v>33.5890410958904</v>
+        <v>35.15561929788993</v>
       </c>
       <c r="L12" t="n">
-        <v>36.06081081081081</v>
+        <v>37.13085344139615</v>
       </c>
       <c r="M12" t="n">
-        <v>38.35675675675676</v>
+        <v>39.16313524411574</v>
       </c>
       <c r="N12" t="n">
-        <v>41.11643835616439</v>
+        <v>41.52615644169531</v>
       </c>
       <c r="O12" t="n">
-        <v>42.85277777777777</v>
+        <v>44.00862259003463</v>
       </c>
       <c r="P12" t="n">
-        <v>44.65600000000001</v>
+        <v>46.39782807908372</v>
       </c>
       <c r="Q12" t="n">
-        <v>46.225</v>
+        <v>48.67217885876158</v>
       </c>
       <c r="R12" t="n">
-        <v>47.98648648648648</v>
+        <v>50.47387704383708</v>
       </c>
       <c r="S12" t="n">
-        <v>48.43733333333332</v>
+        <v>51.614834640258</v>
       </c>
       <c r="T12" t="n">
-        <v>49.5774647887324</v>
+        <v>52.35870591359058</v>
       </c>
       <c r="U12" t="n">
-        <v>49.9068493150685</v>
+        <v>52.82463006948884</v>
       </c>
       <c r="V12" t="n">
-        <v>50.42361111111112</v>
+        <v>53.13971365891743</v>
       </c>
       <c r="W12" t="n">
-        <v>51.10684931506849</v>
+        <v>53.3195982531762</v>
       </c>
       <c r="X12" t="n">
-        <v>51.27260273972603</v>
+        <v>53.30182020405879</v>
       </c>
       <c r="Y12" t="n">
-        <v>51.39864864864865</v>
+        <v>53.12490210676928</v>
       </c>
       <c r="Z12" t="n">
-        <v>52.04857142857143</v>
+        <v>52.91197483538581</v>
       </c>
       <c r="AA12" t="n">
-        <v>52.68873239436619</v>
+        <v>52.77638648528632</v>
       </c>
       <c r="AB12" t="n">
-        <v>53.03698630136986</v>
+        <v>52.71700514286675</v>
       </c>
       <c r="AC12" t="n">
-        <v>52.86216216216216</v>
+        <v>52.66945192195971</v>
       </c>
       <c r="AD12" t="n">
-        <v>53.45</v>
+        <v>52.50950604899551</v>
       </c>
       <c r="AE12" t="n">
-        <v>53.39774774774774</v>
+        <v>52.18668701115743</v>
       </c>
       <c r="AF12" t="n">
-        <v>53.34549549549549</v>
+        <v>51.65364763550923</v>
       </c>
       <c r="AG12" t="n">
-        <v>53.29324324324323</v>
+        <v>51.00493918163537</v>
       </c>
       <c r="AH12" t="n">
-        <v>53.40133333333333</v>
+        <v>50.38959384997223</v>
       </c>
       <c r="AI12" t="n">
-        <v>52.89305555555556</v>
+        <v>49.85227126782386</v>
       </c>
       <c r="AJ12" t="n">
-        <v>52.92083333333333</v>
+        <v>49.32398824759467</v>
       </c>
       <c r="AK12" t="n">
-        <v>52.55479452054794</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
+        <v>48.79618810950571</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>48.28123269969445</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.63.2</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>12.58919</v>
+      </c>
       <c r="C13" t="n">
-        <v>71.75384615384617</v>
+        <v>11.92051647451967</v>
       </c>
       <c r="D13" t="n">
-        <v>7.365454545454546</v>
+        <v>12.29678912387745</v>
       </c>
       <c r="E13" t="n">
-        <v>6.797260273972602</v>
+        <v>12.68192478506891</v>
       </c>
       <c r="F13" t="n">
-        <v>6.878378378378378</v>
+        <v>13.06290824530473</v>
       </c>
       <c r="G13" t="n">
-        <v>7.529729729729729</v>
+        <v>13.70370491534146</v>
       </c>
       <c r="H13" t="n">
-        <v>7.902702702702702</v>
+        <v>14.51965179777704</v>
       </c>
       <c r="I13" t="n">
-        <v>9.091780821917808</v>
+        <v>15.37537516319338</v>
       </c>
       <c r="J13" t="n">
-        <v>11.45616438356164</v>
+        <v>16.32225373072017</v>
       </c>
       <c r="K13" t="n">
-        <v>14.41756756756757</v>
+        <v>17.336310767221</v>
       </c>
       <c r="L13" t="n">
-        <v>17.59295774647887</v>
+        <v>18.30035966801987</v>
       </c>
       <c r="M13" t="n">
-        <v>20.65342465753425</v>
+        <v>19.20151232128301</v>
       </c>
       <c r="N13" t="n">
-        <v>24.49166666666666</v>
+        <v>20.07301402771799</v>
       </c>
       <c r="O13" t="n">
-        <v>106.2621621621622</v>
+        <v>20.87827348710391</v>
       </c>
       <c r="P13" t="n">
-        <v>29.26164383561644</v>
+        <v>21.69780529089629</v>
       </c>
       <c r="Q13" t="n">
-        <v>31.11081081081081</v>
+        <v>22.4733830903781</v>
       </c>
       <c r="R13" t="n">
-        <v>32.57123287671233</v>
+        <v>23.17180724655234</v>
       </c>
       <c r="S13" t="n">
-        <v>32.88493150684931</v>
+        <v>23.88560984710832</v>
       </c>
       <c r="T13" t="n">
-        <v>34.34794520547945</v>
+        <v>24.600712279379</v>
       </c>
       <c r="U13" t="n">
-        <v>33.87866666666667</v>
+        <v>25.27188845523522</v>
       </c>
       <c r="V13" t="n">
-        <v>33.77916666666667</v>
+        <v>25.95701434063582</v>
       </c>
       <c r="W13" t="n">
-        <v>33.32876712328767</v>
+        <v>26.51490635072903</v>
       </c>
       <c r="X13" t="n">
-        <v>33.352</v>
+        <v>26.72991099916484</v>
       </c>
       <c r="Y13" t="n">
-        <v>32.77042253521127</v>
+        <v>26.79131672515973</v>
       </c>
       <c r="Z13" t="n">
-        <v>32.58783783783784</v>
+        <v>26.90988929554425</v>
       </c>
       <c r="AA13" t="n">
-        <v>31.84933333333334</v>
+        <v>26.97818161918257</v>
       </c>
       <c r="AB13" t="n">
-        <v>30.904</v>
+        <v>26.8717559403615</v>
       </c>
       <c r="AC13" t="n">
-        <v>30.99324324324324</v>
+        <v>26.83244936821906</v>
       </c>
       <c r="AD13" t="n">
-        <v>30.96133333333334</v>
+        <v>26.74370403891625</v>
       </c>
       <c r="AE13" t="n">
-        <v>30.18918918918919</v>
+        <v>26.30614992298713</v>
       </c>
       <c r="AF13" t="n">
-        <v>29.62837837837838</v>
+        <v>25.61598246977833</v>
       </c>
       <c r="AG13" t="n">
-        <v>29.15416666666667</v>
+        <v>24.87939238699241</v>
       </c>
       <c r="AH13" t="n">
-        <v>28.125</v>
+        <v>24.184353772915</v>
       </c>
       <c r="AI13" t="n">
-        <v>27.12638888888889</v>
+        <v>23.45941448299109</v>
       </c>
       <c r="AJ13" t="n">
-        <v>105.9835616438356</v>
+        <v>22.84469800193224</v>
       </c>
       <c r="AK13" t="n">
-        <v>25.1972602739726</v>
+        <v>22.26762869721194</v>
       </c>
       <c r="AL13" t="n">
-        <v>24.43150684931507</v>
+        <v>21.73267319642378</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0.5.1</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.680555555555555</v>
+        <v>3.779452</v>
       </c>
       <c r="C14" t="n">
-        <v>20.50958904109589</v>
+        <v>5.057661866624136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.95616438356165</v>
+        <v>5.121809793189969</v>
       </c>
       <c r="E14" t="n">
-        <v>19.86164383561644</v>
+        <v>5.214019527846982</v>
       </c>
       <c r="F14" t="n">
-        <v>19.74459459459459</v>
+        <v>5.330937105728553</v>
       </c>
       <c r="G14" t="n">
-        <v>19.29315068493151</v>
+        <v>5.527088845751994</v>
       </c>
       <c r="H14" t="n">
-        <v>22.19041095890411</v>
+        <v>5.755368650459533</v>
       </c>
       <c r="I14" t="n">
-        <v>102.9180555555556</v>
+        <v>6.037393182068282</v>
       </c>
       <c r="J14" t="n">
-        <v>27.46111111111111</v>
+        <v>6.36032824466582</v>
       </c>
       <c r="K14" t="n">
-        <v>30.27397260273973</v>
+        <v>6.69442450334669</v>
       </c>
       <c r="L14" t="n">
-        <v>32.03333333333333</v>
+        <v>7.08582194368941</v>
       </c>
       <c r="M14" t="n">
-        <v>34.50138888888889</v>
+        <v>7.186536063643275</v>
       </c>
       <c r="N14" t="n">
-        <v>34.99594594594595</v>
+        <v>7.202582512886952</v>
       </c>
       <c r="O14" t="n">
-        <v>36.90405405405405</v>
+        <v>7.263041178660671</v>
       </c>
       <c r="P14" t="n">
-        <v>38.21351351351351</v>
+        <v>7.243041675401221</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.79166666666666</v>
+        <v>7.073932124997054</v>
       </c>
       <c r="R14" t="n">
-        <v>39.53835616438356</v>
+        <v>6.902883494643898</v>
       </c>
       <c r="S14" t="n">
-        <v>40.0972972972973</v>
+        <v>6.727473573516738</v>
       </c>
       <c r="T14" t="n">
-        <v>41.0918918918919</v>
+        <v>6.599457748759466</v>
       </c>
       <c r="U14" t="n">
-        <v>41.4718309859155</v>
+        <v>6.516688853935064</v>
       </c>
       <c r="V14" t="n">
-        <v>41.62876712328767</v>
+        <v>6.45055285887583</v>
       </c>
       <c r="W14" t="n">
-        <v>42.33333333333334</v>
+        <v>6.466049964408352</v>
       </c>
       <c r="X14" t="n">
-        <v>44.83918918918919</v>
+        <v>6.531217208982953</v>
       </c>
       <c r="Y14" t="n">
-        <v>46.33698630136987</v>
+        <v>6.569253596509937</v>
       </c>
       <c r="Z14" t="n">
-        <v>44.8375</v>
+        <v>6.58832509677076</v>
       </c>
       <c r="AA14" t="n">
-        <v>45.3027397260274</v>
+        <v>6.60378886002574</v>
       </c>
       <c r="AB14" t="n">
-        <v>45.26944444444445</v>
+        <v>6.63476515177182</v>
       </c>
       <c r="AC14" t="n">
-        <v>45.99283033033034</v>
+        <v>6.699572703675839</v>
       </c>
       <c r="AD14" t="n">
-        <v>46.71621621621622</v>
+        <v>6.804929205051729</v>
       </c>
       <c r="AE14" t="n">
-        <v>47.69166666666667</v>
+        <v>6.909613239937703</v>
       </c>
       <c r="AF14" t="n">
-        <v>48.03661971830986</v>
+        <v>6.995776420151291</v>
       </c>
       <c r="AG14" t="n">
-        <v>46.65616438356164</v>
+        <v>7.055101418143042</v>
       </c>
       <c r="AH14" t="n">
-        <v>45.475</v>
+        <v>7.071426392221837</v>
       </c>
       <c r="AI14" t="n">
-        <v>44.84864864864865</v>
+        <v>7.040508866153684</v>
       </c>
       <c r="AJ14" t="n">
-        <v>43.83175675675675</v>
+        <v>6.985537340487133</v>
       </c>
       <c r="AK14" t="n">
-        <v>42.81486486486486</v>
+        <v>6.934225911418518</v>
       </c>
       <c r="AL14" t="n">
-        <v>43.12465753424658</v>
+        <v>6.882508919683886</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.5.2</t>
+          <t>0.31.1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.918918918918919</v>
+        <v>11.99867</v>
       </c>
       <c r="C15" t="n">
-        <v>16.15479452054795</v>
+        <v>17.09631431800273</v>
       </c>
       <c r="D15" t="n">
-        <v>12.38055555555556</v>
+        <v>16.19795974805713</v>
       </c>
       <c r="E15" t="n">
-        <v>11.69324324324324</v>
+        <v>15.34650307811787</v>
       </c>
       <c r="F15" t="n">
-        <v>13.82739726027397</v>
+        <v>14.4943951032326</v>
       </c>
       <c r="G15" t="n">
-        <v>15.71388888888889</v>
+        <v>14.0303855343364</v>
       </c>
       <c r="H15" t="n">
-        <v>19.18356164383562</v>
+        <v>13.74355107655602</v>
       </c>
       <c r="I15" t="n">
-        <v>22.02465753424657</v>
+        <v>13.34300954513397</v>
       </c>
       <c r="J15" t="n">
-        <v>102.7054794520548</v>
+        <v>12.97879374851856</v>
       </c>
       <c r="K15" t="n">
-        <v>27.16438356164383</v>
+        <v>12.9032021977626</v>
       </c>
       <c r="L15" t="n">
-        <v>28.67162162162163</v>
+        <v>13.05385572365599</v>
       </c>
       <c r="M15" t="n">
-        <v>31.2958904109589</v>
+        <v>13.44539144057243</v>
       </c>
       <c r="N15" t="n">
-        <v>31.87866666666667</v>
+        <v>14.31551916081747</v>
       </c>
       <c r="O15" t="n">
-        <v>33.1013698630137</v>
+        <v>16.40475782117539</v>
       </c>
       <c r="P15" t="n">
-        <v>34.45205479452055</v>
+        <v>19.40378233747324</v>
       </c>
       <c r="Q15" t="n">
-        <v>35.56986301369863</v>
+        <v>22.7654196263318</v>
       </c>
       <c r="R15" t="n">
-        <v>35.82676056338028</v>
+        <v>26.65778728264023</v>
       </c>
       <c r="S15" t="n">
-        <v>36.27027027027027</v>
+        <v>30.84147079413325</v>
       </c>
       <c r="T15" t="n">
-        <v>36.75342465753424</v>
+        <v>34.3141254696159</v>
       </c>
       <c r="U15" t="n">
-        <v>37.1931506849315</v>
+        <v>37.20793675191531</v>
       </c>
       <c r="V15" t="n">
-        <v>37.32328767123287</v>
+        <v>39.24564137024339</v>
       </c>
       <c r="W15" t="n">
-        <v>38.28378378378378</v>
+        <v>39.54321352574173</v>
       </c>
       <c r="X15" t="n">
-        <v>37.98980855855856</v>
+        <v>38.83025551280386</v>
       </c>
       <c r="Y15" t="n">
-        <v>37.69583333333334</v>
+        <v>37.8230205075698</v>
       </c>
       <c r="Z15" t="n">
-        <v>37.46081081081081</v>
+        <v>36.60631712793846</v>
       </c>
       <c r="AA15" t="n">
-        <v>36.85633802816901</v>
+        <v>35.48643096769287</v>
       </c>
       <c r="AB15" t="n">
-        <v>36.57405942504341</v>
+        <v>34.78005881401906</v>
       </c>
       <c r="AC15" t="n">
-        <v>36.29178082191781</v>
+        <v>34.33922623226103</v>
       </c>
       <c r="AD15" t="n">
-        <v>35.9361111111111</v>
+        <v>33.94402193870418</v>
       </c>
       <c r="AE15" t="n">
-        <v>35.78219178082191</v>
+        <v>33.50233810844743</v>
       </c>
       <c r="AF15" t="n">
-        <v>35.83378378378378</v>
+        <v>32.77400581342334</v>
       </c>
       <c r="AG15" t="n">
-        <v>35.45972222222222</v>
+        <v>31.74106040171941</v>
       </c>
       <c r="AH15" t="n">
-        <v>34.41917808219178</v>
+        <v>30.46823691181445</v>
       </c>
       <c r="AI15" t="n">
-        <v>34.18630136986301</v>
+        <v>29.19929935169789</v>
       </c>
       <c r="AJ15" t="n">
-        <v>34.212</v>
+        <v>28.06256435172136</v>
       </c>
       <c r="AK15" t="n">
-        <v>33.46301369863014</v>
+        <v>26.9477471800908</v>
       </c>
       <c r="AL15" t="n">
-        <v>32.72222222222223</v>
+        <v>25.86805712683629</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.5.3</t>
+          <t>0.31.2</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23.87333333333333</v>
+        <v>7.264384</v>
       </c>
       <c r="C16" t="n">
-        <v>13.03513513513513</v>
+        <v>7.901929812891243</v>
       </c>
       <c r="D16" t="n">
-        <v>14.15</v>
+        <v>7.706821741508063</v>
       </c>
       <c r="E16" t="n">
-        <v>24.97534246575342</v>
+        <v>7.521224335052045</v>
       </c>
       <c r="F16" t="n">
-        <v>16.51643835616439</v>
+        <v>7.337373704217204</v>
       </c>
       <c r="G16" t="n">
-        <v>24.29459459459459</v>
+        <v>7.162733989074759</v>
       </c>
       <c r="H16" t="n">
-        <v>22.27222222222223</v>
+        <v>7.006259880230358</v>
       </c>
       <c r="I16" t="n">
-        <v>25.10405405405405</v>
+        <v>6.849315646775515</v>
       </c>
       <c r="J16" t="n">
-        <v>107.4246575342466</v>
+        <v>6.702696398747606</v>
       </c>
       <c r="K16" t="n">
-        <v>29.25753424657535</v>
+        <v>6.672201972998337</v>
       </c>
       <c r="L16" t="n">
-        <v>32.89444444444444</v>
+        <v>6.903052534753429</v>
       </c>
       <c r="M16" t="n">
-        <v>35.35138888888888</v>
+        <v>7.406427830220929</v>
       </c>
       <c r="N16" t="n">
-        <v>36.53243243243243</v>
+        <v>8.220979294959156</v>
       </c>
       <c r="O16" t="n">
-        <v>38.45890410958904</v>
+        <v>10.05873620319692</v>
       </c>
       <c r="P16" t="n">
-        <v>40.19444444444444</v>
+        <v>12.67880254065195</v>
       </c>
       <c r="Q16" t="n">
-        <v>43.14794520547945</v>
+        <v>15.37724109679853</v>
       </c>
       <c r="R16" t="n">
-        <v>43.39577464788733</v>
+        <v>18.21152382557258</v>
       </c>
       <c r="S16" t="n">
-        <v>45.09166666666667</v>
+        <v>20.78955379820954</v>
       </c>
       <c r="T16" t="n">
-        <v>45.84305555555556</v>
+        <v>21.29047012834109</v>
       </c>
       <c r="U16" t="n">
-        <v>46.10540540540541</v>
+        <v>20.76998128488289</v>
       </c>
       <c r="V16" t="n">
-        <v>46.35211267605634</v>
+        <v>20.56395957995577</v>
       </c>
       <c r="W16" t="n">
-        <v>46.52465753424657</v>
+        <v>19.34835005109713</v>
       </c>
       <c r="X16" t="n">
-        <v>47.13697665444723</v>
+        <v>16.97861529101705</v>
       </c>
       <c r="Y16" t="n">
-        <v>47.74929577464789</v>
+        <v>14.99056972465438</v>
       </c>
       <c r="Z16" t="n">
-        <v>47.80704225352113</v>
+        <v>13.41649587475764</v>
       </c>
       <c r="AA16" t="n">
-        <v>48.41111111111112</v>
+        <v>12.10275844213111</v>
       </c>
       <c r="AB16" t="n">
-        <v>48.18356164383562</v>
+        <v>11.28560453918093</v>
       </c>
       <c r="AC16" t="n">
-        <v>47.78205859969559</v>
+        <v>10.89005138089009</v>
       </c>
       <c r="AD16" t="n">
-        <v>47.38055555555556</v>
+        <v>10.54699184447083</v>
       </c>
       <c r="AE16" t="n">
-        <v>48.09178082191781</v>
+        <v>10.19640168431999</v>
       </c>
       <c r="AF16" t="n">
-        <v>48.5027397260274</v>
+        <v>9.891242173898316</v>
       </c>
       <c r="AG16" t="n">
-        <v>48.35633802816902</v>
+        <v>9.462764726399325</v>
       </c>
       <c r="AH16" t="n">
-        <v>48.13433339764616</v>
+        <v>8.91962580463079</v>
       </c>
       <c r="AI16" t="n">
-        <v>47.91232876712329</v>
+        <v>8.343580058565623</v>
       </c>
       <c r="AJ16" t="n">
-        <v>49.08</v>
+        <v>7.750207376700749</v>
       </c>
       <c r="AK16" t="n">
-        <v>49.30527777777777</v>
+        <v>7.155870603707427</v>
       </c>
       <c r="AL16" t="n">
-        <v>49.53055555555555</v>
+        <v>6.563967238210183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.31.3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.83918918918919</v>
+        <v>13.15915</v>
       </c>
       <c r="C17" t="n">
-        <v>7.62972972972973</v>
+        <v>8.91430076365269</v>
       </c>
       <c r="D17" t="n">
-        <v>6.362162162162162</v>
+        <v>10.78581843416161</v>
       </c>
       <c r="E17" t="n">
-        <v>6.208219178082192</v>
+        <v>12.63943641930759</v>
       </c>
       <c r="F17" t="n">
-        <v>6.270833333333333</v>
+        <v>14.4771103303632</v>
       </c>
       <c r="G17" t="n">
-        <v>5.755405405405406</v>
+        <v>16.3406879119292</v>
       </c>
       <c r="H17" t="n">
-        <v>6.104109589041096</v>
+        <v>18.18259653460636</v>
       </c>
       <c r="I17" t="n">
-        <v>6.185857611421957</v>
+        <v>19.8689388548908</v>
       </c>
       <c r="J17" t="n">
-        <v>6.267605633802817</v>
+        <v>21.44054541816635</v>
       </c>
       <c r="K17" t="n">
-        <v>7.07361111111111</v>
+        <v>22.90251543803382</v>
       </c>
       <c r="L17" t="n">
-        <v>7.431506849315069</v>
+        <v>24.20235126719248</v>
       </c>
       <c r="M17" t="n">
-        <v>8.375999999999999</v>
+        <v>25.34646390402547</v>
       </c>
       <c r="N17" t="n">
-        <v>9.548611111111111</v>
+        <v>26.486433287537</v>
       </c>
       <c r="O17" t="n">
-        <v>11.74788732394366</v>
+        <v>27.62023916898273</v>
       </c>
       <c r="P17" t="n">
-        <v>15.3472972972973</v>
+        <v>28.66191625366476</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.01232876712329</v>
+        <v>29.61500066799116</v>
       </c>
       <c r="R17" t="n">
-        <v>25.71232876712329</v>
+        <v>30.48070240089401</v>
       </c>
       <c r="S17" t="n">
-        <v>31.27428571428572</v>
+        <v>31.2093381452488</v>
       </c>
       <c r="T17" t="n">
-        <v>33.41066666666667</v>
+        <v>31.83025965869446</v>
       </c>
       <c r="U17" t="n">
-        <v>34.45890410958904</v>
+        <v>32.37788010147603</v>
       </c>
       <c r="V17" t="n">
-        <v>38.15342465753425</v>
+        <v>32.80217780942449</v>
       </c>
       <c r="W17" t="n">
-        <v>35.95342465753425</v>
+        <v>33.12830326514946</v>
       </c>
       <c r="X17" t="n">
-        <v>33.0931506849315</v>
+        <v>33.33417568346476</v>
       </c>
       <c r="Y17" t="n">
-        <v>31.35070422535212</v>
+        <v>33.39624863177042</v>
       </c>
       <c r="Z17" t="n">
-        <v>30.09466666666667</v>
+        <v>33.32290111565785</v>
       </c>
       <c r="AA17" t="n">
-        <v>28.72465753424657</v>
+        <v>33.07346656666412</v>
       </c>
       <c r="AB17" t="n">
-        <v>27.82054794520548</v>
+        <v>32.60343428529398</v>
       </c>
       <c r="AC17" t="n">
-        <v>27.08493150684932</v>
+        <v>31.85278719600245</v>
       </c>
       <c r="AD17" t="n">
-        <v>26.08219178082192</v>
+        <v>30.79905819405124</v>
       </c>
       <c r="AE17" t="n">
-        <v>24.712</v>
+        <v>29.53315297078503</v>
       </c>
       <c r="AF17" t="n">
-        <v>23.43333333333334</v>
+        <v>28.30227182616341</v>
       </c>
       <c r="AG17" t="n">
-        <v>22.128</v>
+        <v>27.21449312495052</v>
       </c>
       <c r="AH17" t="n">
-        <v>21.05633802816901</v>
+        <v>26.25093305446989</v>
       </c>
       <c r="AI17" t="n">
-        <v>19.54594594594595</v>
+        <v>25.50207936640286</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.856</v>
+        <v>25.14998215123037</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.53835616438356</v>
+        <v>24.86788308661679</v>
       </c>
       <c r="AL17" t="n">
-        <v>14.68767123287671</v>
+        <v>24.62698278247985</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0.25.1</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8.856164383561646</v>
+        <v>4.613699</v>
       </c>
       <c r="C18" t="n">
-        <v>20.81780821917808</v>
+        <v>4.204054</v>
       </c>
       <c r="D18" t="n">
-        <v>16.9235294117647</v>
+        <v>3.832432</v>
       </c>
       <c r="E18" t="n">
-        <v>15.31142857142857</v>
+        <v>59.15753</v>
       </c>
       <c r="F18" t="n">
-        <v>17.04714285714285</v>
+        <v>4.747887</v>
       </c>
       <c r="G18" t="n">
-        <v>18.46617647058824</v>
+        <v>5.010958000000016</v>
       </c>
       <c r="H18" t="n">
-        <v>19.88676470588236</v>
+        <v>6.700693908874788</v>
       </c>
       <c r="I18" t="n">
-        <v>22.18840579710145</v>
+        <v>8.162968020814159</v>
       </c>
       <c r="J18" t="n">
-        <v>24.80294117647059</v>
+        <v>9.687128579626323</v>
       </c>
       <c r="K18" t="n">
-        <v>26.26619718309859</v>
+        <v>11.20594846748108</v>
       </c>
       <c r="L18" t="n">
-        <v>28.75942028985507</v>
+        <v>12.4961640159673</v>
       </c>
       <c r="M18" t="n">
-        <v>30.81029411764706</v>
+        <v>13.70829512309353</v>
       </c>
       <c r="N18" t="n">
-        <v>31.38285714285714</v>
+        <v>14.84726506595872</v>
       </c>
       <c r="O18" t="n">
-        <v>33.46081081081081</v>
+        <v>15.43673460328499</v>
       </c>
       <c r="P18" t="n">
-        <v>34.30447761194029</v>
+        <v>15.43336702915104</v>
       </c>
       <c r="Q18" t="n">
-        <v>36.59635645302897</v>
+        <v>15.28908493688583</v>
       </c>
       <c r="R18" t="n">
-        <v>38.88823529411765</v>
+        <v>15.03910195935212</v>
       </c>
       <c r="S18" t="n">
-        <v>38.00144927536231</v>
+        <v>14.52217337359903</v>
       </c>
       <c r="T18" t="n">
-        <v>38.59565217391305</v>
+        <v>13.71343998049359</v>
       </c>
       <c r="U18" t="n">
-        <v>39.26527777777778</v>
+        <v>13.0835475945589</v>
       </c>
       <c r="V18" t="n">
-        <v>40.90151515151515</v>
+        <v>12.60157051396699</v>
       </c>
       <c r="W18" t="n">
-        <v>39.13088235294117</v>
+        <v>12.13898709471622</v>
       </c>
       <c r="X18" t="n">
-        <v>38.92222222222222</v>
+        <v>11.74947363986338</v>
       </c>
       <c r="Y18" t="n">
-        <v>39.27808219178083</v>
+        <v>11.51678823299679</v>
       </c>
       <c r="Z18" t="n">
-        <v>38.07866666666667</v>
+        <v>11.41914451946001</v>
       </c>
       <c r="AA18" t="n">
-        <v>39.05405405405406</v>
+        <v>11.29373076136357</v>
       </c>
       <c r="AB18" t="n">
-        <v>38.63150684931507</v>
+        <v>11.20213472203788</v>
       </c>
       <c r="AC18" t="n">
-        <v>37.97826086956522</v>
+        <v>11.09724662666691</v>
       </c>
       <c r="AD18" t="n">
-        <v>36.0972602739726</v>
+        <v>10.96055304375362</v>
       </c>
       <c r="AE18" t="n">
-        <v>37.27534246575343</v>
+        <v>10.83091695129795</v>
       </c>
       <c r="AF18" t="n">
-        <v>37.26216216216216</v>
+        <v>10.67822776872052</v>
       </c>
       <c r="AG18" t="n">
-        <v>36.25652173913043</v>
+        <v>10.48770984452405</v>
       </c>
       <c r="AH18" t="n">
-        <v>36.19054054054055</v>
+        <v>10.3109975095338</v>
       </c>
       <c r="AI18" t="n">
-        <v>35.12328767123287</v>
+        <v>10.12425137361557</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34.3472498962225</v>
+        <v>9.92812915452949</v>
       </c>
       <c r="AK18" t="n">
-        <v>33.57121212121213</v>
+        <v>9.739541827861212</v>
       </c>
       <c r="AL18" t="n">
-        <v>32.7342857142857</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0.25.2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.236000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>4.324324324324324</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3.544</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.532394366197184</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3.498630136986301</v>
-      </c>
-      <c r="G19" t="n">
-        <v>4.002777777777778</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.730555555555556</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5.918666666666667</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7.23888888888889</v>
-      </c>
-      <c r="K19" t="n">
-        <v>9.334285714285716</v>
-      </c>
-      <c r="L19" t="n">
-        <v>77.94305555555556</v>
-      </c>
-      <c r="M19" t="n">
-        <v>15.93194444444444</v>
-      </c>
-      <c r="N19" t="n">
-        <v>17.12465753424657</v>
-      </c>
-      <c r="O19" t="n">
-        <v>16.16986301369863</v>
-      </c>
-      <c r="P19" t="n">
-        <v>16.98243243243244</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>15.95342465753425</v>
-      </c>
-      <c r="R19" t="n">
-        <v>17.04189189189189</v>
-      </c>
-      <c r="S19" t="n">
-        <v>14.84933333333333</v>
-      </c>
-      <c r="T19" t="n">
-        <v>13.32394366197183</v>
-      </c>
-      <c r="U19" t="n">
-        <v>12.14647887323944</v>
-      </c>
-      <c r="V19" t="n">
-        <v>11.48904109589041</v>
-      </c>
-      <c r="W19" t="n">
-        <v>72.21333333333334</v>
-      </c>
-      <c r="X19" t="n">
-        <v>10.04861111111111</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9.751388888888888</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>68.81643835616438</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.084722222222222</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.764864864864863</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>7.795945945945945</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>6.721917808219178</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6.608219178082193</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>5.321333333333333</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>5.476388888888888</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.423287671232877</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>4.883783783783784</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>4.736486486486487</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>4.395890410958905</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>0.125</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>6.103773584905659</v>
-      </c>
-      <c r="C20" t="n">
-        <v>12.83492063492063</v>
-      </c>
-      <c r="D20" t="n">
-        <v>12.06027397260274</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11.52162162162162</v>
-      </c>
-      <c r="F20" t="n">
-        <v>12.70972222222222</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13.99864864864865</v>
-      </c>
-      <c r="H20" t="n">
-        <v>15.96027397260274</v>
-      </c>
-      <c r="I20" t="n">
-        <v>18.01891891891892</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20.73287671232877</v>
-      </c>
-      <c r="K20" t="n">
-        <v>23.25753424657534</v>
-      </c>
-      <c r="L20" t="n">
-        <v>26.10821917808219</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28.8581081081081</v>
-      </c>
-      <c r="N20" t="n">
-        <v>30.82027027027028</v>
-      </c>
-      <c r="O20" t="n">
-        <v>32.40704225352113</v>
-      </c>
-      <c r="P20" t="n">
-        <v>34.43698630136986</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>35.71081081081081</v>
-      </c>
-      <c r="R20" t="n">
-        <v>36.36111111111112</v>
-      </c>
-      <c r="S20" t="n">
-        <v>37.13918918918919</v>
-      </c>
-      <c r="T20" t="n">
-        <v>37.0081081081081</v>
-      </c>
-      <c r="U20" t="n">
-        <v>37.46486486486486</v>
-      </c>
-      <c r="V20" t="n">
-        <v>37.66021021021021</v>
-      </c>
-      <c r="W20" t="n">
-        <v>37.85555555555555</v>
-      </c>
-      <c r="X20" t="n">
-        <v>38.01805555555556</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>37.47123287671232</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>36.88356164383561</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>36.84444444444445</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>36.46081081081081</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>36.44324324324324</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>34.85479452054795</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>34.44</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>34.04109589041095</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>33.22739726027397</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>32.81232876712328</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>31.74931506849314</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>31.11095890410959</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>30.42328767123288</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0.125.1</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3.993150684931506</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3.06031746031746</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2.740540540540541</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.897183098591549</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.825</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.790277777777778</v>
-      </c>
-      <c r="H21" t="n">
-        <v>2.461111111111111</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.976712328767124</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.226027397260274</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.882191780821918</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.491666666666666</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.006756756756756</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.506756756756758</v>
-      </c>
-      <c r="P21" t="n">
-        <v>4.773333333333333</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>63.27808219178083</v>
-      </c>
-      <c r="R21" t="n">
-        <v>64.17297297297296</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7.415068493150685</v>
-      </c>
-      <c r="T21" t="n">
-        <v>9.025675675675677</v>
-      </c>
-      <c r="U21" t="n">
-        <v>10.67162162162162</v>
-      </c>
-      <c r="V21" t="n">
-        <v>12.07066666666667</v>
-      </c>
-      <c r="W21" t="n">
-        <v>13.35694444444444</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14.22253521126761</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15.32465753424658</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>15.20985915492958</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>82.60533333333332</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>14.51111111111111</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>14.10675675675676</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>12.9013698630137</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>11.46756756756757</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.13783783783784</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>8.641666666666666</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>8.574647887323943</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8.025675675675677</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>7.379166666666666</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>6.284722222222222</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>5.846575342465753</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>0.125.2</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.664864864864865</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.841095890410958</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.241095890410959</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.287671232876712</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.445205479452055</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.649333333333333</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.969737089201878</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.290140845070423</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.027027027027027</v>
-      </c>
-      <c r="L22" t="n">
-        <v>5.052054794520548</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.862500000000001</v>
-      </c>
-      <c r="N22" t="n">
-        <v>7.620270270270272</v>
-      </c>
-      <c r="O22" t="n">
-        <v>8.736619718309861</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10.20555555555556</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>12.16351351351352</v>
-      </c>
-      <c r="R22" t="n">
-        <v>13.55833333333333</v>
-      </c>
-      <c r="S22" t="n">
-        <v>15.04027777777778</v>
-      </c>
-      <c r="T22" t="n">
-        <v>15.38888888888889</v>
-      </c>
-      <c r="U22" t="n">
-        <v>15.39589041095891</v>
-      </c>
-      <c r="V22" t="n">
-        <v>14.988</v>
-      </c>
-      <c r="W22" t="n">
-        <v>14.51081081081081</v>
-      </c>
-      <c r="X22" t="n">
-        <v>13.50416666666667</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>13.07162162162162</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>12.56805555555556</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>11.18767123287671</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>72.82739726027397</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.30684931506849</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>9.898648648648647</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>9.063513513513517</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8.56111111111111</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>7.253424657534245</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6.612328767123287</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>5.61917808219178</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>61.41780821917808</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>5.756944444444445</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>0.125.3</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>5.004109589041096</v>
-      </c>
-      <c r="C23" t="n">
-        <v>11.66478873239437</v>
-      </c>
-      <c r="D23" t="n">
-        <v>11.62638888888889</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11.29722222222222</v>
-      </c>
-      <c r="F23" t="n">
-        <v>11.51805555555556</v>
-      </c>
-      <c r="G23" t="n">
-        <v>12.95352112676056</v>
-      </c>
-      <c r="H23" t="n">
-        <v>13.81549295774648</v>
-      </c>
-      <c r="I23" t="n">
-        <v>15.43661971830986</v>
-      </c>
-      <c r="J23" t="n">
-        <v>18.14246575342466</v>
-      </c>
-      <c r="K23" t="n">
-        <v>20.68783783783784</v>
-      </c>
-      <c r="L23" t="n">
-        <v>23.17808219178082</v>
-      </c>
-      <c r="M23" t="n">
-        <v>25.60833333333333</v>
-      </c>
-      <c r="N23" t="n">
-        <v>27.49864864864865</v>
-      </c>
-      <c r="O23" t="n">
-        <v>29.76857142857143</v>
-      </c>
-      <c r="P23" t="n">
-        <v>31.83287671232876</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>32.62876712328767</v>
-      </c>
-      <c r="R23" t="n">
-        <v>33.50270270270271</v>
-      </c>
-      <c r="S23" t="n">
-        <v>34.11369863013699</v>
-      </c>
-      <c r="T23" t="n">
-        <v>34.2661971830986</v>
-      </c>
-      <c r="U23" t="n">
-        <v>32.66249999999999</v>
-      </c>
-      <c r="V23" t="n">
-        <v>33.0958904109589</v>
-      </c>
-      <c r="W23" t="n">
-        <v>32.78513513513514</v>
-      </c>
-      <c r="X23" t="n">
-        <v>32.02837837837838</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>31.02702702702703</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>30.73561643835616</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>30.53521126760563</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>29.37123287671233</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>111.3557142857143</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>28.6986301369863</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>27.03424657534246</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>24.84166666666667</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>24.68513513513513</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>23.74657534246576</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>21.36849315068493</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>20.01351351351351</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5.626666666666667</v>
-      </c>
-      <c r="C24" t="n">
-        <v>7.205128205128204</v>
-      </c>
-      <c r="D24" t="n">
-        <v>6.591935483870967</v>
-      </c>
-      <c r="E24" t="n">
-        <v>6.420000000000001</v>
-      </c>
-      <c r="F24" t="n">
-        <v>6.054166666666666</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.398630136986302</v>
-      </c>
-      <c r="H24" t="n">
-        <v>6.843835616438357</v>
-      </c>
-      <c r="I24" t="n">
-        <v>8.275342465753424</v>
-      </c>
-      <c r="J24" t="n">
-        <v>10.79444444444444</v>
-      </c>
-      <c r="K24" t="n">
-        <v>14.92739726027397</v>
-      </c>
-      <c r="L24" t="n">
-        <v>17.79178082191781</v>
-      </c>
-      <c r="M24" t="n">
-        <v>21.25675675675676</v>
-      </c>
-      <c r="N24" t="n">
-        <v>24.5375</v>
-      </c>
-      <c r="O24" t="n">
-        <v>27.34931506849315</v>
-      </c>
-      <c r="P24" t="n">
-        <v>29.42432432432432</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>30.43380281690141</v>
-      </c>
-      <c r="R24" t="n">
-        <v>30.5972972972973</v>
-      </c>
-      <c r="S24" t="n">
-        <v>30.85616438356164</v>
-      </c>
-      <c r="T24" t="n">
-        <v>30.32676056338029</v>
-      </c>
-      <c r="U24" t="n">
-        <v>29.83472222222223</v>
-      </c>
-      <c r="V24" t="n">
-        <v>29.40933333333334</v>
-      </c>
-      <c r="W24" t="n">
-        <v>28.188</v>
-      </c>
-      <c r="X24" t="n">
-        <v>27.75352112676056</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>27.06575342465754</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>25.87432432432432</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>24.8972972972973</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>24.58533333333333</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>23.51486486486487</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>22.42361111111111</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>20.712</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>20.06216216216216</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>19.0054794520548</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>18.12972972972973</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>17.95810810810811</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>17.04305555555555</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>15.75205479452055</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>15.52191780821918</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>0.062.1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>9.454761904761906</v>
-      </c>
-      <c r="C25" t="n">
-        <v>10.46094259621657</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11.46712328767123</v>
-      </c>
-      <c r="E25" t="n">
-        <v>11.9109375</v>
-      </c>
-      <c r="F25" t="n">
-        <v>13.23698630136986</v>
-      </c>
-      <c r="G25" t="n">
-        <v>17.48904109589041</v>
-      </c>
-      <c r="H25" t="n">
-        <v>21.76571428571429</v>
-      </c>
-      <c r="I25" t="n">
-        <v>27.37671232876712</v>
-      </c>
-      <c r="J25" t="n">
-        <v>31.10277777777777</v>
-      </c>
-      <c r="K25" t="n">
-        <v>34.38611111111111</v>
-      </c>
-      <c r="L25" t="n">
-        <v>36.81081081081081</v>
-      </c>
-      <c r="M25" t="n">
-        <v>38.89315068493151</v>
-      </c>
-      <c r="N25" t="n">
-        <v>40.20945945945946</v>
-      </c>
-      <c r="O25" t="n">
-        <v>41.32876712328767</v>
-      </c>
-      <c r="P25" t="n">
-        <v>42.54383561643836</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>42.81866666666667</v>
-      </c>
-      <c r="R25" t="n">
-        <v>42.37746478873241</v>
-      </c>
-      <c r="S25" t="n">
-        <v>42.86621621621622</v>
-      </c>
-      <c r="T25" t="n">
-        <v>41.77808219178083</v>
-      </c>
-      <c r="U25" t="n">
-        <v>42.25753424657535</v>
-      </c>
-      <c r="V25" t="n">
-        <v>41.19014084507042</v>
-      </c>
-      <c r="W25" t="n">
-        <v>41.0054054054054</v>
-      </c>
-      <c r="X25" t="n">
-        <v>40.56666666666666</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>39.96986301369864</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>38.86571428571428</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>38.31095890410958</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>37.4445945945946</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>37.44782608695653</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>37.01643835616438</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>36.58611111111111</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>36.36216216216216</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>35.23378378378379</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>34.27777777777778</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>33.45890410958904</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>117.7975609756098</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>33.07971014492754</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>34.00540540540541</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>0.062.2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>35.99594594594594</v>
-      </c>
-      <c r="C26" t="n">
-        <v>115.2369230769231</v>
-      </c>
-      <c r="D26" t="n">
-        <v>27.09866666666666</v>
-      </c>
-      <c r="E26" t="n">
-        <v>20.85890410958904</v>
-      </c>
-      <c r="F26" t="n">
-        <v>16.53333333333333</v>
-      </c>
-      <c r="G26" t="n">
-        <v>14.86388888888889</v>
-      </c>
-      <c r="H26" t="n">
-        <v>81.91527777777777</v>
-      </c>
-      <c r="I26" t="n">
-        <v>18.03287671232876</v>
-      </c>
-      <c r="J26" t="n">
-        <v>21.04027777777777</v>
-      </c>
-      <c r="K26" t="n">
-        <v>26.78783783783784</v>
-      </c>
-      <c r="L26" t="n">
-        <v>35.32142857142857</v>
-      </c>
-      <c r="M26" t="n">
-        <v>46.50845070422535</v>
-      </c>
-      <c r="N26" t="n">
-        <v>49.83285714285714</v>
-      </c>
-      <c r="O26" t="n">
-        <v>49.95277777777778</v>
-      </c>
-      <c r="P26" t="n">
-        <v>49.68356164383562</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>49.13239436619717</v>
-      </c>
-      <c r="R26" t="n">
-        <v>49.2958904109589</v>
-      </c>
-      <c r="S26" t="n">
-        <v>48.53333333333333</v>
-      </c>
-      <c r="T26" t="n">
-        <v>46.7304347826087</v>
-      </c>
-      <c r="U26" t="n">
-        <v>45.93972602739726</v>
-      </c>
-      <c r="V26" t="n">
-        <v>46.03972602739727</v>
-      </c>
-      <c r="W26" t="n">
-        <v>46.02328767123287</v>
-      </c>
-      <c r="X26" t="n">
-        <v>44.87945205479452</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>45.42602739726027</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>45.33587084148728</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>45.24571428571429</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>45.21369863013699</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>45.16849315068493</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>45.11351351351351</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>45.47134009009009</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>45.82916666666667</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>45.90277777777778</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>46.2041095890411</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>46.79583333333333</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>46.7027397260274</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>47.33472222222223</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>0.062.3</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>44.41081081081082</v>
-      </c>
-      <c r="C27" t="n">
-        <v>39.84520547945205</v>
-      </c>
-      <c r="D27" t="n">
-        <v>41.40138888888889</v>
-      </c>
-      <c r="E27" t="n">
-        <v>38.93972602739726</v>
-      </c>
-      <c r="F27" t="n">
-        <v>36.87916666666666</v>
-      </c>
-      <c r="G27" t="n">
-        <v>37.50140845070422</v>
-      </c>
-      <c r="H27" t="n">
-        <v>39.92567567567568</v>
-      </c>
-      <c r="I27" t="n">
-        <v>39.76527777777778</v>
-      </c>
-      <c r="J27" t="n">
-        <v>39.51805555555555</v>
-      </c>
-      <c r="K27" t="n">
-        <v>39.87361111111111</v>
-      </c>
-      <c r="L27" t="n">
-        <v>41.53424657534247</v>
-      </c>
-      <c r="M27" t="n">
-        <v>42.26575342465753</v>
-      </c>
-      <c r="N27" t="n">
-        <v>44.3054054054054</v>
-      </c>
-      <c r="O27" t="n">
-        <v>44.76849315068493</v>
-      </c>
-      <c r="P27" t="n">
-        <v>45.31917808219178</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>45.27837837837838</v>
-      </c>
-      <c r="R27" t="n">
-        <v>45.61126760563381</v>
-      </c>
-      <c r="S27" t="n">
-        <v>45.8095890410959</v>
-      </c>
-      <c r="T27" t="n">
-        <v>46.07638888888889</v>
-      </c>
-      <c r="U27" t="n">
-        <v>46.56712328767123</v>
-      </c>
-      <c r="V27" t="n">
-        <v>46.24305555555556</v>
-      </c>
-      <c r="W27" t="n">
-        <v>46.68648648648649</v>
-      </c>
-      <c r="X27" t="n">
-        <v>46.40281690140845</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>46.61095890410959</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>47.32</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>47.17671232876713</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>47.69066666666667</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>47.23424657534248</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>47.52972972972973</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>48.41388888888889</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>48.29726027397261</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>49.27397260273973</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>50.28918918918919</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>49.98904109589041</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>50.02191780821918</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>50.29012557077625</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>50.55833333333333</v>
+        <v>9.545817984120276</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +2559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AL22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3722,3051 +2678,2479 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0438460440953843</v>
+        <v>17.4902297587207</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1325577245901989</v>
+        <v>23.16090011301683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001853465440117</v>
+        <v>23.6866114356036</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1538846441111374</v>
+        <v>23.91067880643185</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1325632062420647</v>
+        <v>23.77900998786014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1597197287232289</v>
+        <v>22.11747794183483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.138844276618472</v>
+        <v>19.96399256539917</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1472084413840603</v>
+        <v>18.93750381120275</v>
       </c>
       <c r="J2" t="n">
-        <v>0.109835339498318</v>
+        <v>18.29102311562101</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1465829103795167</v>
+        <v>18.28776577606485</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1450955397985304</v>
+        <v>19.79214275784842</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1529537384893841</v>
+        <v>22.0047567570381</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1608119371802379</v>
+        <v>23.4244319547438</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1280235415384889</v>
+        <v>24.05865050527091</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1188336654823202</v>
+        <v>23.92839101808126</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1287960404858724</v>
+        <v>23.53818873339668</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1449754293706975</v>
+        <v>23.07660550052616</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1383706391738227</v>
+        <v>22.2331115902837</v>
       </c>
       <c r="T2" t="n">
-        <v>0.130365396283875</v>
+        <v>21.09806955853108</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1271037589794847</v>
+        <v>20.28596083690094</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1281604655358543</v>
+        <v>19.63040725950524</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1679012400799433</v>
+        <v>18.76343058316296</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1365033244768478</v>
+        <v>18.06438474456396</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1291422458560195</v>
+        <v>17.59443590891851</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1308181730871409</v>
+        <v>17.09978894936381</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1324941003182624</v>
+        <v>16.60122043878209</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1207552298544142</v>
+        <v>16.61947903209697</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.1167984080317251</v>
+        <v>16.76446369468771</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0533582794850138</v>
+        <v>16.41587012440744</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1325674494663387</v>
+        <v>15.69491103338801</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1300034654436191</v>
+        <v>14.72123002132633</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.1339236401418415</v>
+        <v>13.876145702347</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1173370094955989</v>
+        <v>13.38058483438562</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1082802650221067</v>
+        <v>13.40845806396476</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0905839056962241</v>
+        <v>14.05863448997451</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.1175110157973347</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>14.80916421082382</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>15.62951014421758</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0525394316440092</v>
+        <v>7.068767954204811</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004936556738262999</v>
+        <v>18.97380481749778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006703815733655</v>
+        <v>19.33555287075745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007229733184711</v>
+        <v>19.59272566880929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0163556133542734</v>
+        <v>19.72803294253843</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007063772245159</v>
+        <v>19.50729684924211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0085993044397256</v>
+        <v>18.87869624156646</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0164922316549353</v>
+        <v>18.08618296682836</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004421860177494</v>
+        <v>17.4135064206359</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005476094788809</v>
+        <v>16.77082630115447</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006413628208967</v>
+        <v>16.14831141575282</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0106064538814687</v>
+        <v>15.36738916914237</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004420390273298</v>
+        <v>14.75801681249927</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004464654587025</v>
+        <v>14.28928463313186</v>
       </c>
       <c r="P3" t="n">
-        <v>0.000501672447854</v>
+        <v>13.99856415660566</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005135566340399999</v>
+        <v>13.99460869814333</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000525440820226</v>
+        <v>14.26520331661364</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004616777580254</v>
+        <v>14.57014145166597</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004374281925367</v>
+        <v>14.72118481616657</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0009604771386144</v>
+        <v>14.70382731482105</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000436213668808</v>
+        <v>14.49702512877554</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005072434438829</v>
+        <v>13.99533307759128</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0004158448642567</v>
+        <v>13.39859687089113</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004281727080013</v>
+        <v>12.93895334773194</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0022665619349583</v>
+        <v>12.68143715516201</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0005679719862784</v>
+        <v>12.39706738801064</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0005121482991377</v>
+        <v>12.17567416980497</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0004012038946269</v>
+        <v>12.1430537847538</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0004570815421923</v>
+        <v>12.32511436504549</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0004941571647113</v>
+        <v>12.52779177003552</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0004812859454838</v>
+        <v>12.60168904950719</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.00056154088342</v>
+        <v>12.6647702950673</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.000461451689901</v>
+        <v>12.68312862060554</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0004079464039159</v>
+        <v>12.56966496919399</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0004584297295229</v>
+        <v>12.66203699967071</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0004634017609933</v>
+        <v>12.80314876993243</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0004683737924638</v>
+        <v>12.96853320680652</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1413670865758164</v>
+        <v>16.61962805939926</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1529710687198649</v>
+        <v>16.89909098890012</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1656099772690194</v>
+        <v>18.05665444855847</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1783456528024012</v>
+        <v>19.15957599360548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1891950346676398</v>
+        <v>20.23232167668926</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1892163803184709</v>
+        <v>20.81999520303365</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1981724536955591</v>
+        <v>21.15457700887396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1821061235960855</v>
+        <v>21.34022658756781</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1933902256798354</v>
+        <v>21.4183820610415</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1778175611907847</v>
+        <v>21.74146061657144</v>
       </c>
       <c r="L4" t="n">
-        <v>0.162244896701734</v>
+        <v>22.18590718034869</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1443769150405395</v>
+        <v>22.65767306359188</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0639674156001767</v>
+        <v>23.4692505698566</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0477528715331185</v>
+        <v>24.23818533146226</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1134492229018851</v>
+        <v>24.56571925846894</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1248959605160534</v>
+        <v>24.58916028560275</v>
       </c>
       <c r="R4" t="n">
-        <v>0.127577529908356</v>
+        <v>24.31548575589989</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1091412129292258</v>
+        <v>23.70302506988179</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907048959500957</v>
+        <v>23.02694293286028</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1029056864821919</v>
+        <v>22.69472050753715</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0528973791404692</v>
+        <v>22.52139886955995</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0427960937861046</v>
+        <v>22.34714134410879</v>
       </c>
       <c r="X4" t="n">
-        <v>0.137532826025186</v>
+        <v>22.21893387772849</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1538125488918836</v>
+        <v>22.17109414332941</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.1301961368422521</v>
+        <v>22.07311547074389</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.062215816121206</v>
+        <v>21.58136403068506</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1284935160280101</v>
+        <v>20.85320633357208</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1252292048364346</v>
+        <v>20.363733586034</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.1443739801245494</v>
+        <v>19.75821186111335</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.125791599449096</v>
+        <v>19.2411492740698</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1436423374942532</v>
+        <v>19.24643417514249</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.1392613948081328</v>
+        <v>19.28093384527322</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.1317783308917428</v>
+        <v>19.04597978630321</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1586113895730399</v>
+        <v>18.77934364328623</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1412021282358201</v>
+        <v>18.30613798307169</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1250398605974725</v>
+        <v>17.82696217314252</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.130396661145775</v>
+        <v>17.33642109898651</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07184635755024089</v>
+        <v>18.25424107387142</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1004356441179816</v>
+        <v>18.80935100099555</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0950779225689294</v>
+        <v>21.3005310441159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04675483475888</v>
+        <v>23.79171108723625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1087767404657958</v>
+        <v>26.2828911303566</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1119094064192624</v>
+        <v>18.48560020294989</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0458085714660809</v>
+        <v>15.94854100080016</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0955364833384698</v>
+        <v>10.83134393699178</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0907726831588391</v>
+        <v>10.26958627295098</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08585238889331689</v>
+        <v>10.11129516592296</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0924781793445634</v>
+        <v>9.72393102764693</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0904331843304982</v>
+        <v>8.9129360078422</v>
       </c>
       <c r="N5" t="n">
-        <v>0.088388189316433</v>
+        <v>8.159519910168921</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07703304385666861</v>
+        <v>7.30322658418449</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0898759453462421</v>
+        <v>6.38325708600887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08481924331202149</v>
+        <v>5.94995415610119</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08275398253571881</v>
+        <v>5.78832592043167</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0890150850471267</v>
+        <v>5.74103311675476</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1209719406567524</v>
+        <v>5.798420852090199</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09726440414763859</v>
+        <v>5.95392807752917</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0846105238640988</v>
+        <v>6.28598760908609</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1005408348889727</v>
+        <v>6.726354342558551</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0709953875595061</v>
+        <v>7.101853326479091</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0414499402300394</v>
+        <v>7.42077671712673</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0005202762158829</v>
+        <v>7.54809632675002</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0005384279812907</v>
+        <v>7.385384893803939</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003958872747585</v>
+        <v>7.071602289193151</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0004378613584437</v>
+        <v>6.798263909116669</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004175690770195</v>
+        <v>6.60479725288948</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.000475850658346</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0368214318847305</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0371274350586247</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0382286394897987</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0322539520512397</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0005554030173075</v>
+        <v>6.54950627386524</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0005050438331758</v>
+        <v>6.54950627386523</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0169184459012511</v>
+        <v>6.54950627386524</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.166304820205857</v>
+        <v>10.66914943959788</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07689431445227719</v>
+        <v>11.89593073708603</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1786480185294241</v>
+        <v>13.87219427007815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1675500605145725</v>
+        <v>15.88888074721985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1553180825575322</v>
+        <v>17.94050210486442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.073795653442986</v>
+        <v>20.32236458807132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1428083901535604</v>
+        <v>22.3004139023869</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0691046969884174</v>
+        <v>23.35001916503822</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1448223007690025</v>
+        <v>24.68180783065078</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1464421585581165</v>
+        <v>25.68793257061645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1376717729495599</v>
+        <v>26.00120895339931</v>
       </c>
       <c r="M6" t="n">
-        <v>0.138797116353612</v>
+        <v>26.86982895574822</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1272446729394464</v>
+        <v>27.87768559411466</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1277356866639583</v>
+        <v>28.37705516022214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1238753097080134</v>
+        <v>28.87175439162482</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08533869136685029</v>
+        <v>28.95811079718658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0955921224825857</v>
+        <v>28.23094960278189</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0878645807001182</v>
+        <v>27.40251692764412</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0338166393450233</v>
+        <v>26.63900526826298</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0925998799339933</v>
+        <v>25.77044703623744</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1157755128245711</v>
+        <v>24.87849218694561</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0961475734647011</v>
+        <v>23.83930631661191</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0924370835759889</v>
+        <v>21.95737099253772</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1023650904508361</v>
+        <v>18.7325632693438</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.1020779848490725</v>
+        <v>15.8857830697955</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0997903164672805</v>
+        <v>14.51057389800727</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1174587756422715</v>
+        <v>13.30080187615435</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1103893042747</v>
+        <v>13.51665866037474</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.1250544628696835</v>
+        <v>14.88205947446574</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1176715969873199</v>
+        <v>15.66829411232546</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1125413058473745</v>
+        <v>15.70951744193439</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1150022181243949</v>
+        <v>15.85644116447086</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1106088609188624</v>
+        <v>16.27603622802609</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.1120646080299371</v>
+        <v>16.68349394510347</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1190205854394707</v>
+        <v>16.96619269776509</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1088922568372681</v>
+        <v>17.24070452317485</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1060273982176991</v>
+        <v>17.43338156330044</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2.5</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>6.051339292432719</v>
+      </c>
       <c r="C7" t="n">
-        <v>0.1182517426768743</v>
+        <v>5.70540721342904</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0645173944578169</v>
+        <v>5.69861823142976</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0107830462387594</v>
+        <v>5.69202654214327</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1729623827959471</v>
+        <v>5.68431310359437</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1825998437852784</v>
+        <v>5.70167549525025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1698840317067916</v>
+        <v>5.72400436473162</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1700652352569399</v>
+        <v>5.75215107484449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.178141655615605</v>
+        <v>5.8497794468741</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0904767447648081</v>
+        <v>6.04575887669993</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1731463289459488</v>
+        <v>6.33748242255388</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0016006263481079</v>
+        <v>6.595376776151431</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0016484500685522</v>
+        <v>6.649236331901929</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1207795370130153</v>
+        <v>6.62793463714826</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1328336815159226</v>
+        <v>6.534125651832989</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1290406930466038</v>
+        <v>6.23527637075151</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1331711098322672</v>
+        <v>6.102396285562009</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1569099317216881</v>
+        <v>6.22323952685764</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1518405867014649</v>
+        <v>6.391161121981261</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1433442045350564</v>
+        <v>6.53133855720682</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1348478223686479</v>
+        <v>6.593962941205129</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1487022043733529</v>
+        <v>6.52360280454162</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1565619650954157</v>
+        <v>6.49167647695952</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1512878030084697</v>
+        <v>6.46963761525058</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.1301500311571645</v>
+        <v>6.46525570411607</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1629972376407777</v>
+        <v>6.53978889396852</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1427303528934759</v>
+        <v>6.634153334139279</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1553474773497138</v>
+        <v>6.66750052409715</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1462770761174357</v>
+        <v>6.69308631308207</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1698354197992299</v>
+        <v>6.74768665604377</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1532398007978945</v>
+        <v>6.81122043285017</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.148419316880924</v>
+        <v>6.843719191436739</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.1571561046417651</v>
+        <v>6.869093164594391</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.1791621511998331</v>
+        <v>6.801972417286289</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1517684565711628</v>
+        <v>6.58893729867213</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1646903082995341</v>
-      </c>
-      <c r="AL7" t="inlineStr"/>
+        <v>6.378220080125891</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6.15566742503474</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.5.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1151342002540544</v>
+        <v>0.06494125502871</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1166306777273177</v>
+        <v>4.57317148216148</v>
       </c>
       <c r="D8" t="n">
-        <v>0.118127155200581</v>
+        <v>4.81915362062287</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1101231016470977</v>
+        <v>5.05669739256793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1075964705826784</v>
+        <v>5.30558514916366</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1327919964383861</v>
+        <v>5.57148548115306</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0989937946349418</v>
+        <v>5.81779655392367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0011072109408626</v>
+        <v>6.08054453709783</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0834302884912647</v>
+        <v>6.316995029302459</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0868207613126882</v>
+        <v>6.577909361677841</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0828716146922291</v>
+        <v>6.849166035212161</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1069635283471451</v>
+        <v>7.1902254565387</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0849563111652101</v>
+        <v>7.746161469937279</v>
       </c>
       <c r="O8" t="n">
-        <v>0.096912127386823</v>
+        <v>8.319121955630211</v>
       </c>
       <c r="P8" t="n">
-        <v>0.074048501269985</v>
+        <v>8.69862533215286</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0709970221268042</v>
+        <v>8.8954615325303</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0870389167110571</v>
+        <v>8.84501241334098</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0700628687916147</v>
+        <v>8.693897836032221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.066278236284978</v>
+        <v>8.505356162264089</v>
       </c>
       <c r="U8" t="n">
-        <v>0.07752670840582609</v>
+        <v>8.298444531674241</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0738141002892494</v>
+        <v>8.160123290180419</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0753679128570639</v>
+        <v>8.07759703461984</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0683760700271419</v>
+        <v>8.039827177470411</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0681906150887419</v>
+        <v>8.081600432801359</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.073492240627803</v>
+        <v>7.824986325486361</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.06522180108950321</v>
+        <v>7.430874595570989</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0681191903240403</v>
+        <v>7.164471651121509</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0583439191398337</v>
+        <v>6.72762528302539</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0625993726645053</v>
+        <v>6.5142840629402</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0523605213650876</v>
+        <v>6.61372259879575</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0610747721135924</v>
+        <v>6.56716540656549</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0624173453093201</v>
+        <v>6.477552462232699</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0610488450358666</v>
+        <v>6.39888929104613</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0609893643918344</v>
+        <v>6.23059535607316</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0689833152439102</v>
+        <v>6.03615100244983</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0705228537642113</v>
-      </c>
-      <c r="AL8" t="inlineStr"/>
+        <v>5.86275782329929</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>5.69706966929833</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5.2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1145408906677329</v>
+        <v>3.78095063418986</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1269045422038187</v>
+        <v>0.83887975211188</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1698363142903615</v>
+        <v>1.67245018026808</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2032514642349643</v>
+        <v>2.48003436058284</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1689138623100515</v>
+        <v>3.27784196457832</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001982799775325</v>
+        <v>3.83147400427559</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1834411097277679</v>
+        <v>4.17949699304003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1675977232783057</v>
+        <v>4.41674684226711</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1827619533498134</v>
+        <v>4.593479169504191</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1600504942258626</v>
+        <v>4.64617812962784</v>
       </c>
       <c r="L9" t="n">
-        <v>0.157998088550562</v>
+        <v>4.59546983856396</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1681238627449239</v>
+        <v>4.53219873389017</v>
       </c>
       <c r="N9" t="n">
-        <v>0.167220957241712</v>
+        <v>4.51323320375422</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1494406031988814</v>
+        <v>4.52756769292452</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1369121863086643</v>
+        <v>4.64545875294198</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1671911102876988</v>
+        <v>4.85792155116708</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1441924675814216</v>
+        <v>5.07579605633729</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1672922597396432</v>
+        <v>5.26666423936428</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1424884082761673</v>
+        <v>5.300096002300729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1464723871648953</v>
+        <v>5.30217952170254</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1471836099595868</v>
+        <v>5.34486696204429</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1709587289539124</v>
+        <v>5.371199936396541</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1420561130013592</v>
+        <v>5.36058578607517</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1603352747436491</v>
+        <v>5.15515799039467</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.150857297087504</v>
+        <v>4.893710006077661</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1431131592004493</v>
+        <v>4.613313265827379</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.144155060214948</v>
+        <v>4.30121497890177</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1653874060159728</v>
+        <v>4.095241594737329</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.1565042695138309</v>
+        <v>4.03790775313439</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.1459010121732416</v>
+        <v>4.04397055022796</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1490569667867003</v>
+        <v>4.03870670628712</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1465380367427575</v>
+        <v>4.05704566960409</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.151049404950637</v>
+        <v>4.119894995050051</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.1577517509047768</v>
+        <v>4.20051555772588</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1485811398029707</v>
+        <v>4.32184146852207</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.1414230527055836</v>
+        <v>4.4540011781706</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1436338815148379</v>
+        <v>4.59739962384607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>17.19532857079312</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20.35502583645191</v>
+      </c>
       <c r="D10" t="n">
-        <v>0.2128148486525875</v>
+        <v>20.25768845566997</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2038243911371114</v>
+        <v>20.0277144673077</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2054126600613331</v>
+        <v>19.82290411937763</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2172285814956222</v>
+        <v>19.3005189344374</v>
       </c>
       <c r="H10" t="n">
-        <v>0.223231011021717</v>
+        <v>18.41952517876018</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2195553702960466</v>
+        <v>17.81972197724935</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2241180023464911</v>
+        <v>17.83399087667295</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1838270461252719</v>
+        <v>18.37206277137181</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1938705953294285</v>
+        <v>19.06195001653661</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1450801050684005</v>
+        <v>19.46686243382508</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1752591383971767</v>
+        <v>19.72477370261604</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1567263618234732</v>
+        <v>19.9284127938995</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1375899225709777</v>
+        <v>19.94577759220744</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1472821255552004</v>
+        <v>19.95715307048348</v>
       </c>
       <c r="R10" t="n">
-        <v>0.135652255014343</v>
+        <v>20.151549926783</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1108692921649325</v>
+        <v>20.03557552831678</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1488425380759826</v>
+        <v>19.8988271345939</v>
       </c>
       <c r="U10" t="n">
-        <v>0.152983421301828</v>
+        <v>20.18800656717638</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1571243045276733</v>
+        <v>20.76847634062949</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1479302675774391</v>
+        <v>21.56188042982454</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1545500840899234</v>
+        <v>22.57473108240078</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1514249688030862</v>
+        <v>23.16985796004056</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1441849650217835</v>
+        <v>23.15772599683563</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1649334515473284</v>
+        <v>22.92895293425466</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1404357464351735</v>
+        <v>22.56741082563215</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1715109447770438</v>
+        <v>22.05422325802082</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.143997742240488</v>
+        <v>21.64537275659065</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1417259365687853</v>
+        <v>21.26765400911962</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1394541308970827</v>
+        <v>20.89868438989172</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1439422018834029</v>
+        <v>20.70413706301624</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1524346313022373</v>
+        <v>20.64987116489978</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.1677442741530951</v>
+        <v>20.57483177090565</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1532915604549989</v>
+        <v>20.38365761387487</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1376758260614098</v>
+        <v>20.14359080101068</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1380539995427682</v>
+        <v>19.8825946176253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.25.1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>10.5335215577657</v>
+      </c>
       <c r="C11" t="n">
-        <v>0.1699307029721248</v>
+        <v>13.16653220424156</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2092966317122545</v>
+        <v>13.41939257086207</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1724339244245528</v>
+        <v>13.68729219799602</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1355712171368511</v>
+        <v>13.95959113581353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1840513641951478</v>
+        <v>14.25162305723907</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1880814640236387</v>
+        <v>14.58012553342566</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1862691093152308</v>
+        <v>14.82882587107441</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1838265415067673</v>
+        <v>14.99397480635532</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1777457648689999</v>
+        <v>15.18089989358859</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1958458632823926</v>
+        <v>15.45957168546024</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1930787152106024</v>
+        <v>15.83784294244667</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1808181003371422</v>
+        <v>16.32740335907798</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2128229325581428</v>
+        <v>16.65125494222622</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2199884760454639</v>
+        <v>16.84822306957316</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2121961728784792</v>
+        <v>16.81607939929177</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2101227853500307</v>
+        <v>16.60918929215188</v>
       </c>
       <c r="S11" t="n">
-        <v>0.163175381781702</v>
+        <v>16.55509980781396</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1908677848105977</v>
+        <v>16.54110985142116</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1710036931056497</v>
+        <v>16.34316946457406</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1427760457791322</v>
+        <v>16.14889985871017</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1674609538949249</v>
+        <v>15.95138722446755</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1465883466710887</v>
+        <v>15.50256024093136</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1253382802765362</v>
+        <v>15.1546989036188</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1410486242950167</v>
+        <v>15.17724290596502</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1669048451770071</v>
+        <v>15.32104106634399</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.153676085115841</v>
+        <v>15.63672335223895</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1519418292146689</v>
+        <v>16.16270798571152</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.1528584800987616</v>
+        <v>16.63212926267598</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1516114756207719</v>
+        <v>16.88397422040087</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1423049822381634</v>
+        <v>17.00049852528584</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1429038785379017</v>
+        <v>16.72256270882589</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1661585876402223</v>
+        <v>16.71123077255912</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.1658861098318023</v>
+        <v>17.06312712098039</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1409105961338816</v>
+        <v>17.95335833629977</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1631877774974832</v>
+        <v>18.9064442977498</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.1350583493534398</v>
+        <v>19.96510562118309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25.2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1832305976966251</v>
+        <v>8.48081354679449</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2078999096471458</v>
+        <v>8.993689684034461</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2453218103510099</v>
+        <v>9.262595645147011</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2173160245783742</v>
+        <v>9.53043647447087</v>
       </c>
       <c r="F12" t="n">
-        <v>0.211020928329552</v>
+        <v>9.805817460419131</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2616196675861051</v>
+        <v>10.05073387432453</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2189253551632952</v>
+        <v>10.27270073058118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2085564376285119</v>
+        <v>10.45442308418627</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2094106833137271</v>
+        <v>10.65222594567822</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2007901476026739</v>
+        <v>10.80437379009555</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2039432912478452</v>
+        <v>10.83735116589838</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1613156678994948</v>
+        <v>10.85164437252295</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09481531130094401</v>
+        <v>10.86407605424577</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1824044127986836</v>
+        <v>10.76223600541268</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2081062991676578</v>
+        <v>10.48628499324165</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2006385512327731</v>
+        <v>9.99957340823943</v>
       </c>
       <c r="R12" t="n">
-        <v>0.193828743952098</v>
+        <v>9.37344541659418</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2248547882530799</v>
+        <v>8.634022755803571</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1799224674845473</v>
+        <v>7.95528973674423</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1905261784517767</v>
+        <v>7.291760825492539</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2333846172724485</v>
+        <v>6.59894400506134</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2168012156381182</v>
+        <v>5.96179194236811</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2316170758047716</v>
+        <v>5.30820688310502</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1930805596672408</v>
+        <v>4.59867929445262</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1700410725880176</v>
+        <v>3.94979720919054</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1992718525484089</v>
+        <v>3.49469553570225</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.195645576552788</v>
+        <v>3.16156612989007</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2231740437206007</v>
+        <v>2.91882265846207</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.2109735340328409</v>
+        <v>2.79928453771116</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.2192248179369883</v>
+        <v>2.76132043630113</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2274761018411356</v>
+        <v>2.75398376177525</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.235727385745283</v>
+        <v>2.75398376177525</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2160640723854268</v>
+        <v>2.75398376177525</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.2282420169750545</v>
+        <v>2.75398376177525</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2386840905102567</v>
+        <v>2.75398376177525</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2003110123113304</v>
-      </c>
-      <c r="AL12" t="inlineStr"/>
+        <v>2.75398376177524</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>2.75398376177525</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.63</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>17.09373681013091</v>
+      </c>
       <c r="C13" t="n">
-        <v>0.0129505573846147</v>
+        <v>12.94494246995834</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1252594853629882</v>
+        <v>12.76142356349168</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1624268295397589</v>
+        <v>12.57869600675464</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1847115407538772</v>
+        <v>12.41908718652923</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2171980095652956</v>
+        <v>12.34090831324896</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2010899167089172</v>
+        <v>12.15493446002052</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1736882658743396</v>
+        <v>11.87980805301018</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07874382104724301</v>
+        <v>11.53991874425828</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1538594930885854</v>
+        <v>11.31896127169357</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1578104530076218</v>
+        <v>11.44461297280654</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1401770796956261</v>
+        <v>11.99769748917089</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1357525584019544</v>
+        <v>12.68558464744748</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1368357819428768</v>
+        <v>13.38070816188269</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1131396773823114</v>
+        <v>14.00046573216055</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1310250925715243</v>
+        <v>14.39009228488797</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1356567927476145</v>
+        <v>14.68845857101139</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1116959158687801</v>
+        <v>15.06330742291614</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1132081681757315</v>
+        <v>15.16449081119883</v>
       </c>
       <c r="U13" t="n">
-        <v>0.120079205436988</v>
+        <v>15.28116760859206</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1086518096643999</v>
+        <v>15.24474800432002</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1217847081722358</v>
+        <v>14.8606827477108</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1334206053348879</v>
+        <v>14.63714326289608</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1170043329263546</v>
+        <v>14.62007287522196</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1175024681143258</v>
+        <v>14.79439544256217</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.1226597649546857</v>
+        <v>15.37716276393408</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1272425448992295</v>
+        <v>15.94961346313839</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1149509369125591</v>
+        <v>16.56206657650606</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.117668958423947</v>
+        <v>17.16380775303225</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.1233772035874131</v>
+        <v>17.63424902204207</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.1071192539155423</v>
+        <v>18.03855415651189</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.1284920892247806</v>
+        <v>18.52544105627529</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.1156647619869291</v>
+        <v>18.85661856429838</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.09792356030073569</v>
+        <v>18.96954108005414</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1072459272855164</v>
+        <v>18.93111276558388</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0995547033413391</v>
+        <v>18.79637051108773</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1021915107933843</v>
+        <v>18.55933919221111</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0.5.1</t>
+          <t>0.63.1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0427969518132663</v>
+        <v>0.08685264735712001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0638621170961314</v>
+        <v>4.49478426800726</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0291598573917127</v>
+        <v>4.960247773292361</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0628714527127379</v>
+        <v>5.42681207855528</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0683943784077215</v>
+        <v>5.881505283808941</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0746855554936238</v>
+        <v>6.30375031627141</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06981430901707179</v>
+        <v>6.753902848052349</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0621407526795719</v>
+        <v>7.015048071870771</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0652808370940951</v>
+        <v>7.13253203153771</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0708153330607096</v>
+        <v>7.270933109940531</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0304266375708097</v>
+        <v>7.4479470626149</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0714207487288028</v>
+        <v>7.65536427843915</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0736340670054898</v>
+        <v>7.84477996338378</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0700600125280028</v>
+        <v>7.998103234219291</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0687793629800125</v>
+        <v>8.137403599921299</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0677640208915213</v>
+        <v>8.205385803933831</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0748859894220537</v>
+        <v>8.112586655588441</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0768910260864839</v>
+        <v>7.853442859176591</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0764139575361137</v>
+        <v>7.676810536905319</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0701693076954214</v>
+        <v>7.49702742582761</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0673369110446944</v>
+        <v>7.25914454878043</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0707471850609846</v>
+        <v>7.27689101101478</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0679469958068101</v>
+        <v>7.371627629950731</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0661676669984077</v>
+        <v>7.44393220595018</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.0728733553193</v>
+        <v>7.49554432147313</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0678747787458797</v>
+        <v>7.50693875653901</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0628123135162563</v>
+        <v>7.469258109878369</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.0657059835953918</v>
+        <v>7.3421863704376</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.06859965367452731</v>
+        <v>7.181543711504861</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.06576819366030651</v>
+        <v>7.035328894096341</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0639010623591168</v>
+        <v>6.917802335473711</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.06903960414602089</v>
+        <v>6.8404916472009</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0594425344200477</v>
+        <v>6.81638171636709</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0711428886880822</v>
+        <v>6.79232527845696</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0668327334563615</v>
+        <v>6.755632235344771</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0625225782246409</v>
+        <v>6.724198366493781</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0567473351415033</v>
+        <v>6.692747953007889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.5.2</t>
+          <t>0.63.2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0019436565048454</v>
+        <v>3.5372848038833</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0838957795284056</v>
+        <v>8.302480777476671</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0736747240829654</v>
+        <v>8.33107272990066</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0779988028202489</v>
+        <v>8.343781087371759</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0722660494200585</v>
+        <v>8.35606075838726</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0753809069112369</v>
+        <v>8.352283595085209</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0710661154317377</v>
+        <v>8.49197360953935</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0623358670705708</v>
+        <v>8.648727763809049</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0599325028449527</v>
+        <v>8.685897148393069</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0655093558215329</v>
+        <v>8.7875829192305</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0585135459623537</v>
+        <v>8.71568799473221</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0662016128974839</v>
+        <v>8.50838254338465</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0624277865195437</v>
+        <v>8.34434514651937</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0606490250454613</v>
+        <v>8.168798261998091</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0597334687969864</v>
+        <v>8.00186581758296</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0609310916838846</v>
+        <v>7.93678074347495</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0600647179134986</v>
+        <v>7.94355373901988</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0610406416525745</v>
+        <v>8.058712753133811</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0597167387026329</v>
+        <v>8.28127075936041</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0577885826889127</v>
+        <v>8.36435974578783</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0603733908306941</v>
+        <v>8.13135809034307</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0575826012464596</v>
+        <v>7.6597217743071</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0583846377534676</v>
+        <v>6.986861999365169</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0591866742604756</v>
+        <v>6.2172897081926</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.06654406630263029</v>
+        <v>5.46259170259129</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.055386620754035</v>
+        <v>4.85520205137457</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0557912553380819</v>
+        <v>4.40297675805774</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0561958899221289</v>
+        <v>4.08659647722504</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0540324912394955</v>
+        <v>3.94007957376992</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.056902229327464</v>
+        <v>3.87115396095867</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0605804455971141</v>
+        <v>3.90191135740589</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0535665487113466</v>
+        <v>3.97508740967993</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0551243002143774</v>
+        <v>4.11578741256361</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0547825245511269</v>
+        <v>4.25787017111564</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.0591681418417801</v>
+        <v>4.33743536782725</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.0532502557500236</v>
+        <v>4.41410679331674</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0524124576782543</v>
+        <v>4.47091120684312</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.5.3</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0575335910655757</v>
+        <v>7.009276281859191</v>
       </c>
       <c r="C16" t="n">
-        <v>0.07590358614133549</v>
+        <v>5.4592631886099</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0671574865913187</v>
+        <v>5.67786028342174</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06495871982715599</v>
+        <v>5.88477777171848</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06641548282175989</v>
+        <v>6.082092073499689</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0742628946964301</v>
+        <v>6.308950103463</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0683664282619915</v>
+        <v>6.492348318043501</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07100627637546809</v>
+        <v>6.552213099108339</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06972680230488951</v>
+        <v>6.50033275871998</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0672137331268868</v>
+        <v>6.40858563332338</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0567655475314161</v>
+        <v>6.361746676281441</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06779156318254061</v>
+        <v>6.355408853365329</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0702399365437638</v>
+        <v>6.35081512640268</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0725231141184019</v>
+        <v>6.403071013637381</v>
       </c>
       <c r="P16" t="n">
-        <v>0.06789574119586</v>
+        <v>6.553930351016129</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0609481775779727</v>
+        <v>6.692265729239249</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0551454670048873</v>
+        <v>6.800059793537019</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0509547313399957</v>
+        <v>7.00637409130601</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0466149280595483</v>
+        <v>7.26950565501767</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0475129579940222</v>
+        <v>7.50940193558956</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0513253065706129</v>
+        <v>7.77570940756791</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0499089476121304</v>
+        <v>8.07093582852343</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0516265147970306</v>
+        <v>8.312716823284159</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0533440819819309</v>
+        <v>8.444603133497381</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0529617433013786</v>
+        <v>8.549184441447121</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.044650757449847</v>
+        <v>8.64021414407862</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0478070876877176</v>
+        <v>8.663633519499921</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.047868499909524</v>
+        <v>8.66708684020565</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0479299121313304</v>
+        <v>8.66785488297236</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0445026288707522</v>
+        <v>8.540612268860039</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0454439427540009</v>
+        <v>8.44670892296409</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0399487455828321</v>
+        <v>8.42129332120944</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0375154776208658</v>
+        <v>8.441968223808169</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0350822096588996</v>
+        <v>8.536974153824509</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0336099833586162</v>
+        <v>8.67778577275409</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.035035690038835</v>
+        <v>8.812120003541921</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.0364613967190537</v>
+        <v>8.94982594276691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.31.1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1755732657962119</v>
+        <v>3.77622541413755</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1551714195109038</v>
+        <v>3.94077766335114</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1594971881639619</v>
+        <v>3.1432846720955</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1448649404719098</v>
+        <v>2.37927512268636</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1758783581629915</v>
+        <v>1.6981299579787</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1291791837927495</v>
+        <v>1.51458384613362</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1378050484331694</v>
+        <v>1.61476725498053</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1337342946439025</v>
+        <v>2.21327931530405</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1296635408546356</v>
+        <v>2.94802074504705</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1589647890412514</v>
+        <v>3.33594668310576</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1385955788157598</v>
+        <v>3.24730166908109</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1341047073093354</v>
+        <v>3.14587615403454</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0640964165018018</v>
+        <v>3.09871382495262</v>
       </c>
       <c r="O17" t="n">
-        <v>0.137289032668111</v>
+        <v>3.01165701687812</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1341241176783059</v>
+        <v>3.11317814965211</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1345183003031125</v>
+        <v>3.36687232026157</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1360616804617031</v>
+        <v>3.5077212861631</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1134003724145918</v>
+        <v>3.65635552321878</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1409778811479764</v>
+        <v>3.99325373868397</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1294828324245885</v>
+        <v>4.22011658149419</v>
       </c>
       <c r="V17" t="n">
-        <v>0.127624856122561</v>
+        <v>4.26984380144669</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1109875263981576</v>
+        <v>4.32455944610455</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1239863313801242</v>
+        <v>4.32398031699159</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1050573705680091</v>
+        <v>4.18206546773413</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1290337521037886</v>
+        <v>4.01468305626077</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.1343340606249503</v>
+        <v>3.77316493429036</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.1268822934111712</v>
+        <v>3.24142456379294</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1265330545608508</v>
+        <v>2.51284303897113</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1046725042361869</v>
+        <v>1.75137265520491</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.1266517793574745</v>
+        <v>1.1632793995807</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1278988304382209</v>
+        <v>1.13409105144389</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.1288552822858767</v>
+        <v>1.62268782237996</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.1209366990248458</v>
+        <v>2.43253826895777</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.1308854533383837</v>
+        <v>3.36827824909584</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1144353945189021</v>
+        <v>4.02972445451165</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.115905451023084</v>
+        <v>4.62577815749627</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.1397626530977186</v>
+        <v>5.16535578542594</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0.25.1</t>
+          <t>0.31.2</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0322880613247309</v>
+        <v>6.63011346269113</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0299051010446905</v>
+        <v>7.00072702956441</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0006957793237999</v>
+        <v>7.043359572296951</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0133127555234567</v>
+        <v>7.09841209543759</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0006870722836655</v>
+        <v>7.1547253595605</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0005910957667276</v>
+        <v>7.24307149500316</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0006570813695814</v>
+        <v>7.352984797216509</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0007083836048556</v>
+        <v>7.46382025564246</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0006268414487982</v>
+        <v>7.555658107005581</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0007107085477458</v>
+        <v>7.641415725632609</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0008849504251097</v>
+        <v>7.720519304553131</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0007149783422249</v>
+        <v>7.67468155568792</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0006216271308872</v>
+        <v>7.49341907700326</v>
       </c>
       <c r="O18" t="n">
-        <v>0.029554668125307</v>
+        <v>7.261432571345621</v>
       </c>
       <c r="P18" t="n">
-        <v>0.000792844525953</v>
+        <v>7.01097776990945</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.000700347418959</v>
+        <v>6.81357962715927</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0006078503119649</v>
+        <v>6.640254528996</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0007438781124662</v>
+        <v>6.5080716045664</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0006330651830591</v>
+        <v>6.47517459196049</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0306276490662268</v>
+        <v>6.332489751571161</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0009321454311935</v>
+        <v>6.35968631872884</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0005000757518374</v>
+        <v>6.55753354572378</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0004384741901008</v>
+        <v>6.70051048411343</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.0336440770319277</v>
+        <v>6.83281579237401</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.0341002983791865</v>
+        <v>6.951743326980051</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.0391328534883408</v>
+        <v>7.03733667091697</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0329116041866823</v>
+        <v>7.08771247740842</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0006958162636822</v>
+        <v>7.06492443410488</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0366554642496958</v>
+        <v>6.953665619474821</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.0329548315829035</v>
+        <v>6.826959363053089</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0325905665740664</v>
+        <v>6.75258500854244</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.0006554057462687</v>
+        <v>6.75114176101514</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.0326974655306621</v>
+        <v>6.859646390954779</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0327324192067022</v>
+        <v>7.055313219303989</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.0176409800246582</v>
+        <v>7.32278836050501</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0025495408426143</v>
+        <v>7.5949176030329</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0007907016565878</v>
+        <v>7.86931466385852</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0.25.2</t>
+          <t>0.31.3</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1483367894502431</v>
+        <v>5.41640793975296</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0939889665308016</v>
+        <v>5.0964400886293</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0814918792585108</v>
+        <v>5.29946981515675</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0747155295372874</v>
+        <v>5.497868396414439</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0386403951453178</v>
+        <v>5.7393237249912</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08057404122256639</v>
+        <v>5.84781013913656</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0812667242327841</v>
+        <v>5.85213907943515</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0377682054185864</v>
+        <v>5.93131128278936</v>
       </c>
       <c r="J19" t="n">
-        <v>0.084180157613521</v>
+        <v>6.06260330374108</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0015560401246642</v>
+        <v>6.21465303827889</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0013433841040684</v>
+        <v>6.39086058587578</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08242674534993349</v>
+        <v>6.509012906487111</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08039653432900989</v>
+        <v>6.526036628728581</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0926119269968507</v>
+        <v>6.46409532064466</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0778527760875555</v>
+        <v>6.368283255957071</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08206010825034191</v>
+        <v>6.272690936789049</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0749811735472545</v>
+        <v>6.1814440670239</v>
       </c>
       <c r="S19" t="n">
-        <v>0.08446912757637259</v>
+        <v>6.062147639696789</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0745086009376239</v>
+        <v>6.03642359009337</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0691960794879232</v>
+        <v>6.077674244796031</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0797640533129632</v>
+        <v>6.10901588768147</v>
       </c>
       <c r="W19" t="n">
-        <v>0.08911512283824009</v>
+        <v>6.22902513902314</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0834135705620636</v>
+        <v>6.34872510778039</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.084269056845949</v>
+        <v>6.354997610114591</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.0864567532506767</v>
+        <v>6.324445284672101</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.09077812760078401</v>
+        <v>6.27956678420552</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0937571911378673</v>
+        <v>6.20727880671791</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1039533991673433</v>
+        <v>6.034696250641311</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.0947323811351873</v>
+        <v>5.73437382857158</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.1100673907653554</v>
+        <v>5.386135115205779</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.1019283982950553</v>
+        <v>4.98447317560956</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.106835442089629</v>
+        <v>4.64930603412366</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.0868603164711296</v>
+        <v>4.41230503199084</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.0909763542672965</v>
+        <v>4.25249530029848</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.0897925159054191</v>
+        <v>4.128169951345391</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.0808507584308116</v>
+        <v>4.0047993603996</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.0919608067035006</v>
+        <v>3.8755689148383</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.0088902818715813</v>
+        <v>0.11571844899627</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0210922089900969</v>
+        <v>0.05002329159134999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0824829170542838</v>
+        <v>0.04940074762523</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2065377653355705</v>
+        <v>0.04858652985433</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2021915515524092</v>
+        <v>0.04770979128596</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1989045134764498</v>
+        <v>0.04562637808511</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2460729606199137</v>
+        <v>0.0438055851573</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2245906764934593</v>
+        <v>0.03975113769096</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2288479146099194</v>
+        <v>0.03801846104597</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2267001173359912</v>
+        <v>0.03876417246887</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2137292500097758</v>
+        <v>0.04025689988726</v>
       </c>
       <c r="M20" t="n">
-        <v>0.192722959697963</v>
+        <v>0.04256417414948</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1916207557631602</v>
+        <v>0.04445878159258</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1869924539950921</v>
+        <v>0.04485232381605</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1910546696824187</v>
+        <v>0.04507589476497</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1787711331842413</v>
+        <v>0.04630589070525</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1694389386358883</v>
+        <v>0.04826617598143</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1995109576149673</v>
+        <v>0.04876145198596</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2018093974127988</v>
+        <v>0.04950191156245</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1712681925737704</v>
+        <v>0.05060319702871999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1822623934315451</v>
+        <v>0.05025517566414</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1932565942893197</v>
+        <v>0.05002710874214</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1772579960165399</v>
+        <v>0.04963291354365</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1812801581623013</v>
+        <v>0.04955741746303</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.1781326923303651</v>
+        <v>0.04893618965438001</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1709640978537503</v>
+        <v>0.04871464823398</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1817101271182748</v>
+        <v>0.04907657578853</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.2063370372554436</v>
+        <v>0.04880427792105</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.1732049344260001</v>
+        <v>0.04817726246709</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.1862744343834403</v>
+        <v>0.04766896756882</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.193722838207691</v>
+        <v>0.04744926011396</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.1926821771142141</v>
+        <v>0.04756073649389</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.1671599681914106</v>
+        <v>0.04792062559698</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.194875226306491</v>
+        <v>0.0482226739197</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.19405366202237</v>
+        <v>0.04785167986841</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.1754188955378523</v>
+        <v>0.0473545612099</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.1674645085754593</v>
+        <v>0.04673170962203</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0.125.1</t>
+          <t>0.16.1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1354847459778925</v>
+        <v>13.07483707637768</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0095781282609707</v>
+        <v>14.52924344188416</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0913548286332576</v>
+        <v>14.26635146654551</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1858602119181119</v>
+        <v>14.01445720584751</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1899241414952078</v>
+        <v>13.76727149135796</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1963516104134922</v>
+        <v>13.5032518375715</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1818283600362098</v>
+        <v>13.0072952410592</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1755016954195297</v>
+        <v>12.62609721673647</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1669290182295841</v>
+        <v>12.49683879183234</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1811028322698581</v>
+        <v>12.2036762081223</v>
       </c>
       <c r="L21" t="n">
-        <v>0.154637622487001</v>
+        <v>12.18590521095298</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1539826654204946</v>
+        <v>12.38476594415165</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1436348276414474</v>
+        <v>12.39517919446969</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1409484103619535</v>
+        <v>12.29474773428309</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0616505103747776</v>
+        <v>12.29421106243129</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.145213853137621</v>
+        <v>12.31276100987286</v>
       </c>
       <c r="R21" t="n">
-        <v>0.131962788901161</v>
+        <v>12.35907058189142</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1164083358625802</v>
+        <v>12.43082500403687</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1079572003378005</v>
+        <v>12.3240664052391</v>
       </c>
       <c r="U21" t="n">
-        <v>0.050178497989638</v>
+        <v>12.00199535876532</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1088413661425828</v>
+        <v>11.7090233301215</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1053628432154247</v>
+        <v>11.55244175696777</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1197286706157068</v>
+        <v>11.52146970682829</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1068681149437408</v>
+        <v>11.63314012471768</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0982399067572749</v>
+        <v>11.84793854315817</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.1591072258515678</v>
+        <v>11.8712638574052</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.1148675207189522</v>
+        <v>11.60985205519787</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.1014224831983116</v>
+        <v>11.46616735383693</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.1110042642509168</v>
+        <v>11.41068249004494</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.124302592543934</v>
+        <v>11.30302081196658</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.1251824050032556</v>
+        <v>11.26252083681901</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.1260032035558541</v>
+        <v>11.29870802803134</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.1256306057880164</v>
+        <v>11.32860658019629</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.1240683985452624</v>
+        <v>11.37172513500087</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.1337689157349397</v>
+        <v>11.38899886958244</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.1534337510581772</v>
+        <v>11.42452130966013</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.1633817336963702</v>
+        <v>11.47046075319794</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>0.125.2</t>
+          <t>0.16.2</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1908904948247531</v>
+        <v>4.96873857369238</v>
       </c>
       <c r="C22" t="n">
-        <v>0.207778941062329</v>
+        <v>9.66871476115703</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1969180024122839</v>
+        <v>9.761364030315329</v>
       </c>
       <c r="E22" t="n">
-        <v>0.191588498497533</v>
+        <v>9.882965612366359</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0023080043453102</v>
+        <v>10.03436748429131</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1720119916059917</v>
+        <v>10.24381107599394</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1865643599115039</v>
+        <v>10.35518777503079</v>
       </c>
       <c r="I22" t="n">
-        <v>0.173593501149412</v>
+        <v>10.4748977094966</v>
       </c>
       <c r="J22" t="n">
-        <v>0.16062264238732</v>
+        <v>10.4379801187799</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1316896704371599</v>
+        <v>10.3665298237506</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1317587213634103</v>
+        <v>10.2955437710199</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1348902308034098</v>
+        <v>10.30068455591643</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1564730616514683</v>
+        <v>10.37831126281555</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1327868612140011</v>
+        <v>10.4696780218101</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1392508598602931</v>
+        <v>10.47130882602911</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1295121866902718</v>
+        <v>10.41249001731256</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1122384172131507</v>
+        <v>10.30531959909541</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0977735101045728</v>
+        <v>10.10047717720342</v>
       </c>
       <c r="T22" t="n">
-        <v>0.105661920740268</v>
+        <v>10.06018168091893</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1115237994612402</v>
+        <v>10.05714861389452</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1222805937326263</v>
+        <v>10.04706186432555</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1222293171688552</v>
+        <v>10.08882644685147</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1325920440256084</v>
+        <v>10.14257353873523</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1240562838264583</v>
+        <v>10.1367054830218</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1006142927895275</v>
+        <v>10.1265256253513</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.0926614913266878</v>
+        <v>10.22987766268375</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.0972678644919921</v>
+        <v>10.29833486386701</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.0903010693405604</v>
+        <v>10.27621423227441</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.0835388123410036</v>
+        <v>10.20244965334106</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.1044546853348939</v>
+        <v>10.09055836001865</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.097119685037746</v>
+        <v>10.00866706504953</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.111139198204204</v>
+        <v>9.95295148883314</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.0967754168038799</v>
+        <v>9.9608045664027</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.09495263804772471</v>
+        <v>10.01629292967224</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.1095107182191342</v>
+        <v>9.821450251764601</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.08997418907326241</v>
+        <v>9.58683992861104</v>
       </c>
       <c r="AL22" t="n">
-        <v>0.0740017330508055</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>0.125.3</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.1924670363759056</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.09465465725913889</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0809691016532554</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0849915596357157</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.0396946407602597</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.09334053727827139</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.08703948852894459</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0724839291422824</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.039310801775406</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.0963091742638771</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.0872013389793236</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.08411575353151909</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.0808956505577146</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.0788092993535424</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.0862807976911914</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.0817451997994913</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.07154841326387019</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.0718701248363172</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.07159158547388079</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.07317319603353491</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.0654818347997113</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0.0700259902694515</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0.0765794362445623</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0.0681275550828722</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0.0781885713288942</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.0626705329336613</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0.06325263863080741</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0.0520704802061848</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.0497580565285433</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0.0590124532435905</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.0556185969755454</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>0.0571679752515881</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0.0549828191838632</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0.0564087430950618</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0.0633726514814576</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>0.0706037962876523</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0.07432672846200911</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>0.062</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0.1265886563207419</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.1549614975469626</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0247175134933624</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.1852925738875905</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.1639264081612378</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.2125637322818334</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.183537718424598</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.0840875354992154</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.1672967838569794</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.1547252176830344</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.1905901329916098</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.1756333027434732</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.1527303959633007</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.1587119611301677</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.1662256905087677</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.1491525441302398</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.1707582369246089</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.1640042333302049</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.1648986127623446</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1534638982730505</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.174307599158282</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.1849798324239796</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.165481097645829</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0.1639367670074792</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0.1617542269355173</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.1839774982669543</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0.1562754490929051</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.1917246407801194</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.1844789553704423</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.1816054283131228</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.1859442959984657</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.1979360508075389</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0.2024343617938317</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.2017388874963099</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.1997575582927225</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0.1789241707362875</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0.0710747292003143</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>0.062.1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0.0361968273967325</v>
-      </c>
-      <c r="C25" t="n">
-        <v>0.1385153330073237</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.2408338386179148</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1139322364999866</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.2001219745539983</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.08884503189138269</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.160445604702413</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.1885566445298256</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.1895129193540975</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.1700574893990388</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.1578475415623179</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.1521382016617477</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.1692028330100596</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.1528215063045555</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.1618452827955325</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.1358163261823027</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.1512721040801542</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.1577599576956359</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.1820548486961826</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.1853921129912508</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.1571730797496439</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0.1794709848112366</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0.1909049933724173</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.1972500312226885</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.1596171012595228</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.1940918437074559</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0.1643076323005425</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.1610583233517803</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.1643480340428796</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0.1446041431426024</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0.1558695421817019</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.1577775752053812</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0.1870258782557214</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0.1577247933991857</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.0977820011868112</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0.1112317140541477</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0.07825948351771229</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>0.062.2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>0.0665654773087723</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.0011907334520564</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0441033365574022</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0883547018394522</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.08923956196112839</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.09935506244323231</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0148557171935027</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0826574811926184</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1095440473144681</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.092612748789949</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.08514892520618279</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.09230615294349211</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.0721472502341988</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.09321597315174029</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.08263304596460259</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.0914365659545532</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.08732750936957979</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.0820161130070963</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.0009508980813553</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.0864351771212844</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.0828650169782929</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0.0777463341719013</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0.08488815183473961</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0.08784343135999741</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0.0966341823076014</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0.0989812513957585</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0.1013283204839155</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0.0982192768412942</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0.123477376439531</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0.1170476142051362</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0.1131231745599022</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0.1091987349146683</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0.0977652748432692</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0.0996657135230305</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0.1047479520119807</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0.09773623694893099</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0.0870749358778846</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>0.062.3</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.06272961442653251</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.08541100377708979</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.0659741694218856</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.0581045727759301</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.06595710690361919</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.0009642440560343</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.08560904818886279</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.0880509263542788</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.0716910160486052</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.063612794339485</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.0879382351002216</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.0855613810752657</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.0936891338242698</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.08297154995067681</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.094654395850003</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.0754913812504126</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.068075599058126</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.0755802647728589</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.0578669298040359</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.0600704395629383</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.0516354790014171</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0.0685814018934577</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0.0609532872894344</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0.0559155447355615</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0.0563485460454965</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.0586189347970668</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0.0635157752129413</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0.0558810026859505</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.0555616279309196</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0.0582865915347488</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.0622605075395852</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0.0579955492505822</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0.065242287479269</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0.057239960170626</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0.0584271023905816</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0.062256635347789</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0.06608616830499631</v>
+        <v>9.31658819745274</v>
       </c>
     </row>
   </sheetData>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
@@ -545,2007 +545,2007 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.65</v>
+        <v>38.15385</v>
       </c>
       <c r="C2" t="n">
-        <v>15.46110913916118</v>
+        <v>41.18440924534995</v>
       </c>
       <c r="D2" t="n">
-        <v>18.54935926913667</v>
+        <v>43.00610472774876</v>
       </c>
       <c r="E2" t="n">
-        <v>21.78694941568939</v>
+        <v>44.77339728849204</v>
       </c>
       <c r="F2" t="n">
-        <v>25.15555954722332</v>
+        <v>46.49455728133365</v>
       </c>
       <c r="G2" t="n">
-        <v>28.81458085605667</v>
+        <v>48.1891009083483</v>
       </c>
       <c r="H2" t="n">
-        <v>32.45646831177407</v>
+        <v>49.88642015604403</v>
       </c>
       <c r="I2" t="n">
-        <v>35.8670826286396</v>
+        <v>51.62535813266145</v>
       </c>
       <c r="J2" t="n">
-        <v>38.74707821881903</v>
+        <v>53.45218894152031</v>
       </c>
       <c r="K2" t="n">
-        <v>40.85599750600296</v>
+        <v>54.77617904694229</v>
       </c>
       <c r="L2" t="n">
-        <v>42.37063537461099</v>
+        <v>55.84454579464544</v>
       </c>
       <c r="M2" t="n">
-        <v>43.54229004790477</v>
+        <v>57.00665028624083</v>
       </c>
       <c r="N2" t="n">
-        <v>44.76148005009369</v>
+        <v>58.35758427196355</v>
       </c>
       <c r="O2" t="n">
-        <v>46.20238965044202</v>
+        <v>59.95454350700548</v>
       </c>
       <c r="P2" t="n">
-        <v>47.9041287907293</v>
+        <v>61.76043357773731</v>
       </c>
       <c r="Q2" t="n">
-        <v>49.87108999373954</v>
+        <v>63.63778475632594</v>
       </c>
       <c r="R2" t="n">
-        <v>52.16859961243863</v>
+        <v>65.52074277799137</v>
       </c>
       <c r="S2" t="n">
-        <v>54.88922832528763</v>
+        <v>67.46056339912576</v>
       </c>
       <c r="T2" t="n">
-        <v>57.8843165076551</v>
+        <v>69.50604263570351</v>
       </c>
       <c r="U2" t="n">
-        <v>60.91656520343245</v>
+        <v>71.4863469357953</v>
       </c>
       <c r="V2" t="n">
-        <v>63.87146863663083</v>
+        <v>73.15962187369836</v>
       </c>
       <c r="W2" t="n">
-        <v>66.6177309795255</v>
+        <v>74.50125182295737</v>
       </c>
       <c r="X2" t="n">
-        <v>68.87214829232791</v>
+        <v>75.58796834297448</v>
       </c>
       <c r="Y2" t="n">
-        <v>70.6225074454231</v>
+        <v>76.43036905110003</v>
       </c>
       <c r="Z2" t="n">
-        <v>72.04269128413308</v>
+        <v>77.00845000007193</v>
       </c>
       <c r="AA2" t="n">
-        <v>73.25190249284908</v>
+        <v>77.37533312849783</v>
       </c>
       <c r="AB2" t="n">
-        <v>74.08856250605247</v>
+        <v>77.61364050314899</v>
       </c>
       <c r="AC2" t="n">
-        <v>74.70540537820682</v>
+        <v>77.77147496942733</v>
       </c>
       <c r="AD2" t="n">
-        <v>75.3486755601544</v>
+        <v>77.8808390862776</v>
       </c>
       <c r="AE2" t="n">
-        <v>75.93489385348214</v>
+        <v>77.96332497201742</v>
       </c>
       <c r="AF2" t="n">
-        <v>76.44435227314752</v>
+        <v>78.05641894065562</v>
       </c>
       <c r="AG2" t="n">
-        <v>76.96859512627096</v>
+        <v>78.15283059561411</v>
       </c>
       <c r="AH2" t="n">
-        <v>77.45978897757188</v>
+        <v>78.25031594747713</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.78183462950511</v>
+        <v>78.3497010103534</v>
       </c>
       <c r="AJ2" t="n">
-        <v>77.97730360276522</v>
+        <v>78.45178507595105</v>
       </c>
       <c r="AK2" t="n">
-        <v>78.17191704180813</v>
+        <v>78.55717974129692</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.34836182488422</v>
+        <v>78.6664606966886</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>12.0.1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.12973</v>
+        <v>8.939189000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>3.25228039473922</v>
+        <v>5.690306474527997</v>
       </c>
       <c r="D3" t="n">
-        <v>3.364212683650287</v>
+        <v>9.757472833114388</v>
       </c>
       <c r="E3" t="n">
-        <v>3.48287177355173</v>
+        <v>13.83356505138237</v>
       </c>
       <c r="F3" t="n">
-        <v>3.605471173249272</v>
+        <v>17.89218186660172</v>
       </c>
       <c r="G3" t="n">
-        <v>3.729644358550961</v>
+        <v>21.90436905975167</v>
       </c>
       <c r="H3" t="n">
-        <v>3.864440643052854</v>
+        <v>25.85252304568188</v>
       </c>
       <c r="I3" t="n">
-        <v>3.989227608506113</v>
+        <v>29.74384578774674</v>
       </c>
       <c r="J3" t="n">
-        <v>4.02578611658015</v>
+        <v>33.65149486363735</v>
       </c>
       <c r="K3" t="n">
-        <v>3.983985999999987</v>
+        <v>37.26725360312446</v>
       </c>
       <c r="L3" t="n">
-        <v>24.827226</v>
+        <v>40.60987695877966</v>
       </c>
       <c r="M3" t="n">
-        <v>42.64999999999974</v>
+        <v>43.51145449862248</v>
       </c>
       <c r="N3" t="n">
-        <v>43.92647158240941</v>
+        <v>46.10075727048326</v>
       </c>
       <c r="O3" t="n">
-        <v>45.62294152566175</v>
+        <v>48.58588585421567</v>
       </c>
       <c r="P3" t="n">
-        <v>47.39843074614056</v>
+        <v>51.05896738692934</v>
       </c>
       <c r="Q3" t="n">
-        <v>48.86377706684392</v>
+        <v>53.57758553171818</v>
       </c>
       <c r="R3" t="n">
-        <v>50.14980627566681</v>
+        <v>56.13784615330489</v>
       </c>
       <c r="S3" t="n">
-        <v>51.33238789059841</v>
+        <v>58.69683544883144</v>
       </c>
       <c r="T3" t="n">
-        <v>52.25815007245286</v>
+        <v>61.24225398699563</v>
       </c>
       <c r="U3" t="n">
-        <v>53.08098689436493</v>
+        <v>63.79179441527732</v>
       </c>
       <c r="V3" t="n">
-        <v>53.97803545431091</v>
+        <v>66.33251348027126</v>
       </c>
       <c r="W3" t="n">
-        <v>54.89395080360104</v>
+        <v>68.76114934886355</v>
       </c>
       <c r="X3" t="n">
-        <v>55.80648646616048</v>
+        <v>70.91529884974</v>
       </c>
       <c r="Y3" t="n">
-        <v>56.71785604204922</v>
+        <v>72.69589122033932</v>
       </c>
       <c r="Z3" t="n">
-        <v>57.54661289204992</v>
+        <v>74.09436020239282</v>
       </c>
       <c r="AA3" t="n">
-        <v>58.33333228214769</v>
+        <v>75.16280379576749</v>
       </c>
       <c r="AB3" t="n">
-        <v>59.13217009365904</v>
+        <v>75.99411283515776</v>
       </c>
       <c r="AC3" t="n">
-        <v>59.90738148721586</v>
+        <v>76.66059968843074</v>
       </c>
       <c r="AD3" t="n">
-        <v>60.64849323320785</v>
+        <v>77.20629912959062</v>
       </c>
       <c r="AE3" t="n">
-        <v>61.34033651290144</v>
+        <v>77.64772816525735</v>
       </c>
       <c r="AF3" t="n">
-        <v>61.9017322318532</v>
+        <v>77.89473724047748</v>
       </c>
       <c r="AG3" t="n">
-        <v>62.28692040464059</v>
+        <v>78.12731310447916</v>
       </c>
       <c r="AH3" t="n">
-        <v>62.60854203504828</v>
+        <v>78.35199082062151</v>
       </c>
       <c r="AI3" t="n">
-        <v>62.86005339944435</v>
+        <v>78.56806915689523</v>
       </c>
       <c r="AJ3" t="n">
-        <v>62.93339635309037</v>
+        <v>78.77383955124071</v>
       </c>
       <c r="AK3" t="n">
-        <v>63.01839617799696</v>
+        <v>78.96803833437224</v>
       </c>
       <c r="AL3" t="n">
-        <v>63.10295976546545</v>
+        <v>79.15006103427092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>5.0.1</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.964865</v>
+        <v>5.001613</v>
       </c>
       <c r="C4" t="n">
-        <v>5.291480936428114</v>
+        <v>-2.029368501092248</v>
       </c>
       <c r="D4" t="n">
-        <v>6.005287715968212</v>
+        <v>1.167479767702273</v>
       </c>
       <c r="E4" t="n">
-        <v>6.747712947322447</v>
+        <v>4.372754946056205</v>
       </c>
       <c r="F4" t="n">
-        <v>7.512599396201913</v>
+        <v>7.585493357189227</v>
       </c>
       <c r="G4" t="n">
-        <v>8.451296166220136</v>
+        <v>10.79914389765527</v>
       </c>
       <c r="H4" t="n">
-        <v>10.02086437468918</v>
+        <v>14.01219199504057</v>
       </c>
       <c r="I4" t="n">
-        <v>11.8499214661563</v>
+        <v>17.22919978146577</v>
       </c>
       <c r="J4" t="n">
-        <v>13.80431178721747</v>
+        <v>20.46644210015365</v>
       </c>
       <c r="K4" t="n">
-        <v>15.96766516001771</v>
+        <v>24.18824917733735</v>
       </c>
       <c r="L4" t="n">
-        <v>18.86985630983473</v>
+        <v>28.40859732819048</v>
       </c>
       <c r="M4" t="n">
-        <v>21.8939564354245</v>
+        <v>32.26800773754054</v>
       </c>
       <c r="N4" t="n">
-        <v>24.75827965141584</v>
+        <v>36.16570279906732</v>
       </c>
       <c r="O4" t="n">
-        <v>27.5324244252263</v>
+        <v>39.97179941310271</v>
       </c>
       <c r="P4" t="n">
-        <v>30.13699462737576</v>
+        <v>43.88634582365443</v>
       </c>
       <c r="Q4" t="n">
-        <v>32.47017922929259</v>
+        <v>48.45857932493874</v>
       </c>
       <c r="R4" t="n">
-        <v>34.66086440229379</v>
+        <v>53.54925342201144</v>
       </c>
       <c r="S4" t="n">
-        <v>36.7697131490673</v>
+        <v>55.58081334536693</v>
       </c>
       <c r="T4" t="n">
-        <v>38.81949447505011</v>
+        <v>56.3828058323403</v>
       </c>
       <c r="U4" t="n">
-        <v>40.89437154318029</v>
+        <v>57.20735908791123</v>
       </c>
       <c r="V4" t="n">
-        <v>43.01014518092033</v>
+        <v>58.0834850767618</v>
       </c>
       <c r="W4" t="n">
-        <v>44.88084969938217</v>
+        <v>59.01511394708411</v>
       </c>
       <c r="X4" t="n">
-        <v>46.62280267369698</v>
+        <v>59.98595561585708</v>
       </c>
       <c r="Y4" t="n">
-        <v>48.32061970748242</v>
+        <v>60.97367655405558</v>
       </c>
       <c r="Z4" t="n">
-        <v>49.78862127591312</v>
+        <v>61.96384791555136</v>
       </c>
       <c r="AA4" t="n">
-        <v>50.85833357902915</v>
+        <v>62.94751053201913</v>
       </c>
       <c r="AB4" t="n">
-        <v>51.84194334783509</v>
+        <v>63.9149679230768</v>
       </c>
       <c r="AC4" t="n">
-        <v>52.82985333431148</v>
+        <v>64.85464063975373</v>
       </c>
       <c r="AD4" t="n">
-        <v>53.80128445200702</v>
+        <v>65.74275314775858</v>
       </c>
       <c r="AE4" t="n">
-        <v>54.69168281959904</v>
+        <v>66.55002298668049</v>
       </c>
       <c r="AF4" t="n">
-        <v>55.50763305461435</v>
+        <v>67.1544897257962</v>
       </c>
       <c r="AG4" t="n">
-        <v>56.27939891994482</v>
+        <v>67.74336866630934</v>
       </c>
       <c r="AH4" t="n">
-        <v>56.98025894804638</v>
+        <v>68.32179862174127</v>
       </c>
       <c r="AI4" t="n">
-        <v>57.5771197432014</v>
+        <v>68.88823419529949</v>
       </c>
       <c r="AJ4" t="n">
-        <v>58.02048210560845</v>
+        <v>69.44127456285338</v>
       </c>
       <c r="AK4" t="n">
-        <v>58.46286756062535</v>
+        <v>69.9792311884845</v>
       </c>
       <c r="AL4" t="n">
-        <v>58.89995906154616</v>
+        <v>70.50124561561532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>5.0.2</t>
+          <t>6.0.1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.26316</v>
+        <v>29.44151</v>
       </c>
       <c r="C5" t="n">
-        <v>31.17857346319187</v>
+        <v>12.87978735956546</v>
       </c>
       <c r="D5" t="n">
-        <v>32.26250208622808</v>
+        <v>16.45982839840487</v>
       </c>
       <c r="E5" t="n">
-        <v>33.32991287739645</v>
+        <v>20.02977054016261</v>
       </c>
       <c r="F5" t="n">
-        <v>34.39722039667004</v>
+        <v>23.58075124982324</v>
       </c>
       <c r="G5" t="n">
-        <v>35.4749546446668</v>
+        <v>27.1003237595179</v>
       </c>
       <c r="H5" t="n">
-        <v>36.57949487038102</v>
+        <v>30.59295558523418</v>
       </c>
       <c r="I5" t="n">
-        <v>37.79706652334375</v>
+        <v>34.09234994587251</v>
       </c>
       <c r="J5" t="n">
-        <v>39.16912191224822</v>
+        <v>37.72617862975618</v>
       </c>
       <c r="K5" t="n">
-        <v>40.66986513912704</v>
+        <v>41.69669803570388</v>
       </c>
       <c r="L5" t="n">
-        <v>42.19084908835267</v>
+        <v>45.69166783122434</v>
       </c>
       <c r="M5" t="n">
-        <v>43.63692739943872</v>
+        <v>48.6422712725649</v>
       </c>
       <c r="N5" t="n">
-        <v>44.98147496385357</v>
+        <v>49.9068465294166</v>
       </c>
       <c r="O5" t="n">
-        <v>46.37808707089665</v>
+        <v>50.7525896656044</v>
       </c>
       <c r="P5" t="n">
-        <v>47.92156009815821</v>
+        <v>51.56897501039063</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.60578792040895</v>
+        <v>52.42610162864796</v>
       </c>
       <c r="R5" t="n">
-        <v>51.60223125562006</v>
+        <v>53.34420461013102</v>
       </c>
       <c r="S5" t="n">
-        <v>53.76953866639514</v>
+        <v>54.30277959191759</v>
       </c>
       <c r="T5" t="n">
-        <v>55.94906170297703</v>
+        <v>55.28363910929025</v>
       </c>
       <c r="U5" t="n">
-        <v>57.90654274549994</v>
+        <v>56.28849453204322</v>
       </c>
       <c r="V5" t="n">
-        <v>59.51218192325025</v>
+        <v>57.32982343501502</v>
       </c>
       <c r="W5" t="n">
-        <v>60.90270396031817</v>
+        <v>58.41211565592474</v>
       </c>
       <c r="X5" t="n">
-        <v>62.05252006905096</v>
+        <v>59.5139935746579</v>
       </c>
       <c r="Y5" t="n">
-        <v>62.89991614844624</v>
+        <v>60.59071173152635</v>
       </c>
       <c r="Z5" t="n">
-        <v>63.61611797321594</v>
+        <v>61.60237320345753</v>
       </c>
       <c r="AA5" t="n">
-        <v>64.42028391329363</v>
+        <v>62.53676848893712</v>
       </c>
       <c r="AB5" t="n">
-        <v>65.4450012103994</v>
+        <v>63.38498815624804</v>
       </c>
       <c r="AC5" t="n">
-        <v>66.55031682088253</v>
+        <v>64.14689545542244</v>
       </c>
       <c r="AD5" t="n">
-        <v>67.65515516977804</v>
+        <v>64.82003741269602</v>
       </c>
       <c r="AE5" t="n">
-        <v>68.79383731445751</v>
+        <v>65.40613628154198</v>
       </c>
       <c r="AF5" t="n">
-        <v>69.81835003071336</v>
+        <v>65.85155775749095</v>
       </c>
       <c r="AG5" t="n">
-        <v>70.67677604046037</v>
+        <v>66.29081239024745</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.55734703730126</v>
+        <v>66.72565917587434</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.45225632336499</v>
+        <v>67.15462895929505</v>
       </c>
       <c r="AJ5" t="n">
-        <v>73.27684608656055</v>
+        <v>67.57633499278512</v>
       </c>
       <c r="AK5" t="n">
-        <v>74.11589180760028</v>
+        <v>67.99017095999825</v>
       </c>
       <c r="AL5" t="n">
-        <v>74.95057841386782</v>
+        <v>68.39666365315698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.0.2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.447945</v>
+        <v>6.951429</v>
       </c>
       <c r="C6" t="n">
-        <v>10.87932119499448</v>
+        <v>5.858295703763565</v>
       </c>
       <c r="D6" t="n">
-        <v>10.62255451165437</v>
+        <v>8.227357998192874</v>
       </c>
       <c r="E6" t="n">
-        <v>10.38178658784931</v>
+        <v>10.63963908735974</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1673609688286</v>
+        <v>13.09370821474319</v>
       </c>
       <c r="G6" t="n">
-        <v>10.09564592782764</v>
+        <v>15.5788890603055</v>
       </c>
       <c r="H6" t="n">
-        <v>10.01051957256907</v>
+        <v>18.08147546837781</v>
       </c>
       <c r="I6" t="n">
-        <v>9.947244983539671</v>
+        <v>20.58855663889699</v>
       </c>
       <c r="J6" t="n">
-        <v>9.935498443367919</v>
+        <v>23.09156226970834</v>
       </c>
       <c r="K6" t="n">
-        <v>9.6991296133096</v>
+        <v>25.88573190221823</v>
       </c>
       <c r="L6" t="n">
-        <v>14.84064669291528</v>
+        <v>28.86933734083511</v>
       </c>
       <c r="M6" t="n">
-        <v>18.67259963438416</v>
+        <v>32.05718550227014</v>
       </c>
       <c r="N6" t="n">
-        <v>22.51448075</v>
+        <v>35.39385636505409</v>
       </c>
       <c r="O6" t="n">
-        <v>26.76249999999999</v>
+        <v>38.81696177663581</v>
       </c>
       <c r="P6" t="n">
-        <v>31.29764980334756</v>
+        <v>42.27230192249594</v>
       </c>
       <c r="Q6" t="n">
-        <v>35.33052154499513</v>
+        <v>45.63013939491663</v>
       </c>
       <c r="R6" t="n">
-        <v>39.37702086242754</v>
+        <v>48.74419773919736</v>
       </c>
       <c r="S6" t="n">
-        <v>43.65819448388204</v>
+        <v>51.61960810310787</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6383525742102</v>
+        <v>54.35098518324812</v>
       </c>
       <c r="U6" t="n">
-        <v>45.40621800145292</v>
+        <v>57.0137815385764</v>
       </c>
       <c r="V6" t="n">
-        <v>46.21110092166333</v>
+        <v>59.58735361363851</v>
       </c>
       <c r="W6" t="n">
-        <v>47.0079973771416</v>
+        <v>62.00920937281028</v>
       </c>
       <c r="X6" t="n">
-        <v>47.76854883649862</v>
+        <v>64.21436589525258</v>
       </c>
       <c r="Y6" t="n">
-        <v>48.42665519268038</v>
+        <v>66.12809883096894</v>
       </c>
       <c r="Z6" t="n">
-        <v>48.85840642801567</v>
+        <v>67.74689046538288</v>
       </c>
       <c r="AA6" t="n">
-        <v>49.01927951332792</v>
+        <v>69.16998926714888</v>
       </c>
       <c r="AB6" t="n">
-        <v>49.02501382215354</v>
+        <v>70.47454633299941</v>
       </c>
       <c r="AC6" t="n">
-        <v>48.91264397950726</v>
+        <v>71.67050462971537</v>
       </c>
       <c r="AD6" t="n">
-        <v>48.71771074394292</v>
+        <v>72.75286372151186</v>
       </c>
       <c r="AE6" t="n">
-        <v>48.51745056374924</v>
+        <v>73.6996430330228</v>
       </c>
       <c r="AF6" t="n">
-        <v>48.31418086816166</v>
+        <v>74.29650155421407</v>
       </c>
       <c r="AG6" t="n">
-        <v>48.09153937573616</v>
+        <v>74.87765585001662</v>
       </c>
       <c r="AH6" t="n">
-        <v>47.95575740780998</v>
+        <v>75.43934618007835</v>
       </c>
       <c r="AI6" t="n">
-        <v>47.94500382251788</v>
+        <v>75.97967434496864</v>
       </c>
       <c r="AJ6" t="n">
-        <v>47.97430429169253</v>
+        <v>76.49831016742779</v>
       </c>
       <c r="AK6" t="n">
-        <v>48.00138578905763</v>
+        <v>76.99780389867504</v>
       </c>
       <c r="AL6" t="n">
-        <v>48.02681467784694</v>
+        <v>77.48219208247627</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.17286</v>
+        <v>23.7549</v>
       </c>
       <c r="C7" t="n">
-        <v>14.26105904580309</v>
+        <v>40.61659335992471</v>
       </c>
       <c r="D7" t="n">
-        <v>13.9098926239275</v>
+        <v>41.18252819531157</v>
       </c>
       <c r="E7" t="n">
-        <v>13.63958475458608</v>
+        <v>41.74965250166994</v>
       </c>
       <c r="F7" t="n">
-        <v>13.3793951841015</v>
+        <v>42.31827669973266</v>
       </c>
       <c r="G7" t="n">
-        <v>13.74553710014854</v>
+        <v>42.88882793263019</v>
       </c>
       <c r="H7" t="n">
-        <v>14.63412983260628</v>
+        <v>43.46190959203667</v>
       </c>
       <c r="I7" t="n">
-        <v>15.88968721298384</v>
+        <v>44.03840048014107</v>
       </c>
       <c r="J7" t="n">
-        <v>17.32711236962222</v>
+        <v>44.61962705170373</v>
       </c>
       <c r="K7" t="n">
-        <v>18.66309845644065</v>
+        <v>45.2813399283156</v>
       </c>
       <c r="L7" t="n">
-        <v>19.79191914522078</v>
+        <v>46.1439583809475</v>
       </c>
       <c r="M7" t="n">
-        <v>20.67627948137896</v>
+        <v>46.88931742532812</v>
       </c>
       <c r="N7" t="n">
-        <v>20.8945724092169</v>
+        <v>47.41625994489108</v>
       </c>
       <c r="O7" t="n">
-        <v>23.08931156937978</v>
+        <v>47.80712380175977</v>
       </c>
       <c r="P7" t="n">
-        <v>25.11694134468588</v>
+        <v>48.12768755571934</v>
       </c>
       <c r="Q7" t="n">
-        <v>27.0974690811125</v>
+        <v>48.38201597216268</v>
       </c>
       <c r="R7" t="n">
-        <v>29.15068089416545</v>
+        <v>48.56047029269077</v>
       </c>
       <c r="S7" t="n">
-        <v>32.3430172107745</v>
+        <v>48.66706780443199</v>
       </c>
       <c r="T7" t="n">
-        <v>34.8419967413932</v>
+        <v>48.72046446920793</v>
       </c>
       <c r="U7" t="n">
-        <v>36.8384549667144</v>
+        <v>48.73886618898326</v>
       </c>
       <c r="V7" t="n">
-        <v>38.26071725307348</v>
+        <v>48.72134786552585</v>
       </c>
       <c r="W7" t="n">
-        <v>39.12605162192885</v>
+        <v>48.66950081433539</v>
       </c>
       <c r="X7" t="n">
-        <v>39.58161980686216</v>
+        <v>48.58933695134671</v>
       </c>
       <c r="Y7" t="n">
-        <v>39.83633275672819</v>
+        <v>48.47842884563546</v>
       </c>
       <c r="Z7" t="n">
-        <v>40.06263848002204</v>
+        <v>48.33982680077087</v>
       </c>
       <c r="AA7" t="n">
-        <v>40.26531049485698</v>
+        <v>48.19100840123597</v>
       </c>
       <c r="AB7" t="n">
-        <v>40.38486767371072</v>
+        <v>48.05720357580576</v>
       </c>
       <c r="AC7" t="n">
-        <v>40.49607321798293</v>
+        <v>47.94837103282163</v>
       </c>
       <c r="AD7" t="n">
-        <v>40.6024921865476</v>
+        <v>47.85930437730013</v>
       </c>
       <c r="AE7" t="n">
-        <v>40.60570580932152</v>
+        <v>47.78179496883637</v>
       </c>
       <c r="AF7" t="n">
-        <v>40.65024278760167</v>
+        <v>47.7390184901161</v>
       </c>
       <c r="AG7" t="n">
-        <v>40.89626372446228</v>
+        <v>47.69669119742512</v>
       </c>
       <c r="AH7" t="n">
-        <v>41.18905413735824</v>
+        <v>47.6565809971016</v>
       </c>
       <c r="AI7" t="n">
-        <v>41.41143692408546</v>
+        <v>47.62082353186583</v>
       </c>
       <c r="AJ7" t="n">
-        <v>41.73075645691105</v>
+        <v>47.59058956562207</v>
       </c>
       <c r="AK7" t="n">
-        <v>42.05026733983939</v>
+        <v>47.56641326963968</v>
       </c>
       <c r="AL7" t="n">
-        <v>42.34643011921254</v>
+        <v>47.54819416875782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.697297000000001</v>
+        <v>18.79718</v>
       </c>
       <c r="C8" t="n">
-        <v>13.67713470146214</v>
+        <v>-2.833509489327127</v>
       </c>
       <c r="D8" t="n">
-        <v>12.89350048452637</v>
+        <v>1.757229720641175</v>
       </c>
       <c r="E8" t="n">
-        <v>12.09915254278754</v>
+        <v>6.335662509690906</v>
       </c>
       <c r="F8" t="n">
-        <v>11.31554998191995</v>
+        <v>10.89559332258662</v>
       </c>
       <c r="G8" t="n">
-        <v>10.61955486923859</v>
+        <v>15.43563961285314</v>
       </c>
       <c r="H8" t="n">
-        <v>9.782709853460464</v>
+        <v>19.9624519270276</v>
       </c>
       <c r="I8" t="n">
-        <v>14.20933544710776</v>
+        <v>24.50761220839373</v>
       </c>
       <c r="J8" t="n">
-        <v>17.40971531627517</v>
+        <v>29.23702032277017</v>
       </c>
       <c r="K8" t="n">
-        <v>20.59368515001883</v>
+        <v>34.2794809858074</v>
       </c>
       <c r="L8" t="n">
-        <v>24.26756999999999</v>
+        <v>39.48221086498919</v>
       </c>
       <c r="M8" t="n">
-        <v>28.55634500000001</v>
+        <v>42.59239994561067</v>
       </c>
       <c r="N8" t="n">
-        <v>32.21032942811716</v>
+        <v>44.76512590070772</v>
       </c>
       <c r="O8" t="n">
-        <v>35.78679678100372</v>
+        <v>46.80213973935584</v>
       </c>
       <c r="P8" t="n">
-        <v>40.80029413258546</v>
+        <v>48.74013331909192</v>
       </c>
       <c r="Q8" t="n">
-        <v>40.00443083845147</v>
+        <v>50.52849197629491</v>
       </c>
       <c r="R8" t="n">
-        <v>39.95327148181164</v>
+        <v>52.09193061383048</v>
       </c>
       <c r="S8" t="n">
-        <v>40.16595467106236</v>
+        <v>53.43698465451939</v>
       </c>
       <c r="T8" t="n">
-        <v>40.52264385778156</v>
+        <v>54.61887720276199</v>
       </c>
       <c r="U8" t="n">
-        <v>40.79862627433637</v>
+        <v>55.6814638016976</v>
       </c>
       <c r="V8" t="n">
-        <v>40.93317272396174</v>
+        <v>56.63952600263072</v>
       </c>
       <c r="W8" t="n">
-        <v>41.08654993420453</v>
+        <v>57.49144998995355</v>
       </c>
       <c r="X8" t="n">
-        <v>41.24807645862219</v>
+        <v>58.21989780198557</v>
       </c>
       <c r="Y8" t="n">
-        <v>41.6947028537048</v>
+        <v>58.7953471731268</v>
       </c>
       <c r="Z8" t="n">
-        <v>42.47085508650417</v>
+        <v>59.20542598379162</v>
       </c>
       <c r="AA8" t="n">
-        <v>43.19849073169033</v>
+        <v>59.49690346562</v>
       </c>
       <c r="AB8" t="n">
-        <v>43.69798399412674</v>
+        <v>59.73040436238623</v>
       </c>
       <c r="AC8" t="n">
-        <v>44.05896294838508</v>
+        <v>59.94423611258437</v>
       </c>
       <c r="AD8" t="n">
-        <v>44.13926233224553</v>
+        <v>60.15584390690478</v>
       </c>
       <c r="AE8" t="n">
-        <v>43.91222607511288</v>
+        <v>60.37283994032313</v>
       </c>
       <c r="AF8" t="n">
-        <v>43.5279372362061</v>
+        <v>60.62661304046892</v>
       </c>
       <c r="AG8" t="n">
-        <v>42.98449487888816</v>
+        <v>60.88706711046522</v>
       </c>
       <c r="AH8" t="n">
-        <v>42.32975792441082</v>
+        <v>61.15211698831309</v>
       </c>
       <c r="AI8" t="n">
-        <v>41.72962476766737</v>
+        <v>61.42031118434847</v>
       </c>
       <c r="AJ8" t="n">
-        <v>41.16779353473536</v>
+        <v>61.69012133380792</v>
       </c>
       <c r="AK8" t="n">
-        <v>40.59263209708094</v>
+        <v>61.96147659404727</v>
       </c>
       <c r="AL8" t="n">
-        <v>40.05178745089067</v>
+        <v>62.23481438416374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.394521</v>
+        <v>28.98116</v>
       </c>
       <c r="C9" t="n">
-        <v>3.547632805503286</v>
+        <v>-2.036347334554794</v>
       </c>
       <c r="D9" t="n">
-        <v>5.116186109467545</v>
+        <v>2.690064015853756</v>
       </c>
       <c r="E9" t="n">
-        <v>6.707166621569808</v>
+        <v>7.393011751975226</v>
       </c>
       <c r="F9" t="n">
-        <v>8.314975876545873</v>
+        <v>12.06249403972683</v>
       </c>
       <c r="G9" t="n">
-        <v>9.955183979858829</v>
+        <v>16.69484099544187</v>
       </c>
       <c r="H9" t="n">
-        <v>11.78586005404437</v>
+        <v>21.29761637566087</v>
       </c>
       <c r="I9" t="n">
-        <v>13.91460591102136</v>
+        <v>25.91553201399539</v>
       </c>
       <c r="J9" t="n">
-        <v>15.83764208034098</v>
+        <v>30.80710052439923</v>
       </c>
       <c r="K9" t="n">
-        <v>17.66332277221579</v>
+        <v>36.14930180843632</v>
       </c>
       <c r="L9" t="n">
-        <v>19.44413970039853</v>
+        <v>42.86971559248266</v>
       </c>
       <c r="M9" t="n">
-        <v>20.9417282410296</v>
+        <v>45.90270945094067</v>
       </c>
       <c r="N9" t="n">
-        <v>22.08821553717624</v>
+        <v>46.6833867479489</v>
       </c>
       <c r="O9" t="n">
-        <v>23.24176443031644</v>
+        <v>47.19272577590739</v>
       </c>
       <c r="P9" t="n">
-        <v>24.39336897765064</v>
+        <v>47.52085326135006</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.60626136258676</v>
+        <v>47.69776635311219</v>
       </c>
       <c r="R9" t="n">
-        <v>26.82601833338154</v>
+        <v>47.73810806726219</v>
       </c>
       <c r="S9" t="n">
-        <v>27.96829323963454</v>
+        <v>47.64815701442612</v>
       </c>
       <c r="T9" t="n">
-        <v>28.92506949133712</v>
+        <v>47.449362804484</v>
       </c>
       <c r="U9" t="n">
-        <v>29.72754885901848</v>
+        <v>47.23087369181012</v>
       </c>
       <c r="V9" t="n">
-        <v>30.39115449439561</v>
+        <v>47.02195127630789</v>
       </c>
       <c r="W9" t="n">
-        <v>30.88902683833037</v>
+        <v>46.83201907274125</v>
       </c>
       <c r="X9" t="n">
-        <v>31.24750116043358</v>
+        <v>46.67193890239377</v>
       </c>
       <c r="Y9" t="n">
-        <v>31.56214838075532</v>
+        <v>46.54159507120721</v>
       </c>
       <c r="Z9" t="n">
-        <v>31.84953919821209</v>
+        <v>46.43211162405765</v>
       </c>
       <c r="AA9" t="n">
-        <v>31.96873280366306</v>
+        <v>46.32815289798353</v>
       </c>
       <c r="AB9" t="n">
-        <v>31.83468056276029</v>
+        <v>46.22598864901195</v>
       </c>
       <c r="AC9" t="n">
-        <v>31.58123692663064</v>
+        <v>46.12770252847479</v>
       </c>
       <c r="AD9" t="n">
-        <v>31.23312174998874</v>
+        <v>46.02980604480427</v>
       </c>
       <c r="AE9" t="n">
-        <v>30.76940806717779</v>
+        <v>45.9342470211758</v>
       </c>
       <c r="AF9" t="n">
-        <v>30.3273181490677</v>
+        <v>45.81302562716695</v>
       </c>
       <c r="AG9" t="n">
-        <v>30.02109314794908</v>
+        <v>45.68501560037969</v>
       </c>
       <c r="AH9" t="n">
-        <v>29.80703127866024</v>
+        <v>45.55232678122326</v>
       </c>
       <c r="AI9" t="n">
-        <v>29.6522776816847</v>
+        <v>45.41567744960653</v>
       </c>
       <c r="AJ9" t="n">
-        <v>29.50803029598542</v>
+        <v>45.27556544569953</v>
       </c>
       <c r="AK9" t="n">
-        <v>29.366838706493</v>
+        <v>45.13193766973242</v>
       </c>
       <c r="AL9" t="n">
-        <v>29.21978108793043</v>
+        <v>44.98471688932641</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>1.25.1</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.539726</v>
+        <v>7.772603</v>
       </c>
       <c r="C10" t="n">
-        <v>16.87027323955277</v>
+        <v>6.742385562189478</v>
       </c>
       <c r="D10" t="n">
-        <v>17.74286052750478</v>
+        <v>9.443867181147796</v>
       </c>
       <c r="E10" t="n">
-        <v>18.64183833232763</v>
+        <v>12.17409552443433</v>
       </c>
       <c r="F10" t="n">
-        <v>19.55610832529299</v>
+        <v>14.91883576810328</v>
       </c>
       <c r="G10" t="n">
-        <v>20.52438796514669</v>
+        <v>17.66696555740661</v>
       </c>
       <c r="H10" t="n">
-        <v>21.76018544975185</v>
+        <v>20.40518837810045</v>
       </c>
       <c r="I10" t="n">
-        <v>23.64627591583746</v>
+        <v>23.0854618797357</v>
       </c>
       <c r="J10" t="n">
-        <v>25.43883211228479</v>
+        <v>25.46494678833732</v>
       </c>
       <c r="K10" t="n">
-        <v>27.12989518237</v>
+        <v>28.14278779300882</v>
       </c>
       <c r="L10" t="n">
-        <v>28.76206289815297</v>
+        <v>31.41712499771928</v>
       </c>
       <c r="M10" t="n">
-        <v>30.3616995831565</v>
+        <v>35.08286072818826</v>
       </c>
       <c r="N10" t="n">
-        <v>32.19355835170914</v>
+        <v>38.2071622065037</v>
       </c>
       <c r="O10" t="n">
-        <v>34.43443980166904</v>
+        <v>40.80082136065668</v>
       </c>
       <c r="P10" t="n">
-        <v>36.9335056915852</v>
+        <v>42.96178686388116</v>
       </c>
       <c r="Q10" t="n">
-        <v>39.60830582349993</v>
+        <v>44.78134476565633</v>
       </c>
       <c r="R10" t="n">
-        <v>42.25222764231462</v>
+        <v>46.33584508022105</v>
       </c>
       <c r="S10" t="n">
-        <v>44.54851695805557</v>
+        <v>47.58927224806572</v>
       </c>
       <c r="T10" t="n">
-        <v>46.53803300442479</v>
+        <v>48.27363460836148</v>
       </c>
       <c r="U10" t="n">
-        <v>48.15203867215413</v>
+        <v>48.38055889483341</v>
       </c>
       <c r="V10" t="n">
-        <v>49.3110699439448</v>
+        <v>48.1934213963317</v>
       </c>
       <c r="W10" t="n">
-        <v>50.22228042295586</v>
+        <v>47.84313867758479</v>
       </c>
       <c r="X10" t="n">
-        <v>51.01247782870399</v>
+        <v>47.34306264748182</v>
       </c>
       <c r="Y10" t="n">
-        <v>51.56806359694946</v>
+        <v>46.75430809054365</v>
       </c>
       <c r="Z10" t="n">
-        <v>51.89859225284453</v>
+        <v>46.1495940179727</v>
       </c>
       <c r="AA10" t="n">
-        <v>52.09730832112618</v>
+        <v>45.53455214971615</v>
       </c>
       <c r="AB10" t="n">
-        <v>52.14017712163138</v>
+        <v>44.88180803648409</v>
       </c>
       <c r="AC10" t="n">
-        <v>52.00762828612966</v>
+        <v>44.19589764890869</v>
       </c>
       <c r="AD10" t="n">
-        <v>51.69738174902004</v>
+        <v>43.50413902665835</v>
       </c>
       <c r="AE10" t="n">
-        <v>51.28743231991752</v>
+        <v>42.83568516483171</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.89913859478774</v>
+        <v>42.24989583416663</v>
       </c>
       <c r="AG10" t="n">
-        <v>50.53856435734566</v>
+        <v>41.67741165628581</v>
       </c>
       <c r="AH10" t="n">
-        <v>50.14604475555712</v>
+        <v>41.10168713439932</v>
       </c>
       <c r="AI10" t="n">
-        <v>49.769139677822</v>
+        <v>40.52190837566918</v>
       </c>
       <c r="AJ10" t="n">
-        <v>49.39305643040008</v>
+        <v>39.941533614442</v>
       </c>
       <c r="AK10" t="n">
-        <v>49.00426572308648</v>
+        <v>39.36429122491349</v>
       </c>
       <c r="AL10" t="n">
-        <v>48.60333310097825</v>
+        <v>38.79289897662358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18.47838</v>
+        <v>5.120635</v>
       </c>
       <c r="C11" t="n">
-        <v>30.34358452631288</v>
+        <v>5.184893020146289</v>
       </c>
       <c r="D11" t="n">
-        <v>32.04622690339809</v>
+        <v>5.167931614661287</v>
       </c>
       <c r="E11" t="n">
-        <v>33.79929860742717</v>
+        <v>5.233322807625944</v>
       </c>
       <c r="F11" t="n">
-        <v>35.5893516805206</v>
+        <v>5.403057999023743</v>
       </c>
       <c r="G11" t="n">
-        <v>37.47224545662907</v>
+        <v>5.717285982511148</v>
       </c>
       <c r="H11" t="n">
-        <v>39.38138502684003</v>
+        <v>6.25935597480546</v>
       </c>
       <c r="I11" t="n">
-        <v>41.29573687911231</v>
+        <v>7.232576305401626</v>
       </c>
       <c r="J11" t="n">
-        <v>43.09933421160717</v>
+        <v>9.217558787020966</v>
       </c>
       <c r="K11" t="n">
-        <v>44.70725170199128</v>
+        <v>14.43214639117764</v>
       </c>
       <c r="L11" t="n">
-        <v>46.12392027064128</v>
+        <v>20.1251878865922</v>
       </c>
       <c r="M11" t="n">
-        <v>47.36102223691622</v>
+        <v>24.63730868219257</v>
       </c>
       <c r="N11" t="n">
-        <v>48.41170103060246</v>
+        <v>28.4875751512727</v>
       </c>
       <c r="O11" t="n">
-        <v>49.36723650836419</v>
+        <v>32.55345312562871</v>
       </c>
       <c r="P11" t="n">
-        <v>50.25668852532555</v>
+        <v>37.9837570743931</v>
       </c>
       <c r="Q11" t="n">
-        <v>51.09619397818028</v>
+        <v>44.49704870590677</v>
       </c>
       <c r="R11" t="n">
-        <v>51.92718188635356</v>
+        <v>47.9040918564676</v>
       </c>
       <c r="S11" t="n">
-        <v>52.71202844753101</v>
+        <v>49.11973925220926</v>
       </c>
       <c r="T11" t="n">
-        <v>53.47013369550854</v>
+        <v>49.7101513464662</v>
       </c>
       <c r="U11" t="n">
-        <v>54.1986703494188</v>
+        <v>49.85959814054113</v>
       </c>
       <c r="V11" t="n">
-        <v>54.87934718975951</v>
+        <v>49.60904923300191</v>
       </c>
       <c r="W11" t="n">
-        <v>55.46608988690353</v>
+        <v>49.05542877473051</v>
       </c>
       <c r="X11" t="n">
-        <v>55.76899541360326</v>
+        <v>48.35820531978283</v>
       </c>
       <c r="Y11" t="n">
-        <v>55.82022272656231</v>
+        <v>47.5656534960671</v>
       </c>
       <c r="Z11" t="n">
-        <v>55.78938684636199</v>
+        <v>46.70306351763428</v>
       </c>
       <c r="AA11" t="n">
-        <v>55.7222399693989</v>
+        <v>45.80367539515434</v>
       </c>
       <c r="AB11" t="n">
-        <v>55.60937375482213</v>
+        <v>44.90168935324535</v>
       </c>
       <c r="AC11" t="n">
-        <v>55.4019274314695</v>
+        <v>44.05192589807711</v>
       </c>
       <c r="AD11" t="n">
-        <v>55.13742003194418</v>
+        <v>43.33988097607647</v>
       </c>
       <c r="AE11" t="n">
-        <v>54.82172735318736</v>
+        <v>42.81707656715781</v>
       </c>
       <c r="AF11" t="n">
-        <v>54.45686498578919</v>
+        <v>42.70244119402566</v>
       </c>
       <c r="AG11" t="n">
-        <v>54.14406749637669</v>
+        <v>42.59173850794348</v>
       </c>
       <c r="AH11" t="n">
-        <v>53.92903072515974</v>
+        <v>42.48390753470559</v>
       </c>
       <c r="AI11" t="n">
-        <v>53.78471707708577</v>
+        <v>42.39320272189092</v>
       </c>
       <c r="AJ11" t="n">
-        <v>53.63774674993581</v>
+        <v>42.33148112859441</v>
       </c>
       <c r="AK11" t="n">
-        <v>53.48329775490136</v>
+        <v>42.30802972846276</v>
       </c>
       <c r="AL11" t="n">
-        <v>53.33202545464782</v>
+        <v>42.32570134619775</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0.63.1</t>
+          <t>0.75.1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>85.85890000000001</v>
+        <v>43.76087</v>
       </c>
       <c r="C12" t="n">
-        <v>26.84247</v>
+        <v>26.04787848961938</v>
       </c>
       <c r="D12" t="n">
-        <v>24.09718</v>
+        <v>26.99358886950431</v>
       </c>
       <c r="E12" t="n">
-        <v>23.81644</v>
+        <v>28.04451445087595</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>29.21617206741121</v>
       </c>
       <c r="G12" t="n">
-        <v>33.04324</v>
+        <v>30.49800855993066</v>
       </c>
       <c r="H12" t="n">
-        <v>27.55079999999996</v>
+        <v>31.86434393165161</v>
       </c>
       <c r="I12" t="n">
-        <v>30.80308725869812</v>
+        <v>33.28753839643392</v>
       </c>
       <c r="J12" t="n">
-        <v>33.10799437487991</v>
+        <v>34.72206438674223</v>
       </c>
       <c r="K12" t="n">
-        <v>35.15561929788993</v>
+        <v>36.83544549696323</v>
       </c>
       <c r="L12" t="n">
-        <v>37.13085344139615</v>
+        <v>39.03730417226933</v>
       </c>
       <c r="M12" t="n">
-        <v>39.16313524411574</v>
+        <v>41.38529834439864</v>
       </c>
       <c r="N12" t="n">
-        <v>41.52615644169531</v>
+        <v>43.83523559924078</v>
       </c>
       <c r="O12" t="n">
-        <v>44.00862259003463</v>
+        <v>46.03485513682858</v>
       </c>
       <c r="P12" t="n">
-        <v>46.39782807908372</v>
+        <v>47.8681130508944</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.67217885876158</v>
+        <v>49.3815632454317</v>
       </c>
       <c r="R12" t="n">
-        <v>50.47387704383708</v>
+        <v>50.60177037687082</v>
       </c>
       <c r="S12" t="n">
-        <v>51.614834640258</v>
+        <v>51.360388457326</v>
       </c>
       <c r="T12" t="n">
-        <v>52.35870591359058</v>
+        <v>51.45990780798074</v>
       </c>
       <c r="U12" t="n">
-        <v>52.82463006948884</v>
+        <v>51.12383075539452</v>
       </c>
       <c r="V12" t="n">
-        <v>53.13971365891743</v>
+        <v>50.72097538565567</v>
       </c>
       <c r="W12" t="n">
-        <v>53.3195982531762</v>
+        <v>50.37911700749085</v>
       </c>
       <c r="X12" t="n">
-        <v>53.30182020405879</v>
+        <v>50.10882593429849</v>
       </c>
       <c r="Y12" t="n">
-        <v>53.12490210676928</v>
+        <v>49.87326115229109</v>
       </c>
       <c r="Z12" t="n">
-        <v>52.91197483538581</v>
+        <v>49.64470805248325</v>
       </c>
       <c r="AA12" t="n">
-        <v>52.77638648528632</v>
+        <v>49.44347588444416</v>
       </c>
       <c r="AB12" t="n">
-        <v>52.71700514286675</v>
+        <v>49.26482797403543</v>
       </c>
       <c r="AC12" t="n">
-        <v>52.66945192195971</v>
+        <v>49.07326683094413</v>
       </c>
       <c r="AD12" t="n">
-        <v>52.50950604899551</v>
+        <v>48.86004598849495</v>
       </c>
       <c r="AE12" t="n">
-        <v>52.18668701115743</v>
+        <v>48.65243048058624</v>
       </c>
       <c r="AF12" t="n">
-        <v>51.65364763550923</v>
+        <v>48.52405002091347</v>
       </c>
       <c r="AG12" t="n">
-        <v>51.00493918163537</v>
+        <v>48.41911507669493</v>
       </c>
       <c r="AH12" t="n">
-        <v>50.38959384997223</v>
+        <v>48.3232671238735</v>
       </c>
       <c r="AI12" t="n">
-        <v>49.85227126782386</v>
+        <v>48.23197828805164</v>
       </c>
       <c r="AJ12" t="n">
-        <v>49.32398824759467</v>
+        <v>48.14481655419755</v>
       </c>
       <c r="AK12" t="n">
-        <v>48.79618810950571</v>
+        <v>48.06438859260853</v>
       </c>
       <c r="AL12" t="n">
-        <v>48.28123269969445</v>
+        <v>47.99465847361407</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0.63.2</t>
+          <t>0.75.3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12.58919</v>
+        <v>32.70405</v>
       </c>
       <c r="C13" t="n">
-        <v>11.92051647451967</v>
+        <v>22.78782840107007</v>
       </c>
       <c r="D13" t="n">
-        <v>12.29678912387745</v>
+        <v>24.76619660838036</v>
       </c>
       <c r="E13" t="n">
-        <v>12.68192478506891</v>
+        <v>26.7442480043972</v>
       </c>
       <c r="F13" t="n">
-        <v>13.06290824530473</v>
+        <v>28.72081565832552</v>
       </c>
       <c r="G13" t="n">
-        <v>13.70370491534146</v>
+        <v>30.69370455849132</v>
       </c>
       <c r="H13" t="n">
-        <v>14.51965179777704</v>
+        <v>32.65946685300336</v>
       </c>
       <c r="I13" t="n">
-        <v>15.37537516319338</v>
+        <v>34.61319873164013</v>
       </c>
       <c r="J13" t="n">
-        <v>16.32225373072017</v>
+        <v>36.55043492169501</v>
       </c>
       <c r="K13" t="n">
-        <v>17.336310767221</v>
+        <v>38.21114708285955</v>
       </c>
       <c r="L13" t="n">
-        <v>18.30035966801987</v>
+        <v>39.88883322970322</v>
       </c>
       <c r="M13" t="n">
-        <v>19.20151232128301</v>
+        <v>41.3928808900239</v>
       </c>
       <c r="N13" t="n">
-        <v>20.07301402771799</v>
+        <v>42.72872762564756</v>
       </c>
       <c r="O13" t="n">
-        <v>20.87827348710391</v>
+        <v>44.07804069282426</v>
       </c>
       <c r="P13" t="n">
-        <v>21.69780529089629</v>
+        <v>45.57815848267152</v>
       </c>
       <c r="Q13" t="n">
-        <v>22.4733830903781</v>
+        <v>46.91197841928541</v>
       </c>
       <c r="R13" t="n">
-        <v>23.17180724655234</v>
+        <v>47.12659206491915</v>
       </c>
       <c r="S13" t="n">
-        <v>23.88560984710832</v>
+        <v>46.96585449240145</v>
       </c>
       <c r="T13" t="n">
-        <v>24.600712279379</v>
+        <v>46.78015336918865</v>
       </c>
       <c r="U13" t="n">
-        <v>25.27188845523522</v>
+        <v>46.55509899329936</v>
       </c>
       <c r="V13" t="n">
-        <v>25.95701434063582</v>
+        <v>46.29248641459997</v>
       </c>
       <c r="W13" t="n">
-        <v>26.51490635072903</v>
+        <v>46.00634515444708</v>
       </c>
       <c r="X13" t="n">
-        <v>26.72991099916484</v>
+        <v>45.70770251265486</v>
       </c>
       <c r="Y13" t="n">
-        <v>26.79131672515973</v>
+        <v>45.40032496436849</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.90988929554425</v>
+        <v>45.07951111383041</v>
       </c>
       <c r="AA13" t="n">
-        <v>26.97818161918257</v>
+        <v>44.75603358020075</v>
       </c>
       <c r="AB13" t="n">
-        <v>26.8717559403615</v>
+        <v>44.45233011786974</v>
       </c>
       <c r="AC13" t="n">
-        <v>26.83244936821906</v>
+        <v>44.18329743731998</v>
       </c>
       <c r="AD13" t="n">
-        <v>26.74370403891625</v>
+        <v>43.98204328846818</v>
       </c>
       <c r="AE13" t="n">
-        <v>26.30614992298713</v>
+        <v>43.86652046398672</v>
       </c>
       <c r="AF13" t="n">
-        <v>25.61598246977833</v>
+        <v>43.89585557496724</v>
       </c>
       <c r="AG13" t="n">
-        <v>24.87939238699241</v>
+        <v>43.92747043978092</v>
       </c>
       <c r="AH13" t="n">
-        <v>24.184353772915</v>
+        <v>43.96474362516069</v>
       </c>
       <c r="AI13" t="n">
-        <v>23.45941448299109</v>
+        <v>44.01072670748176</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22.84469800193224</v>
+        <v>44.06545541967496</v>
       </c>
       <c r="AK13" t="n">
-        <v>22.26762869721194</v>
+        <v>44.1299589809592</v>
       </c>
       <c r="AL13" t="n">
-        <v>21.73267319642378</v>
+        <v>44.20437250998094</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.779452</v>
+        <v>5.554054</v>
       </c>
       <c r="C14" t="n">
-        <v>5.057661866624136</v>
+        <v>3.970234269695089</v>
       </c>
       <c r="D14" t="n">
-        <v>5.121809793189969</v>
+        <v>3.913414901392776</v>
       </c>
       <c r="E14" t="n">
-        <v>5.214019527846982</v>
+        <v>3.879814929426592</v>
       </c>
       <c r="F14" t="n">
-        <v>5.330937105728553</v>
+        <v>3.870184190634042</v>
       </c>
       <c r="G14" t="n">
-        <v>5.527088845751994</v>
+        <v>3.887131850699631</v>
       </c>
       <c r="H14" t="n">
-        <v>5.755368650459533</v>
+        <v>3.936790496706615</v>
       </c>
       <c r="I14" t="n">
-        <v>6.037393182068282</v>
+        <v>4.029531830515119</v>
       </c>
       <c r="J14" t="n">
-        <v>6.36032824466582</v>
+        <v>4.193886128498258</v>
       </c>
       <c r="K14" t="n">
-        <v>6.69442450334669</v>
+        <v>5.167552209102475</v>
       </c>
       <c r="L14" t="n">
-        <v>7.08582194368941</v>
+        <v>6.546393043144861</v>
       </c>
       <c r="M14" t="n">
-        <v>7.186536063643275</v>
+        <v>8.258712018792588</v>
       </c>
       <c r="N14" t="n">
-        <v>7.202582512886952</v>
+        <v>10.24258496306072</v>
       </c>
       <c r="O14" t="n">
-        <v>7.263041178660671</v>
+        <v>12.51785865698777</v>
       </c>
       <c r="P14" t="n">
-        <v>7.243041675401221</v>
+        <v>15.15382666872597</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.073932124997054</v>
+        <v>17.38117587040242</v>
       </c>
       <c r="R14" t="n">
-        <v>6.902883494643898</v>
+        <v>18.91967494343168</v>
       </c>
       <c r="S14" t="n">
-        <v>6.727473573516738</v>
+        <v>20.50448890268419</v>
       </c>
       <c r="T14" t="n">
-        <v>6.599457748759466</v>
+        <v>22.06801109480529</v>
       </c>
       <c r="U14" t="n">
-        <v>6.516688853935064</v>
+        <v>23.46258761208776</v>
       </c>
       <c r="V14" t="n">
-        <v>6.45055285887583</v>
+        <v>24.86951812421212</v>
       </c>
       <c r="W14" t="n">
-        <v>6.466049964408352</v>
+        <v>26.50895540486844</v>
       </c>
       <c r="X14" t="n">
-        <v>6.531217208982953</v>
+        <v>27.30846259288729</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.569253596509937</v>
+        <v>26.58423672196864</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.58832509677076</v>
+        <v>25.54043192990853</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.60378886002574</v>
+        <v>24.5063110530079</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.63476515177182</v>
+        <v>23.47843544418684</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.699572703675839</v>
+        <v>22.44603994887835</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.804929205051729</v>
+        <v>21.42577792784748</v>
       </c>
       <c r="AE14" t="n">
-        <v>6.909613239937703</v>
+        <v>20.45264710756068</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.995776420151291</v>
+        <v>19.58063436173431</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.055101418143042</v>
+        <v>18.74443954449937</v>
       </c>
       <c r="AH14" t="n">
-        <v>7.071426392221837</v>
+        <v>17.91054257941729</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.040508866153684</v>
+        <v>17.07341987710683</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.985537340487133</v>
+        <v>16.23600348430221</v>
       </c>
       <c r="AK14" t="n">
-        <v>6.934225911418518</v>
+        <v>15.40544952058173</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.882508919683886</v>
+        <v>14.58948956723246</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.31.1</t>
+          <t>0.38.2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.99867</v>
+        <v>7.164865</v>
       </c>
       <c r="C15" t="n">
-        <v>17.09631431800273</v>
+        <v>0.7383628018745154</v>
       </c>
       <c r="D15" t="n">
-        <v>16.19795974805713</v>
+        <v>1.004139979982479</v>
       </c>
       <c r="E15" t="n">
-        <v>15.34650307811787</v>
+        <v>1.287787901209829</v>
       </c>
       <c r="F15" t="n">
-        <v>14.4943951032326</v>
+        <v>1.590784483353774</v>
       </c>
       <c r="G15" t="n">
-        <v>14.0303855343364</v>
+        <v>1.914442181655084</v>
       </c>
       <c r="H15" t="n">
-        <v>13.74355107655602</v>
+        <v>2.260357241459245</v>
       </c>
       <c r="I15" t="n">
-        <v>13.34300954513397</v>
+        <v>2.631348730199145</v>
       </c>
       <c r="J15" t="n">
-        <v>12.97879374851856</v>
+        <v>3.038392323992182</v>
       </c>
       <c r="K15" t="n">
-        <v>12.9032021977626</v>
+        <v>3.877186184943046</v>
       </c>
       <c r="L15" t="n">
-        <v>13.05385572365599</v>
+        <v>4.938469668644903</v>
       </c>
       <c r="M15" t="n">
-        <v>13.44539144057243</v>
+        <v>6.199778815551579</v>
       </c>
       <c r="N15" t="n">
-        <v>14.31551916081747</v>
+        <v>7.696439820870166</v>
       </c>
       <c r="O15" t="n">
-        <v>16.40475782117539</v>
+        <v>9.481020224084162</v>
       </c>
       <c r="P15" t="n">
-        <v>19.40378233747324</v>
+        <v>11.3703474061295</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.7654196263318</v>
+        <v>13.01961880926614</v>
       </c>
       <c r="R15" t="n">
-        <v>26.65778728264023</v>
+        <v>14.44737009683168</v>
       </c>
       <c r="S15" t="n">
-        <v>30.84147079413325</v>
+        <v>15.74376916233286</v>
       </c>
       <c r="T15" t="n">
-        <v>34.3141254696159</v>
+        <v>16.89287587079932</v>
       </c>
       <c r="U15" t="n">
-        <v>37.20793675191531</v>
+        <v>17.89688651089838</v>
       </c>
       <c r="V15" t="n">
-        <v>39.24564137024339</v>
+        <v>18.81995298483163</v>
       </c>
       <c r="W15" t="n">
-        <v>39.54321352574173</v>
+        <v>19.49185735585768</v>
       </c>
       <c r="X15" t="n">
-        <v>38.83025551280386</v>
+        <v>19.33417573695892</v>
       </c>
       <c r="Y15" t="n">
-        <v>37.8230205075698</v>
+        <v>18.41232018778138</v>
       </c>
       <c r="Z15" t="n">
-        <v>36.60631712793846</v>
+        <v>17.30659909779346</v>
       </c>
       <c r="AA15" t="n">
-        <v>35.48643096769287</v>
+        <v>16.20573645682061</v>
       </c>
       <c r="AB15" t="n">
-        <v>34.78005881401906</v>
+        <v>15.13951961980687</v>
       </c>
       <c r="AC15" t="n">
-        <v>34.33922623226103</v>
+        <v>14.12212973299624</v>
       </c>
       <c r="AD15" t="n">
-        <v>33.94402193870418</v>
+        <v>13.1977508717569</v>
       </c>
       <c r="AE15" t="n">
-        <v>33.50233810844743</v>
+        <v>12.38125137991545</v>
       </c>
       <c r="AF15" t="n">
-        <v>32.77400581342334</v>
+        <v>11.69572921659731</v>
       </c>
       <c r="AG15" t="n">
-        <v>31.74106040171941</v>
+        <v>11.00511316263293</v>
       </c>
       <c r="AH15" t="n">
-        <v>30.46823691181445</v>
+        <v>10.3186945328986</v>
       </c>
       <c r="AI15" t="n">
-        <v>29.19929935169789</v>
+        <v>9.642657443250251</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28.06256435172136</v>
+        <v>8.979737978571462</v>
       </c>
       <c r="AK15" t="n">
-        <v>26.9477471800908</v>
+        <v>8.330788541132993</v>
       </c>
       <c r="AL15" t="n">
-        <v>25.86805712683629</v>
+        <v>7.694628145296324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.31.2</t>
+          <t>0.38.3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.264384</v>
+        <v>31.15211</v>
       </c>
       <c r="C16" t="n">
-        <v>7.901929812891243</v>
+        <v>12.43982229492576</v>
       </c>
       <c r="D16" t="n">
-        <v>7.706821741508063</v>
+        <v>13.97903962170888</v>
       </c>
       <c r="E16" t="n">
-        <v>7.521224335052045</v>
+        <v>15.52231748858738</v>
       </c>
       <c r="F16" t="n">
-        <v>7.337373704217204</v>
+        <v>17.06223726620678</v>
       </c>
       <c r="G16" t="n">
-        <v>7.162733989074759</v>
+        <v>18.59514233754301</v>
       </c>
       <c r="H16" t="n">
-        <v>7.006259880230358</v>
+        <v>20.11994731776964</v>
       </c>
       <c r="I16" t="n">
-        <v>6.849315646775515</v>
+        <v>21.63776101100851</v>
       </c>
       <c r="J16" t="n">
-        <v>6.702696398747606</v>
+        <v>23.15721322840479</v>
       </c>
       <c r="K16" t="n">
-        <v>6.672201972998337</v>
+        <v>24.4633827269874</v>
       </c>
       <c r="L16" t="n">
-        <v>6.903052534753429</v>
+        <v>25.99375501270293</v>
       </c>
       <c r="M16" t="n">
-        <v>7.406427830220929</v>
+        <v>27.16856585421496</v>
       </c>
       <c r="N16" t="n">
-        <v>8.220979294959156</v>
+        <v>28.00308216003014</v>
       </c>
       <c r="O16" t="n">
-        <v>10.05873620319692</v>
+        <v>28.74715647687576</v>
       </c>
       <c r="P16" t="n">
-        <v>12.67880254065195</v>
+        <v>29.46671501862959</v>
       </c>
       <c r="Q16" t="n">
-        <v>15.37724109679853</v>
+        <v>30.18791160423817</v>
       </c>
       <c r="R16" t="n">
-        <v>18.21152382557258</v>
+        <v>30.63844161905373</v>
       </c>
       <c r="S16" t="n">
-        <v>20.78955379820954</v>
+        <v>30.50370512311081</v>
       </c>
       <c r="T16" t="n">
-        <v>21.29047012834109</v>
+        <v>30.17417671273778</v>
       </c>
       <c r="U16" t="n">
-        <v>20.76998128488289</v>
+        <v>29.8211289842733</v>
       </c>
       <c r="V16" t="n">
-        <v>20.56395957995577</v>
+        <v>29.49197698709851</v>
       </c>
       <c r="W16" t="n">
-        <v>19.34835005109713</v>
+        <v>29.22040149998607</v>
       </c>
       <c r="X16" t="n">
-        <v>16.97861529101705</v>
+        <v>29.00018916211656</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.99056972465438</v>
+        <v>28.81200228495918</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.41649587475764</v>
+        <v>28.64384497997732</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.10275844213111</v>
+        <v>28.49283030191714</v>
       </c>
       <c r="AB16" t="n">
-        <v>11.28560453918093</v>
+        <v>28.38781517857544</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.89005138089009</v>
+        <v>28.36278207318695</v>
       </c>
       <c r="AD16" t="n">
-        <v>10.54699184447083</v>
+        <v>28.43062557398389</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.19640168431999</v>
+        <v>28.56651081419083</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.891242173898316</v>
+        <v>28.76684279141253</v>
       </c>
       <c r="AG16" t="n">
-        <v>9.462764726399325</v>
+        <v>28.96954770331371</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.91962580463079</v>
+        <v>29.17269145629887</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.343580058565623</v>
+        <v>29.37923563137265</v>
       </c>
       <c r="AJ16" t="n">
-        <v>7.750207376700749</v>
+        <v>29.59191310773671</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.155870603707427</v>
+        <v>29.81231846728144</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.563967238210183</v>
+        <v>30.04085579975755</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0.31.3</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.15915</v>
+        <v>12.25</v>
       </c>
       <c r="C17" t="n">
-        <v>8.91430076365269</v>
+        <v>17.26668963423637</v>
       </c>
       <c r="D17" t="n">
-        <v>10.78581843416161</v>
+        <v>18.29842894020815</v>
       </c>
       <c r="E17" t="n">
-        <v>12.63943641930759</v>
+        <v>19.33553649373899</v>
       </c>
       <c r="F17" t="n">
-        <v>14.4771103303632</v>
+        <v>20.37629513813237</v>
       </c>
       <c r="G17" t="n">
-        <v>16.3406879119292</v>
+        <v>21.41840701104019</v>
       </c>
       <c r="H17" t="n">
-        <v>18.18259653460636</v>
+        <v>22.46005519995176</v>
       </c>
       <c r="I17" t="n">
-        <v>19.8689388548908</v>
+        <v>23.49964089807863</v>
       </c>
       <c r="J17" t="n">
-        <v>21.44054541816635</v>
+        <v>24.54016777829444</v>
       </c>
       <c r="K17" t="n">
-        <v>22.90251543803382</v>
+        <v>25.59796771277609</v>
       </c>
       <c r="L17" t="n">
-        <v>24.20235126719248</v>
+        <v>26.65926360727123</v>
       </c>
       <c r="M17" t="n">
-        <v>25.34646390402547</v>
+        <v>27.69736429028521</v>
       </c>
       <c r="N17" t="n">
-        <v>26.486433287537</v>
+        <v>28.68057654051392</v>
       </c>
       <c r="O17" t="n">
-        <v>27.62023916898273</v>
+        <v>29.57676161783853</v>
       </c>
       <c r="P17" t="n">
-        <v>28.66191625366476</v>
+        <v>30.37701434993448</v>
       </c>
       <c r="Q17" t="n">
-        <v>29.61500066799116</v>
+        <v>31.08749900985712</v>
       </c>
       <c r="R17" t="n">
-        <v>30.48070240089401</v>
+        <v>31.71146777794869</v>
       </c>
       <c r="S17" t="n">
-        <v>31.2093381452488</v>
+        <v>32.24217409895524</v>
       </c>
       <c r="T17" t="n">
-        <v>31.83025965869446</v>
+        <v>32.67438291445415</v>
       </c>
       <c r="U17" t="n">
-        <v>32.37788010147603</v>
+        <v>33.0087181805776</v>
       </c>
       <c r="V17" t="n">
-        <v>32.80217780942449</v>
+        <v>33.24270386629833</v>
       </c>
       <c r="W17" t="n">
-        <v>33.12830326514946</v>
+        <v>33.38485642559138</v>
       </c>
       <c r="X17" t="n">
-        <v>33.33417568346476</v>
+        <v>33.46231096938727</v>
       </c>
       <c r="Y17" t="n">
-        <v>33.39624863177042</v>
+        <v>33.4942574057423</v>
       </c>
       <c r="Z17" t="n">
-        <v>33.32290111565785</v>
+        <v>33.47703273849884</v>
       </c>
       <c r="AA17" t="n">
-        <v>33.07346656666412</v>
+        <v>33.41405151858697</v>
       </c>
       <c r="AB17" t="n">
-        <v>32.60343428529398</v>
+        <v>33.3157855906202</v>
       </c>
       <c r="AC17" t="n">
-        <v>31.85278719600245</v>
+        <v>33.17976475526559</v>
       </c>
       <c r="AD17" t="n">
-        <v>30.79905819405124</v>
+        <v>33.01426195118492</v>
       </c>
       <c r="AE17" t="n">
-        <v>29.53315297078503</v>
+        <v>32.82986860405993</v>
       </c>
       <c r="AF17" t="n">
-        <v>28.30227182616341</v>
+        <v>32.57854621894961</v>
       </c>
       <c r="AG17" t="n">
-        <v>27.21449312495052</v>
+        <v>32.32537153217987</v>
       </c>
       <c r="AH17" t="n">
-        <v>26.25093305446989</v>
+        <v>32.06792546245821</v>
       </c>
       <c r="AI17" t="n">
-        <v>25.50207936640286</v>
+        <v>31.80500833601794</v>
       </c>
       <c r="AJ17" t="n">
-        <v>25.14998215123037</v>
+        <v>31.53600784045796</v>
       </c>
       <c r="AK17" t="n">
-        <v>24.86788308661679</v>
+        <v>31.26199015339047</v>
       </c>
       <c r="AL17" t="n">
-        <v>24.62698278247985</v>
+        <v>30.98476168790144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.613699</v>
+        <v>9.218919</v>
       </c>
       <c r="C18" t="n">
-        <v>4.204054</v>
+        <v>5.124967995559309</v>
       </c>
       <c r="D18" t="n">
-        <v>3.832432</v>
+        <v>6.050786169806373</v>
       </c>
       <c r="E18" t="n">
-        <v>59.15753</v>
+        <v>6.989018090788802</v>
       </c>
       <c r="F18" t="n">
-        <v>4.747887</v>
+        <v>7.944765174150591</v>
       </c>
       <c r="G18" t="n">
-        <v>5.010958000000016</v>
+        <v>8.912093300229339</v>
       </c>
       <c r="H18" t="n">
-        <v>6.700693908874788</v>
+        <v>9.882663361029923</v>
       </c>
       <c r="I18" t="n">
-        <v>8.162968020814159</v>
+        <v>10.84927359807047</v>
       </c>
       <c r="J18" t="n">
-        <v>9.687128579626323</v>
+        <v>11.80859710453251</v>
       </c>
       <c r="K18" t="n">
-        <v>11.20594846748108</v>
+        <v>13.03502545123697</v>
       </c>
       <c r="L18" t="n">
-        <v>12.4961640159673</v>
+        <v>14.50581033913512</v>
       </c>
       <c r="M18" t="n">
-        <v>13.70829512309353</v>
+        <v>16.19821877754703</v>
       </c>
       <c r="N18" t="n">
-        <v>14.84726506595872</v>
+        <v>18.06917416073146</v>
       </c>
       <c r="O18" t="n">
-        <v>15.43673460328499</v>
+        <v>20.0038055852124</v>
       </c>
       <c r="P18" t="n">
-        <v>15.43336702915104</v>
+        <v>20.97828860061442</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.28908493688583</v>
+        <v>20.61912158801414</v>
       </c>
       <c r="R18" t="n">
-        <v>15.03910195935212</v>
+        <v>20.42192404640803</v>
       </c>
       <c r="S18" t="n">
-        <v>14.52217337359903</v>
+        <v>20.90509828012074</v>
       </c>
       <c r="T18" t="n">
-        <v>13.71343998049359</v>
+        <v>21.7029535903798</v>
       </c>
       <c r="U18" t="n">
-        <v>13.0835475945589</v>
+        <v>22.45303230568089</v>
       </c>
       <c r="V18" t="n">
-        <v>12.60157051396699</v>
+        <v>22.71913794404298</v>
       </c>
       <c r="W18" t="n">
-        <v>12.13898709471622</v>
+        <v>22.31763567731337</v>
       </c>
       <c r="X18" t="n">
-        <v>11.74947363986338</v>
+        <v>22.0956738497656</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.51678823299679</v>
+        <v>22.26886792875764</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.41914451946001</v>
+        <v>21.93964382472404</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.29373076136357</v>
+        <v>21.20793134265844</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.20213472203788</v>
+        <v>20.307842827665</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.09724662666691</v>
+        <v>19.35037156012171</v>
       </c>
       <c r="AD18" t="n">
-        <v>10.96055304375362</v>
+        <v>18.38284438108582</v>
       </c>
       <c r="AE18" t="n">
-        <v>10.83091695129795</v>
+        <v>17.46393380625316</v>
       </c>
       <c r="AF18" t="n">
-        <v>10.67822776872052</v>
+        <v>17.10069426006302</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.48770984452405</v>
+        <v>16.72785561199995</v>
       </c>
       <c r="AH18" t="n">
-        <v>10.3109975095338</v>
+        <v>16.37685938463441</v>
       </c>
       <c r="AI18" t="n">
-        <v>10.12425137361557</v>
+        <v>16.08140159970897</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9.92812915452949</v>
+        <v>15.86171668729515</v>
       </c>
       <c r="AK18" t="n">
-        <v>9.739541827861212</v>
+        <v>15.72940595783296</v>
       </c>
       <c r="AL18" t="n">
-        <v>9.545817984120276</v>
+        <v>15.68154327080633</v>
       </c>
     </row>
   </sheetData>
@@ -2678,2479 +2678,2479 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.4902297587207</v>
+        <v>14.37741057344263</v>
       </c>
       <c r="C2" t="n">
-        <v>23.16090011301683</v>
+        <v>21.7474471809553</v>
       </c>
       <c r="D2" t="n">
-        <v>23.6866114356036</v>
+        <v>21.76408958270174</v>
       </c>
       <c r="E2" t="n">
-        <v>23.91067880643185</v>
+        <v>21.78613931096429</v>
       </c>
       <c r="F2" t="n">
-        <v>23.77900998786014</v>
+        <v>21.8133182450156</v>
       </c>
       <c r="G2" t="n">
-        <v>22.11747794183483</v>
+        <v>21.84282225954429</v>
       </c>
       <c r="H2" t="n">
-        <v>19.96399256539917</v>
+        <v>21.86598175134331</v>
       </c>
       <c r="I2" t="n">
-        <v>18.93750381120275</v>
+        <v>21.87968793811289</v>
       </c>
       <c r="J2" t="n">
-        <v>18.29102311562101</v>
+        <v>21.89292457416693</v>
       </c>
       <c r="K2" t="n">
-        <v>18.28776577606485</v>
+        <v>21.93353740678399</v>
       </c>
       <c r="L2" t="n">
-        <v>19.79214275784842</v>
+        <v>22.01262469262853</v>
       </c>
       <c r="M2" t="n">
-        <v>22.0047567570381</v>
+        <v>22.09414393477639</v>
       </c>
       <c r="N2" t="n">
-        <v>23.4244319547438</v>
+        <v>22.0907491052804</v>
       </c>
       <c r="O2" t="n">
-        <v>24.05865050527091</v>
+        <v>21.94401263540777</v>
       </c>
       <c r="P2" t="n">
-        <v>23.92839101808126</v>
+        <v>21.63256656288042</v>
       </c>
       <c r="Q2" t="n">
-        <v>23.53818873339668</v>
+        <v>21.15464977419397</v>
       </c>
       <c r="R2" t="n">
-        <v>23.07660550052616</v>
+        <v>20.51457308696539</v>
       </c>
       <c r="S2" t="n">
-        <v>22.2331115902837</v>
+        <v>19.74837183849549</v>
       </c>
       <c r="T2" t="n">
-        <v>21.09806955853108</v>
+        <v>18.90540953192469</v>
       </c>
       <c r="U2" t="n">
-        <v>20.28596083690094</v>
+        <v>17.998813188849</v>
       </c>
       <c r="V2" t="n">
-        <v>19.63040725950524</v>
+        <v>17.08786566560391</v>
       </c>
       <c r="W2" t="n">
-        <v>18.76343058316296</v>
+        <v>16.21244499832756</v>
       </c>
       <c r="X2" t="n">
-        <v>18.06438474456396</v>
+        <v>15.44043699806549</v>
       </c>
       <c r="Y2" t="n">
-        <v>17.59443590891851</v>
+        <v>14.82568395045654</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.09978894936381</v>
+        <v>14.38720093530845</v>
       </c>
       <c r="AA2" t="n">
-        <v>16.60122043878209</v>
+        <v>14.1271469588379</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.61947903209697</v>
+        <v>14.0259847501675</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.76446369468771</v>
+        <v>14.06658318303443</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.41587012440744</v>
+        <v>14.1791362670889</v>
       </c>
       <c r="AE2" t="n">
-        <v>15.69491103338801</v>
+        <v>14.28386014576889</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.72123002132633</v>
+        <v>14.23476835350475</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.876145702347</v>
+        <v>14.17023295655885</v>
       </c>
       <c r="AH2" t="n">
-        <v>13.38058483438562</v>
+        <v>14.09887214345896</v>
       </c>
       <c r="AI2" t="n">
-        <v>13.40845806396476</v>
+        <v>14.0187316940115</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14.05863448997451</v>
+        <v>13.9283690411809</v>
       </c>
       <c r="AK2" t="n">
-        <v>14.80916421082382</v>
+        <v>13.82521816676243</v>
       </c>
       <c r="AL2" t="n">
-        <v>15.62951014421758</v>
+        <v>13.70764372280019</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.068767954204811</v>
+        <v>0.03581679895107</v>
       </c>
       <c r="C3" t="n">
-        <v>18.97380481749778</v>
+        <v>-0.15984724084715</v>
       </c>
       <c r="D3" t="n">
-        <v>19.33555287075745</v>
+        <v>-0.04426607645369</v>
       </c>
       <c r="E3" t="n">
-        <v>19.59272566880929</v>
+        <v>0.07313698520551</v>
       </c>
       <c r="F3" t="n">
-        <v>19.72803294253843</v>
+        <v>0.19142055939148</v>
       </c>
       <c r="G3" t="n">
-        <v>19.50729684924211</v>
+        <v>0.30944030844812</v>
       </c>
       <c r="H3" t="n">
-        <v>18.87869624156646</v>
+        <v>0.4262227054936401</v>
       </c>
       <c r="I3" t="n">
-        <v>18.08618296682836</v>
+        <v>0.54186570711743</v>
       </c>
       <c r="J3" t="n">
-        <v>17.4135064206359</v>
+        <v>0.6610977110826399</v>
       </c>
       <c r="K3" t="n">
-        <v>16.77082630115447</v>
+        <v>0.73700069739049</v>
       </c>
       <c r="L3" t="n">
-        <v>16.14831141575282</v>
+        <v>0.8024998922780799</v>
       </c>
       <c r="M3" t="n">
-        <v>15.36738916914237</v>
+        <v>0.8957936011882199</v>
       </c>
       <c r="N3" t="n">
-        <v>14.75801681249927</v>
+        <v>1.0305461066501</v>
       </c>
       <c r="O3" t="n">
-        <v>14.28928463313186</v>
+        <v>1.17138541323494</v>
       </c>
       <c r="P3" t="n">
-        <v>13.99856415660566</v>
+        <v>1.27213098846647</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.99460869814333</v>
+        <v>1.32572899582335</v>
       </c>
       <c r="R3" t="n">
-        <v>14.26520331661364</v>
+        <v>1.37684327032488</v>
       </c>
       <c r="S3" t="n">
-        <v>14.57014145166597</v>
+        <v>1.47389906230446</v>
       </c>
       <c r="T3" t="n">
-        <v>14.72118481616657</v>
+        <v>1.64333859379014</v>
       </c>
       <c r="U3" t="n">
-        <v>14.70382731482105</v>
+        <v>1.85433254285214</v>
       </c>
       <c r="V3" t="n">
-        <v>14.49702512877554</v>
+        <v>2.06688367383659</v>
       </c>
       <c r="W3" t="n">
-        <v>13.99533307759128</v>
+        <v>2.22858934339364</v>
       </c>
       <c r="X3" t="n">
-        <v>13.39859687089113</v>
+        <v>2.31023234486593</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.93895334773194</v>
+        <v>2.35172236914829</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.68143715516201</v>
+        <v>2.36987555451669</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.39706738801064</v>
+        <v>2.35183279363562</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.17567416980497</v>
+        <v>2.26286367386211</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.1430537847538</v>
+        <v>2.07429170940501</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.32511436504549</v>
+        <v>1.79851261868582</v>
       </c>
       <c r="AE3" t="n">
-        <v>12.52779177003552</v>
+        <v>1.48103268920811</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.60168904950719</v>
+        <v>1.20116884126805</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.6647702950673</v>
+        <v>0.92515957201981</v>
       </c>
       <c r="AH3" t="n">
-        <v>12.68312862060554</v>
+        <v>0.64736402684787</v>
       </c>
       <c r="AI3" t="n">
-        <v>12.56966496919399</v>
+        <v>0.37057438666256</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.66203699967071</v>
+        <v>0.09826362248381</v>
       </c>
       <c r="AK3" t="n">
-        <v>12.80314876993243</v>
+        <v>-0.16657817152169</v>
       </c>
       <c r="AL3" t="n">
-        <v>12.96853320680652</v>
+        <v>-0.42201497910202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.61962805939926</v>
+        <v>16.34534073022172</v>
       </c>
       <c r="C4" t="n">
-        <v>16.89909098890012</v>
+        <v>13.40786444582871</v>
       </c>
       <c r="D4" t="n">
-        <v>18.05665444855847</v>
+        <v>14.35825557524247</v>
       </c>
       <c r="E4" t="n">
-        <v>19.15957599360548</v>
+        <v>15.29771771625615</v>
       </c>
       <c r="F4" t="n">
-        <v>20.23232167668926</v>
+        <v>16.22761274503157</v>
       </c>
       <c r="G4" t="n">
-        <v>20.81999520303365</v>
+        <v>17.14997135293033</v>
       </c>
       <c r="H4" t="n">
-        <v>21.15457700887396</v>
+        <v>18.0675532295756</v>
       </c>
       <c r="I4" t="n">
-        <v>21.34022658756781</v>
+        <v>18.98103336788544</v>
       </c>
       <c r="J4" t="n">
-        <v>21.4183820610415</v>
+        <v>19.8771248649682</v>
       </c>
       <c r="K4" t="n">
-        <v>21.74146061657144</v>
+        <v>20.46079022533457</v>
       </c>
       <c r="L4" t="n">
-        <v>22.18590718034869</v>
+        <v>20.59799437470664</v>
       </c>
       <c r="M4" t="n">
-        <v>22.65767306359188</v>
+        <v>20.52484976463862</v>
       </c>
       <c r="N4" t="n">
-        <v>23.4692505698566</v>
+        <v>20.44159419814127</v>
       </c>
       <c r="O4" t="n">
-        <v>24.23818533146226</v>
+        <v>20.2624238028459</v>
       </c>
       <c r="P4" t="n">
-        <v>24.56571925846894</v>
+        <v>19.98759530296046</v>
       </c>
       <c r="Q4" t="n">
-        <v>24.58916028560275</v>
+        <v>19.57387591543294</v>
       </c>
       <c r="R4" t="n">
-        <v>24.31548575589989</v>
+        <v>18.95664015128587</v>
       </c>
       <c r="S4" t="n">
-        <v>23.70302506988179</v>
+        <v>18.22818876636438</v>
       </c>
       <c r="T4" t="n">
-        <v>23.02694293286028</v>
+        <v>17.47649301315304</v>
       </c>
       <c r="U4" t="n">
-        <v>22.69472050753715</v>
+        <v>16.81097322119229</v>
       </c>
       <c r="V4" t="n">
-        <v>22.52139886955995</v>
+        <v>16.19747137121765</v>
       </c>
       <c r="W4" t="n">
-        <v>22.34714134410879</v>
+        <v>15.61913774040216</v>
       </c>
       <c r="X4" t="n">
-        <v>22.21893387772849</v>
+        <v>15.0935912342528</v>
       </c>
       <c r="Y4" t="n">
-        <v>22.17109414332941</v>
+        <v>14.62180436021654</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.07311547074389</v>
+        <v>14.19862458064144</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.58136403068506</v>
+        <v>13.85270712991771</v>
       </c>
       <c r="AB4" t="n">
-        <v>20.85320633357208</v>
+        <v>13.61336540554598</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.363733586034</v>
+        <v>13.46273601998969</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.75821186111335</v>
+        <v>13.36354381323436</v>
       </c>
       <c r="AE4" t="n">
-        <v>19.2411492740698</v>
+        <v>13.33719622963148</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.24643417514249</v>
+        <v>13.45461335434987</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.28093384527322</v>
+        <v>13.59409069527734</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.04597978630321</v>
+        <v>13.73664155931068</v>
       </c>
       <c r="AI4" t="n">
-        <v>18.77934364328623</v>
+        <v>13.87901262568878</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.30613798307169</v>
+        <v>14.02279060995212</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.82696217314252</v>
+        <v>14.17250079532628</v>
       </c>
       <c r="AL4" t="n">
-        <v>17.33642109898651</v>
+        <v>14.3329953879658</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.25424107387142</v>
+        <v>0.8515621032983</v>
       </c>
       <c r="C5" t="n">
-        <v>18.80935100099555</v>
+        <v>11.84931001520035</v>
       </c>
       <c r="D5" t="n">
-        <v>21.3005310441159</v>
+        <v>12.20920377829373</v>
       </c>
       <c r="E5" t="n">
-        <v>23.79171108723625</v>
+        <v>12.57057446964454</v>
       </c>
       <c r="F5" t="n">
-        <v>26.2828911303566</v>
+        <v>12.94841175802449</v>
       </c>
       <c r="G5" t="n">
-        <v>18.48560020294989</v>
+        <v>13.34958209128886</v>
       </c>
       <c r="H5" t="n">
-        <v>15.94854100080016</v>
+        <v>13.76818937792581</v>
       </c>
       <c r="I5" t="n">
-        <v>10.83134393699178</v>
+        <v>14.18509072123755</v>
       </c>
       <c r="J5" t="n">
-        <v>10.26958627295098</v>
+        <v>14.50226000920175</v>
       </c>
       <c r="K5" t="n">
-        <v>10.11129516592296</v>
+        <v>14.73568097579991</v>
       </c>
       <c r="L5" t="n">
-        <v>9.72393102764693</v>
+        <v>15.03732725747204</v>
       </c>
       <c r="M5" t="n">
-        <v>8.9129360078422</v>
+        <v>15.43535162898641</v>
       </c>
       <c r="N5" t="n">
-        <v>8.159519910168921</v>
+        <v>15.84677873801777</v>
       </c>
       <c r="O5" t="n">
-        <v>7.30322658418449</v>
+        <v>16.2105478869391</v>
       </c>
       <c r="P5" t="n">
-        <v>6.38325708600887</v>
+        <v>16.54708327420341</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.94995415610119</v>
+        <v>16.86462506113895</v>
       </c>
       <c r="R5" t="n">
-        <v>5.78832592043167</v>
+        <v>17.15209031644942</v>
       </c>
       <c r="S5" t="n">
-        <v>5.74103311675476</v>
+        <v>17.37784317894474</v>
       </c>
       <c r="T5" t="n">
-        <v>5.798420852090199</v>
+        <v>17.53083903276096</v>
       </c>
       <c r="U5" t="n">
-        <v>5.95392807752917</v>
+        <v>17.63792295569587</v>
       </c>
       <c r="V5" t="n">
-        <v>6.28598760908609</v>
+        <v>17.71558130932709</v>
       </c>
       <c r="W5" t="n">
-        <v>6.726354342558551</v>
+        <v>17.74791374243773</v>
       </c>
       <c r="X5" t="n">
-        <v>7.101853326479091</v>
+        <v>17.7191716032345</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.42077671712673</v>
+        <v>17.63905058378615</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.54809632675002</v>
+        <v>17.52328670232829</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.385384893803939</v>
+        <v>17.3833975430549</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.071602289193151</v>
+        <v>17.23794242062066</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.798263909116669</v>
+        <v>17.10065442033395</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.60479725288948</v>
+        <v>16.98106596951487</v>
       </c>
       <c r="AE5" t="n">
-        <v>6.54950627386524</v>
+        <v>16.89869819945501</v>
       </c>
       <c r="AF5" t="n">
-        <v>6.54950627386524</v>
+        <v>16.92923367038617</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.54950627386524</v>
+        <v>16.997349911072</v>
       </c>
       <c r="AH5" t="n">
-        <v>6.54950627386524</v>
+        <v>17.07779339708997</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.54950627386524</v>
+        <v>17.16496840193913</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6.54950627386524</v>
+        <v>17.25604681911585</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.54950627386523</v>
+        <v>17.35323121444154</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.54950627386524</v>
+        <v>17.46147455585514</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.66914943959788</v>
+        <v>1.35755626297589</v>
       </c>
       <c r="C6" t="n">
-        <v>11.89593073708603</v>
+        <v>16.92014913416581</v>
       </c>
       <c r="D6" t="n">
-        <v>13.87219427007815</v>
+        <v>17.43145426423156</v>
       </c>
       <c r="E6" t="n">
-        <v>15.88888074721985</v>
+        <v>17.95069986444343</v>
       </c>
       <c r="F6" t="n">
-        <v>17.94050210486442</v>
+        <v>18.48003575449557</v>
       </c>
       <c r="G6" t="n">
-        <v>20.32236458807132</v>
+        <v>19.02125098396675</v>
       </c>
       <c r="H6" t="n">
-        <v>22.3004139023869</v>
+        <v>19.56875620646867</v>
       </c>
       <c r="I6" t="n">
-        <v>23.35001916503822</v>
+        <v>20.11522436558819</v>
       </c>
       <c r="J6" t="n">
-        <v>24.68180783065078</v>
+        <v>20.6521942320935</v>
       </c>
       <c r="K6" t="n">
-        <v>25.68793257061645</v>
+        <v>21.21874788581784</v>
       </c>
       <c r="L6" t="n">
-        <v>26.00120895339931</v>
+        <v>21.78105528955673</v>
       </c>
       <c r="M6" t="n">
-        <v>26.86982895574822</v>
+        <v>22.1562430599376</v>
       </c>
       <c r="N6" t="n">
-        <v>27.87768559411466</v>
+        <v>22.17863075614247</v>
       </c>
       <c r="O6" t="n">
-        <v>28.37705516022214</v>
+        <v>21.89892540863413</v>
       </c>
       <c r="P6" t="n">
-        <v>28.87175439162482</v>
+        <v>21.48763061891744</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.95811079718658</v>
+        <v>21.05635194367256</v>
       </c>
       <c r="R6" t="n">
-        <v>28.23094960278189</v>
+        <v>20.65326951944667</v>
       </c>
       <c r="S6" t="n">
-        <v>27.40251692764412</v>
+        <v>20.25964848022899</v>
       </c>
       <c r="T6" t="n">
-        <v>26.63900526826298</v>
+        <v>19.78838530179654</v>
       </c>
       <c r="U6" t="n">
-        <v>25.77044703623744</v>
+        <v>19.18935737040941</v>
       </c>
       <c r="V6" t="n">
-        <v>24.87849218694561</v>
+        <v>18.58747208000335</v>
       </c>
       <c r="W6" t="n">
-        <v>23.83930631661191</v>
+        <v>18.20818508436263</v>
       </c>
       <c r="X6" t="n">
-        <v>21.95737099253772</v>
+        <v>18.06588923828365</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.7325632693438</v>
+        <v>18.02594651367462</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.8857830697955</v>
+        <v>17.97364617080623</v>
       </c>
       <c r="AA6" t="n">
-        <v>14.51057389800727</v>
+        <v>17.88025287395741</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.30080187615435</v>
+        <v>17.78467073311642</v>
       </c>
       <c r="AC6" t="n">
-        <v>13.51665866037474</v>
+        <v>17.71669622732139</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.88205947446574</v>
+        <v>17.64938655181844</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.66829411232546</v>
+        <v>17.59348467246231</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.70951744193439</v>
+        <v>17.6414995264807</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.85644116447086</v>
+        <v>17.69264817978535</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.27603622802609</v>
+        <v>17.74831397810387</v>
       </c>
       <c r="AI6" t="n">
-        <v>16.68349394510347</v>
+        <v>17.80975237671818</v>
       </c>
       <c r="AJ6" t="n">
-        <v>16.96619269776509</v>
+        <v>17.87616335266047</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.24070452317485</v>
+        <v>17.94646075836115</v>
       </c>
       <c r="AL6" t="n">
-        <v>17.43338156330044</v>
+        <v>18.01903008581389</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.051339292432719</v>
+        <v>0.25584597328538</v>
       </c>
       <c r="C7" t="n">
-        <v>5.70540721342904</v>
+        <v>14.63805496115414</v>
       </c>
       <c r="D7" t="n">
-        <v>5.69861823142976</v>
+        <v>15.54525069760765</v>
       </c>
       <c r="E7" t="n">
-        <v>5.69202654214327</v>
+        <v>16.43254020196094</v>
       </c>
       <c r="F7" t="n">
-        <v>5.68431310359437</v>
+        <v>17.29768435764659</v>
       </c>
       <c r="G7" t="n">
-        <v>5.70167549525025</v>
+        <v>18.14188540510641</v>
       </c>
       <c r="H7" t="n">
-        <v>5.72400436473162</v>
+        <v>18.96552429650731</v>
       </c>
       <c r="I7" t="n">
-        <v>5.75215107484449</v>
+        <v>19.76409176254462</v>
       </c>
       <c r="J7" t="n">
-        <v>5.8497794468741</v>
+        <v>20.5247486746955</v>
       </c>
       <c r="K7" t="n">
-        <v>6.04575887669993</v>
+        <v>21.00367099557938</v>
       </c>
       <c r="L7" t="n">
-        <v>6.33748242255388</v>
+        <v>21.40039218283846</v>
       </c>
       <c r="M7" t="n">
-        <v>6.595376776151431</v>
+        <v>21.68923755550265</v>
       </c>
       <c r="N7" t="n">
-        <v>6.649236331901929</v>
+        <v>21.72109175906094</v>
       </c>
       <c r="O7" t="n">
-        <v>6.62793463714826</v>
+        <v>21.22354962119354</v>
       </c>
       <c r="P7" t="n">
-        <v>6.534125651832989</v>
+        <v>20.08758962826388</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.23527637075151</v>
+        <v>18.59341799747228</v>
       </c>
       <c r="R7" t="n">
-        <v>6.102396285562009</v>
+        <v>17.13761774225797</v>
       </c>
       <c r="S7" t="n">
-        <v>6.22323952685764</v>
+        <v>15.75251924603664</v>
       </c>
       <c r="T7" t="n">
-        <v>6.391161121981261</v>
+        <v>14.2940199920701</v>
       </c>
       <c r="U7" t="n">
-        <v>6.53133855720682</v>
+        <v>12.66121910800322</v>
       </c>
       <c r="V7" t="n">
-        <v>6.593962941205129</v>
+        <v>10.92493876677527</v>
       </c>
       <c r="W7" t="n">
-        <v>6.52360280454162</v>
+        <v>9.21457485387057</v>
       </c>
       <c r="X7" t="n">
-        <v>6.49167647695952</v>
+        <v>7.841954547266091</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.46963761525058</v>
+        <v>6.89511131569417</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.46525570411607</v>
+        <v>6.21136690386225</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.53978889396852</v>
+        <v>5.68319096107792</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.634153334139279</v>
+        <v>5.282488457268119</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.66750052409715</v>
+        <v>4.964796592593681</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.69308631308207</v>
+        <v>4.72189299120313</v>
       </c>
       <c r="AE7" t="n">
-        <v>6.74768665604377</v>
+        <v>4.56228374172929</v>
       </c>
       <c r="AF7" t="n">
-        <v>6.81122043285017</v>
+        <v>4.57275787776938</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.843719191436739</v>
+        <v>4.58490373261625</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.869093164594391</v>
+        <v>4.59954863715161</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.801972417286289</v>
+        <v>4.62033271582674</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6.58893729867213</v>
+        <v>4.64904170719842</v>
       </c>
       <c r="AK7" t="n">
-        <v>6.378220080125891</v>
+        <v>4.68632071596607</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.15566742503474</v>
+        <v>4.73245569461013</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>2.5.1</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06494125502871</v>
+        <v>0.10927060768256</v>
       </c>
       <c r="C8" t="n">
-        <v>4.57317148216148</v>
+        <v>2.57634221125989</v>
       </c>
       <c r="D8" t="n">
-        <v>4.81915362062287</v>
+        <v>3.05199613184565</v>
       </c>
       <c r="E8" t="n">
-        <v>5.05669739256793</v>
+        <v>3.52425164057815</v>
       </c>
       <c r="F8" t="n">
-        <v>5.30558514916366</v>
+        <v>3.99577706594399</v>
       </c>
       <c r="G8" t="n">
-        <v>5.57148548115306</v>
+        <v>4.46767228955007</v>
       </c>
       <c r="H8" t="n">
-        <v>5.81779655392367</v>
+        <v>4.93883413488955</v>
       </c>
       <c r="I8" t="n">
-        <v>6.08054453709783</v>
+        <v>5.40418745792123</v>
       </c>
       <c r="J8" t="n">
-        <v>6.316995029302459</v>
+        <v>5.8519766083003</v>
       </c>
       <c r="K8" t="n">
-        <v>6.577909361677841</v>
+        <v>6.28522691666346</v>
       </c>
       <c r="L8" t="n">
-        <v>6.849166035212161</v>
+        <v>6.729288337611659</v>
       </c>
       <c r="M8" t="n">
-        <v>7.1902254565387</v>
+        <v>7.190864082774031</v>
       </c>
       <c r="N8" t="n">
-        <v>7.746161469937279</v>
+        <v>7.67716394733553</v>
       </c>
       <c r="O8" t="n">
-        <v>8.319121955630211</v>
+        <v>8.1947660797822</v>
       </c>
       <c r="P8" t="n">
-        <v>8.69862533215286</v>
+        <v>8.72617566671458</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.8954615325303</v>
+        <v>9.230511092064059</v>
       </c>
       <c r="R8" t="n">
-        <v>8.84501241334098</v>
+        <v>9.679336540146091</v>
       </c>
       <c r="S8" t="n">
-        <v>8.693897836032221</v>
+        <v>10.06025664578818</v>
       </c>
       <c r="T8" t="n">
-        <v>8.505356162264089</v>
+        <v>10.38853293766878</v>
       </c>
       <c r="U8" t="n">
-        <v>8.298444531674241</v>
+        <v>10.69976642778947</v>
       </c>
       <c r="V8" t="n">
-        <v>8.160123290180419</v>
+        <v>11.00230556276952</v>
       </c>
       <c r="W8" t="n">
-        <v>8.07759703461984</v>
+        <v>11.2730866934928</v>
       </c>
       <c r="X8" t="n">
-        <v>8.039827177470411</v>
+        <v>11.4724024022169</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.081600432801359</v>
+        <v>11.58739205758019</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.824986325486361</v>
+        <v>11.67335759103995</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.430874595570989</v>
+        <v>11.78511535729566</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.164471651121509</v>
+        <v>11.93848703145402</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.72762528302539</v>
+        <v>12.13877744820046</v>
       </c>
       <c r="AD8" t="n">
-        <v>6.5142840629402</v>
+        <v>12.37388119574234</v>
       </c>
       <c r="AE8" t="n">
-        <v>6.61372259879575</v>
+        <v>12.61698476131278</v>
       </c>
       <c r="AF8" t="n">
-        <v>6.56716540656549</v>
+        <v>12.84066250056435</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.477552462232699</v>
+        <v>13.06102277023365</v>
       </c>
       <c r="AH8" t="n">
-        <v>6.39888929104613</v>
+        <v>13.28511037373635</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.23059535607316</v>
+        <v>13.51188634878473</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6.03615100244983</v>
+        <v>13.73974283901139</v>
       </c>
       <c r="AK8" t="n">
-        <v>5.86275782329929</v>
+        <v>13.96719116126517</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.69706966929833</v>
+        <v>14.19306627499202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2.5.2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.78095063418986</v>
+        <v>10.65185742791435</v>
       </c>
       <c r="C9" t="n">
-        <v>0.83887975211188</v>
+        <v>7.57399982247834</v>
       </c>
       <c r="D9" t="n">
-        <v>1.67245018026808</v>
+        <v>7.66881820112455</v>
       </c>
       <c r="E9" t="n">
-        <v>2.48003436058284</v>
+        <v>7.75871011513358</v>
       </c>
       <c r="F9" t="n">
-        <v>3.27784196457832</v>
+        <v>7.843579987898821</v>
       </c>
       <c r="G9" t="n">
-        <v>3.83147400427559</v>
+        <v>7.92249817621805</v>
       </c>
       <c r="H9" t="n">
-        <v>4.17949699304003</v>
+        <v>7.99475637869783</v>
       </c>
       <c r="I9" t="n">
-        <v>4.41674684226711</v>
+        <v>8.0601200829246</v>
       </c>
       <c r="J9" t="n">
-        <v>4.593479169504191</v>
+        <v>8.117451599081599</v>
       </c>
       <c r="K9" t="n">
-        <v>4.64617812962784</v>
+        <v>8.10422275394127</v>
       </c>
       <c r="L9" t="n">
-        <v>4.59546983856396</v>
+        <v>8.053142951516611</v>
       </c>
       <c r="M9" t="n">
-        <v>4.53219873389017</v>
+        <v>7.96949211516363</v>
       </c>
       <c r="N9" t="n">
-        <v>4.51323320375422</v>
+        <v>7.87117483088905</v>
       </c>
       <c r="O9" t="n">
-        <v>4.52756769292452</v>
+        <v>7.7955372289283</v>
       </c>
       <c r="P9" t="n">
-        <v>4.64545875294198</v>
+        <v>7.7555328653687</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.85792155116708</v>
+        <v>7.72919750683661</v>
       </c>
       <c r="R9" t="n">
-        <v>5.07579605633729</v>
+        <v>7.71534860435242</v>
       </c>
       <c r="S9" t="n">
-        <v>5.26666423936428</v>
+        <v>7.71755935584353</v>
       </c>
       <c r="T9" t="n">
-        <v>5.300096002300729</v>
+        <v>7.74174674583262</v>
       </c>
       <c r="U9" t="n">
-        <v>5.30217952170254</v>
+        <v>7.7922457848083</v>
       </c>
       <c r="V9" t="n">
-        <v>5.34486696204429</v>
+        <v>7.864195632581961</v>
       </c>
       <c r="W9" t="n">
-        <v>5.371199936396541</v>
+        <v>7.97008464722736</v>
       </c>
       <c r="X9" t="n">
-        <v>5.36058578607517</v>
+        <v>8.107355971857109</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.15515799039467</v>
+        <v>8.26508521187109</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.893710006077661</v>
+        <v>8.42824995016176</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.613313265827379</v>
+        <v>8.594282781636121</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.30121497890177</v>
+        <v>8.7648192592395</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.095241594737329</v>
+        <v>8.939261349696311</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.03790775313439</v>
+        <v>9.119091717638241</v>
       </c>
       <c r="AE9" t="n">
-        <v>4.04397055022796</v>
+        <v>9.287998431982899</v>
       </c>
       <c r="AF9" t="n">
-        <v>4.03870670628712</v>
+        <v>9.38115350000562</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.05704566960409</v>
+        <v>9.45986009001318</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.119894995050051</v>
+        <v>9.530145064205579</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.20051555772588</v>
+        <v>9.59334741025109</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.32184146852207</v>
+        <v>9.6492667733737</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.4540011781706</v>
+        <v>9.69796307799904</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.59739962384607</v>
+        <v>9.73922129801341</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17.19532857079312</v>
+        <v>9.83263377527388</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35502583645191</v>
+        <v>16.49485479495654</v>
       </c>
       <c r="D10" t="n">
-        <v>20.25768845566997</v>
+        <v>16.46027318621306</v>
       </c>
       <c r="E10" t="n">
-        <v>20.0277144673077</v>
+        <v>16.42481576518264</v>
       </c>
       <c r="F10" t="n">
-        <v>19.82290411937763</v>
+        <v>16.38965782780285</v>
       </c>
       <c r="G10" t="n">
-        <v>19.3005189344374</v>
+        <v>16.35339102990734</v>
       </c>
       <c r="H10" t="n">
-        <v>18.41952517876018</v>
+        <v>16.31320156049322</v>
       </c>
       <c r="I10" t="n">
-        <v>17.81972197724935</v>
+        <v>16.2672741665681</v>
       </c>
       <c r="J10" t="n">
-        <v>17.83399087667295</v>
+        <v>16.21314016181219</v>
       </c>
       <c r="K10" t="n">
-        <v>18.37206277137181</v>
+        <v>16.25655379736336</v>
       </c>
       <c r="L10" t="n">
-        <v>19.06195001653661</v>
+        <v>16.41447417661384</v>
       </c>
       <c r="M10" t="n">
-        <v>19.46686243382508</v>
+        <v>16.6551701138717</v>
       </c>
       <c r="N10" t="n">
-        <v>19.72477370261604</v>
+        <v>16.89553576633216</v>
       </c>
       <c r="O10" t="n">
-        <v>19.9284127938995</v>
+        <v>17.11386934151145</v>
       </c>
       <c r="P10" t="n">
-        <v>19.94577759220744</v>
+        <v>17.32513918929775</v>
       </c>
       <c r="Q10" t="n">
-        <v>19.95715307048348</v>
+        <v>17.51149063820839</v>
       </c>
       <c r="R10" t="n">
-        <v>20.151549926783</v>
+        <v>17.66855623952953</v>
       </c>
       <c r="S10" t="n">
-        <v>20.03557552831678</v>
+        <v>17.67372030954402</v>
       </c>
       <c r="T10" t="n">
-        <v>19.8988271345939</v>
+        <v>17.5140828271701</v>
       </c>
       <c r="U10" t="n">
-        <v>20.18800656717638</v>
+        <v>17.34278396569448</v>
       </c>
       <c r="V10" t="n">
-        <v>20.76847634062949</v>
+        <v>17.1931112400695</v>
       </c>
       <c r="W10" t="n">
-        <v>21.56188042982454</v>
+        <v>16.99415318841129</v>
       </c>
       <c r="X10" t="n">
-        <v>22.57473108240078</v>
+        <v>16.74446900235179</v>
       </c>
       <c r="Y10" t="n">
-        <v>23.16985796004056</v>
+        <v>16.50440036571257</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.15772599683563</v>
+        <v>16.3291769382265</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.92895293425466</v>
+        <v>16.28906629429235</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.56741082563215</v>
+        <v>16.37784578965181</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.05422325802082</v>
+        <v>16.53463476729915</v>
       </c>
       <c r="AD10" t="n">
-        <v>21.64537275659065</v>
+        <v>16.61396555350194</v>
       </c>
       <c r="AE10" t="n">
-        <v>21.26765400911962</v>
+        <v>16.53277704091845</v>
       </c>
       <c r="AF10" t="n">
-        <v>20.89868438989172</v>
+        <v>16.34322498546354</v>
       </c>
       <c r="AG10" t="n">
-        <v>20.70413706301624</v>
+        <v>16.21843105529727</v>
       </c>
       <c r="AH10" t="n">
-        <v>20.64987116489978</v>
+        <v>16.10077528050607</v>
       </c>
       <c r="AI10" t="n">
-        <v>20.57483177090565</v>
+        <v>15.97213497487913</v>
       </c>
       <c r="AJ10" t="n">
-        <v>20.38365761387487</v>
+        <v>15.82752601937678</v>
       </c>
       <c r="AK10" t="n">
-        <v>20.14359080101068</v>
+        <v>15.66741734172635</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.8825946176253</v>
+        <v>15.49759465776242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>1.25.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10.5335215577657</v>
+        <v>6.50537836826959</v>
       </c>
       <c r="C11" t="n">
-        <v>13.16653220424156</v>
+        <v>13.37859003905076</v>
       </c>
       <c r="D11" t="n">
-        <v>13.41939257086207</v>
+        <v>13.21924355935771</v>
       </c>
       <c r="E11" t="n">
-        <v>13.68729219799602</v>
+        <v>13.06226378868056</v>
       </c>
       <c r="F11" t="n">
-        <v>13.95959113581353</v>
+        <v>12.90302512403289</v>
       </c>
       <c r="G11" t="n">
-        <v>14.25162305723907</v>
+        <v>12.73850275235819</v>
       </c>
       <c r="H11" t="n">
-        <v>14.58012553342566</v>
+        <v>12.56999733667285</v>
       </c>
       <c r="I11" t="n">
-        <v>14.82882587107441</v>
+        <v>12.40618348125082</v>
       </c>
       <c r="J11" t="n">
-        <v>14.99397480635532</v>
+        <v>12.27366596705975</v>
       </c>
       <c r="K11" t="n">
-        <v>15.18089989358859</v>
+        <v>12.2568672723651</v>
       </c>
       <c r="L11" t="n">
-        <v>15.45957168546024</v>
+        <v>12.28607997947327</v>
       </c>
       <c r="M11" t="n">
-        <v>15.83784294244667</v>
+        <v>12.33787970138901</v>
       </c>
       <c r="N11" t="n">
-        <v>16.32740335907798</v>
+        <v>12.42234940113742</v>
       </c>
       <c r="O11" t="n">
-        <v>16.65125494222622</v>
+        <v>12.54161576050523</v>
       </c>
       <c r="P11" t="n">
-        <v>16.84822306957316</v>
+        <v>12.6877866409371</v>
       </c>
       <c r="Q11" t="n">
-        <v>16.81607939929177</v>
+        <v>12.82897290307948</v>
       </c>
       <c r="R11" t="n">
-        <v>16.60918929215188</v>
+        <v>12.94356009206485</v>
       </c>
       <c r="S11" t="n">
-        <v>16.55509980781396</v>
+        <v>13.00481130157694</v>
       </c>
       <c r="T11" t="n">
-        <v>16.54110985142116</v>
+        <v>13.01449922023524</v>
       </c>
       <c r="U11" t="n">
-        <v>16.34316946457406</v>
+        <v>12.97223990134752</v>
       </c>
       <c r="V11" t="n">
-        <v>16.14889985871017</v>
+        <v>12.86046932120265</v>
       </c>
       <c r="W11" t="n">
-        <v>15.95138722446755</v>
+        <v>12.68295717395045</v>
       </c>
       <c r="X11" t="n">
-        <v>15.50256024093136</v>
+        <v>12.4767231964182</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.1546989036188</v>
+        <v>12.27312917837293</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.17724290596502</v>
+        <v>12.06644024181408</v>
       </c>
       <c r="AA11" t="n">
-        <v>15.32104106634399</v>
+        <v>11.85591494533517</v>
       </c>
       <c r="AB11" t="n">
-        <v>15.63672335223895</v>
+        <v>11.65690572529051</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.16270798571152</v>
+        <v>11.46577448734554</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.63212926267598</v>
+        <v>11.27152762658071</v>
       </c>
       <c r="AE11" t="n">
-        <v>16.88397422040087</v>
+        <v>11.03150531569299</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.00049852528584</v>
+        <v>10.6236595078683</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.72256270882589</v>
+        <v>10.2043303819842</v>
       </c>
       <c r="AH11" t="n">
-        <v>16.71123077255912</v>
+        <v>9.789878775309219</v>
       </c>
       <c r="AI11" t="n">
-        <v>17.06312712098039</v>
+        <v>9.37475856332048</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.95335833629977</v>
+        <v>8.954094537267011</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.9064442977498</v>
+        <v>8.523829312424901</v>
       </c>
       <c r="AL11" t="n">
-        <v>19.96510562118309</v>
+        <v>8.08134181257989</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>1.25.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.48081354679449</v>
+        <v>7.05820970262431</v>
       </c>
       <c r="C12" t="n">
-        <v>8.993689684034461</v>
+        <v>4.66057190399238</v>
       </c>
       <c r="D12" t="n">
-        <v>9.262595645147011</v>
+        <v>5.44806604380792</v>
       </c>
       <c r="E12" t="n">
-        <v>9.53043647447087</v>
+        <v>6.22041475880707</v>
       </c>
       <c r="F12" t="n">
-        <v>9.805817460419131</v>
+        <v>6.98046027858821</v>
       </c>
       <c r="G12" t="n">
-        <v>10.05073387432453</v>
+        <v>7.72838521082386</v>
       </c>
       <c r="H12" t="n">
-        <v>10.27270073058118</v>
+        <v>8.461159931686749</v>
       </c>
       <c r="I12" t="n">
-        <v>10.45442308418627</v>
+        <v>9.17400784743764</v>
       </c>
       <c r="J12" t="n">
-        <v>10.65222594567822</v>
+        <v>9.84713220158366</v>
       </c>
       <c r="K12" t="n">
-        <v>10.80437379009555</v>
+        <v>10.24030116222129</v>
       </c>
       <c r="L12" t="n">
-        <v>10.83735116589838</v>
+        <v>10.48350309999994</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85164437252295</v>
+        <v>10.60347768627562</v>
       </c>
       <c r="N12" t="n">
-        <v>10.86407605424577</v>
+        <v>10.59526735076413</v>
       </c>
       <c r="O12" t="n">
-        <v>10.76223600541268</v>
+        <v>10.43736804456653</v>
       </c>
       <c r="P12" t="n">
-        <v>10.48628499324165</v>
+        <v>10.13828299115167</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.99957340823943</v>
+        <v>9.7440611352053</v>
       </c>
       <c r="R12" t="n">
-        <v>9.37344541659418</v>
+        <v>9.32509573875558</v>
       </c>
       <c r="S12" t="n">
-        <v>8.634022755803571</v>
+        <v>8.96310317699003</v>
       </c>
       <c r="T12" t="n">
-        <v>7.95528973674423</v>
+        <v>8.6845451415762</v>
       </c>
       <c r="U12" t="n">
-        <v>7.291760825492539</v>
+        <v>8.50759733102063</v>
       </c>
       <c r="V12" t="n">
-        <v>6.59894400506134</v>
+        <v>8.44947202538018</v>
       </c>
       <c r="W12" t="n">
-        <v>5.96179194236811</v>
+        <v>8.523507262624621</v>
       </c>
       <c r="X12" t="n">
-        <v>5.30820688310502</v>
+        <v>8.723125408362529</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.59867929445262</v>
+        <v>8.99494985387169</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.94979720919054</v>
+        <v>9.28751121779735</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.49469553570225</v>
+        <v>9.57421396611878</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.16156612989007</v>
+        <v>9.844215550569061</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.91882265846207</v>
+        <v>10.09092815263715</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.79928453771116</v>
+        <v>10.292705390221</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.76132043630113</v>
+        <v>10.42596266896754</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.41631771099301</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.38159944870747</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.34006655959955</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.29433487226437</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.24141939854014</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.75398376177524</v>
+        <v>10.17538260155719</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.75398376177525</v>
+        <v>10.09097173902126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17.09373681013091</v>
+        <v>0.09197605078966001</v>
       </c>
       <c r="C13" t="n">
-        <v>12.94494246995834</v>
+        <v>9.08996216466409</v>
       </c>
       <c r="D13" t="n">
-        <v>12.76142356349168</v>
+        <v>9.02638213330374</v>
       </c>
       <c r="E13" t="n">
-        <v>12.57869600675464</v>
+        <v>8.94866184789992</v>
       </c>
       <c r="F13" t="n">
-        <v>12.41908718652923</v>
+        <v>8.859098285912321</v>
       </c>
       <c r="G13" t="n">
-        <v>12.34090831324896</v>
+        <v>8.760980298844901</v>
       </c>
       <c r="H13" t="n">
-        <v>12.15493446002052</v>
+        <v>8.656943688548651</v>
       </c>
       <c r="I13" t="n">
-        <v>11.87980805301018</v>
+        <v>8.550391300224961</v>
       </c>
       <c r="J13" t="n">
-        <v>11.53991874425828</v>
+        <v>8.444138238280841</v>
       </c>
       <c r="K13" t="n">
-        <v>11.31896127169357</v>
+        <v>8.248158091081439</v>
       </c>
       <c r="L13" t="n">
-        <v>11.44461297280654</v>
+        <v>7.99290086033445</v>
       </c>
       <c r="M13" t="n">
-        <v>11.99769748917089</v>
+        <v>7.69373591862553</v>
       </c>
       <c r="N13" t="n">
-        <v>12.68558464744748</v>
+        <v>7.38967582800652</v>
       </c>
       <c r="O13" t="n">
-        <v>13.38070816188269</v>
+        <v>7.11151469837792</v>
       </c>
       <c r="P13" t="n">
-        <v>14.00046573216055</v>
+        <v>6.87552915295014</v>
       </c>
       <c r="Q13" t="n">
-        <v>14.39009228488797</v>
+        <v>6.69193490706329</v>
       </c>
       <c r="R13" t="n">
-        <v>14.68845857101139</v>
+        <v>6.56270292549148</v>
       </c>
       <c r="S13" t="n">
-        <v>15.06330742291614</v>
+        <v>6.482278013534359</v>
       </c>
       <c r="T13" t="n">
-        <v>15.16449081119883</v>
+        <v>6.43495292425444</v>
       </c>
       <c r="U13" t="n">
-        <v>15.28116760859206</v>
+        <v>6.40697008400254</v>
       </c>
       <c r="V13" t="n">
-        <v>15.24474800432002</v>
+        <v>6.40407714817021</v>
       </c>
       <c r="W13" t="n">
-        <v>14.8606827477108</v>
+        <v>6.41809941663207</v>
       </c>
       <c r="X13" t="n">
-        <v>14.63714326289608</v>
+        <v>6.422656570492979</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.62007287522196</v>
+        <v>6.399398144037651</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.79439544256217</v>
+        <v>6.3511488726072</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.37716276393408</v>
+        <v>6.29296948420882</v>
       </c>
       <c r="AB13" t="n">
-        <v>15.94961346313839</v>
+        <v>6.22285600007287</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.56206657650606</v>
+        <v>6.143733654209941</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.16380775303225</v>
+        <v>6.06302310269932</v>
       </c>
       <c r="AE13" t="n">
-        <v>17.63424902204207</v>
+        <v>5.98711119991722</v>
       </c>
       <c r="AF13" t="n">
-        <v>18.03855415651189</v>
+        <v>5.96263534534118</v>
       </c>
       <c r="AG13" t="n">
-        <v>18.52544105627529</v>
+        <v>5.95443302995398</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.85661856429838</v>
+        <v>5.953751138094669</v>
       </c>
       <c r="AI13" t="n">
-        <v>18.96954108005414</v>
+        <v>5.95684524801985</v>
       </c>
       <c r="AJ13" t="n">
-        <v>18.93111276558388</v>
+        <v>5.96300985678206</v>
       </c>
       <c r="AK13" t="n">
-        <v>18.79637051108773</v>
+        <v>5.97271806236767</v>
       </c>
       <c r="AL13" t="n">
-        <v>18.55933919221111</v>
+        <v>5.986657814265451</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0.63.1</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08685264735712001</v>
+        <v>16.16088398222855</v>
       </c>
       <c r="C14" t="n">
-        <v>4.49478426800726</v>
+        <v>20.99277818739163</v>
       </c>
       <c r="D14" t="n">
-        <v>4.960247773292361</v>
+        <v>19.94869125807722</v>
       </c>
       <c r="E14" t="n">
-        <v>5.42681207855528</v>
+        <v>18.88286645856128</v>
       </c>
       <c r="F14" t="n">
-        <v>5.881505283808941</v>
+        <v>17.7881474993589</v>
       </c>
       <c r="G14" t="n">
-        <v>6.30375031627141</v>
+        <v>16.66234393564239</v>
       </c>
       <c r="H14" t="n">
-        <v>6.753902848052349</v>
+        <v>15.51329284203404</v>
       </c>
       <c r="I14" t="n">
-        <v>7.015048071870771</v>
+        <v>14.36520252338695</v>
       </c>
       <c r="J14" t="n">
-        <v>7.13253203153771</v>
+        <v>13.27981462690542</v>
       </c>
       <c r="K14" t="n">
-        <v>7.270933109940531</v>
+        <v>11.98493586890891</v>
       </c>
       <c r="L14" t="n">
-        <v>7.4479470626149</v>
+        <v>10.55239772945337</v>
       </c>
       <c r="M14" t="n">
-        <v>7.65536427843915</v>
+        <v>8.971308191922429</v>
       </c>
       <c r="N14" t="n">
-        <v>7.84477996338378</v>
+        <v>7.32886563794888</v>
       </c>
       <c r="O14" t="n">
-        <v>7.998103234219291</v>
+        <v>5.770045484212869</v>
       </c>
       <c r="P14" t="n">
-        <v>8.137403599921299</v>
+        <v>4.43974958071299</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.205385803933831</v>
+        <v>3.45317978399208</v>
       </c>
       <c r="R14" t="n">
-        <v>8.112586655588441</v>
+        <v>2.80773350741052</v>
       </c>
       <c r="S14" t="n">
-        <v>7.853442859176591</v>
+        <v>2.45310920845875</v>
       </c>
       <c r="T14" t="n">
-        <v>7.676810536905319</v>
+        <v>2.36544106990073</v>
       </c>
       <c r="U14" t="n">
-        <v>7.49702742582761</v>
+        <v>2.51707557106096</v>
       </c>
       <c r="V14" t="n">
-        <v>7.25914454878043</v>
+        <v>2.88143464542464</v>
       </c>
       <c r="W14" t="n">
-        <v>7.27689101101478</v>
+        <v>3.44977710643795</v>
       </c>
       <c r="X14" t="n">
-        <v>7.371627629950731</v>
+        <v>4.18715461250335</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.44393220595018</v>
+        <v>4.96782555248013</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.49554432147313</v>
+        <v>5.70429531133528</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.50693875653901</v>
+        <v>6.366510920674701</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.469258109878369</v>
+        <v>6.93951404762959</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3421863704376</v>
+        <v>7.41363382601153</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.181543711504861</v>
+        <v>7.79199257174686</v>
       </c>
       <c r="AE14" t="n">
-        <v>7.035328894096341</v>
+        <v>8.08915055130244</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.917802335473711</v>
+        <v>8.26963299781435</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.8404916472009</v>
+        <v>8.44068069580328</v>
       </c>
       <c r="AH14" t="n">
-        <v>6.81638171636709</v>
+        <v>8.61474435980341</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.79232527845696</v>
+        <v>8.78987742122767</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6.755632235344771</v>
+        <v>8.96117617016119</v>
       </c>
       <c r="AK14" t="n">
-        <v>6.724198366493781</v>
+        <v>9.124425786140911</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.692747953007889</v>
+        <v>9.27697329521418</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.63.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5372848038833</v>
+        <v>2.56993078498844</v>
       </c>
       <c r="C15" t="n">
-        <v>8.302480777476671</v>
+        <v>16.68921781880388</v>
       </c>
       <c r="D15" t="n">
-        <v>8.33107272990066</v>
+        <v>15.68389454493824</v>
       </c>
       <c r="E15" t="n">
-        <v>8.343781087371759</v>
+        <v>14.68995406409459</v>
       </c>
       <c r="F15" t="n">
-        <v>8.35606075838726</v>
+        <v>13.71416575244609</v>
       </c>
       <c r="G15" t="n">
-        <v>8.352283595085209</v>
+        <v>12.76091201375093</v>
       </c>
       <c r="H15" t="n">
-        <v>8.49197360953935</v>
+        <v>11.83307696866528</v>
       </c>
       <c r="I15" t="n">
-        <v>8.648727763809049</v>
+        <v>10.92715043596129</v>
       </c>
       <c r="J15" t="n">
-        <v>8.685897148393069</v>
+        <v>10.01025890312865</v>
       </c>
       <c r="K15" t="n">
-        <v>8.7875829192305</v>
+        <v>9.260424401267329</v>
       </c>
       <c r="L15" t="n">
-        <v>8.71568799473221</v>
+        <v>8.52465948526463</v>
       </c>
       <c r="M15" t="n">
-        <v>8.50838254338465</v>
+        <v>7.8888337479068</v>
       </c>
       <c r="N15" t="n">
-        <v>8.34434514651937</v>
+        <v>7.51822120488758</v>
       </c>
       <c r="O15" t="n">
-        <v>8.168798261998091</v>
+        <v>7.425231323623829</v>
       </c>
       <c r="P15" t="n">
-        <v>8.00186581758296</v>
+        <v>7.431618988070871</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.93678074347495</v>
+        <v>7.459740184539659</v>
       </c>
       <c r="R15" t="n">
-        <v>7.94355373901988</v>
+        <v>7.49567162370532</v>
       </c>
       <c r="S15" t="n">
-        <v>8.058712753133811</v>
+        <v>7.521560752357461</v>
       </c>
       <c r="T15" t="n">
-        <v>8.28127075936041</v>
+        <v>7.52434983255397</v>
       </c>
       <c r="U15" t="n">
-        <v>8.36435974578783</v>
+        <v>7.523762233648861</v>
       </c>
       <c r="V15" t="n">
-        <v>8.13135809034307</v>
+        <v>7.52916722606693</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6597217743071</v>
+        <v>7.516003473835391</v>
       </c>
       <c r="X15" t="n">
-        <v>6.986861999365169</v>
+        <v>7.46664045028599</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.2172897081926</v>
+        <v>7.35275465825595</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.46259170259129</v>
+        <v>7.14139264183994</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.85520205137457</v>
+        <v>6.838893594158479</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.40297675805774</v>
+        <v>6.4570513857904</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.08659647722504</v>
+        <v>5.97423494284089</v>
       </c>
       <c r="AD15" t="n">
-        <v>3.94007957376992</v>
+        <v>5.38571222552931</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.87115396095867</v>
+        <v>4.71883434054838</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.90191135740589</v>
+        <v>3.94905067270277</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.97508740967993</v>
+        <v>3.19538510709134</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.11578741256361</v>
+        <v>2.44082544942741</v>
       </c>
       <c r="AI15" t="n">
-        <v>4.25787017111564</v>
+        <v>1.67896617858712</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.33743536782725</v>
+        <v>0.9070248584259301</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.41410679331674</v>
+        <v>0.12670839790658</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.47091120684312</v>
+        <v>-0.657997109025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.75.1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.009276281859191</v>
+        <v>0.05565964956717</v>
       </c>
       <c r="C16" t="n">
-        <v>5.4592631886099</v>
+        <v>0.04911725230458</v>
       </c>
       <c r="D16" t="n">
-        <v>5.67786028342174</v>
+        <v>0.04925215200649</v>
       </c>
       <c r="E16" t="n">
-        <v>5.88477777171848</v>
+        <v>0.04966267156019</v>
       </c>
       <c r="F16" t="n">
-        <v>6.082092073499689</v>
+        <v>0.05045854399077999</v>
       </c>
       <c r="G16" t="n">
-        <v>6.308950103463</v>
+        <v>0.05186811760241</v>
       </c>
       <c r="H16" t="n">
-        <v>6.492348318043501</v>
+        <v>0.05444247186758</v>
       </c>
       <c r="I16" t="n">
-        <v>6.552213099108339</v>
+        <v>0.0597841384782</v>
       </c>
       <c r="J16" t="n">
-        <v>6.50033275871998</v>
+        <v>0.07391723482654999</v>
       </c>
       <c r="K16" t="n">
-        <v>6.40858563332338</v>
+        <v>0.13073263345192</v>
       </c>
       <c r="L16" t="n">
-        <v>6.361746676281441</v>
+        <v>0.16890837875867</v>
       </c>
       <c r="M16" t="n">
-        <v>6.355408853365329</v>
+        <v>0.19974917614354</v>
       </c>
       <c r="N16" t="n">
-        <v>6.35081512640268</v>
+        <v>0.23008801055911</v>
       </c>
       <c r="O16" t="n">
-        <v>6.403071013637381</v>
+        <v>0.26181644787606</v>
       </c>
       <c r="P16" t="n">
-        <v>6.553930351016129</v>
+        <v>0.29865260279762</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.692265729239249</v>
+        <v>0.32769384264457</v>
       </c>
       <c r="R16" t="n">
-        <v>6.800059793537019</v>
+        <v>0.28803504496799</v>
       </c>
       <c r="S16" t="n">
-        <v>7.00637409130601</v>
+        <v>0.24739402941746</v>
       </c>
       <c r="T16" t="n">
-        <v>7.26950565501767</v>
+        <v>0.20919683870894</v>
       </c>
       <c r="U16" t="n">
-        <v>7.50940193558956</v>
+        <v>0.17253165860749</v>
       </c>
       <c r="V16" t="n">
-        <v>7.77570940756791</v>
+        <v>0.13505538574945</v>
       </c>
       <c r="W16" t="n">
-        <v>8.07093582852343</v>
+        <v>0.09257311497417001</v>
       </c>
       <c r="X16" t="n">
-        <v>8.312716823284159</v>
+        <v>0.05249164486767</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.444603133497381</v>
+        <v>0.04214314442686</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.549184441447121</v>
+        <v>0.04172381857412</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.64021414407862</v>
+        <v>0.04171839217126</v>
       </c>
       <c r="AB16" t="n">
-        <v>8.663633519499921</v>
+        <v>0.04201916050791</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.66708684020565</v>
+        <v>0.04244404410086</v>
       </c>
       <c r="AD16" t="n">
-        <v>8.66785488297236</v>
+        <v>0.04288636607886</v>
       </c>
       <c r="AE16" t="n">
-        <v>8.540612268860039</v>
+        <v>0.04330530506328</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.44670892296409</v>
+        <v>0.04315121510799</v>
       </c>
       <c r="AG16" t="n">
-        <v>8.42129332120944</v>
+        <v>0.04292117466339</v>
       </c>
       <c r="AH16" t="n">
-        <v>8.441968223808169</v>
+        <v>0.04266923679216</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.536974153824509</v>
+        <v>0.04237848548463</v>
       </c>
       <c r="AJ16" t="n">
-        <v>8.67778577275409</v>
+        <v>0.04202471384216</v>
       </c>
       <c r="AK16" t="n">
-        <v>8.812120003541921</v>
+        <v>0.04159448943124</v>
       </c>
       <c r="AL16" t="n">
-        <v>8.94982594276691</v>
+        <v>0.04107934275965</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0.31.1</t>
+          <t>0.75.3</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.77622541413755</v>
+        <v>7.07866695768459</v>
       </c>
       <c r="C17" t="n">
-        <v>3.94077766335114</v>
+        <v>0.04820789816604</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1432846720955</v>
+        <v>0.04660974345125</v>
       </c>
       <c r="E17" t="n">
-        <v>2.37927512268636</v>
+        <v>0.04499745384129</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6981299579787</v>
+        <v>0.04336029862888</v>
       </c>
       <c r="G17" t="n">
-        <v>1.51458384613362</v>
+        <v>0.0417265822665</v>
       </c>
       <c r="H17" t="n">
-        <v>1.61476725498053</v>
+        <v>0.0401472848377</v>
       </c>
       <c r="I17" t="n">
-        <v>2.21327931530405</v>
+        <v>0.03871084463572</v>
       </c>
       <c r="J17" t="n">
-        <v>2.94802074504705</v>
+        <v>0.03741992887895</v>
       </c>
       <c r="K17" t="n">
-        <v>3.33594668310576</v>
+        <v>0.03568584286256</v>
       </c>
       <c r="L17" t="n">
-        <v>3.24730166908109</v>
+        <v>0.22228921435179</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14587615403454</v>
+        <v>0.9949776056950301</v>
       </c>
       <c r="N17" t="n">
-        <v>3.09871382495262</v>
+        <v>1.66140190216023</v>
       </c>
       <c r="O17" t="n">
-        <v>3.01165701687812</v>
+        <v>2.11319023438838</v>
       </c>
       <c r="P17" t="n">
-        <v>3.11317814965211</v>
+        <v>2.49729319829859</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.36687232026157</v>
+        <v>2.91980710090376</v>
       </c>
       <c r="R17" t="n">
-        <v>3.5077212861631</v>
+        <v>3.52083831303481</v>
       </c>
       <c r="S17" t="n">
-        <v>3.65635552321878</v>
+        <v>4.32069303938327</v>
       </c>
       <c r="T17" t="n">
-        <v>3.99325373868397</v>
+        <v>4.55957635463253</v>
       </c>
       <c r="U17" t="n">
-        <v>4.22011658149419</v>
+        <v>4.57080033405364</v>
       </c>
       <c r="V17" t="n">
-        <v>4.26984380144669</v>
+        <v>4.59652506489605</v>
       </c>
       <c r="W17" t="n">
-        <v>4.32455944610455</v>
+        <v>4.632432908556909</v>
       </c>
       <c r="X17" t="n">
-        <v>4.32398031699159</v>
+        <v>4.66332376086684</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.18206546773413</v>
+        <v>4.675847746317039</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.01468305626077</v>
+        <v>4.66755553123807</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.77316493429036</v>
+        <v>4.64596487907894</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.24142456379294</v>
+        <v>4.620048771511899</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51284303897113</v>
+        <v>4.58551597264155</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.75137265520491</v>
+        <v>4.53396500977693</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.1632793995807</v>
+        <v>4.46997250836332</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.13409105144389</v>
+        <v>4.40342398875273</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.62268782237996</v>
+        <v>4.34029970034066</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.43253826895777</v>
+        <v>4.27841665849214</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.36827824909584</v>
+        <v>4.21797868055938</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.02972445451165</v>
+        <v>4.15956339325037</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.62577815749627</v>
+        <v>4.10376423479067</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.16535578542594</v>
+        <v>4.05109422802771</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0.31.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6.63011346269113</v>
+        <v>14.48771669399818</v>
       </c>
       <c r="C18" t="n">
-        <v>7.00072702956441</v>
+        <v>8.62029056005712</v>
       </c>
       <c r="D18" t="n">
-        <v>7.043359572296951</v>
+        <v>8.60665951334307</v>
       </c>
       <c r="E18" t="n">
-        <v>7.09841209543759</v>
+        <v>8.579373476957999</v>
       </c>
       <c r="F18" t="n">
-        <v>7.1547253595605</v>
+        <v>8.53940052715585</v>
       </c>
       <c r="G18" t="n">
-        <v>7.24307149500316</v>
+        <v>8.4922166344984</v>
       </c>
       <c r="H18" t="n">
-        <v>7.352984797216509</v>
+        <v>8.442331538366519</v>
       </c>
       <c r="I18" t="n">
-        <v>7.46382025564246</v>
+        <v>8.389680599660471</v>
       </c>
       <c r="J18" t="n">
-        <v>7.555658107005581</v>
+        <v>8.325811350318329</v>
       </c>
       <c r="K18" t="n">
-        <v>7.641415725632609</v>
+        <v>8.21573533110989</v>
       </c>
       <c r="L18" t="n">
-        <v>7.720519304553131</v>
+        <v>8.10933222382034</v>
       </c>
       <c r="M18" t="n">
-        <v>7.67468155568792</v>
+        <v>8.017270736902599</v>
       </c>
       <c r="N18" t="n">
-        <v>7.49341907700326</v>
+        <v>7.958177899947811</v>
       </c>
       <c r="O18" t="n">
-        <v>7.261432571345621</v>
+        <v>7.93328792444624</v>
       </c>
       <c r="P18" t="n">
-        <v>7.01097776990945</v>
+        <v>7.925037516858879</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.81357962715927</v>
+        <v>7.91543635057458</v>
       </c>
       <c r="R18" t="n">
-        <v>6.640254528996</v>
+        <v>7.903432153248199</v>
       </c>
       <c r="S18" t="n">
-        <v>6.5080716045664</v>
+        <v>7.887078183192769</v>
       </c>
       <c r="T18" t="n">
-        <v>6.47517459196049</v>
+        <v>7.849144821733139</v>
       </c>
       <c r="U18" t="n">
-        <v>6.332489751571161</v>
+        <v>7.76379590816561</v>
       </c>
       <c r="V18" t="n">
-        <v>6.35968631872884</v>
+        <v>7.627592529553021</v>
       </c>
       <c r="W18" t="n">
-        <v>6.55753354572378</v>
+        <v>7.47039390274105</v>
       </c>
       <c r="X18" t="n">
-        <v>6.70051048411343</v>
+        <v>7.32553068839875</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.83281579237401</v>
+        <v>7.206201647395261</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.951743326980051</v>
+        <v>7.12126428758334</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.03733667091697</v>
+        <v>7.08165120374062</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.08771247740842</v>
+        <v>7.081331008457751</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.06492443410488</v>
+        <v>7.10019631966117</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.953665619474821</v>
+        <v>7.136523402027541</v>
       </c>
       <c r="AE18" t="n">
-        <v>6.826959363053089</v>
+        <v>7.21516363545814</v>
       </c>
       <c r="AF18" t="n">
-        <v>6.75258500854244</v>
+        <v>7.369540552972791</v>
       </c>
       <c r="AG18" t="n">
-        <v>6.75114176101514</v>
+        <v>7.54393228680232</v>
       </c>
       <c r="AH18" t="n">
-        <v>6.859646390954779</v>
+        <v>7.7198126988364</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.055313219303989</v>
+        <v>7.89144732650735</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7.32278836050501</v>
+        <v>8.05844743535936</v>
       </c>
       <c r="AK18" t="n">
-        <v>7.5949176030329</v>
+        <v>8.223283493103411</v>
       </c>
       <c r="AL18" t="n">
-        <v>7.86931466385852</v>
+        <v>8.38942798244301</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>0.31.3</t>
+          <t>0.38.2</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.41640793975296</v>
+        <v>7.72115984116729</v>
       </c>
       <c r="C19" t="n">
-        <v>5.0964400886293</v>
+        <v>21.81289580189764</v>
       </c>
       <c r="D19" t="n">
-        <v>5.29946981515675</v>
+        <v>21.33703678904137</v>
       </c>
       <c r="E19" t="n">
-        <v>5.497868396414439</v>
+        <v>20.86806681041621</v>
       </c>
       <c r="F19" t="n">
-        <v>5.7393237249912</v>
+        <v>20.40284880510433</v>
       </c>
       <c r="G19" t="n">
-        <v>5.84781013913656</v>
+        <v>19.93971565673503</v>
       </c>
       <c r="H19" t="n">
-        <v>5.85213907943515</v>
+        <v>19.47967215267237</v>
       </c>
       <c r="I19" t="n">
-        <v>5.93131128278936</v>
+        <v>19.02810614944222</v>
       </c>
       <c r="J19" t="n">
-        <v>6.06260330374108</v>
+        <v>18.60347301771073</v>
       </c>
       <c r="K19" t="n">
-        <v>6.21465303827889</v>
+        <v>18.30398462686055</v>
       </c>
       <c r="L19" t="n">
-        <v>6.39086058587578</v>
+        <v>18.03196766558911</v>
       </c>
       <c r="M19" t="n">
-        <v>6.509012906487111</v>
+        <v>17.79078976780458</v>
       </c>
       <c r="N19" t="n">
-        <v>6.526036628728581</v>
+        <v>17.62252003093646</v>
       </c>
       <c r="O19" t="n">
-        <v>6.46409532064466</v>
+        <v>17.55080044119005</v>
       </c>
       <c r="P19" t="n">
-        <v>6.368283255957071</v>
+        <v>17.57236360511077</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.272690936789049</v>
+        <v>17.67430896453093</v>
       </c>
       <c r="R19" t="n">
-        <v>6.1814440670239</v>
+        <v>17.81920057032667</v>
       </c>
       <c r="S19" t="n">
-        <v>6.062147639696789</v>
+        <v>17.98267421312218</v>
       </c>
       <c r="T19" t="n">
-        <v>6.03642359009337</v>
+        <v>18.15688003872699</v>
       </c>
       <c r="U19" t="n">
-        <v>6.077674244796031</v>
+        <v>18.31664317294548</v>
       </c>
       <c r="V19" t="n">
-        <v>6.10901588768147</v>
+        <v>18.43919058166659</v>
       </c>
       <c r="W19" t="n">
-        <v>6.22902513902314</v>
+        <v>18.52825299332555</v>
       </c>
       <c r="X19" t="n">
-        <v>6.34872510778039</v>
+        <v>18.58481999654846</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.354997610114591</v>
+        <v>18.61752005320687</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.324445284672101</v>
+        <v>18.64443809121219</v>
       </c>
       <c r="AA19" t="n">
-        <v>6.27956678420552</v>
+        <v>18.64753938721886</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.20727880671791</v>
+        <v>18.62173317051957</v>
       </c>
       <c r="AC19" t="n">
-        <v>6.034696250641311</v>
+        <v>18.57508266230732</v>
       </c>
       <c r="AD19" t="n">
-        <v>5.73437382857158</v>
+        <v>18.54317226786188</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.386135115205779</v>
+        <v>18.54138657870084</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.98447317560956</v>
+        <v>18.60195156643908</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.64930603412366</v>
+        <v>18.6626114925928</v>
       </c>
       <c r="AH19" t="n">
-        <v>4.41230503199084</v>
+        <v>18.72359596464694</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.25249530029848</v>
+        <v>18.78685248644932</v>
       </c>
       <c r="AJ19" t="n">
-        <v>4.128169951345391</v>
+        <v>18.85308925139378</v>
       </c>
       <c r="AK19" t="n">
-        <v>4.0047993603996</v>
+        <v>18.92221789464155</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.8755689148383</v>
+        <v>18.9932352484084</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.38.3</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.11571844899627</v>
+        <v>4.08739546042457</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05002329159134999</v>
+        <v>0.0389594195666</v>
       </c>
       <c r="D20" t="n">
-        <v>0.04940074762523</v>
+        <v>0.03906500170734</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04858652985433</v>
+        <v>0.03916581358131</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04770979128596</v>
+        <v>0.03925364829266</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04562637808511</v>
+        <v>0.03932800778687</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0438055851573</v>
+        <v>0.03939001832537</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03975113769096</v>
+        <v>0.03945862270167</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03801846104597</v>
+        <v>0.0396008510322</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03876417246887</v>
+        <v>0.03961961445991</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04025689988726</v>
+        <v>0.03971070628713</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04256417414948</v>
+        <v>0.03998471058406</v>
       </c>
       <c r="N20" t="n">
-        <v>0.04445878159258</v>
+        <v>0.04039693060821</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04485232381605</v>
+        <v>0.04086797358919</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04507589476497</v>
+        <v>0.04136097852215</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.04630589070525</v>
+        <v>0.0417955721475</v>
       </c>
       <c r="R20" t="n">
-        <v>0.04826617598143</v>
+        <v>0.04216295407378</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04876145198596</v>
+        <v>0.04250546393267</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04950191156245</v>
+        <v>0.04290331529183</v>
       </c>
       <c r="U20" t="n">
-        <v>0.05060319702871999</v>
+        <v>0.04329178817601</v>
       </c>
       <c r="V20" t="n">
-        <v>0.05025517566414</v>
+        <v>0.04338030627480999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.05002710874214</v>
+        <v>0.04301065466109</v>
       </c>
       <c r="X20" t="n">
-        <v>0.04963291354365</v>
+        <v>0.04236450963045</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.04955741746303</v>
+        <v>0.04167986961887001</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04893618965438001</v>
+        <v>0.04123495685739</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04871464823398</v>
+        <v>0.04103375933679</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.04907657578853</v>
+        <v>0.04093226383366</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.04880427792105</v>
+        <v>0.04088081623243</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.04817726246709</v>
+        <v>0.04083868509141</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.04766896756882</v>
+        <v>0.0406133835203</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.04744926011396</v>
+        <v>0.03994158250358</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.04756073649389</v>
+        <v>0.03916569547471</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.04792062559698</v>
+        <v>0.03841756570208</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.0482226739197</v>
+        <v>0.03766464160909</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.04785167986841</v>
+        <v>0.03686140718297</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.0473545612099</v>
+        <v>0.03599088853756</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.04673170962203</v>
+        <v>0.03504710419806</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0.16.1</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.07483707637768</v>
+        <v>13.41677839163405</v>
       </c>
       <c r="C21" t="n">
-        <v>14.52924344188416</v>
+        <v>10.49989288989755</v>
       </c>
       <c r="D21" t="n">
-        <v>14.26635146654551</v>
+        <v>10.62721500438955</v>
       </c>
       <c r="E21" t="n">
-        <v>14.01445720584751</v>
+        <v>10.75371558213798</v>
       </c>
       <c r="F21" t="n">
-        <v>13.76727149135796</v>
+        <v>10.88165863490804</v>
       </c>
       <c r="G21" t="n">
-        <v>13.5032518375715</v>
+        <v>11.0125838202117</v>
       </c>
       <c r="H21" t="n">
-        <v>13.0072952410592</v>
+        <v>11.14889588194684</v>
       </c>
       <c r="I21" t="n">
-        <v>12.62609721673647</v>
+        <v>11.29082650123824</v>
       </c>
       <c r="J21" t="n">
-        <v>12.49683879183234</v>
+        <v>11.43139298493428</v>
       </c>
       <c r="K21" t="n">
-        <v>12.2036762081223</v>
+        <v>11.58799686662585</v>
       </c>
       <c r="L21" t="n">
-        <v>12.18590521095298</v>
+        <v>11.73461229387227</v>
       </c>
       <c r="M21" t="n">
-        <v>12.38476594415165</v>
+        <v>11.86880833718122</v>
       </c>
       <c r="N21" t="n">
-        <v>12.39517919446969</v>
+        <v>12.00390057128172</v>
       </c>
       <c r="O21" t="n">
-        <v>12.29474773428309</v>
+        <v>12.16193773245956</v>
       </c>
       <c r="P21" t="n">
-        <v>12.29421106243129</v>
+        <v>12.33495940749035</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.31276100987286</v>
+        <v>12.4868066391524</v>
       </c>
       <c r="R21" t="n">
-        <v>12.35907058189142</v>
+        <v>12.59104021106149</v>
       </c>
       <c r="S21" t="n">
-        <v>12.43082500403687</v>
+        <v>12.64703779423143</v>
       </c>
       <c r="T21" t="n">
-        <v>12.3240664052391</v>
+        <v>12.66275694242431</v>
       </c>
       <c r="U21" t="n">
-        <v>12.00199535876532</v>
+        <v>12.65611910161433</v>
       </c>
       <c r="V21" t="n">
-        <v>11.7090233301215</v>
+        <v>12.65567667697276</v>
       </c>
       <c r="W21" t="n">
-        <v>11.55244175696777</v>
+        <v>12.67191527021179</v>
       </c>
       <c r="X21" t="n">
-        <v>11.52146970682829</v>
+        <v>12.68887573231013</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.63314012471768</v>
+        <v>12.706442570746</v>
       </c>
       <c r="Z21" t="n">
-        <v>11.84793854315817</v>
+        <v>12.72341492250849</v>
       </c>
       <c r="AA21" t="n">
-        <v>11.8712638574052</v>
+        <v>12.75202910582981</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.60985205519787</v>
+        <v>12.80440718288365</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.46616735383693</v>
+        <v>12.87529760018607</v>
       </c>
       <c r="AD21" t="n">
-        <v>11.41068249004494</v>
+        <v>12.95550478082803</v>
       </c>
       <c r="AE21" t="n">
-        <v>11.30302081196658</v>
+        <v>13.03225639560133</v>
       </c>
       <c r="AF21" t="n">
-        <v>11.26252083681901</v>
+        <v>13.13348046764809</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.29870802803134</v>
+        <v>13.25133314058034</v>
       </c>
       <c r="AH21" t="n">
-        <v>11.32860658019629</v>
+        <v>13.37342524003249</v>
       </c>
       <c r="AI21" t="n">
-        <v>11.37172513500087</v>
+        <v>13.49507761185668</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11.38899886958244</v>
+        <v>13.61552969458212</v>
       </c>
       <c r="AK21" t="n">
-        <v>11.42452130966013</v>
+        <v>13.73628262826409</v>
       </c>
       <c r="AL21" t="n">
-        <v>11.47046075319794</v>
+        <v>13.85887292595112</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>0.16.2</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.96873857369238</v>
+        <v>15.46442256271067</v>
       </c>
       <c r="C22" t="n">
-        <v>9.66871476115703</v>
+        <v>5.93725923371544</v>
       </c>
       <c r="D22" t="n">
-        <v>9.761364030315329</v>
+        <v>5.687023214274229</v>
       </c>
       <c r="E22" t="n">
-        <v>9.882965612366359</v>
+        <v>5.43351143852005</v>
       </c>
       <c r="F22" t="n">
-        <v>10.03436748429131</v>
+        <v>5.17769895307514</v>
       </c>
       <c r="G22" t="n">
-        <v>10.24381107599394</v>
+        <v>4.9224667701289</v>
       </c>
       <c r="H22" t="n">
-        <v>10.35518777503079</v>
+        <v>4.675005885024619</v>
       </c>
       <c r="I22" t="n">
-        <v>10.4748977094966</v>
+        <v>4.436435086901231</v>
       </c>
       <c r="J22" t="n">
-        <v>10.4379801187799</v>
+        <v>4.20294575859206</v>
       </c>
       <c r="K22" t="n">
-        <v>10.3665298237506</v>
+        <v>4.04235372825587</v>
       </c>
       <c r="L22" t="n">
-        <v>10.2955437710199</v>
+        <v>3.8441451557356</v>
       </c>
       <c r="M22" t="n">
-        <v>10.30068455591643</v>
+        <v>3.59648659857274</v>
       </c>
       <c r="N22" t="n">
-        <v>10.37831126281555</v>
+        <v>3.34986961957634</v>
       </c>
       <c r="O22" t="n">
-        <v>10.4696780218101</v>
+        <v>3.20744474531291</v>
       </c>
       <c r="P22" t="n">
-        <v>10.47130882602911</v>
+        <v>3.02976784349728</v>
       </c>
       <c r="Q22" t="n">
-        <v>10.41249001731256</v>
+        <v>2.61566140126465</v>
       </c>
       <c r="R22" t="n">
-        <v>10.30531959909541</v>
+        <v>2.14872896986709</v>
       </c>
       <c r="S22" t="n">
-        <v>10.10047717720342</v>
+        <v>1.7242390262244</v>
       </c>
       <c r="T22" t="n">
-        <v>10.06018168091893</v>
+        <v>1.34797711518935</v>
       </c>
       <c r="U22" t="n">
-        <v>10.05714861389452</v>
+        <v>1.01144388294473</v>
       </c>
       <c r="V22" t="n">
-        <v>10.04706186432555</v>
+        <v>0.70723771280523</v>
       </c>
       <c r="W22" t="n">
-        <v>10.08882644685147</v>
+        <v>0.4458539043360999</v>
       </c>
       <c r="X22" t="n">
-        <v>10.14257353873523</v>
+        <v>0.2505851412568</v>
       </c>
       <c r="Y22" t="n">
-        <v>10.1367054830218</v>
+        <v>0.1268610596615</v>
       </c>
       <c r="Z22" t="n">
-        <v>10.1265256253513</v>
+        <v>0.06563651862357001</v>
       </c>
       <c r="AA22" t="n">
-        <v>10.22987766268375</v>
+        <v>0.04619930254166</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.29833486386701</v>
+        <v>0.04438922300228</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.27621423227441</v>
+        <v>0.04540412237792</v>
       </c>
       <c r="AD22" t="n">
-        <v>10.20244965334106</v>
+        <v>0.04580244119295</v>
       </c>
       <c r="AE22" t="n">
-        <v>10.09055836001865</v>
+        <v>0.04536725220196</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.00866706504953</v>
+        <v>0.04384632685741</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.95295148883314</v>
+        <v>0.04243045835006</v>
       </c>
       <c r="AH22" t="n">
-        <v>9.9608045664027</v>
+        <v>0.04104084139428</v>
       </c>
       <c r="AI22" t="n">
-        <v>10.01629292967224</v>
+        <v>0.03965238903264</v>
       </c>
       <c r="AJ22" t="n">
-        <v>9.821450251764601</v>
+        <v>0.03825089649378999</v>
       </c>
       <c r="AK22" t="n">
-        <v>9.58683992861104</v>
+        <v>0.03682358461771</v>
       </c>
       <c r="AL22" t="n">
-        <v>9.31658819745274</v>
+        <v>0.03538632589048</v>
       </c>
     </row>
   </sheetData>

--- a/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_3/Fig_3a_data.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_O2_mean_final" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_Amp_std_final" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_O2_mean_sorted" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap_Amp_std_sorted" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,115 +549,115 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.15385</v>
+        <v>38.05509415510316</v>
       </c>
       <c r="C2" t="n">
-        <v>41.18440924534995</v>
+        <v>39.98144736451847</v>
       </c>
       <c r="D2" t="n">
-        <v>43.00610472774876</v>
+        <v>41.88178629800783</v>
       </c>
       <c r="E2" t="n">
-        <v>44.77339728849204</v>
+        <v>43.74982946632797</v>
       </c>
       <c r="F2" t="n">
-        <v>46.49455728133365</v>
+        <v>45.58816552059282</v>
       </c>
       <c r="G2" t="n">
-        <v>48.1891009083483</v>
+        <v>47.41298108321939</v>
       </c>
       <c r="H2" t="n">
-        <v>49.88642015604403</v>
+        <v>49.27838126071152</v>
       </c>
       <c r="I2" t="n">
-        <v>51.62535813266145</v>
+        <v>51.36179886476458</v>
       </c>
       <c r="J2" t="n">
-        <v>53.45218894152031</v>
+        <v>53.11940234221569</v>
       </c>
       <c r="K2" t="n">
-        <v>54.77617904694229</v>
+        <v>54.62585609170932</v>
       </c>
       <c r="L2" t="n">
-        <v>55.84454579464544</v>
+        <v>55.75464348427575</v>
       </c>
       <c r="M2" t="n">
-        <v>57.00665028624083</v>
+        <v>56.90713459888554</v>
       </c>
       <c r="N2" t="n">
-        <v>58.35758427196355</v>
+        <v>58.26774452588216</v>
       </c>
       <c r="O2" t="n">
-        <v>59.95454350700548</v>
+        <v>59.89412047596404</v>
       </c>
       <c r="P2" t="n">
-        <v>61.76043357773731</v>
+        <v>61.72071399541297</v>
       </c>
       <c r="Q2" t="n">
-        <v>63.63778475632594</v>
+        <v>63.61263032068704</v>
       </c>
       <c r="R2" t="n">
-        <v>65.52074277799137</v>
+        <v>65.50553484995527</v>
       </c>
       <c r="S2" t="n">
-        <v>67.46056339912576</v>
+        <v>67.45048504057171</v>
       </c>
       <c r="T2" t="n">
-        <v>69.50604263570351</v>
+        <v>69.49799323424426</v>
       </c>
       <c r="U2" t="n">
-        <v>71.4863469357953</v>
+        <v>71.4815153626694</v>
       </c>
       <c r="V2" t="n">
-        <v>73.15962187369836</v>
+        <v>73.15909870712409</v>
       </c>
       <c r="W2" t="n">
-        <v>74.50125182295737</v>
+        <v>74.50285791692711</v>
       </c>
       <c r="X2" t="n">
-        <v>75.58796834297448</v>
+        <v>75.58901696230707</v>
       </c>
       <c r="Y2" t="n">
-        <v>76.43036905110003</v>
+        <v>76.42976320678967</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.00845000007193</v>
+        <v>77.00723045824884</v>
       </c>
       <c r="AA2" t="n">
-        <v>77.37533312849783</v>
+        <v>77.37451494022777</v>
       </c>
       <c r="AB2" t="n">
-        <v>77.61364050314899</v>
+        <v>77.61328208451849</v>
       </c>
       <c r="AC2" t="n">
-        <v>77.77147496942733</v>
+        <v>77.77137258628848</v>
       </c>
       <c r="AD2" t="n">
-        <v>77.8808390862776</v>
+        <v>77.88082922134474</v>
       </c>
       <c r="AE2" t="n">
-        <v>77.96332497201742</v>
+        <v>77.96333523487498</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.05641894065562</v>
+        <v>78.05643356996714</v>
       </c>
       <c r="AG2" t="n">
-        <v>78.15283059561411</v>
+        <v>78.15284402155271</v>
       </c>
       <c r="AH2" t="n">
-        <v>78.25031594747713</v>
+        <v>78.25032491645756</v>
       </c>
       <c r="AI2" t="n">
-        <v>78.3497010103534</v>
+        <v>78.34970415883917</v>
       </c>
       <c r="AJ2" t="n">
-        <v>78.45178507595105</v>
+        <v>78.45178193953245</v>
       </c>
       <c r="AK2" t="n">
-        <v>78.55717974129692</v>
+        <v>78.55717029348705</v>
       </c>
       <c r="AL2" t="n">
-        <v>78.6664606966886</v>
+        <v>78.66644511086918</v>
       </c>
     </row>
     <row r="3">
@@ -667,1885 +667,2003 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.939189000000001</v>
+        <v>5.732024422964265</v>
       </c>
       <c r="C3" t="n">
-        <v>5.690306474527997</v>
+        <v>9.258600899896274</v>
       </c>
       <c r="D3" t="n">
-        <v>9.757472833114388</v>
+        <v>12.8229935307259</v>
       </c>
       <c r="E3" t="n">
-        <v>13.83356505138237</v>
+        <v>16.40874079092919</v>
       </c>
       <c r="F3" t="n">
-        <v>17.89218186660172</v>
+        <v>19.98842005864244</v>
       </c>
       <c r="G3" t="n">
-        <v>21.90436905975167</v>
+        <v>23.53418882414088</v>
       </c>
       <c r="H3" t="n">
-        <v>25.85252304568188</v>
+        <v>27.02227386295917</v>
       </c>
       <c r="I3" t="n">
-        <v>29.74384578774674</v>
+        <v>30.50574312091603</v>
       </c>
       <c r="J3" t="n">
-        <v>33.65149486363735</v>
+        <v>34.1491853630155</v>
       </c>
       <c r="K3" t="n">
-        <v>37.26725360312446</v>
+        <v>37.69058625019379</v>
       </c>
       <c r="L3" t="n">
-        <v>40.60987695877966</v>
+        <v>40.90777767441072</v>
       </c>
       <c r="M3" t="n">
-        <v>43.51145449862248</v>
+        <v>43.6504376107362</v>
       </c>
       <c r="N3" t="n">
-        <v>46.10075727048326</v>
+        <v>46.14604706230136</v>
       </c>
       <c r="O3" t="n">
-        <v>48.58588585421567</v>
+        <v>48.6069692669114</v>
       </c>
       <c r="P3" t="n">
-        <v>51.05896738692934</v>
+        <v>51.08366632701529</v>
       </c>
       <c r="Q3" t="n">
-        <v>53.57758553171818</v>
+        <v>53.60653525627159</v>
       </c>
       <c r="R3" t="n">
-        <v>56.13784615330489</v>
+        <v>56.16712133924139</v>
       </c>
       <c r="S3" t="n">
-        <v>58.69683544883144</v>
+        <v>58.72228949000974</v>
       </c>
       <c r="T3" t="n">
-        <v>61.24225398699563</v>
+        <v>61.26047160025882</v>
       </c>
       <c r="U3" t="n">
-        <v>63.79179441527732</v>
+        <v>63.80294906816644</v>
       </c>
       <c r="V3" t="n">
-        <v>66.33251348027126</v>
+        <v>66.34042832191706</v>
       </c>
       <c r="W3" t="n">
-        <v>68.76114934886355</v>
+        <v>68.76793067847311</v>
       </c>
       <c r="X3" t="n">
-        <v>70.91529884974</v>
+        <v>70.91875355674303</v>
       </c>
       <c r="Y3" t="n">
-        <v>72.69589122033932</v>
+        <v>72.69594047559319</v>
       </c>
       <c r="Z3" t="n">
-        <v>74.09436020239282</v>
+        <v>74.094496271982</v>
       </c>
       <c r="AA3" t="n">
-        <v>75.16280379576749</v>
+        <v>75.16438821351022</v>
       </c>
       <c r="AB3" t="n">
-        <v>75.99411283515776</v>
+        <v>75.99573102548815</v>
       </c>
       <c r="AC3" t="n">
-        <v>76.66059968843074</v>
+        <v>76.66143460622997</v>
       </c>
       <c r="AD3" t="n">
-        <v>77.20629912959062</v>
+        <v>77.20651941490587</v>
       </c>
       <c r="AE3" t="n">
-        <v>77.64772816525735</v>
+        <v>77.64769292257525</v>
       </c>
       <c r="AF3" t="n">
-        <v>77.89473724047748</v>
+        <v>77.89473736372389</v>
       </c>
       <c r="AG3" t="n">
-        <v>78.12731310447916</v>
+        <v>78.12731535420569</v>
       </c>
       <c r="AH3" t="n">
-        <v>78.35199082062151</v>
+        <v>78.35197399583814</v>
       </c>
       <c r="AI3" t="n">
-        <v>78.56806915689523</v>
+        <v>78.5680241116431</v>
       </c>
       <c r="AJ3" t="n">
-        <v>78.77383955124071</v>
+        <v>78.77376409401829</v>
       </c>
       <c r="AK3" t="n">
-        <v>78.96803833437224</v>
+        <v>78.96793407464584</v>
       </c>
       <c r="AL3" t="n">
-        <v>79.15006103427092</v>
+        <v>79.14993162885666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.0.1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.001613</v>
+        <v>16.47814047241391</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.029368501092248</v>
+        <v>19.47302122349542</v>
       </c>
       <c r="D4" t="n">
-        <v>1.167479767702273</v>
+        <v>22.46464264622113</v>
       </c>
       <c r="E4" t="n">
-        <v>4.372754946056205</v>
+        <v>25.44924006690494</v>
       </c>
       <c r="F4" t="n">
-        <v>7.585493357189227</v>
+        <v>28.41893004149769</v>
       </c>
       <c r="G4" t="n">
-        <v>10.79914389765527</v>
+        <v>31.3716406738301</v>
       </c>
       <c r="H4" t="n">
-        <v>14.01219199504057</v>
+        <v>34.31456560508953</v>
       </c>
       <c r="I4" t="n">
-        <v>17.22919978146577</v>
+        <v>37.28824772925871</v>
       </c>
       <c r="J4" t="n">
-        <v>20.46644210015365</v>
+        <v>40.31230511752419</v>
       </c>
       <c r="K4" t="n">
-        <v>24.18824917733735</v>
+        <v>43.52571252568583</v>
       </c>
       <c r="L4" t="n">
-        <v>28.40859732819048</v>
+        <v>46.50476597249448</v>
       </c>
       <c r="M4" t="n">
-        <v>32.26800773754054</v>
+        <v>48.19484975271821</v>
       </c>
       <c r="N4" t="n">
-        <v>36.16570279906732</v>
+        <v>49.35834202150922</v>
       </c>
       <c r="O4" t="n">
-        <v>39.97179941310271</v>
+        <v>50.39297595063238</v>
       </c>
       <c r="P4" t="n">
-        <v>43.88634582365443</v>
+        <v>51.36403209386843</v>
       </c>
       <c r="Q4" t="n">
-        <v>48.45857932493874</v>
+        <v>52.33059896270819</v>
       </c>
       <c r="R4" t="n">
-        <v>53.54925342201144</v>
+        <v>53.30957922357309</v>
       </c>
       <c r="S4" t="n">
-        <v>55.58081334536693</v>
+        <v>54.28491779986993</v>
       </c>
       <c r="T4" t="n">
-        <v>56.3828058323403</v>
+        <v>55.26669364868742</v>
       </c>
       <c r="U4" t="n">
-        <v>57.20735908791123</v>
+        <v>56.27311831046529</v>
       </c>
       <c r="V4" t="n">
-        <v>58.0834850767618</v>
+        <v>57.31746217330823</v>
       </c>
       <c r="W4" t="n">
-        <v>59.01511394708411</v>
+        <v>58.40303005517737</v>
       </c>
       <c r="X4" t="n">
-        <v>59.98595561585708</v>
+        <v>59.50729758051245</v>
       </c>
       <c r="Y4" t="n">
-        <v>60.97367655405558</v>
+        <v>60.58609748458647</v>
       </c>
       <c r="Z4" t="n">
-        <v>61.96384791555136</v>
+        <v>61.60009487748641</v>
       </c>
       <c r="AA4" t="n">
-        <v>62.94751053201913</v>
+        <v>62.53710903846424</v>
       </c>
       <c r="AB4" t="n">
-        <v>63.9149679230768</v>
+        <v>63.38728952167413</v>
       </c>
       <c r="AC4" t="n">
-        <v>64.85464063975373</v>
+        <v>64.14933733857418</v>
       </c>
       <c r="AD4" t="n">
-        <v>65.74275314775858</v>
+        <v>64.82172453851986</v>
       </c>
       <c r="AE4" t="n">
-        <v>66.55002298668049</v>
+        <v>65.40696168062578</v>
       </c>
       <c r="AF4" t="n">
-        <v>67.1544897257962</v>
+        <v>65.85198601332816</v>
       </c>
       <c r="AG4" t="n">
-        <v>67.74336866630934</v>
+        <v>66.29101261493096</v>
       </c>
       <c r="AH4" t="n">
-        <v>68.32179862174127</v>
+        <v>66.72572028411052</v>
       </c>
       <c r="AI4" t="n">
-        <v>68.88823419529949</v>
+        <v>67.15459782899933</v>
       </c>
       <c r="AJ4" t="n">
-        <v>69.44127456285338</v>
+        <v>67.57623696090675</v>
       </c>
       <c r="AK4" t="n">
-        <v>69.9792311884845</v>
+        <v>67.99001977829018</v>
       </c>
       <c r="AL4" t="n">
-        <v>70.50124561561532</v>
+        <v>68.39646775914861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6.0.1</t>
+          <t>6.0.2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.44151</v>
+        <v>5.662409942696555</v>
       </c>
       <c r="C5" t="n">
-        <v>12.87978735956546</v>
+        <v>7.71901414319762</v>
       </c>
       <c r="D5" t="n">
-        <v>16.45982839840487</v>
+        <v>9.811969889163073</v>
       </c>
       <c r="E5" t="n">
-        <v>20.02977054016261</v>
+        <v>11.94188464365822</v>
       </c>
       <c r="F5" t="n">
-        <v>23.58075124982324</v>
+        <v>14.10291865848437</v>
       </c>
       <c r="G5" t="n">
-        <v>27.1003237595179</v>
+        <v>16.28189592302551</v>
       </c>
       <c r="H5" t="n">
-        <v>30.59295558523418</v>
+        <v>18.45976747226641</v>
       </c>
       <c r="I5" t="n">
-        <v>34.09234994587251</v>
+        <v>20.63314257844392</v>
       </c>
       <c r="J5" t="n">
-        <v>37.72617862975618</v>
+        <v>23.1898854514336</v>
       </c>
       <c r="K5" t="n">
-        <v>41.69669803570388</v>
+        <v>25.91287733052033</v>
       </c>
       <c r="L5" t="n">
-        <v>45.69166783122434</v>
+        <v>28.86375680513869</v>
       </c>
       <c r="M5" t="n">
-        <v>48.6422712725649</v>
+        <v>32.05334983814783</v>
       </c>
       <c r="N5" t="n">
-        <v>49.9068465294166</v>
+        <v>35.39574047765728</v>
       </c>
       <c r="O5" t="n">
-        <v>50.7525896656044</v>
+        <v>38.82195727783898</v>
       </c>
       <c r="P5" t="n">
-        <v>51.56897501039063</v>
+        <v>42.27894956271921</v>
       </c>
       <c r="Q5" t="n">
-        <v>52.42610162864796</v>
+        <v>45.64035439924574</v>
       </c>
       <c r="R5" t="n">
-        <v>53.34420461013102</v>
+        <v>48.76341187514434</v>
       </c>
       <c r="S5" t="n">
-        <v>54.30277959191759</v>
+        <v>51.64869039548305</v>
       </c>
       <c r="T5" t="n">
-        <v>55.28363910929025</v>
+        <v>54.38559958239343</v>
       </c>
       <c r="U5" t="n">
-        <v>56.28849453204322</v>
+        <v>57.04918216120632</v>
       </c>
       <c r="V5" t="n">
-        <v>57.32982343501502</v>
+        <v>59.62015188466481</v>
       </c>
       <c r="W5" t="n">
-        <v>58.41211565592474</v>
+        <v>62.03609076998059</v>
       </c>
       <c r="X5" t="n">
-        <v>59.5139935746579</v>
+        <v>64.23286003741758</v>
       </c>
       <c r="Y5" t="n">
-        <v>60.59071173152635</v>
+        <v>66.14013118924002</v>
       </c>
       <c r="Z5" t="n">
-        <v>61.60237320345753</v>
+        <v>67.75643633565218</v>
       </c>
       <c r="AA5" t="n">
-        <v>62.53676848893712</v>
+        <v>69.17884529486902</v>
       </c>
       <c r="AB5" t="n">
-        <v>63.38498815624804</v>
+        <v>70.48329132156711</v>
       </c>
       <c r="AC5" t="n">
-        <v>64.14689545542244</v>
+        <v>71.67910548908354</v>
       </c>
       <c r="AD5" t="n">
-        <v>64.82003741269602</v>
+        <v>72.76032567873705</v>
       </c>
       <c r="AE5" t="n">
-        <v>65.40613628154198</v>
+        <v>73.70465654180818</v>
       </c>
       <c r="AF5" t="n">
-        <v>65.85155775749095</v>
+        <v>74.30022139486806</v>
       </c>
       <c r="AG5" t="n">
-        <v>66.29081239024745</v>
+        <v>74.88041522461907</v>
       </c>
       <c r="AH5" t="n">
-        <v>66.72565917587434</v>
+        <v>75.44134348782796</v>
       </c>
       <c r="AI5" t="n">
-        <v>67.15462895929505</v>
+        <v>75.98103141863322</v>
       </c>
       <c r="AJ5" t="n">
-        <v>67.57633499278512</v>
+        <v>76.49910414363302</v>
       </c>
       <c r="AK5" t="n">
-        <v>67.99017095999825</v>
+        <v>76.99808585274801</v>
       </c>
       <c r="AL5" t="n">
-        <v>68.39666365315698</v>
+        <v>77.4819986408701</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6.0.2</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.951429</v>
+        <v>-1.978228164385297</v>
       </c>
       <c r="C6" t="n">
-        <v>5.858295703763565</v>
+        <v>0.8826692505533942</v>
       </c>
       <c r="D6" t="n">
-        <v>8.227357998192874</v>
+        <v>3.767549020356491</v>
       </c>
       <c r="E6" t="n">
-        <v>10.63963908735974</v>
+        <v>6.675739999310274</v>
       </c>
       <c r="F6" t="n">
-        <v>13.09370821474319</v>
+        <v>9.597316229691154</v>
       </c>
       <c r="G6" t="n">
-        <v>15.5788890603055</v>
+        <v>12.530206878746</v>
       </c>
       <c r="H6" t="n">
-        <v>18.08147546837781</v>
+        <v>15.48123639098052</v>
       </c>
       <c r="I6" t="n">
-        <v>20.58855663889699</v>
+        <v>18.46468885485183</v>
       </c>
       <c r="J6" t="n">
-        <v>23.09156226970834</v>
+        <v>21.59754939691199</v>
       </c>
       <c r="K6" t="n">
-        <v>25.88573190221823</v>
+        <v>25.32912370368311</v>
       </c>
       <c r="L6" t="n">
-        <v>28.86933734083511</v>
+        <v>29.04404237046151</v>
       </c>
       <c r="M6" t="n">
-        <v>32.05718550227014</v>
+        <v>32.87677496635168</v>
       </c>
       <c r="N6" t="n">
-        <v>35.39385636505409</v>
+        <v>36.83103435956626</v>
       </c>
       <c r="O6" t="n">
-        <v>38.81696177663581</v>
+        <v>40.73370672393719</v>
       </c>
       <c r="P6" t="n">
-        <v>42.27230192249594</v>
+        <v>44.79171081645906</v>
       </c>
       <c r="Q6" t="n">
-        <v>45.63013939491663</v>
+        <v>49.32949856950273</v>
       </c>
       <c r="R6" t="n">
-        <v>48.74419773919736</v>
+        <v>53.6685093221087</v>
       </c>
       <c r="S6" t="n">
-        <v>51.61960810310787</v>
+        <v>55.51421443552749</v>
       </c>
       <c r="T6" t="n">
-        <v>54.35098518324812</v>
+        <v>56.36814226185051</v>
       </c>
       <c r="U6" t="n">
-        <v>57.0137815385764</v>
+        <v>57.19894531680964</v>
       </c>
       <c r="V6" t="n">
-        <v>59.58735361363851</v>
+        <v>58.07851277397703</v>
       </c>
       <c r="W6" t="n">
-        <v>62.00920937281028</v>
+        <v>59.01212484549671</v>
       </c>
       <c r="X6" t="n">
-        <v>64.21436589525258</v>
+        <v>59.98407560606463</v>
       </c>
       <c r="Y6" t="n">
-        <v>66.12809883096894</v>
+        <v>60.97242651429931</v>
       </c>
       <c r="Z6" t="n">
-        <v>67.74689046538288</v>
+        <v>61.96312164749963</v>
       </c>
       <c r="AA6" t="n">
-        <v>69.16998926714888</v>
+        <v>62.94753447520156</v>
       </c>
       <c r="AB6" t="n">
-        <v>70.47454633299941</v>
+        <v>63.91599510508755</v>
       </c>
       <c r="AC6" t="n">
-        <v>71.67050462971537</v>
+        <v>64.85659749014521</v>
       </c>
       <c r="AD6" t="n">
-        <v>72.75286372151186</v>
+        <v>65.74565338453573</v>
       </c>
       <c r="AE6" t="n">
-        <v>73.6996430330228</v>
+        <v>66.55320688604681</v>
       </c>
       <c r="AF6" t="n">
-        <v>74.29650155421407</v>
+        <v>67.15600354920896</v>
       </c>
       <c r="AG6" t="n">
-        <v>74.87765585001662</v>
+        <v>67.74311552228951</v>
       </c>
       <c r="AH6" t="n">
-        <v>75.43934618007835</v>
+        <v>68.31987923663957</v>
       </c>
       <c r="AI6" t="n">
-        <v>75.97967434496864</v>
+        <v>68.8847316698817</v>
       </c>
       <c r="AJ6" t="n">
-        <v>76.49831016742779</v>
+        <v>69.43626980874112</v>
       </c>
       <c r="AK6" t="n">
-        <v>76.99780389867504</v>
+        <v>69.97279843997651</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.48219208247627</v>
+        <v>70.4934405609805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.0.1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.7549</v>
+        <v>-1.369277041951011</v>
       </c>
       <c r="C7" t="n">
-        <v>40.61659335992471</v>
+        <v>2.6583022297207</v>
       </c>
       <c r="D7" t="n">
-        <v>41.18252819531157</v>
+        <v>6.68388669871662</v>
       </c>
       <c r="E7" t="n">
-        <v>41.74965250166994</v>
+        <v>10.70636793530534</v>
       </c>
       <c r="F7" t="n">
-        <v>42.31827669973266</v>
+        <v>14.7250858534286</v>
       </c>
       <c r="G7" t="n">
-        <v>42.88882793263019</v>
+        <v>18.74060608274533</v>
       </c>
       <c r="H7" t="n">
-        <v>43.46190959203667</v>
+        <v>22.75878965107662</v>
       </c>
       <c r="I7" t="n">
-        <v>44.03840048014107</v>
+        <v>26.82095285521033</v>
       </c>
       <c r="J7" t="n">
-        <v>44.61962705170373</v>
+        <v>31.09110250133459</v>
       </c>
       <c r="K7" t="n">
-        <v>45.2813399283156</v>
+        <v>36.22974970132616</v>
       </c>
       <c r="L7" t="n">
-        <v>46.1439583809475</v>
+        <v>40.00180221795428</v>
       </c>
       <c r="M7" t="n">
-        <v>46.88931742532812</v>
+        <v>42.46333041487856</v>
       </c>
       <c r="N7" t="n">
-        <v>47.41625994489108</v>
+        <v>44.67581991329226</v>
       </c>
       <c r="O7" t="n">
-        <v>47.80712380175977</v>
+        <v>46.74695912324082</v>
       </c>
       <c r="P7" t="n">
-        <v>48.12768755571934</v>
+        <v>48.71159301668224</v>
       </c>
       <c r="Q7" t="n">
-        <v>48.38201597216268</v>
+        <v>50.52610915565224</v>
       </c>
       <c r="R7" t="n">
-        <v>48.56047029269077</v>
+        <v>52.12143019642076</v>
       </c>
       <c r="S7" t="n">
-        <v>48.66706780443199</v>
+        <v>53.4918637733217</v>
       </c>
       <c r="T7" t="n">
-        <v>48.72046446920793</v>
+        <v>54.69092007846783</v>
       </c>
       <c r="U7" t="n">
-        <v>48.73886618898326</v>
+        <v>55.75983224722865</v>
       </c>
       <c r="V7" t="n">
-        <v>48.72134786552585</v>
+        <v>56.71337829107225</v>
       </c>
       <c r="W7" t="n">
-        <v>48.66950081433539</v>
+        <v>57.55395090367452</v>
       </c>
       <c r="X7" t="n">
-        <v>48.58933695134671</v>
+        <v>58.26515387813073</v>
       </c>
       <c r="Y7" t="n">
-        <v>48.47842884563546</v>
+        <v>58.82180887927631</v>
       </c>
       <c r="Z7" t="n">
-        <v>48.33982680077087</v>
+        <v>59.21784923634485</v>
       </c>
       <c r="AA7" t="n">
-        <v>48.19100840123597</v>
+        <v>59.50250928907108</v>
       </c>
       <c r="AB7" t="n">
-        <v>48.05720357580576</v>
+        <v>59.73293143956252</v>
       </c>
       <c r="AC7" t="n">
-        <v>47.94837103282163</v>
+        <v>59.94469087174203</v>
       </c>
       <c r="AD7" t="n">
-        <v>47.85930437730013</v>
+        <v>60.15560786099893</v>
       </c>
       <c r="AE7" t="n">
-        <v>47.78179496883637</v>
+        <v>60.37229259925432</v>
       </c>
       <c r="AF7" t="n">
-        <v>47.7390184901161</v>
+        <v>60.62581378711119</v>
       </c>
       <c r="AG7" t="n">
-        <v>47.69669119742512</v>
+        <v>60.8860934682326</v>
       </c>
       <c r="AH7" t="n">
-        <v>47.6565809971016</v>
+        <v>61.15100814827836</v>
       </c>
       <c r="AI7" t="n">
-        <v>47.62082353186583</v>
+        <v>61.41908768578577</v>
       </c>
       <c r="AJ7" t="n">
-        <v>47.59058956562207</v>
+        <v>61.68879144524369</v>
       </c>
       <c r="AK7" t="n">
-        <v>47.56641326963968</v>
+        <v>61.96005233876674</v>
       </c>
       <c r="AL7" t="n">
-        <v>47.54819416875782</v>
+        <v>62.23331111218624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>3.0.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.79718</v>
+        <v>24.09084815343396</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.833509489327127</v>
+        <v>26.00548457267825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.757229720641175</v>
+        <v>27.9095802530745</v>
       </c>
       <c r="E8" t="n">
-        <v>6.335662509690906</v>
+        <v>29.80663003895102</v>
       </c>
       <c r="F8" t="n">
-        <v>10.89559332258662</v>
+        <v>31.69905407654375</v>
       </c>
       <c r="G8" t="n">
-        <v>15.43563961285314</v>
+        <v>33.59034104021934</v>
       </c>
       <c r="H8" t="n">
-        <v>19.9624519270276</v>
+        <v>35.4938509572234</v>
       </c>
       <c r="I8" t="n">
-        <v>24.50761220839373</v>
+        <v>37.46547693130717</v>
       </c>
       <c r="J8" t="n">
-        <v>29.23702032277017</v>
+        <v>39.3169802867823</v>
       </c>
       <c r="K8" t="n">
-        <v>34.2794809858074</v>
+        <v>42.34147885989186</v>
       </c>
       <c r="L8" t="n">
-        <v>39.48221086498919</v>
+        <v>46.13881768469395</v>
       </c>
       <c r="M8" t="n">
-        <v>42.59239994561067</v>
+        <v>46.87945622629166</v>
       </c>
       <c r="N8" t="n">
-        <v>44.76512590070772</v>
+        <v>47.40490042847193</v>
       </c>
       <c r="O8" t="n">
-        <v>46.80213973935584</v>
+        <v>47.79631085497534</v>
       </c>
       <c r="P8" t="n">
-        <v>48.74013331909192</v>
+        <v>48.11785038498461</v>
       </c>
       <c r="Q8" t="n">
-        <v>50.52849197629491</v>
+        <v>48.37333814373305</v>
       </c>
       <c r="R8" t="n">
-        <v>52.09193061383048</v>
+        <v>48.55325528034345</v>
       </c>
       <c r="S8" t="n">
-        <v>53.43698465451939</v>
+        <v>48.66170798716494</v>
       </c>
       <c r="T8" t="n">
-        <v>54.61887720276199</v>
+        <v>48.71737940106509</v>
       </c>
       <c r="U8" t="n">
-        <v>55.6814638016976</v>
+        <v>48.7381063185754</v>
       </c>
       <c r="V8" t="n">
-        <v>56.63952600263072</v>
+        <v>48.72191562631598</v>
       </c>
       <c r="W8" t="n">
-        <v>57.49144998995355</v>
+        <v>48.6701978597722</v>
       </c>
       <c r="X8" t="n">
-        <v>58.21989780198557</v>
+        <v>48.58987319977837</v>
       </c>
       <c r="Y8" t="n">
-        <v>58.7953471731268</v>
+        <v>48.47880829708763</v>
       </c>
       <c r="Z8" t="n">
-        <v>59.20542598379162</v>
+        <v>48.34006121357458</v>
       </c>
       <c r="AA8" t="n">
-        <v>59.49690346562</v>
+        <v>48.19108895839238</v>
       </c>
       <c r="AB8" t="n">
-        <v>59.73040436238623</v>
+        <v>48.05715852472215</v>
       </c>
       <c r="AC8" t="n">
-        <v>59.94423611258437</v>
+        <v>47.9482651051898</v>
       </c>
       <c r="AD8" t="n">
-        <v>60.15584390690478</v>
+        <v>47.85915823404426</v>
       </c>
       <c r="AE8" t="n">
-        <v>60.37283994032313</v>
+        <v>47.7816198687947</v>
       </c>
       <c r="AF8" t="n">
-        <v>60.62661304046892</v>
+        <v>47.73884944623825</v>
       </c>
       <c r="AG8" t="n">
-        <v>60.88706711046522</v>
+        <v>47.69652330887563</v>
       </c>
       <c r="AH8" t="n">
-        <v>61.15211698831309</v>
+        <v>47.65641255669617</v>
       </c>
       <c r="AI8" t="n">
-        <v>61.42031118434847</v>
+        <v>47.62065725878834</v>
       </c>
       <c r="AJ8" t="n">
-        <v>61.69012133380792</v>
+        <v>47.59042969167854</v>
       </c>
       <c r="AK8" t="n">
-        <v>61.96147659404727</v>
+        <v>47.56626411005871</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.23481438416374</v>
+        <v>47.54805946428081</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.98116</v>
+        <v>6.103824240151527</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.036347334554794</v>
+        <v>8.511188213817583</v>
       </c>
       <c r="D9" t="n">
-        <v>2.690064015853756</v>
+        <v>10.96402143574228</v>
       </c>
       <c r="E9" t="n">
-        <v>7.393011751975226</v>
+        <v>13.44998531064664</v>
       </c>
       <c r="F9" t="n">
-        <v>12.06249403972683</v>
+        <v>15.95367322295391</v>
       </c>
       <c r="G9" t="n">
-        <v>16.69484099544187</v>
+        <v>18.45934350818391</v>
       </c>
       <c r="H9" t="n">
-        <v>21.29761637566087</v>
+        <v>20.92541674495381</v>
       </c>
       <c r="I9" t="n">
-        <v>25.91553201399539</v>
+        <v>23.15178051258757</v>
       </c>
       <c r="J9" t="n">
-        <v>30.80710052439923</v>
+        <v>25.68811282316782</v>
       </c>
       <c r="K9" t="n">
-        <v>36.14930180843632</v>
+        <v>28.16217701871969</v>
       </c>
       <c r="L9" t="n">
-        <v>42.86971559248266</v>
+        <v>31.513885416678</v>
       </c>
       <c r="M9" t="n">
-        <v>45.90270945094067</v>
+        <v>35.209764008305</v>
       </c>
       <c r="N9" t="n">
-        <v>46.6833867479489</v>
+        <v>38.33361762874932</v>
       </c>
       <c r="O9" t="n">
-        <v>47.19272577590739</v>
+        <v>40.92778767601978</v>
       </c>
       <c r="P9" t="n">
-        <v>47.52085326135006</v>
+        <v>43.0813078844881</v>
       </c>
       <c r="Q9" t="n">
-        <v>47.69776635311219</v>
+        <v>44.88140852629668</v>
       </c>
       <c r="R9" t="n">
-        <v>47.73810806726219</v>
+        <v>46.39949245461004</v>
       </c>
       <c r="S9" t="n">
-        <v>47.64815701442612</v>
+        <v>47.60389420744815</v>
       </c>
       <c r="T9" t="n">
-        <v>47.449362804484</v>
+        <v>48.25911720987418</v>
       </c>
       <c r="U9" t="n">
-        <v>47.23087369181012</v>
+        <v>48.36736196546036</v>
       </c>
       <c r="V9" t="n">
-        <v>47.02195127630789</v>
+        <v>48.18663197230641</v>
       </c>
       <c r="W9" t="n">
-        <v>46.83201907274125</v>
+        <v>47.84005218890196</v>
       </c>
       <c r="X9" t="n">
-        <v>46.67193890239377</v>
+        <v>47.34189833495434</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.54159507120721</v>
+        <v>46.75417095553303</v>
       </c>
       <c r="Z9" t="n">
-        <v>46.43211162405765</v>
+        <v>46.15025916443666</v>
       </c>
       <c r="AA9" t="n">
-        <v>46.32815289798353</v>
+        <v>45.53596114956817</v>
       </c>
       <c r="AB9" t="n">
-        <v>46.22598864901195</v>
+        <v>44.88390715582207</v>
       </c>
       <c r="AC9" t="n">
-        <v>46.12770252847479</v>
+        <v>44.19851836858642</v>
       </c>
       <c r="AD9" t="n">
-        <v>46.02980604480427</v>
+        <v>43.50692888326224</v>
       </c>
       <c r="AE9" t="n">
-        <v>45.9342470211758</v>
+        <v>42.83832370207461</v>
       </c>
       <c r="AF9" t="n">
-        <v>45.81302562716695</v>
+        <v>42.25196942088421</v>
       </c>
       <c r="AG9" t="n">
-        <v>45.68501560037969</v>
+        <v>41.67918285100919</v>
       </c>
       <c r="AH9" t="n">
-        <v>45.55232678122326</v>
+        <v>41.10317908138553</v>
       </c>
       <c r="AI9" t="n">
-        <v>45.41567744960653</v>
+        <v>40.52306218393755</v>
       </c>
       <c r="AJ9" t="n">
-        <v>45.27556544569953</v>
+        <v>39.9422765076534</v>
       </c>
       <c r="AK9" t="n">
-        <v>45.13193766973242</v>
+        <v>39.36455625472639</v>
       </c>
       <c r="AL9" t="n">
-        <v>44.98471688932641</v>
+        <v>38.79263199489552</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.772603</v>
+        <v>9.897479860350719</v>
       </c>
       <c r="C10" t="n">
-        <v>6.742385562189478</v>
+        <v>13.06311342790168</v>
       </c>
       <c r="D10" t="n">
-        <v>9.443867181147796</v>
+        <v>16.22538324752123</v>
       </c>
       <c r="E10" t="n">
-        <v>12.17409552443433</v>
+        <v>19.3832340365109</v>
       </c>
       <c r="F10" t="n">
-        <v>14.91883576810328</v>
+        <v>22.53558507660814</v>
       </c>
       <c r="G10" t="n">
-        <v>17.66696555740661</v>
+        <v>25.68163764841042</v>
       </c>
       <c r="H10" t="n">
-        <v>20.40518837810045</v>
+        <v>28.82290237279295</v>
       </c>
       <c r="I10" t="n">
-        <v>23.0854618797357</v>
+        <v>31.98077847217209</v>
       </c>
       <c r="J10" t="n">
-        <v>25.46494678833732</v>
+        <v>34.98983280615847</v>
       </c>
       <c r="K10" t="n">
-        <v>28.14278779300882</v>
+        <v>41.3202472500957</v>
       </c>
       <c r="L10" t="n">
-        <v>31.41712499771928</v>
+        <v>49.8127301348971</v>
       </c>
       <c r="M10" t="n">
-        <v>35.08286072818826</v>
+        <v>49.3852186680413</v>
       </c>
       <c r="N10" t="n">
-        <v>38.2071622065037</v>
+        <v>49.0287296017535</v>
       </c>
       <c r="O10" t="n">
-        <v>40.80082136065668</v>
+        <v>48.72066458881307</v>
       </c>
       <c r="P10" t="n">
-        <v>42.96178686388116</v>
+        <v>48.44121674108909</v>
       </c>
       <c r="Q10" t="n">
-        <v>44.78134476565633</v>
+        <v>48.1701112274948</v>
       </c>
       <c r="R10" t="n">
-        <v>46.33584508022105</v>
+        <v>47.91175367898879</v>
       </c>
       <c r="S10" t="n">
-        <v>47.58927224806572</v>
+        <v>47.67137932471213</v>
       </c>
       <c r="T10" t="n">
-        <v>48.27363460836148</v>
+        <v>47.44096200790815</v>
       </c>
       <c r="U10" t="n">
-        <v>48.38055889483341</v>
+        <v>47.21708284060707</v>
       </c>
       <c r="V10" t="n">
-        <v>48.1934213963317</v>
+        <v>47.00114766988083</v>
       </c>
       <c r="W10" t="n">
-        <v>47.84313867758479</v>
+        <v>46.80364379554368</v>
       </c>
       <c r="X10" t="n">
-        <v>47.34306264748182</v>
+        <v>46.63392270784097</v>
       </c>
       <c r="Y10" t="n">
-        <v>46.75430809054365</v>
+        <v>46.49466641954011</v>
       </c>
       <c r="Z10" t="n">
-        <v>46.1495940179727</v>
+        <v>46.38132587441114</v>
       </c>
       <c r="AA10" t="n">
-        <v>45.53455214971615</v>
+        <v>46.27889757209253</v>
       </c>
       <c r="AB10" t="n">
-        <v>44.88180803648409</v>
+        <v>46.18260863269298</v>
       </c>
       <c r="AC10" t="n">
-        <v>44.19589764890869</v>
+        <v>46.09600980869602</v>
       </c>
       <c r="AD10" t="n">
-        <v>43.50413902665835</v>
+        <v>46.01561806724645</v>
       </c>
       <c r="AE10" t="n">
-        <v>42.83568516483171</v>
+        <v>45.93940386683913</v>
       </c>
       <c r="AF10" t="n">
-        <v>42.24989583416663</v>
+        <v>45.83260629837454</v>
       </c>
       <c r="AG10" t="n">
-        <v>41.67741165628581</v>
+        <v>45.71731283032697</v>
       </c>
       <c r="AH10" t="n">
-        <v>41.10168713439932</v>
+        <v>45.59776877816819</v>
       </c>
       <c r="AI10" t="n">
-        <v>40.52190837566918</v>
+        <v>45.47483910319531</v>
       </c>
       <c r="AJ10" t="n">
-        <v>39.941533614442</v>
+        <v>45.34873183293207</v>
       </c>
       <c r="AK10" t="n">
-        <v>39.36429122491349</v>
+        <v>45.21848059734457</v>
       </c>
       <c r="AL10" t="n">
-        <v>38.79289897662358</v>
+        <v>45.08333601538179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.75.1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.120635</v>
+        <v>39.38696959311238</v>
       </c>
       <c r="C11" t="n">
-        <v>5.184893020146289</v>
+        <v>38.68019431031336</v>
       </c>
       <c r="D11" t="n">
-        <v>5.167931614661287</v>
+        <v>38.08407971198625</v>
       </c>
       <c r="E11" t="n">
-        <v>5.233322807625944</v>
+        <v>37.58730947729689</v>
       </c>
       <c r="F11" t="n">
-        <v>5.403057999023743</v>
+        <v>37.16509275575498</v>
       </c>
       <c r="G11" t="n">
-        <v>5.717285982511148</v>
+        <v>36.78611042197641</v>
       </c>
       <c r="H11" t="n">
-        <v>6.25935597480546</v>
+        <v>36.39114134596166</v>
       </c>
       <c r="I11" t="n">
-        <v>7.232576305401626</v>
+        <v>35.79486767796514</v>
       </c>
       <c r="J11" t="n">
-        <v>9.217558787020966</v>
+        <v>36.32988955804637</v>
       </c>
       <c r="K11" t="n">
-        <v>14.43214639117764</v>
+        <v>37.16276616558225</v>
       </c>
       <c r="L11" t="n">
-        <v>20.1251878865922</v>
+        <v>38.82789648560885</v>
       </c>
       <c r="M11" t="n">
-        <v>24.63730868219257</v>
+        <v>41.46580459363191</v>
       </c>
       <c r="N11" t="n">
-        <v>28.4875751512727</v>
+        <v>44.07032945615597</v>
       </c>
       <c r="O11" t="n">
-        <v>32.55345312562871</v>
+        <v>46.2485512648831</v>
       </c>
       <c r="P11" t="n">
-        <v>37.9837570743931</v>
+        <v>48.03899979888362</v>
       </c>
       <c r="Q11" t="n">
-        <v>44.49704870590677</v>
+        <v>49.51267850045812</v>
       </c>
       <c r="R11" t="n">
-        <v>47.9040918564676</v>
+        <v>50.68782297074985</v>
       </c>
       <c r="S11" t="n">
-        <v>49.11973925220926</v>
+        <v>51.39541195104482</v>
       </c>
       <c r="T11" t="n">
-        <v>49.7101513464662</v>
+        <v>51.46933521350319</v>
       </c>
       <c r="U11" t="n">
-        <v>49.85959814054113</v>
+        <v>51.13106146628174</v>
       </c>
       <c r="V11" t="n">
-        <v>49.60904923300191</v>
+        <v>50.72644490133323</v>
       </c>
       <c r="W11" t="n">
-        <v>49.05542877473051</v>
+        <v>50.38162102607344</v>
       </c>
       <c r="X11" t="n">
-        <v>48.35820531978283</v>
+        <v>50.10949534570673</v>
       </c>
       <c r="Y11" t="n">
-        <v>47.5656534960671</v>
+        <v>49.87368029908074</v>
       </c>
       <c r="Z11" t="n">
-        <v>46.70306351763428</v>
+        <v>49.64532747491522</v>
       </c>
       <c r="AA11" t="n">
-        <v>45.80367539515434</v>
+        <v>49.44436390305027</v>
       </c>
       <c r="AB11" t="n">
-        <v>44.90168935324535</v>
+        <v>49.26607854671228</v>
       </c>
       <c r="AC11" t="n">
-        <v>44.05192589807711</v>
+        <v>49.07482494096035</v>
       </c>
       <c r="AD11" t="n">
-        <v>43.33988097607647</v>
+        <v>48.86178419136757</v>
       </c>
       <c r="AE11" t="n">
-        <v>42.81707656715781</v>
+        <v>48.65430667310102</v>
       </c>
       <c r="AF11" t="n">
-        <v>42.70244119402566</v>
+        <v>48.52595708235083</v>
       </c>
       <c r="AG11" t="n">
-        <v>42.59173850794348</v>
+        <v>48.42109767240636</v>
       </c>
       <c r="AH11" t="n">
-        <v>42.48390753470559</v>
+        <v>48.32530602424593</v>
       </c>
       <c r="AI11" t="n">
-        <v>42.39320272189092</v>
+        <v>48.23404823998153</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42.33148112859441</v>
+        <v>48.14689545433684</v>
       </c>
       <c r="AK11" t="n">
-        <v>42.30802972846276</v>
+        <v>48.06645951858322</v>
       </c>
       <c r="AL11" t="n">
-        <v>42.32570134619775</v>
+        <v>47.99671059909667</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0.75.1</t>
+          <t>0.75.3</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43.76087</v>
+        <v>20.69439031689452</v>
       </c>
       <c r="C12" t="n">
-        <v>26.04787848961938</v>
+        <v>22.68826742510553</v>
       </c>
       <c r="D12" t="n">
-        <v>26.99358886950431</v>
+        <v>24.68542666139796</v>
       </c>
       <c r="E12" t="n">
-        <v>28.04451445087595</v>
+        <v>26.6869530482424</v>
       </c>
       <c r="F12" t="n">
-        <v>29.21617206741121</v>
+        <v>28.6940301918467</v>
       </c>
       <c r="G12" t="n">
-        <v>30.49800855993066</v>
+        <v>30.70684908859523</v>
       </c>
       <c r="H12" t="n">
-        <v>31.86434393165161</v>
+        <v>32.72470011754987</v>
       </c>
       <c r="I12" t="n">
-        <v>33.28753839643392</v>
+        <v>34.74504232307214</v>
       </c>
       <c r="J12" t="n">
-        <v>34.72206438674223</v>
+        <v>36.58693882365584</v>
       </c>
       <c r="K12" t="n">
-        <v>36.83544549696323</v>
+        <v>38.24834817025378</v>
       </c>
       <c r="L12" t="n">
-        <v>39.03730417226933</v>
+        <v>39.92904004559863</v>
       </c>
       <c r="M12" t="n">
-        <v>41.38529834439864</v>
+        <v>41.43149418818405</v>
       </c>
       <c r="N12" t="n">
-        <v>43.83523559924078</v>
+        <v>42.76174975587294</v>
       </c>
       <c r="O12" t="n">
-        <v>46.03485513682858</v>
+        <v>44.10109853357411</v>
       </c>
       <c r="P12" t="n">
-        <v>47.8681130508944</v>
+        <v>45.58507888425705</v>
       </c>
       <c r="Q12" t="n">
-        <v>49.3815632454317</v>
+        <v>46.90702359633548</v>
       </c>
       <c r="R12" t="n">
-        <v>50.60177037687082</v>
+        <v>47.1269787120852</v>
       </c>
       <c r="S12" t="n">
-        <v>51.360388457326</v>
+        <v>46.96727002131708</v>
       </c>
       <c r="T12" t="n">
-        <v>51.45990780798074</v>
+        <v>46.78109237661868</v>
       </c>
       <c r="U12" t="n">
-        <v>51.12383075539452</v>
+        <v>46.55570975349757</v>
       </c>
       <c r="V12" t="n">
-        <v>50.72097538565567</v>
+        <v>46.29291362599067</v>
       </c>
       <c r="W12" t="n">
-        <v>50.37911700749085</v>
+        <v>46.00670318182763</v>
       </c>
       <c r="X12" t="n">
-        <v>50.10882593429849</v>
+        <v>45.70803562781898</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.87326115229109</v>
+        <v>45.40059820478204</v>
       </c>
       <c r="Z12" t="n">
-        <v>49.64470805248325</v>
+        <v>45.07970714569157</v>
       </c>
       <c r="AA12" t="n">
-        <v>49.44347588444416</v>
+        <v>44.75617773526947</v>
       </c>
       <c r="AB12" t="n">
-        <v>49.26482797403543</v>
+        <v>44.45247444941146</v>
       </c>
       <c r="AC12" t="n">
-        <v>49.07326683094413</v>
+        <v>44.18340264312795</v>
       </c>
       <c r="AD12" t="n">
-        <v>48.86004598849495</v>
+        <v>43.98199056504696</v>
       </c>
       <c r="AE12" t="n">
-        <v>48.65243048058624</v>
+        <v>43.86626979544216</v>
       </c>
       <c r="AF12" t="n">
-        <v>48.52405002091347</v>
+        <v>43.8954554777448</v>
       </c>
       <c r="AG12" t="n">
-        <v>48.41911507669493</v>
+        <v>43.92700528282617</v>
       </c>
       <c r="AH12" t="n">
-        <v>48.3232671238735</v>
+        <v>43.96424151024311</v>
       </c>
       <c r="AI12" t="n">
-        <v>48.23197828805164</v>
+        <v>44.01019372132427</v>
       </c>
       <c r="AJ12" t="n">
-        <v>48.14481655419755</v>
+        <v>44.06488997057635</v>
       </c>
       <c r="AK12" t="n">
-        <v>48.06438859260853</v>
+        <v>44.12936265245271</v>
       </c>
       <c r="AL12" t="n">
-        <v>47.99465847361407</v>
+        <v>44.20375100864557</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0.75.3</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.70405</v>
+        <v>5.895955758820271</v>
       </c>
       <c r="C13" t="n">
-        <v>22.78782840107007</v>
+        <v>5.707820469240463</v>
       </c>
       <c r="D13" t="n">
-        <v>24.76619660838036</v>
+        <v>5.526576245259352</v>
       </c>
       <c r="E13" t="n">
-        <v>26.7442480043972</v>
+        <v>5.35194881987902</v>
       </c>
       <c r="F13" t="n">
-        <v>28.72081565832552</v>
+        <v>5.180868606036417</v>
       </c>
       <c r="G13" t="n">
-        <v>30.69370455849132</v>
+        <v>5.009456138638575</v>
       </c>
       <c r="H13" t="n">
-        <v>32.65946685300336</v>
+        <v>4.838573765652601</v>
       </c>
       <c r="I13" t="n">
-        <v>34.61319873164013</v>
+        <v>4.717993916527218</v>
       </c>
       <c r="J13" t="n">
-        <v>36.55043492169501</v>
+        <v>4.764919973761772</v>
       </c>
       <c r="K13" t="n">
-        <v>38.21114708285955</v>
+        <v>8.565556300919663</v>
       </c>
       <c r="L13" t="n">
-        <v>39.88883322970322</v>
+        <v>18.14856436450379</v>
       </c>
       <c r="M13" t="n">
-        <v>41.3928808900239</v>
+        <v>23.79324072362292</v>
       </c>
       <c r="N13" t="n">
-        <v>42.72872762564756</v>
+        <v>27.6812992764303</v>
       </c>
       <c r="O13" t="n">
-        <v>44.07804069282426</v>
+        <v>31.48994488483282</v>
       </c>
       <c r="P13" t="n">
-        <v>45.57815848267152</v>
+        <v>36.84649778737142</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.91197841928541</v>
+        <v>46.32016129655801</v>
       </c>
       <c r="R13" t="n">
-        <v>47.12659206491915</v>
+        <v>50.90930407891065</v>
       </c>
       <c r="S13" t="n">
-        <v>46.96585449240145</v>
+        <v>50.96901577773837</v>
       </c>
       <c r="T13" t="n">
-        <v>46.78015336918865</v>
+        <v>50.68486263415301</v>
       </c>
       <c r="U13" t="n">
-        <v>46.55509899329936</v>
+        <v>50.26007743579822</v>
       </c>
       <c r="V13" t="n">
-        <v>46.29248641459997</v>
+        <v>49.71537929708514</v>
       </c>
       <c r="W13" t="n">
-        <v>46.00634515444708</v>
+        <v>49.07481987223284</v>
       </c>
       <c r="X13" t="n">
-        <v>45.70770251265486</v>
+        <v>48.35539828021516</v>
       </c>
       <c r="Y13" t="n">
-        <v>45.40032496436849</v>
+        <v>47.56387571736213</v>
       </c>
       <c r="Z13" t="n">
-        <v>45.07951111383041</v>
+        <v>46.70486289270971</v>
       </c>
       <c r="AA13" t="n">
-        <v>44.75603358020075</v>
+        <v>45.80438631925966</v>
       </c>
       <c r="AB13" t="n">
-        <v>44.45233011786974</v>
+        <v>44.89788219960449</v>
       </c>
       <c r="AC13" t="n">
-        <v>44.18329743731998</v>
+        <v>44.04801256717416</v>
       </c>
       <c r="AD13" t="n">
-        <v>43.98204328846818</v>
+        <v>43.35312860440428</v>
       </c>
       <c r="AE13" t="n">
-        <v>43.86652046398672</v>
+        <v>42.86460616096873</v>
       </c>
       <c r="AF13" t="n">
-        <v>43.89585557496724</v>
+        <v>42.78042353531215</v>
       </c>
       <c r="AG13" t="n">
-        <v>43.92747043978092</v>
+        <v>42.67516668402828</v>
       </c>
       <c r="AH13" t="n">
-        <v>43.96474362516069</v>
+        <v>42.56235403569985</v>
       </c>
       <c r="AI13" t="n">
-        <v>44.01072670748176</v>
+        <v>42.46163053324358</v>
       </c>
       <c r="AJ13" t="n">
-        <v>44.06545541967496</v>
+        <v>42.38625197621774</v>
       </c>
       <c r="AK13" t="n">
-        <v>44.1299589809592</v>
+        <v>42.34598142011014</v>
       </c>
       <c r="AL13" t="n">
-        <v>44.20437250998094</v>
+        <v>42.34393258357737</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.75.2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.554054</v>
+        <v>6.983273374540343</v>
       </c>
       <c r="C14" t="n">
-        <v>3.970234269695089</v>
+        <v>6.900761547462926</v>
       </c>
       <c r="D14" t="n">
-        <v>3.913414901392776</v>
+        <v>6.923146861439101</v>
       </c>
       <c r="E14" t="n">
-        <v>3.879814929426592</v>
+        <v>7.08454577529236</v>
       </c>
       <c r="F14" t="n">
-        <v>3.870184190634042</v>
+        <v>7.427151831366819</v>
       </c>
       <c r="G14" t="n">
-        <v>3.887131850699631</v>
+        <v>8.019252348574421</v>
       </c>
       <c r="H14" t="n">
-        <v>3.936790496706615</v>
+        <v>9.013531619434005</v>
       </c>
       <c r="I14" t="n">
-        <v>4.029531830515119</v>
+        <v>10.76202877245274</v>
       </c>
       <c r="J14" t="n">
-        <v>4.193886128498258</v>
+        <v>14.33621664982689</v>
       </c>
       <c r="K14" t="n">
-        <v>5.167552209102475</v>
+        <v>17.72319508527309</v>
       </c>
       <c r="L14" t="n">
-        <v>6.546393043144861</v>
+        <v>20.55505148919481</v>
       </c>
       <c r="M14" t="n">
-        <v>8.258712018792588</v>
+        <v>23.21347487848464</v>
       </c>
       <c r="N14" t="n">
-        <v>10.24258496306072</v>
+        <v>26.36611738363092</v>
       </c>
       <c r="O14" t="n">
-        <v>12.51785865698777</v>
+        <v>30.5908547995651</v>
       </c>
       <c r="P14" t="n">
-        <v>15.15382666872597</v>
+        <v>34.18658306517985</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.38117587040242</v>
+        <v>35.77876042489289</v>
       </c>
       <c r="R14" t="n">
-        <v>18.91967494343168</v>
+        <v>36.65081553129881</v>
       </c>
       <c r="S14" t="n">
-        <v>20.50448890268419</v>
+        <v>37.20338163116417</v>
       </c>
       <c r="T14" t="n">
-        <v>22.06801109480529</v>
+        <v>37.46411210788394</v>
       </c>
       <c r="U14" t="n">
-        <v>23.46258761208776</v>
+        <v>37.45296155322941</v>
       </c>
       <c r="V14" t="n">
-        <v>24.86951812421212</v>
+        <v>37.23330458374372</v>
       </c>
       <c r="W14" t="n">
-        <v>26.50895540486844</v>
+        <v>36.94127933149787</v>
       </c>
       <c r="X14" t="n">
-        <v>27.30846259288729</v>
+        <v>36.60756633565236</v>
       </c>
       <c r="Y14" t="n">
-        <v>26.58423672196864</v>
+        <v>36.24615044551829</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.54043192990853</v>
+        <v>35.88684236869126</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.5063110530079</v>
+        <v>35.55827951682569</v>
       </c>
       <c r="AB14" t="n">
-        <v>23.47843544418684</v>
+        <v>35.26672316057716</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.44603994887835</v>
+        <v>34.98190893903525</v>
       </c>
       <c r="AD14" t="n">
-        <v>21.42577792784748</v>
+        <v>34.64574226673328</v>
       </c>
       <c r="AE14" t="n">
-        <v>20.45264710756068</v>
+        <v>34.19733024591962</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.58063436173431</v>
+        <v>33.48947457693603</v>
       </c>
       <c r="AG14" t="n">
-        <v>18.74443954449937</v>
+        <v>32.74978826733648</v>
       </c>
       <c r="AH14" t="n">
-        <v>17.91054257941729</v>
+        <v>32.00911305924451</v>
       </c>
       <c r="AI14" t="n">
-        <v>17.07341987710683</v>
+        <v>31.26482457007298</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.23600348430221</v>
+        <v>30.50764580146463</v>
       </c>
       <c r="AK14" t="n">
-        <v>15.40544952058173</v>
+        <v>29.72681957227628</v>
       </c>
       <c r="AL14" t="n">
-        <v>14.58948956723246</v>
+        <v>28.91319268337034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.38.2</t>
+          <t>0.38.3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.164865</v>
+        <v>14.33849752632064</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7383628018745154</v>
+        <v>15.4788402225509</v>
       </c>
       <c r="D15" t="n">
-        <v>1.004139979982479</v>
+        <v>16.65221000789008</v>
       </c>
       <c r="E15" t="n">
-        <v>1.287787901209829</v>
+        <v>17.84909556285423</v>
       </c>
       <c r="F15" t="n">
-        <v>1.590784483353774</v>
+        <v>19.06001118913785</v>
       </c>
       <c r="G15" t="n">
-        <v>1.914442181655084</v>
+        <v>20.28345659649408</v>
       </c>
       <c r="H15" t="n">
-        <v>2.260357241459245</v>
+        <v>21.5182865153311</v>
       </c>
       <c r="I15" t="n">
-        <v>2.631348730199145</v>
+        <v>22.72550841187969</v>
       </c>
       <c r="J15" t="n">
-        <v>3.038392323992182</v>
+        <v>24.0118232389704</v>
       </c>
       <c r="K15" t="n">
-        <v>3.877186184943046</v>
+        <v>25.36526385289788</v>
       </c>
       <c r="L15" t="n">
-        <v>4.938469668644903</v>
+        <v>27.04738384300028</v>
       </c>
       <c r="M15" t="n">
-        <v>6.199778815551579</v>
+        <v>28.25789440300827</v>
       </c>
       <c r="N15" t="n">
-        <v>7.696439820870166</v>
+        <v>29.10387127761758</v>
       </c>
       <c r="O15" t="n">
-        <v>9.481020224084162</v>
+        <v>29.78276331568614</v>
       </c>
       <c r="P15" t="n">
-        <v>11.3703474061295</v>
+        <v>30.35830250523214</v>
       </c>
       <c r="Q15" t="n">
-        <v>13.01961880926614</v>
+        <v>30.7964780764794</v>
       </c>
       <c r="R15" t="n">
-        <v>14.44737009683168</v>
+        <v>30.91050371709623</v>
       </c>
       <c r="S15" t="n">
-        <v>15.74376916233286</v>
+        <v>30.62828934670368</v>
       </c>
       <c r="T15" t="n">
-        <v>16.89287587079932</v>
+        <v>30.23500060241519</v>
       </c>
       <c r="U15" t="n">
-        <v>17.89688651089838</v>
+        <v>29.84550017918859</v>
       </c>
       <c r="V15" t="n">
-        <v>18.81995298483163</v>
+        <v>29.4981966580651</v>
       </c>
       <c r="W15" t="n">
-        <v>19.49185735585768</v>
+        <v>29.2226174169706</v>
       </c>
       <c r="X15" t="n">
-        <v>19.33417573695892</v>
+        <v>29.0044586627266</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.41232018778138</v>
+        <v>28.81841576771575</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.30659909779346</v>
+        <v>28.65108395039924</v>
       </c>
       <c r="AA15" t="n">
-        <v>16.20573645682061</v>
+        <v>28.50078495682966</v>
       </c>
       <c r="AB15" t="n">
-        <v>15.13951961980687</v>
+        <v>28.39658437908276</v>
       </c>
       <c r="AC15" t="n">
-        <v>14.12212973299624</v>
+        <v>28.37267658502637</v>
       </c>
       <c r="AD15" t="n">
-        <v>13.1977508717569</v>
+        <v>28.44257491849689</v>
       </c>
       <c r="AE15" t="n">
-        <v>12.38125137991545</v>
+        <v>28.57951325021025</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.69572921659731</v>
+        <v>28.77802456644498</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.00511316263293</v>
+        <v>28.97800297750215</v>
       </c>
       <c r="AH15" t="n">
-        <v>10.3186945328986</v>
+        <v>29.17763051804505</v>
       </c>
       <c r="AI15" t="n">
-        <v>9.642657443250251</v>
+        <v>29.38020774064942</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8.979737978571462</v>
+        <v>29.58871577458309</v>
       </c>
       <c r="AK15" t="n">
-        <v>8.330788541132993</v>
+        <v>29.80491981785665</v>
       </c>
       <c r="AL15" t="n">
-        <v>7.694628145296324</v>
+        <v>30.02933302282739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.38.3</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31.15211</v>
+        <v>4.897620564927206</v>
       </c>
       <c r="C16" t="n">
-        <v>12.43982229492576</v>
+        <v>4.663700804544428</v>
       </c>
       <c r="D16" t="n">
-        <v>13.97903962170888</v>
+        <v>4.443768795870614</v>
       </c>
       <c r="E16" t="n">
-        <v>15.52231748858738</v>
+        <v>4.236208062148417</v>
       </c>
       <c r="F16" t="n">
-        <v>17.06223726620678</v>
+        <v>4.039858173403052</v>
       </c>
       <c r="G16" t="n">
-        <v>18.59514233754301</v>
+        <v>3.85756529412004</v>
       </c>
       <c r="H16" t="n">
-        <v>20.11994731776964</v>
+        <v>3.702639691176311</v>
       </c>
       <c r="I16" t="n">
-        <v>21.63776101100851</v>
+        <v>3.61938975319742</v>
       </c>
       <c r="J16" t="n">
-        <v>23.15721322840479</v>
+        <v>4.259202081234545</v>
       </c>
       <c r="K16" t="n">
-        <v>24.4633827269874</v>
+        <v>5.609288587370719</v>
       </c>
       <c r="L16" t="n">
-        <v>25.99375501270293</v>
+        <v>7.259389706692135</v>
       </c>
       <c r="M16" t="n">
-        <v>27.16856585421496</v>
+        <v>9.0772232313057</v>
       </c>
       <c r="N16" t="n">
-        <v>28.00308216003014</v>
+        <v>11.04326012449706</v>
       </c>
       <c r="O16" t="n">
-        <v>28.74715647687576</v>
+        <v>13.19486552755365</v>
       </c>
       <c r="P16" t="n">
-        <v>29.46671501862959</v>
+        <v>15.59570282895816</v>
       </c>
       <c r="Q16" t="n">
-        <v>30.18791160423817</v>
+        <v>17.56558783091662</v>
       </c>
       <c r="R16" t="n">
-        <v>30.63844161905373</v>
+        <v>18.82757848152193</v>
       </c>
       <c r="S16" t="n">
-        <v>30.50370512311081</v>
+        <v>20.30173395525756</v>
       </c>
       <c r="T16" t="n">
-        <v>30.17417671273778</v>
+        <v>21.57226042380284</v>
       </c>
       <c r="U16" t="n">
-        <v>29.8211289842733</v>
+        <v>22.71556740112841</v>
       </c>
       <c r="V16" t="n">
-        <v>29.49197698709851</v>
+        <v>24.09874956656363</v>
       </c>
       <c r="W16" t="n">
-        <v>29.22040149998607</v>
+        <v>26.08983628261618</v>
       </c>
       <c r="X16" t="n">
-        <v>29.00018916211656</v>
+        <v>27.04070255880009</v>
       </c>
       <c r="Y16" t="n">
-        <v>28.81200228495918</v>
+        <v>26.32504340210934</v>
       </c>
       <c r="Z16" t="n">
-        <v>28.64384497997732</v>
+        <v>25.37013659886308</v>
       </c>
       <c r="AA16" t="n">
-        <v>28.49283030191714</v>
+        <v>24.40748084619981</v>
       </c>
       <c r="AB16" t="n">
-        <v>28.38781517857544</v>
+        <v>23.43274680545654</v>
       </c>
       <c r="AC16" t="n">
-        <v>28.36278207318695</v>
+        <v>22.43719448591779</v>
       </c>
       <c r="AD16" t="n">
-        <v>28.43062557398389</v>
+        <v>21.43544383144948</v>
       </c>
       <c r="AE16" t="n">
-        <v>28.56651081419083</v>
+        <v>20.46597585833221</v>
       </c>
       <c r="AF16" t="n">
-        <v>28.76684279141253</v>
+        <v>19.58465487061225</v>
       </c>
       <c r="AG16" t="n">
-        <v>28.96954770331371</v>
+        <v>18.73636327515442</v>
       </c>
       <c r="AH16" t="n">
-        <v>29.17269145629887</v>
+        <v>17.88986314869154</v>
       </c>
       <c r="AI16" t="n">
-        <v>29.37923563137265</v>
+        <v>17.03976540840705</v>
       </c>
       <c r="AJ16" t="n">
-        <v>29.59191310773671</v>
+        <v>16.18887075872919</v>
       </c>
       <c r="AK16" t="n">
-        <v>29.81231846728144</v>
+        <v>15.34403579340343</v>
       </c>
       <c r="AL16" t="n">
-        <v>30.04085579975755</v>
+        <v>14.51269949977345</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.38.2</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12.25</v>
+        <v>0.8067353623648429</v>
       </c>
       <c r="C17" t="n">
-        <v>17.26668963423637</v>
+        <v>0.996527043370206</v>
       </c>
       <c r="D17" t="n">
-        <v>18.29842894020815</v>
+        <v>1.19984097380685</v>
       </c>
       <c r="E17" t="n">
-        <v>19.33553649373899</v>
+        <v>1.417548579407745</v>
       </c>
       <c r="F17" t="n">
-        <v>20.37629513813237</v>
+        <v>1.650274026118721</v>
       </c>
       <c r="G17" t="n">
-        <v>21.41840701104019</v>
+        <v>1.898980357788876</v>
       </c>
       <c r="H17" t="n">
-        <v>22.46005519995176</v>
+        <v>2.165681456832366</v>
       </c>
       <c r="I17" t="n">
-        <v>23.49964089807863</v>
+        <v>2.455712856500158</v>
       </c>
       <c r="J17" t="n">
-        <v>24.54016777829444</v>
+        <v>3.036669378752727</v>
       </c>
       <c r="K17" t="n">
-        <v>25.59796771277609</v>
+        <v>3.874748117330183</v>
       </c>
       <c r="L17" t="n">
-        <v>26.65926360727123</v>
+        <v>4.939621529942122</v>
       </c>
       <c r="M17" t="n">
-        <v>27.69736429028521</v>
+        <v>6.208682304380111</v>
       </c>
       <c r="N17" t="n">
-        <v>28.68057654051392</v>
+        <v>7.715986038250798</v>
       </c>
       <c r="O17" t="n">
-        <v>29.57676161783853</v>
+        <v>9.509580122445895</v>
       </c>
       <c r="P17" t="n">
-        <v>30.37701434993448</v>
+        <v>11.40227263809347</v>
       </c>
       <c r="Q17" t="n">
-        <v>31.08749900985712</v>
+        <v>13.05693652207579</v>
       </c>
       <c r="R17" t="n">
-        <v>31.71146777794869</v>
+        <v>14.49180522289283</v>
       </c>
       <c r="S17" t="n">
-        <v>32.24217409895524</v>
+        <v>15.79345442201731</v>
       </c>
       <c r="T17" t="n">
-        <v>32.67438291445415</v>
+        <v>16.94486976248994</v>
       </c>
       <c r="U17" t="n">
-        <v>33.0087181805776</v>
+        <v>17.94565300074463</v>
       </c>
       <c r="V17" t="n">
-        <v>33.24270386629833</v>
+        <v>18.85282975887032</v>
       </c>
       <c r="W17" t="n">
-        <v>33.38485642559138</v>
+        <v>19.49583541896017</v>
       </c>
       <c r="X17" t="n">
-        <v>33.46231096938727</v>
+        <v>19.32550195449398</v>
       </c>
       <c r="Y17" t="n">
-        <v>33.4942574057423</v>
+        <v>18.40855131720682</v>
       </c>
       <c r="Z17" t="n">
-        <v>33.47703273849884</v>
+        <v>17.30553172130501</v>
       </c>
       <c r="AA17" t="n">
-        <v>33.41405151858697</v>
+        <v>16.20543351781691</v>
       </c>
       <c r="AB17" t="n">
-        <v>33.3157855906202</v>
+        <v>15.13941124861719</v>
       </c>
       <c r="AC17" t="n">
-        <v>33.17976475526559</v>
+        <v>14.1219315092881</v>
       </c>
       <c r="AD17" t="n">
-        <v>33.01426195118492</v>
+        <v>13.19751351118241</v>
       </c>
       <c r="AE17" t="n">
-        <v>32.82986860405993</v>
+        <v>12.38104400189297</v>
       </c>
       <c r="AF17" t="n">
-        <v>32.57854621894961</v>
+        <v>11.69555868545538</v>
       </c>
       <c r="AG17" t="n">
-        <v>32.32537153217987</v>
+        <v>11.00495608651892</v>
       </c>
       <c r="AH17" t="n">
-        <v>32.06792546245821</v>
+        <v>10.31854245503578</v>
       </c>
       <c r="AI17" t="n">
-        <v>31.80500833601794</v>
+        <v>9.642508675047255</v>
       </c>
       <c r="AJ17" t="n">
-        <v>31.53600784045796</v>
+        <v>8.979593716419222</v>
       </c>
       <c r="AK17" t="n">
-        <v>31.26199015339047</v>
+        <v>8.330651327034658</v>
       </c>
       <c r="AL17" t="n">
-        <v>30.98476168790144</v>
+        <v>7.694500798582012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16.25843293164631</v>
+      </c>
+      <c r="C18" t="n">
+        <v>17.2766151149838</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18.3013920947224</v>
+      </c>
+      <c r="E18" t="n">
+        <v>19.33315588761059</v>
+      </c>
+      <c r="F18" t="n">
+        <v>20.37004388556529</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.4093934617336</v>
+      </c>
+      <c r="H18" t="n">
+        <v>22.44904017649366</v>
+      </c>
+      <c r="I18" t="n">
+        <v>23.48721355329419</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.53918348108497</v>
+      </c>
+      <c r="K18" t="n">
+        <v>25.59748806567373</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.65899168608197</v>
+      </c>
+      <c r="M18" t="n">
+        <v>27.69718432623549</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28.68025051209442</v>
+      </c>
+      <c r="O18" t="n">
+        <v>29.57583363164969</v>
+      </c>
+      <c r="P18" t="n">
+        <v>30.37535311767387</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>31.08527084546132</v>
+      </c>
+      <c r="R18" t="n">
+        <v>31.70890696888601</v>
+      </c>
+      <c r="S18" t="n">
+        <v>32.23957077653595</v>
+      </c>
+      <c r="T18" t="n">
+        <v>32.6722122267735</v>
+      </c>
+      <c r="U18" t="n">
+        <v>33.00747135418194</v>
+      </c>
+      <c r="V18" t="n">
+        <v>33.24243616785144</v>
+      </c>
+      <c r="W18" t="n">
+        <v>33.38499081271684</v>
+      </c>
+      <c r="X18" t="n">
+        <v>33.4623249395949</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>33.49407445719677</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>33.4766744956114</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>33.41356865153796</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>33.31525213798925</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>33.17921742200983</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>33.01371043051154</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>32.82932282315163</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>32.57806218843001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>32.32496100531635</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>32.06759980788343</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>31.80477576836436</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>31.53587473983611</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>31.26196020328</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>30.98483581117499</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>0.094</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>9.218919</v>
-      </c>
-      <c r="C18" t="n">
-        <v>5.124967995559309</v>
-      </c>
-      <c r="D18" t="n">
-        <v>6.050786169806373</v>
-      </c>
-      <c r="E18" t="n">
-        <v>6.989018090788802</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7.944765174150591</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8.912093300229339</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9.882663361029923</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.84927359807047</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11.80859710453251</v>
-      </c>
-      <c r="K18" t="n">
-        <v>13.03502545123697</v>
-      </c>
-      <c r="L18" t="n">
-        <v>14.50581033913512</v>
-      </c>
-      <c r="M18" t="n">
-        <v>16.19821877754703</v>
-      </c>
-      <c r="N18" t="n">
-        <v>18.06917416073146</v>
-      </c>
-      <c r="O18" t="n">
-        <v>20.0038055852124</v>
-      </c>
-      <c r="P18" t="n">
-        <v>20.97828860061442</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>20.61912158801414</v>
-      </c>
-      <c r="R18" t="n">
-        <v>20.42192404640803</v>
-      </c>
-      <c r="S18" t="n">
-        <v>20.90509828012074</v>
-      </c>
-      <c r="T18" t="n">
-        <v>21.7029535903798</v>
-      </c>
-      <c r="U18" t="n">
-        <v>22.45303230568089</v>
-      </c>
-      <c r="V18" t="n">
-        <v>22.71913794404298</v>
-      </c>
-      <c r="W18" t="n">
-        <v>22.31763567731337</v>
-      </c>
-      <c r="X18" t="n">
-        <v>22.0956738497656</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>22.26886792875764</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>21.93964382472404</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>21.20793134265844</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>20.307842827665</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>19.35037156012171</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18.38284438108582</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>17.46393380625316</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17.10069426006302</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>16.72785561199995</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>16.37685938463441</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>16.08140159970897</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>15.86171668729515</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>15.72940595783296</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>15.68154327080633</v>
+      <c r="B19" t="n">
+        <v>6.085108737558086</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.714058371314732</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7.362583198196823</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8.028518026631422</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.715035863533004</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9.416577563626694</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.12880128563038</v>
+      </c>
+      <c r="I19" t="n">
+        <v>10.87287797078926</v>
+      </c>
+      <c r="J19" t="n">
+        <v>11.84957461165018</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13.04372022842822</v>
+      </c>
+      <c r="L19" t="n">
+        <v>14.48611158039151</v>
+      </c>
+      <c r="M19" t="n">
+        <v>16.16012200571176</v>
+      </c>
+      <c r="N19" t="n">
+        <v>18.01289225799083</v>
+      </c>
+      <c r="O19" t="n">
+        <v>19.92177813831406</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20.86019031481458</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>20.50597262032536</v>
+      </c>
+      <c r="R19" t="n">
+        <v>20.33363856835242</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20.82014627899716</v>
+      </c>
+      <c r="T19" t="n">
+        <v>21.60831141447843</v>
+      </c>
+      <c r="U19" t="n">
+        <v>22.35109185821797</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22.62302723036066</v>
+      </c>
+      <c r="W19" t="n">
+        <v>22.2410075813406</v>
+      </c>
+      <c r="X19" t="n">
+        <v>22.04010245967075</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>22.21596056212213</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21.89076270419992</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>21.16801350100195</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20.2797452205376</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>19.3343992284947</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>18.37522667961967</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>17.459725852213</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17.09725585731206</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16.725574417107</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>16.37597601853521</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>16.08204005225642</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>15.86394181132146</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>15.73324227330329</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>15.6869736810899</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,115 +2800,115 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.37741057344263</v>
+        <v>17.00702484163679</v>
       </c>
       <c r="C2" t="n">
-        <v>21.7474471809553</v>
+        <v>17.79446433545673</v>
       </c>
       <c r="D2" t="n">
-        <v>21.76408958270174</v>
+        <v>18.54066989954327</v>
       </c>
       <c r="E2" t="n">
-        <v>21.78613931096429</v>
+        <v>19.2566315605953</v>
       </c>
       <c r="F2" t="n">
-        <v>21.8133182450156</v>
+        <v>19.95388577879271</v>
       </c>
       <c r="G2" t="n">
-        <v>21.84282225954429</v>
+        <v>20.63437669868915</v>
       </c>
       <c r="H2" t="n">
-        <v>21.86598175134331</v>
+        <v>21.27150999635149</v>
       </c>
       <c r="I2" t="n">
-        <v>21.87968793811289</v>
+        <v>21.72109842030006</v>
       </c>
       <c r="J2" t="n">
-        <v>21.89292457416693</v>
+        <v>21.81168604640611</v>
       </c>
       <c r="K2" t="n">
-        <v>21.93353740678399</v>
+        <v>21.88611907057738</v>
       </c>
       <c r="L2" t="n">
-        <v>22.01262469262853</v>
+        <v>21.99547228166952</v>
       </c>
       <c r="M2" t="n">
-        <v>22.09414393477639</v>
+        <v>22.09717782746957</v>
       </c>
       <c r="N2" t="n">
-        <v>22.0907491052804</v>
+        <v>22.09999109989644</v>
       </c>
       <c r="O2" t="n">
-        <v>21.94401263540777</v>
+        <v>21.9533661401682</v>
       </c>
       <c r="P2" t="n">
-        <v>21.63256656288042</v>
+        <v>21.64011413212681</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.15464977419397</v>
+        <v>21.16059822070116</v>
       </c>
       <c r="R2" t="n">
-        <v>20.51457308696539</v>
+        <v>20.51843748176545</v>
       </c>
       <c r="S2" t="n">
-        <v>19.74837183849549</v>
+        <v>19.74981585185212</v>
       </c>
       <c r="T2" t="n">
-        <v>18.90540953192469</v>
+        <v>18.90500151843258</v>
       </c>
       <c r="U2" t="n">
-        <v>17.998813188849</v>
+        <v>17.99751190457874</v>
       </c>
       <c r="V2" t="n">
-        <v>17.08786566560391</v>
+        <v>17.08551535013616</v>
       </c>
       <c r="W2" t="n">
-        <v>16.21244499832756</v>
+        <v>16.20910046971272</v>
       </c>
       <c r="X2" t="n">
-        <v>15.44043699806549</v>
+        <v>15.43660275381878</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.82568395045654</v>
+        <v>14.8217106364857</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.38720093530845</v>
+        <v>14.38357290047544</v>
       </c>
       <c r="AA2" t="n">
-        <v>14.1271469588379</v>
+        <v>14.12427893195012</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.0259847501675</v>
+        <v>14.02397609295476</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.06658318303443</v>
+        <v>14.0652451013718</v>
       </c>
       <c r="AD2" t="n">
-        <v>14.1791362670889</v>
+        <v>14.17832747754122</v>
       </c>
       <c r="AE2" t="n">
-        <v>14.28386014576889</v>
+        <v>14.28343590342282</v>
       </c>
       <c r="AF2" t="n">
-        <v>14.23476835350475</v>
+        <v>14.23445347731017</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.17023295655885</v>
+        <v>14.16998938558001</v>
       </c>
       <c r="AH2" t="n">
-        <v>14.09887214345896</v>
+        <v>14.09871602297305</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.0187316940115</v>
+        <v>14.01868077468806</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13.9283690411809</v>
+        <v>13.92843473920215</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.82521816676243</v>
+        <v>13.82540424362587</v>
       </c>
       <c r="AL2" t="n">
-        <v>13.70764372280019</v>
+        <v>13.70794710276031</v>
       </c>
     </row>
     <row r="3">
@@ -2800,115 +2918,115 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03581679895107</v>
+        <v>-0.1713556453471823</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.15984724084715</v>
+        <v>-0.0757430147032889</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04426607645369</v>
+        <v>0.02328342707516614</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07313698520551</v>
+        <v>0.1251798086877141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.19142055939148</v>
+        <v>0.2291173485109823</v>
       </c>
       <c r="G3" t="n">
-        <v>0.30944030844812</v>
+        <v>0.3342237515743048</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4262227054936401</v>
+        <v>0.4400217954472839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.54186570711743</v>
+        <v>0.5494938504355513</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6610977110826399</v>
+        <v>0.6555519348032189</v>
       </c>
       <c r="K3" t="n">
-        <v>0.73700069739049</v>
+        <v>0.7297025450716247</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8024998922780799</v>
+        <v>0.7941177683946146</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8957936011882199</v>
+        <v>0.8867501409193823</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0305461066501</v>
+        <v>1.020870608986817</v>
       </c>
       <c r="O3" t="n">
-        <v>1.17138541323494</v>
+        <v>1.161108246954358</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27213098846647</v>
+        <v>1.261995118801671</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.32572899582335</v>
+        <v>1.31702185807219</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37684327032488</v>
+        <v>1.370712389016999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.47389906230446</v>
+        <v>1.471322960111025</v>
       </c>
       <c r="T3" t="n">
-        <v>1.64333859379014</v>
+        <v>1.644756819853582</v>
       </c>
       <c r="U3" t="n">
-        <v>1.85433254285214</v>
+        <v>1.859327958790865</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06688367383659</v>
+        <v>2.074399499909105</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22858934339364</v>
+        <v>2.238156773653063</v>
       </c>
       <c r="X3" t="n">
-        <v>2.31023234486593</v>
+        <v>2.321240705944465</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35172236914829</v>
+        <v>2.362951584219664</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.36987555451669</v>
+        <v>2.379342837248758</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.35183279363562</v>
+        <v>2.357903623781229</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.26286367386211</v>
+        <v>2.265573665297983</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.07429170940501</v>
+        <v>2.074325817287052</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.79851261868582</v>
+        <v>1.796903431492745</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.48103268920811</v>
+        <v>1.478159974524172</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.20116884126805</v>
+        <v>1.197609636852326</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.92515957201981</v>
+        <v>0.921230372992824</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.64736402684787</v>
+        <v>0.643529919715938</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.37057438666256</v>
+        <v>0.3672687926580535</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.09826362248381</v>
+        <v>0.09586389309731375</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.16657817152169</v>
+        <v>-0.1677559983085361</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.42201497910202</v>
+        <v>-0.4217149142897931</v>
       </c>
     </row>
     <row r="4">
@@ -2918,115 +3036,115 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.34534073022172</v>
+        <v>13.51289130487</v>
       </c>
       <c r="C4" t="n">
-        <v>13.40786444582871</v>
+        <v>14.33442002709932</v>
       </c>
       <c r="D4" t="n">
-        <v>14.35825557524247</v>
+        <v>15.15674214261302</v>
       </c>
       <c r="E4" t="n">
-        <v>15.29771771625615</v>
+        <v>15.97485755419229</v>
       </c>
       <c r="F4" t="n">
-        <v>16.22761274503157</v>
+        <v>16.78778476801181</v>
       </c>
       <c r="G4" t="n">
-        <v>17.14997135293033</v>
+        <v>17.6014325328664</v>
       </c>
       <c r="H4" t="n">
-        <v>18.0675532295756</v>
+        <v>18.43446167627649</v>
       </c>
       <c r="I4" t="n">
-        <v>18.98103336788544</v>
+        <v>19.32538858826613</v>
       </c>
       <c r="J4" t="n">
-        <v>19.8771248649682</v>
+        <v>20.15151098278522</v>
       </c>
       <c r="K4" t="n">
-        <v>20.46079022533457</v>
+        <v>20.76039980869833</v>
       </c>
       <c r="L4" t="n">
-        <v>20.59799437470664</v>
+        <v>20.95905371543519</v>
       </c>
       <c r="M4" t="n">
-        <v>20.52484976463862</v>
+        <v>20.88581083822673</v>
       </c>
       <c r="N4" t="n">
-        <v>20.44159419814127</v>
+        <v>20.74149011024501</v>
       </c>
       <c r="O4" t="n">
-        <v>20.2624238028459</v>
+        <v>20.51454235926535</v>
       </c>
       <c r="P4" t="n">
-        <v>19.98759530296046</v>
+        <v>20.19923517626368</v>
       </c>
       <c r="Q4" t="n">
-        <v>19.57387591543294</v>
+        <v>19.73824889627338</v>
       </c>
       <c r="R4" t="n">
-        <v>18.95664015128587</v>
+        <v>19.07247087582691</v>
       </c>
       <c r="S4" t="n">
-        <v>18.22818876636438</v>
+        <v>18.30097485019418</v>
       </c>
       <c r="T4" t="n">
-        <v>17.47649301315304</v>
+        <v>17.50364823830209</v>
       </c>
       <c r="U4" t="n">
-        <v>16.81097322119229</v>
+        <v>16.79832130762444</v>
       </c>
       <c r="V4" t="n">
-        <v>16.19747137121765</v>
+        <v>16.1742927755954</v>
       </c>
       <c r="W4" t="n">
-        <v>15.61913774040216</v>
+        <v>15.59790973705312</v>
       </c>
       <c r="X4" t="n">
-        <v>15.0935912342528</v>
+        <v>15.07169211280458</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.62180436021654</v>
+        <v>14.59890121270745</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.19862458064144</v>
+        <v>14.17685341846876</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.85270712991771</v>
+        <v>13.83374924168691</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.61336540554598</v>
+        <v>13.59778545726038</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.46273601998969</v>
+        <v>13.45118326583718</v>
       </c>
       <c r="AD4" t="n">
-        <v>13.36354381323436</v>
+        <v>13.35634882550925</v>
       </c>
       <c r="AE4" t="n">
-        <v>13.33719622963148</v>
+        <v>13.33358917944572</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.45461335434987</v>
+        <v>13.45267276554241</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.59409069527734</v>
+        <v>13.59328795634218</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.73664155931068</v>
+        <v>13.7366372230378</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.87901262568878</v>
+        <v>13.87958529545092</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.02279060995212</v>
+        <v>14.02377863244647</v>
       </c>
       <c r="AK4" t="n">
-        <v>14.17250079532628</v>
+        <v>14.17378620933799</v>
       </c>
       <c r="AL4" t="n">
-        <v>14.3329953879658</v>
+        <v>14.33448696589164</v>
       </c>
     </row>
     <row r="5">
@@ -3036,115 +3154,115 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8515621032983</v>
+        <v>8.76160102588817</v>
       </c>
       <c r="C5" t="n">
-        <v>11.84931001520035</v>
+        <v>9.370468959077231</v>
       </c>
       <c r="D5" t="n">
-        <v>12.20920377829373</v>
+        <v>9.98442109587049</v>
       </c>
       <c r="E5" t="n">
-        <v>12.57057446964454</v>
+        <v>10.60355498102265</v>
       </c>
       <c r="F5" t="n">
-        <v>12.94841175802449</v>
+        <v>11.22680423713443</v>
       </c>
       <c r="G5" t="n">
-        <v>13.34958209128886</v>
+        <v>11.84912486436382</v>
       </c>
       <c r="H5" t="n">
-        <v>13.76818937792581</v>
+        <v>12.45776259850671</v>
       </c>
       <c r="I5" t="n">
-        <v>14.18509072123755</v>
+        <v>13.03982561466296</v>
       </c>
       <c r="J5" t="n">
-        <v>14.50226000920175</v>
+        <v>13.66879500531025</v>
       </c>
       <c r="K5" t="n">
-        <v>14.73568097579991</v>
+        <v>14.28613599142683</v>
       </c>
       <c r="L5" t="n">
-        <v>15.03732725747204</v>
+        <v>14.85715944732257</v>
       </c>
       <c r="M5" t="n">
-        <v>15.43535162898641</v>
+        <v>15.38094924798162</v>
       </c>
       <c r="N5" t="n">
-        <v>15.84677873801777</v>
+        <v>15.8324958989488</v>
       </c>
       <c r="O5" t="n">
-        <v>16.2105478869391</v>
+        <v>16.20480504242408</v>
       </c>
       <c r="P5" t="n">
-        <v>16.54708327420341</v>
+        <v>16.54370355044883</v>
       </c>
       <c r="Q5" t="n">
-        <v>16.86462506113895</v>
+        <v>16.86333419497273</v>
       </c>
       <c r="R5" t="n">
-        <v>17.15209031644942</v>
+        <v>17.15195556518281</v>
       </c>
       <c r="S5" t="n">
-        <v>17.37784317894474</v>
+        <v>17.37831900144238</v>
       </c>
       <c r="T5" t="n">
-        <v>17.53083903276096</v>
+        <v>17.53147976087843</v>
       </c>
       <c r="U5" t="n">
-        <v>17.63792295569587</v>
+        <v>17.63845876868518</v>
       </c>
       <c r="V5" t="n">
-        <v>17.71558130932709</v>
+        <v>17.71602533544196</v>
       </c>
       <c r="W5" t="n">
-        <v>17.74791374243773</v>
+        <v>17.74825930394371</v>
       </c>
       <c r="X5" t="n">
-        <v>17.7191716032345</v>
+        <v>17.71940442161386</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.63905058378615</v>
+        <v>17.63916607534699</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.52328670232829</v>
+        <v>17.52329423469905</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.3833975430549</v>
+        <v>17.3833551220952</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.23794242062066</v>
+        <v>17.23789462133814</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.10065442033395</v>
+        <v>17.10069036066129</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.98106596951487</v>
+        <v>16.98134186639507</v>
       </c>
       <c r="AE5" t="n">
-        <v>16.89869819945501</v>
+        <v>16.89926011517694</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.92923367038617</v>
+        <v>16.92996867215897</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.997349911072</v>
+        <v>16.99810759131452</v>
       </c>
       <c r="AH5" t="n">
-        <v>17.07779339708997</v>
+        <v>17.07852175953382</v>
       </c>
       <c r="AI5" t="n">
-        <v>17.16496840193913</v>
+        <v>17.16566011324299</v>
       </c>
       <c r="AJ5" t="n">
-        <v>17.25604681911585</v>
+        <v>17.25670911736738</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.35323121444154</v>
+        <v>17.35385931084863</v>
       </c>
       <c r="AL5" t="n">
-        <v>17.46147455585514</v>
+        <v>17.46204842618467</v>
       </c>
     </row>
     <row r="6">
@@ -3154,115 +3272,115 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.35755626297589</v>
+        <v>1.311424890330565</v>
       </c>
       <c r="C6" t="n">
-        <v>16.92014913416581</v>
+        <v>3.73557378075712</v>
       </c>
       <c r="D6" t="n">
-        <v>17.43145426423156</v>
+        <v>6.109661698313563</v>
       </c>
       <c r="E6" t="n">
-        <v>17.95069986444343</v>
+        <v>8.429739457493632</v>
       </c>
       <c r="F6" t="n">
-        <v>18.48003575449557</v>
+        <v>10.70614879095642</v>
       </c>
       <c r="G6" t="n">
-        <v>19.02125098396675</v>
+        <v>12.96892386171469</v>
       </c>
       <c r="H6" t="n">
-        <v>19.56875620646867</v>
+        <v>15.30584743325667</v>
       </c>
       <c r="I6" t="n">
-        <v>20.11522436558819</v>
+        <v>17.95909582175605</v>
       </c>
       <c r="J6" t="n">
-        <v>20.6521942320935</v>
+        <v>19.8601779781599</v>
       </c>
       <c r="K6" t="n">
-        <v>21.21874788581784</v>
+        <v>21.03547416557655</v>
       </c>
       <c r="L6" t="n">
-        <v>21.78105528955673</v>
+        <v>21.76421992645707</v>
       </c>
       <c r="M6" t="n">
-        <v>22.1562430599376</v>
+        <v>22.20748213904985</v>
       </c>
       <c r="N6" t="n">
-        <v>22.17863075614247</v>
+        <v>22.25985148354964</v>
       </c>
       <c r="O6" t="n">
-        <v>21.89892540863413</v>
+        <v>21.99600595740036</v>
       </c>
       <c r="P6" t="n">
-        <v>21.48763061891744</v>
+        <v>21.59053374092803</v>
       </c>
       <c r="Q6" t="n">
-        <v>21.05635194367256</v>
+        <v>21.15537070482345</v>
       </c>
       <c r="R6" t="n">
-        <v>20.65326951944667</v>
+        <v>20.74337480133067</v>
       </c>
       <c r="S6" t="n">
-        <v>20.25964848022899</v>
+        <v>20.34116379824189</v>
       </c>
       <c r="T6" t="n">
-        <v>19.78838530179654</v>
+        <v>19.86304026608042</v>
       </c>
       <c r="U6" t="n">
-        <v>19.18935737040941</v>
+        <v>19.2571091707524</v>
       </c>
       <c r="V6" t="n">
-        <v>18.58747208000335</v>
+        <v>18.63703310541131</v>
       </c>
       <c r="W6" t="n">
-        <v>18.20818508436263</v>
+        <v>18.229605776602</v>
       </c>
       <c r="X6" t="n">
-        <v>18.06588923828365</v>
+        <v>18.07182926372741</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.02594651367462</v>
+        <v>18.03224817135393</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.97364617080623</v>
+        <v>17.98238879826621</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.88025287395741</v>
+        <v>17.88934079164071</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.78467073311642</v>
+        <v>17.79165691519395</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.71669622732139</v>
+        <v>17.72170397309356</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.64938655181844</v>
+        <v>17.65298319592109</v>
       </c>
       <c r="AE6" t="n">
-        <v>17.59348467246231</v>
+        <v>17.5956408160111</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.6414995264807</v>
+        <v>17.64274991744101</v>
       </c>
       <c r="AG6" t="n">
-        <v>17.69264817978535</v>
+        <v>17.69298670264181</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.74831397810387</v>
+        <v>17.74774628287911</v>
       </c>
       <c r="AI6" t="n">
-        <v>17.80975237671818</v>
+        <v>17.80829532245935</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17.87616335266047</v>
+        <v>17.87383985290143</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.94646075836115</v>
+        <v>17.94329342975464</v>
       </c>
       <c r="AL6" t="n">
-        <v>18.01903008581389</v>
+        <v>18.01503860619093</v>
       </c>
     </row>
     <row r="7">
@@ -3272,115 +3390,115 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.25584597328538</v>
+        <v>13.44518923100246</v>
       </c>
       <c r="C7" t="n">
-        <v>14.63805496115414</v>
+        <v>14.42691652825058</v>
       </c>
       <c r="D7" t="n">
-        <v>15.54525069760765</v>
+        <v>15.39257076231459</v>
       </c>
       <c r="E7" t="n">
-        <v>16.43254020196094</v>
+        <v>16.34030924421558</v>
       </c>
       <c r="F7" t="n">
-        <v>17.29768435764659</v>
+        <v>17.2671355484617</v>
       </c>
       <c r="G7" t="n">
-        <v>18.14188540510641</v>
+        <v>18.17454565246335</v>
       </c>
       <c r="H7" t="n">
-        <v>18.96552429650731</v>
+        <v>19.06311762483082</v>
       </c>
       <c r="I7" t="n">
-        <v>19.76409176254462</v>
+        <v>19.9258913434679</v>
       </c>
       <c r="J7" t="n">
-        <v>20.5247486746955</v>
+        <v>20.53008670725961</v>
       </c>
       <c r="K7" t="n">
-        <v>21.00367099557938</v>
+        <v>21.00752791255196</v>
       </c>
       <c r="L7" t="n">
-        <v>21.40039218283846</v>
+        <v>21.40121834343644</v>
       </c>
       <c r="M7" t="n">
-        <v>21.68923755550265</v>
+        <v>21.68619568144596</v>
       </c>
       <c r="N7" t="n">
-        <v>21.72109175906094</v>
+        <v>21.73215924923333</v>
       </c>
       <c r="O7" t="n">
-        <v>21.22354962119354</v>
+        <v>21.30684806021316</v>
       </c>
       <c r="P7" t="n">
-        <v>20.08758962826388</v>
+        <v>20.27851634880352</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.59341799747228</v>
+        <v>18.84549438426432</v>
       </c>
       <c r="R7" t="n">
-        <v>17.13761774225797</v>
+        <v>17.38208797250866</v>
       </c>
       <c r="S7" t="n">
-        <v>15.75251924603664</v>
+        <v>15.96156207629469</v>
       </c>
       <c r="T7" t="n">
-        <v>14.2940199920701</v>
+        <v>14.47429210239854</v>
       </c>
       <c r="U7" t="n">
-        <v>12.66121910800322</v>
+        <v>12.84454968503098</v>
       </c>
       <c r="V7" t="n">
-        <v>10.92493876677527</v>
+        <v>11.1364355593825</v>
       </c>
       <c r="W7" t="n">
-        <v>9.21457485387057</v>
+        <v>9.426876946655446</v>
       </c>
       <c r="X7" t="n">
-        <v>7.841954547266091</v>
+        <v>7.978812411973762</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.89511131569417</v>
+        <v>6.955130190270135</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.21136690386225</v>
+        <v>6.233120356692327</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.68319096107792</v>
+        <v>5.682773409782202</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.282488457268119</v>
+        <v>5.26882119163634</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.964796592593681</v>
+        <v>4.939675897696183</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.72189299120313</v>
+        <v>4.687284613546555</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.56228374172929</v>
+        <v>4.522212137866339</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.57275787776938</v>
+        <v>4.534131495915542</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.58490373261625</v>
+        <v>4.54705317285142</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.59954863715161</v>
+        <v>4.561853551433503</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.62033271582674</v>
+        <v>4.583108367983592</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.64904170719842</v>
+        <v>4.613154640068799</v>
       </c>
       <c r="AK7" t="n">
-        <v>4.68632071596607</v>
+        <v>4.652862046865688</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.73245569461013</v>
+        <v>4.702539032376191</v>
       </c>
     </row>
     <row r="8">
@@ -3390,115 +3508,115 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.10927060768256</v>
+        <v>0.3758040603449068</v>
       </c>
       <c r="C8" t="n">
-        <v>2.57634221125989</v>
+        <v>1.090449100787796</v>
       </c>
       <c r="D8" t="n">
-        <v>3.05199613184565</v>
+        <v>1.791742398785234</v>
       </c>
       <c r="E8" t="n">
-        <v>3.52425164057815</v>
+        <v>2.481562144980784</v>
       </c>
       <c r="F8" t="n">
-        <v>3.99577706594399</v>
+        <v>3.165217109936715</v>
       </c>
       <c r="G8" t="n">
-        <v>4.46767228955007</v>
+        <v>3.851049294933884</v>
       </c>
       <c r="H8" t="n">
-        <v>4.93883413488955</v>
+        <v>4.55277244440706</v>
       </c>
       <c r="I8" t="n">
-        <v>5.40418745792123</v>
+        <v>5.273507172288963</v>
       </c>
       <c r="J8" t="n">
-        <v>5.8519766083003</v>
+        <v>5.815428824029547</v>
       </c>
       <c r="K8" t="n">
-        <v>6.28522691666346</v>
+        <v>6.279329718274888</v>
       </c>
       <c r="L8" t="n">
-        <v>6.729288337611659</v>
+        <v>6.728540118904128</v>
       </c>
       <c r="M8" t="n">
-        <v>7.190864082774031</v>
+        <v>7.192279932203409</v>
       </c>
       <c r="N8" t="n">
-        <v>7.67716394733553</v>
+        <v>7.682434811864451</v>
       </c>
       <c r="O8" t="n">
-        <v>8.1947660797822</v>
+        <v>8.204458150731156</v>
       </c>
       <c r="P8" t="n">
-        <v>8.72617566671458</v>
+        <v>8.738943957891699</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.230511092064059</v>
+        <v>9.244978190842987</v>
       </c>
       <c r="R8" t="n">
-        <v>9.679336540146091</v>
+        <v>9.693816662948816</v>
       </c>
       <c r="S8" t="n">
-        <v>10.06025664578818</v>
+        <v>10.07460691465963</v>
       </c>
       <c r="T8" t="n">
-        <v>10.38853293766878</v>
+        <v>10.40352509811502</v>
       </c>
       <c r="U8" t="n">
-        <v>10.69976642778947</v>
+        <v>10.71465097071965</v>
       </c>
       <c r="V8" t="n">
-        <v>11.00230556276952</v>
+        <v>11.01479199168689</v>
       </c>
       <c r="W8" t="n">
-        <v>11.2730866934928</v>
+        <v>11.28005482207086</v>
       </c>
       <c r="X8" t="n">
-        <v>11.4724024022169</v>
+        <v>11.47272006511563</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.58739205758019</v>
+        <v>11.58382402948918</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.67335759103995</v>
+        <v>11.6687123937699</v>
       </c>
       <c r="AA8" t="n">
-        <v>11.78511535729566</v>
+        <v>11.78100010336844</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.93848703145402</v>
+        <v>11.93685781915442</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.13877744820046</v>
+        <v>12.14072720638936</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.37388119574234</v>
+        <v>12.37949945213247</v>
       </c>
       <c r="AE8" t="n">
-        <v>12.61698476131278</v>
+        <v>12.62589980590791</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.84066250056435</v>
+        <v>12.85081931101064</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.06102277023365</v>
+        <v>13.07180658880591</v>
       </c>
       <c r="AH8" t="n">
-        <v>13.28511037373635</v>
+        <v>13.29676846476885</v>
       </c>
       <c r="AI8" t="n">
-        <v>13.51188634878473</v>
+        <v>13.5247057309176</v>
       </c>
       <c r="AJ8" t="n">
-        <v>13.73974283901139</v>
+        <v>13.7538086964876</v>
       </c>
       <c r="AK8" t="n">
-        <v>13.96719116126517</v>
+        <v>13.98243841395135</v>
       </c>
       <c r="AL8" t="n">
-        <v>14.19306627499202</v>
+        <v>14.20932546650953</v>
       </c>
     </row>
     <row r="9">
@@ -3508,115 +3626,115 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10.65185742791435</v>
+        <v>7.487534542647016</v>
       </c>
       <c r="C9" t="n">
-        <v>7.57399982247834</v>
+        <v>7.592750132165637</v>
       </c>
       <c r="D9" t="n">
-        <v>7.66881820112455</v>
+        <v>7.692574117793989</v>
       </c>
       <c r="E9" t="n">
-        <v>7.75871011513358</v>
+        <v>7.788166350004071</v>
       </c>
       <c r="F9" t="n">
-        <v>7.843579987898821</v>
+        <v>7.879048529674853</v>
       </c>
       <c r="G9" t="n">
-        <v>7.92249817621805</v>
+        <v>7.96351734866277</v>
       </c>
       <c r="H9" t="n">
-        <v>7.99475637869783</v>
+        <v>8.040090615434025</v>
       </c>
       <c r="I9" t="n">
-        <v>8.0601200829246</v>
+        <v>8.107967688740482</v>
       </c>
       <c r="J9" t="n">
-        <v>8.117451599081599</v>
+        <v>8.124402560298417</v>
       </c>
       <c r="K9" t="n">
-        <v>8.10422275394127</v>
+        <v>8.109633069334485</v>
       </c>
       <c r="L9" t="n">
-        <v>8.053142951516611</v>
+        <v>8.057311411694796</v>
       </c>
       <c r="M9" t="n">
-        <v>7.96949211516363</v>
+        <v>7.972495273871726</v>
       </c>
       <c r="N9" t="n">
-        <v>7.87117483088905</v>
+        <v>7.876084712468466</v>
       </c>
       <c r="O9" t="n">
-        <v>7.7955372289283</v>
+        <v>7.803747966280096</v>
       </c>
       <c r="P9" t="n">
-        <v>7.7555328653687</v>
+        <v>7.765866407342438</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.72919750683661</v>
+        <v>7.740588536322377</v>
       </c>
       <c r="R9" t="n">
-        <v>7.71534860435242</v>
+        <v>7.727253169423531</v>
       </c>
       <c r="S9" t="n">
-        <v>7.71755935584353</v>
+        <v>7.72974298259345</v>
       </c>
       <c r="T9" t="n">
-        <v>7.74174674583262</v>
+        <v>7.754275362161732</v>
       </c>
       <c r="U9" t="n">
-        <v>7.7922457848083</v>
+        <v>7.805285017490933</v>
       </c>
       <c r="V9" t="n">
-        <v>7.864195632581961</v>
+        <v>7.878106840139088</v>
       </c>
       <c r="W9" t="n">
-        <v>7.97008464722736</v>
+        <v>7.985333599526643</v>
       </c>
       <c r="X9" t="n">
-        <v>8.107355971857109</v>
+        <v>8.123448827391966</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.26508521187109</v>
+        <v>8.280422135495561</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.42824995016176</v>
+        <v>8.44164746547038</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.594282781636121</v>
+        <v>8.605956668641639</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.7648192592395</v>
+        <v>8.77597332721477</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.939261349696311</v>
+        <v>8.950442210696465</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.119091717638241</v>
+        <v>9.12998917216952</v>
       </c>
       <c r="AE9" t="n">
-        <v>9.287998431982899</v>
+        <v>9.297534668247041</v>
       </c>
       <c r="AF9" t="n">
-        <v>9.38115350000562</v>
+        <v>9.387850781768744</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.45986009001318</v>
+        <v>9.463949205052243</v>
       </c>
       <c r="AH9" t="n">
-        <v>9.530145064205579</v>
+        <v>9.531802746391287</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.59334741025109</v>
+        <v>9.592738216992943</v>
       </c>
       <c r="AJ9" t="n">
-        <v>9.6492667733737</v>
+        <v>9.646538801909644</v>
       </c>
       <c r="AK9" t="n">
-        <v>9.69796307799904</v>
+        <v>9.693245135749834</v>
       </c>
       <c r="AL9" t="n">
-        <v>9.73922129801341</v>
+        <v>9.732626151049569</v>
       </c>
     </row>
     <row r="10">
@@ -3626,115 +3744,115 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9.83263377527388</v>
+        <v>14.53638611138429</v>
       </c>
       <c r="C10" t="n">
-        <v>16.49485479495654</v>
+        <v>14.78863315375946</v>
       </c>
       <c r="D10" t="n">
-        <v>16.46027318621306</v>
+        <v>15.03065085789569</v>
       </c>
       <c r="E10" t="n">
-        <v>16.42481576518264</v>
+        <v>15.26788531884148</v>
       </c>
       <c r="F10" t="n">
-        <v>16.38965782780285</v>
+        <v>15.50053571876158</v>
       </c>
       <c r="G10" t="n">
-        <v>16.35339102990734</v>
+        <v>15.71816946905116</v>
       </c>
       <c r="H10" t="n">
-        <v>16.31320156049322</v>
+        <v>15.89944536193815</v>
       </c>
       <c r="I10" t="n">
-        <v>16.2672741665681</v>
+        <v>15.99600552209442</v>
       </c>
       <c r="J10" t="n">
-        <v>16.21314016181219</v>
+        <v>15.97008444331981</v>
       </c>
       <c r="K10" t="n">
-        <v>16.25655379736336</v>
+        <v>16.047482540474</v>
       </c>
       <c r="L10" t="n">
-        <v>16.41447417661384</v>
+        <v>16.24540550806665</v>
       </c>
       <c r="M10" t="n">
-        <v>16.6551701138717</v>
+        <v>16.51409091593306</v>
       </c>
       <c r="N10" t="n">
-        <v>16.89553576633216</v>
+        <v>16.76117042320511</v>
       </c>
       <c r="O10" t="n">
-        <v>17.11386934151145</v>
+        <v>16.98275415901475</v>
       </c>
       <c r="P10" t="n">
-        <v>17.32513918929775</v>
+        <v>17.20795763622212</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.51149063820839</v>
+        <v>17.41712808565974</v>
       </c>
       <c r="R10" t="n">
-        <v>17.66855623952953</v>
+        <v>17.58864860950378</v>
       </c>
       <c r="S10" t="n">
-        <v>17.67372030954402</v>
+        <v>17.60159543698845</v>
       </c>
       <c r="T10" t="n">
-        <v>17.5140828271701</v>
+        <v>17.44439379669496</v>
       </c>
       <c r="U10" t="n">
-        <v>17.34278396569448</v>
+        <v>17.26512635834901</v>
       </c>
       <c r="V10" t="n">
-        <v>17.1931112400695</v>
+        <v>17.1065563670449</v>
       </c>
       <c r="W10" t="n">
-        <v>16.99415318841129</v>
+        <v>16.90034719995301</v>
       </c>
       <c r="X10" t="n">
-        <v>16.74446900235179</v>
+        <v>16.6447526203588</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.50440036571257</v>
+        <v>16.40172318433006</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.3291769382265</v>
+        <v>16.23308322932458</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.28906629429235</v>
+        <v>16.20580785960516</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.37784578965181</v>
+        <v>16.29307670808234</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.53463476729915</v>
+        <v>16.42313304223606</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.61396555350194</v>
+        <v>16.46411208890653</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.53277704091845</v>
+        <v>16.36333957433116</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.34322498546354</v>
+        <v>16.18504840190261</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.21843105529727</v>
+        <v>16.06113322026958</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.10077528050607</v>
+        <v>15.93724943235935</v>
       </c>
       <c r="AI10" t="n">
-        <v>15.97213497487913</v>
+        <v>15.79831364233077</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.82752601937678</v>
+        <v>15.64277600071999</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.66741734172635</v>
+        <v>15.47359007936036</v>
       </c>
       <c r="AL10" t="n">
-        <v>15.49759465776242</v>
+        <v>15.2978784447981</v>
       </c>
     </row>
     <row r="11">
@@ -3744,115 +3862,115 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.50537836826959</v>
+        <v>13.52628506759902</v>
       </c>
       <c r="C11" t="n">
-        <v>13.37859003905076</v>
+        <v>13.35721320786847</v>
       </c>
       <c r="D11" t="n">
-        <v>13.21924355935771</v>
+        <v>13.19539469368938</v>
       </c>
       <c r="E11" t="n">
-        <v>13.06226378868056</v>
+        <v>13.03636408156381</v>
       </c>
       <c r="F11" t="n">
-        <v>12.90302512403289</v>
+        <v>12.87345422389556</v>
       </c>
       <c r="G11" t="n">
-        <v>12.73850275235819</v>
+        <v>12.70172922207937</v>
       </c>
       <c r="H11" t="n">
-        <v>12.56999733667285</v>
+        <v>12.52231374807518</v>
       </c>
       <c r="I11" t="n">
-        <v>12.40618348125082</v>
+        <v>12.34961179250361</v>
       </c>
       <c r="J11" t="n">
-        <v>12.27366596705975</v>
+        <v>12.25592555012174</v>
       </c>
       <c r="K11" t="n">
-        <v>12.2568672723651</v>
+        <v>12.24352558543062</v>
       </c>
       <c r="L11" t="n">
-        <v>12.28607997947327</v>
+        <v>12.2782018196266</v>
       </c>
       <c r="M11" t="n">
-        <v>12.33787970138901</v>
+        <v>12.33511604267184</v>
       </c>
       <c r="N11" t="n">
-        <v>12.42234940113742</v>
+        <v>12.42327150164146</v>
       </c>
       <c r="O11" t="n">
-        <v>12.54161576050523</v>
+        <v>12.54559302594664</v>
       </c>
       <c r="P11" t="n">
-        <v>12.6877866409371</v>
+        <v>12.69431744299763</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.82897290307948</v>
+        <v>12.83704194485826</v>
       </c>
       <c r="R11" t="n">
-        <v>12.94356009206485</v>
+        <v>12.95210859560742</v>
       </c>
       <c r="S11" t="n">
-        <v>13.00481130157694</v>
+        <v>13.0134638601029</v>
       </c>
       <c r="T11" t="n">
-        <v>13.01449922023524</v>
+        <v>13.02323789218147</v>
       </c>
       <c r="U11" t="n">
-        <v>12.97223990134752</v>
+        <v>12.98073013508048</v>
       </c>
       <c r="V11" t="n">
-        <v>12.86046932120265</v>
+        <v>12.86764199111298</v>
       </c>
       <c r="W11" t="n">
-        <v>12.68295717395045</v>
+        <v>12.68803206560781</v>
       </c>
       <c r="X11" t="n">
-        <v>12.4767231964182</v>
+        <v>12.47967997503645</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.27312917837293</v>
+        <v>12.27453644978406</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.06644024181408</v>
+        <v>12.06720114411263</v>
       </c>
       <c r="AA11" t="n">
-        <v>11.85591494533517</v>
+        <v>11.85640128165494</v>
       </c>
       <c r="AB11" t="n">
-        <v>11.65690572529051</v>
+        <v>11.65740540781461</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.46577448734554</v>
+        <v>11.467043619525</v>
       </c>
       <c r="AD11" t="n">
-        <v>11.27152762658071</v>
+        <v>11.274574109898</v>
       </c>
       <c r="AE11" t="n">
-        <v>11.03150531569299</v>
+        <v>11.03719821553395</v>
       </c>
       <c r="AF11" t="n">
-        <v>10.6236595078683</v>
+        <v>10.63143146713174</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.2043303819842</v>
+        <v>10.21327376287225</v>
       </c>
       <c r="AH11" t="n">
-        <v>9.789878775309219</v>
+        <v>9.799906833186848</v>
       </c>
       <c r="AI11" t="n">
-        <v>9.37475856332048</v>
+        <v>9.386013632099834</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8.954094537267011</v>
+        <v>8.96676581894649</v>
       </c>
       <c r="AK11" t="n">
-        <v>8.523829312424901</v>
+        <v>8.537955259571984</v>
       </c>
       <c r="AL11" t="n">
-        <v>8.08134181257989</v>
+        <v>8.096807569436372</v>
       </c>
     </row>
     <row r="12">
@@ -3862,587 +3980,587 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7.05820970262431</v>
+        <v>5.068224596172908</v>
       </c>
       <c r="C12" t="n">
-        <v>4.66057190399238</v>
+        <v>5.685188325551354</v>
       </c>
       <c r="D12" t="n">
-        <v>5.44806604380792</v>
+        <v>6.300080792331674</v>
       </c>
       <c r="E12" t="n">
-        <v>6.22041475880707</v>
+        <v>6.911479736966708</v>
       </c>
       <c r="F12" t="n">
-        <v>6.98046027858821</v>
+        <v>7.522312680629753</v>
       </c>
       <c r="G12" t="n">
-        <v>7.72838521082386</v>
+        <v>8.134564126444737</v>
       </c>
       <c r="H12" t="n">
-        <v>8.461159931686749</v>
+        <v>8.752005791951857</v>
       </c>
       <c r="I12" t="n">
-        <v>9.17400784743764</v>
+        <v>9.388451068973756</v>
       </c>
       <c r="J12" t="n">
-        <v>9.84713220158366</v>
+        <v>9.904771334383858</v>
       </c>
       <c r="K12" t="n">
-        <v>10.24030116222129</v>
+        <v>10.28596274613459</v>
       </c>
       <c r="L12" t="n">
-        <v>10.48350309999994</v>
+        <v>10.52234941094001</v>
       </c>
       <c r="M12" t="n">
-        <v>10.60347768627562</v>
+        <v>10.63666878777313</v>
       </c>
       <c r="N12" t="n">
-        <v>10.59526735076413</v>
+        <v>10.61795550272979</v>
       </c>
       <c r="O12" t="n">
-        <v>10.43736804456653</v>
+        <v>10.44921309299449</v>
       </c>
       <c r="P12" t="n">
-        <v>10.13828299115167</v>
+        <v>10.13930279582878</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.7440611352053</v>
+        <v>9.733639316927659</v>
       </c>
       <c r="R12" t="n">
-        <v>9.32509573875558</v>
+        <v>9.306306569215367</v>
       </c>
       <c r="S12" t="n">
-        <v>8.96310317699003</v>
+        <v>8.935664649298843</v>
       </c>
       <c r="T12" t="n">
-        <v>8.6845451415762</v>
+        <v>8.65042157415103</v>
       </c>
       <c r="U12" t="n">
-        <v>8.50759733102063</v>
+        <v>8.475281285298045</v>
       </c>
       <c r="V12" t="n">
-        <v>8.44947202538018</v>
+        <v>8.433342205518761</v>
       </c>
       <c r="W12" t="n">
-        <v>8.523507262624621</v>
+        <v>8.52396068022218</v>
       </c>
       <c r="X12" t="n">
-        <v>8.723125408362529</v>
+        <v>8.730906395530187</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.99494985387169</v>
+        <v>9.005034249110027</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.28751121779735</v>
+        <v>9.300496431740553</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.57421396611878</v>
+        <v>9.590875035807381</v>
       </c>
       <c r="AB12" t="n">
-        <v>9.844215550569061</v>
+        <v>9.864012701329539</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.09092815263715</v>
+        <v>10.11273108720417</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.292705390221</v>
+        <v>10.31568571762388</v>
       </c>
       <c r="AE12" t="n">
-        <v>10.42596266896754</v>
+        <v>10.44301739151588</v>
       </c>
       <c r="AF12" t="n">
-        <v>10.41631771099301</v>
+        <v>10.38759348448444</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.38159944870747</v>
+        <v>10.29667731920596</v>
       </c>
       <c r="AH12" t="n">
-        <v>10.34006655959955</v>
+        <v>10.19747311208515</v>
       </c>
       <c r="AI12" t="n">
-        <v>10.29433487226437</v>
+        <v>10.09354665656425</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10.24141939854014</v>
+        <v>9.981797669390415</v>
       </c>
       <c r="AK12" t="n">
-        <v>10.17538260155719</v>
+        <v>9.855689415200196</v>
       </c>
       <c r="AL12" t="n">
-        <v>10.09097173902126</v>
+        <v>9.708750463668444</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>1.5.1</t>
+          <t>1.5.2</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.09197605078966001</v>
+        <v>20.8323678710586</v>
       </c>
       <c r="C13" t="n">
-        <v>9.08996216466409</v>
+        <v>19.97972935651005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.02638213330374</v>
+        <v>19.11032760122897</v>
       </c>
       <c r="E13" t="n">
-        <v>8.94866184789992</v>
+        <v>18.21696141445761</v>
       </c>
       <c r="F13" t="n">
-        <v>8.859098285912321</v>
+        <v>17.29294263457772</v>
       </c>
       <c r="G13" t="n">
-        <v>8.760980298844901</v>
+        <v>16.33410869090659</v>
       </c>
       <c r="H13" t="n">
-        <v>8.656943688548651</v>
+        <v>15.34532328046608</v>
       </c>
       <c r="I13" t="n">
-        <v>8.550391300224961</v>
+        <v>14.34694873528162</v>
       </c>
       <c r="J13" t="n">
-        <v>8.444138238280841</v>
+        <v>13.1397090281688</v>
       </c>
       <c r="K13" t="n">
-        <v>8.248158091081439</v>
+        <v>11.87594545631286</v>
       </c>
       <c r="L13" t="n">
-        <v>7.99290086033445</v>
+        <v>10.48556604716808</v>
       </c>
       <c r="M13" t="n">
-        <v>7.69373591862553</v>
+        <v>8.935877019391027</v>
       </c>
       <c r="N13" t="n">
-        <v>7.38967582800652</v>
+        <v>7.304410811843369</v>
       </c>
       <c r="O13" t="n">
-        <v>7.11151469837792</v>
+        <v>5.755356908793793</v>
       </c>
       <c r="P13" t="n">
-        <v>6.87552915295014</v>
+        <v>4.443008890119946</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.69193490706329</v>
+        <v>3.485436518479874</v>
       </c>
       <c r="R13" t="n">
-        <v>6.56270292549148</v>
+        <v>2.86780182229289</v>
       </c>
       <c r="S13" t="n">
-        <v>6.482278013534359</v>
+        <v>2.526088427935863</v>
       </c>
       <c r="T13" t="n">
-        <v>6.43495292425444</v>
+        <v>2.433277829458294</v>
       </c>
       <c r="U13" t="n">
-        <v>6.40697008400254</v>
+        <v>2.56649929327773</v>
       </c>
       <c r="V13" t="n">
-        <v>6.40407714817021</v>
+        <v>2.908680795715457</v>
       </c>
       <c r="W13" t="n">
-        <v>6.41809941663207</v>
+        <v>3.463189966290144</v>
       </c>
       <c r="X13" t="n">
-        <v>6.422656570492979</v>
+        <v>4.199686917617461</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.399398144037651</v>
+        <v>4.98195083086934</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3511488726072</v>
+        <v>5.717059783367821</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.29296948420882</v>
+        <v>6.374341508690809</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.22285600007287</v>
+        <v>6.941287107465594</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.143733654209941</v>
+        <v>7.41130896347785</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.06302310269932</v>
+        <v>7.788071424020782</v>
       </c>
       <c r="AE13" t="n">
-        <v>5.98711119991722</v>
+        <v>8.084396039554026</v>
       </c>
       <c r="AF13" t="n">
-        <v>5.96263534534118</v>
+        <v>8.264360540273941</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.95443302995398</v>
+        <v>8.435215317770755</v>
       </c>
       <c r="AH13" t="n">
-        <v>5.953751138094669</v>
+        <v>8.609094615511726</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.95684524801985</v>
+        <v>8.784038879290819</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5.96300985678206</v>
+        <v>8.955213110580575</v>
       </c>
       <c r="AK13" t="n">
-        <v>5.97271806236767</v>
+        <v>9.118451911768632</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.986657814265451</v>
+        <v>9.271124870236095</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>1.5.2</t>
+          <t>1.5.1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16.16088398222855</v>
+        <v>7.24873186548239</v>
       </c>
       <c r="C14" t="n">
-        <v>20.99277818739163</v>
+        <v>7.453140929093395</v>
       </c>
       <c r="D14" t="n">
-        <v>19.94869125807722</v>
+        <v>7.636069129719799</v>
       </c>
       <c r="E14" t="n">
-        <v>18.88286645856128</v>
+        <v>7.800534961620019</v>
       </c>
       <c r="F14" t="n">
-        <v>17.7881474993589</v>
+        <v>7.952172277152393</v>
       </c>
       <c r="G14" t="n">
-        <v>16.66234393564239</v>
+        <v>8.097418493781753</v>
       </c>
       <c r="H14" t="n">
-        <v>15.51329284203404</v>
+        <v>8.246545776306233</v>
       </c>
       <c r="I14" t="n">
-        <v>14.36520252338695</v>
+        <v>8.42269609470023</v>
       </c>
       <c r="J14" t="n">
-        <v>13.27981462690542</v>
+        <v>8.421062058860734</v>
       </c>
       <c r="K14" t="n">
-        <v>11.98493586890891</v>
+        <v>8.277590886266964</v>
       </c>
       <c r="L14" t="n">
-        <v>10.55239772945337</v>
+        <v>8.008364535972229</v>
       </c>
       <c r="M14" t="n">
-        <v>8.971308191922429</v>
+        <v>7.696532286263104</v>
       </c>
       <c r="N14" t="n">
-        <v>7.32886563794888</v>
+        <v>7.387377139605805</v>
       </c>
       <c r="O14" t="n">
-        <v>5.770045484212869</v>
+        <v>7.105866146453872</v>
       </c>
       <c r="P14" t="n">
-        <v>4.43974958071299</v>
+        <v>6.867227362929092</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.45317978399208</v>
+        <v>6.68146116301511</v>
       </c>
       <c r="R14" t="n">
-        <v>2.80773350741052</v>
+        <v>6.551214280270239</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45310920845875</v>
+        <v>6.471178102810586</v>
       </c>
       <c r="T14" t="n">
-        <v>2.36544106990073</v>
+        <v>6.425366895451552</v>
       </c>
       <c r="U14" t="n">
-        <v>2.51707557106096</v>
+        <v>6.399739329882177</v>
       </c>
       <c r="V14" t="n">
-        <v>2.88143464542464</v>
+        <v>6.399139540728774</v>
       </c>
       <c r="W14" t="n">
-        <v>3.44977710643795</v>
+        <v>6.413387712543132</v>
       </c>
       <c r="X14" t="n">
-        <v>4.18715461250335</v>
+        <v>6.41636599184433</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.96782555248013</v>
+        <v>6.392007246834706</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.70429531133528</v>
+        <v>6.342768805962415</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.366510920674701</v>
+        <v>6.283236047616604</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.93951404762959</v>
+        <v>6.211967346890609</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.41363382601153</v>
+        <v>6.132086827807738</v>
       </c>
       <c r="AD14" t="n">
-        <v>7.79199257174686</v>
+        <v>6.050921088897865</v>
       </c>
       <c r="AE14" t="n">
-        <v>8.08915055130244</v>
+        <v>5.975699058288519</v>
       </c>
       <c r="AF14" t="n">
-        <v>8.26963299781435</v>
+        <v>5.957848100079731</v>
       </c>
       <c r="AG14" t="n">
-        <v>8.44068069580328</v>
+        <v>5.957644812556382</v>
       </c>
       <c r="AH14" t="n">
-        <v>8.61474435980341</v>
+        <v>5.965233723882936</v>
       </c>
       <c r="AI14" t="n">
-        <v>8.78987742122767</v>
+        <v>5.976729398680687</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8.96117617016119</v>
+        <v>5.991429768656429</v>
       </c>
       <c r="AK14" t="n">
-        <v>9.124425786140911</v>
+        <v>6.009872621522063</v>
       </c>
       <c r="AL14" t="n">
-        <v>9.27697329521418</v>
+        <v>6.032880758789404</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.75.2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.56993078498844</v>
+        <v>19.18454532586006</v>
       </c>
       <c r="C15" t="n">
-        <v>16.68921781880388</v>
+        <v>19.42393306558171</v>
       </c>
       <c r="D15" t="n">
-        <v>15.68389454493824</v>
+        <v>19.64486094509615</v>
       </c>
       <c r="E15" t="n">
-        <v>14.68995406409459</v>
+        <v>19.84342772291974</v>
       </c>
       <c r="F15" t="n">
-        <v>13.71416575244609</v>
+        <v>20.01715564064884</v>
       </c>
       <c r="G15" t="n">
-        <v>12.76091201375093</v>
+        <v>20.1718927704666</v>
       </c>
       <c r="H15" t="n">
-        <v>11.83307696866528</v>
+        <v>20.32426201043397</v>
       </c>
       <c r="I15" t="n">
-        <v>10.92715043596129</v>
+        <v>20.49883564051598</v>
       </c>
       <c r="J15" t="n">
-        <v>10.01025890312865</v>
+        <v>20.56776766266109</v>
       </c>
       <c r="K15" t="n">
-        <v>9.260424401267329</v>
+        <v>20.56956824437717</v>
       </c>
       <c r="L15" t="n">
-        <v>8.52465948526463</v>
+        <v>20.46744919094486</v>
       </c>
       <c r="M15" t="n">
-        <v>7.8888337479068</v>
+        <v>20.23261440679586</v>
       </c>
       <c r="N15" t="n">
-        <v>7.51822120488758</v>
+        <v>19.94317811513922</v>
       </c>
       <c r="O15" t="n">
-        <v>7.425231323623829</v>
+        <v>19.70878311257224</v>
       </c>
       <c r="P15" t="n">
-        <v>7.431618988070871</v>
+        <v>19.59697652808007</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.459740184539659</v>
+        <v>19.55124121972189</v>
       </c>
       <c r="R15" t="n">
-        <v>7.49567162370532</v>
+        <v>19.576395442424</v>
       </c>
       <c r="S15" t="n">
-        <v>7.521560752357461</v>
+        <v>19.67171901188738</v>
       </c>
       <c r="T15" t="n">
-        <v>7.52434983255397</v>
+        <v>19.84469559717635</v>
       </c>
       <c r="U15" t="n">
-        <v>7.523762233648861</v>
+        <v>20.14965433073628</v>
       </c>
       <c r="V15" t="n">
-        <v>7.52916722606693</v>
+        <v>20.60477241061823</v>
       </c>
       <c r="W15" t="n">
-        <v>7.516003473835391</v>
+        <v>21.2059245983124</v>
       </c>
       <c r="X15" t="n">
-        <v>7.46664045028599</v>
+        <v>21.88256080432173</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.35275465825595</v>
+        <v>22.47257026211566</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.14139264183994</v>
+        <v>22.87990176894706</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.838893594158479</v>
+        <v>22.99263234545731</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.4570513857904</v>
+        <v>22.7613804893248</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.97423494284089</v>
+        <v>22.21600187410031</v>
       </c>
       <c r="AD15" t="n">
-        <v>5.38571222552931</v>
+        <v>21.57839780959816</v>
       </c>
       <c r="AE15" t="n">
-        <v>4.71883434054838</v>
+        <v>21.04936988932661</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.94905067270277</v>
+        <v>20.85406641871474</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.19538510709134</v>
+        <v>20.66350702130247</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.44082544942741</v>
+        <v>20.43757380215905</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.67896617858712</v>
+        <v>20.20113546073647</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.9070248584259301</v>
+        <v>19.98517209156414</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.12670839790658</v>
+        <v>19.81886989964242</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.657997109025</v>
+        <v>19.72215974577709</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>0.75.1</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05565964956717</v>
+        <v>17.98153806582489</v>
       </c>
       <c r="C16" t="n">
-        <v>0.04911725230458</v>
+        <v>16.84645548549788</v>
       </c>
       <c r="D16" t="n">
-        <v>0.04925215200649</v>
+        <v>15.71982591108921</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04966267156019</v>
+        <v>14.60753447706525</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05045854399077999</v>
+        <v>13.51941167356</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05186811760241</v>
+        <v>12.46227566130351</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05444247186758</v>
+        <v>11.43906352719358</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0597841384782</v>
+        <v>10.43736878548429</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07391723482654999</v>
+        <v>9.638045598652486</v>
       </c>
       <c r="K16" t="n">
-        <v>0.13073263345192</v>
+        <v>8.886556979451338</v>
       </c>
       <c r="L16" t="n">
-        <v>0.16890837875867</v>
+        <v>8.202124385021328</v>
       </c>
       <c r="M16" t="n">
-        <v>0.19974917614354</v>
+        <v>7.681171953535948</v>
       </c>
       <c r="N16" t="n">
-        <v>0.23008801055911</v>
+        <v>7.429347511828621</v>
       </c>
       <c r="O16" t="n">
-        <v>0.26181644787606</v>
+        <v>7.3909816583916</v>
       </c>
       <c r="P16" t="n">
-        <v>0.29865260279762</v>
+        <v>7.41590631660768</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.32769384264457</v>
+        <v>7.453170401867824</v>
       </c>
       <c r="R16" t="n">
-        <v>0.28803504496799</v>
+        <v>7.493406993000737</v>
       </c>
       <c r="S16" t="n">
-        <v>0.24739402941746</v>
+        <v>7.520561535351448</v>
       </c>
       <c r="T16" t="n">
-        <v>0.20919683870894</v>
+        <v>7.523552818291187</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17253165860749</v>
+        <v>7.522952111234684</v>
       </c>
       <c r="V16" t="n">
-        <v>0.13505538574945</v>
+        <v>7.528410484474557</v>
       </c>
       <c r="W16" t="n">
-        <v>0.09257311497417001</v>
+        <v>7.515987532471319</v>
       </c>
       <c r="X16" t="n">
-        <v>0.05249164486767</v>
+        <v>7.468258038178749</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.04214314442686</v>
+        <v>7.356067498277609</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.04172381857412</v>
+        <v>7.145769802724572</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.04171839217126</v>
+        <v>6.843561132855943</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.04201916050791</v>
+        <v>6.461241578916754</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.04244404410086</v>
+        <v>5.977147138044389</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.04288636607886</v>
+        <v>5.387234653435007</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.04330530506328</v>
+        <v>4.719201772866418</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.04315121510799</v>
+        <v>3.948424236034175</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.04292117466339</v>
+        <v>3.193830321297357</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.04266923679216</v>
+        <v>2.438320195208231</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.04237848548463</v>
+        <v>1.675465016658163</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.04202471384216</v>
+        <v>0.9024825502994948</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.04159448943124</v>
+        <v>0.121128676309888</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.04107934275965</v>
+        <v>-0.6645711903064146</v>
       </c>
     </row>
     <row r="17">
@@ -4452,233 +4570,233 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7.07866695768459</v>
+        <v>0.04984586062899506</v>
       </c>
       <c r="C17" t="n">
-        <v>0.04820789816604</v>
+        <v>0.04821546771108142</v>
       </c>
       <c r="D17" t="n">
-        <v>0.04660974345125</v>
+        <v>0.04661211645879132</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04499745384129</v>
+        <v>0.04499171849667365</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04336029862888</v>
+        <v>0.04333956936298643</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0417265822665</v>
+        <v>0.04169331237818172</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0401472848377</v>
+        <v>0.04012674251496156</v>
       </c>
       <c r="I17" t="n">
-        <v>0.03871084463572</v>
+        <v>0.03876437145922708</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03741992887895</v>
+        <v>0.03744964880907437</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03568584286256</v>
+        <v>0.03565208165337909</v>
       </c>
       <c r="L17" t="n">
-        <v>0.22228921435179</v>
+        <v>0.2559731789663171</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9949776056950301</v>
+        <v>1.076095339446672</v>
       </c>
       <c r="N17" t="n">
-        <v>1.66140190216023</v>
+        <v>1.720540960709376</v>
       </c>
       <c r="O17" t="n">
-        <v>2.11319023438838</v>
+        <v>2.156445715027895</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49729319829859</v>
+        <v>2.535729801789016</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.91980710090376</v>
+        <v>2.969219293216967</v>
       </c>
       <c r="R17" t="n">
-        <v>3.52083831303481</v>
+        <v>3.617758351094597</v>
       </c>
       <c r="S17" t="n">
-        <v>4.32069303938327</v>
+        <v>4.39210160228859</v>
       </c>
       <c r="T17" t="n">
-        <v>4.55957635463253</v>
+        <v>4.562923356590187</v>
       </c>
       <c r="U17" t="n">
-        <v>4.57080033405364</v>
+        <v>4.574152555058381</v>
       </c>
       <c r="V17" t="n">
-        <v>4.59652506489605</v>
+        <v>4.602584102048417</v>
       </c>
       <c r="W17" t="n">
-        <v>4.632432908556909</v>
+        <v>4.640088768111999</v>
       </c>
       <c r="X17" t="n">
-        <v>4.66332376086684</v>
+        <v>4.671981462921289</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.675847746317039</v>
+        <v>4.685242348094421</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.66755553123807</v>
+        <v>4.677170786026704</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.64596487907894</v>
+        <v>4.654732861995232</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.620048771511899</v>
+        <v>4.626872930565897</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.58551597264155</v>
+        <v>4.589869009972391</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.53396500977693</v>
+        <v>4.536181167434474</v>
       </c>
       <c r="AE17" t="n">
-        <v>4.46997250836332</v>
+        <v>4.470822791673533</v>
       </c>
       <c r="AF17" t="n">
-        <v>4.40342398875273</v>
+        <v>4.404805291536061</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.34029970034066</v>
+        <v>4.342533691148027</v>
       </c>
       <c r="AH17" t="n">
-        <v>4.27841665849214</v>
+        <v>4.281589552685743</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.21797868055938</v>
+        <v>4.222174865535858</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.15956339325037</v>
+        <v>4.164886036850084</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.10376423479067</v>
+        <v>4.110341745696572</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.05109422802771</v>
+        <v>4.059088611771969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.75.1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14.48771669399818</v>
+        <v>0.05350972022504714</v>
       </c>
       <c r="C18" t="n">
-        <v>8.62029056005712</v>
+        <v>0.05263790658386427</v>
       </c>
       <c r="D18" t="n">
-        <v>8.60665951334307</v>
+        <v>0.05181280784013905</v>
       </c>
       <c r="E18" t="n">
-        <v>8.579373476957999</v>
+        <v>0.05102137678682098</v>
       </c>
       <c r="F18" t="n">
-        <v>8.53940052715585</v>
+        <v>0.05025786346062383</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4922166344984</v>
+        <v>0.04954552911107181</v>
       </c>
       <c r="H18" t="n">
-        <v>8.442331538366519</v>
+        <v>0.04902424668730355</v>
       </c>
       <c r="I18" t="n">
-        <v>8.389680599660471</v>
+        <v>0.04923848321508325</v>
       </c>
       <c r="J18" t="n">
-        <v>8.325811350318329</v>
+        <v>0.06691756914576326</v>
       </c>
       <c r="K18" t="n">
-        <v>8.21573533110989</v>
+        <v>0.1191989257807542</v>
       </c>
       <c r="L18" t="n">
-        <v>8.10933222382034</v>
+        <v>0.1597220102600225</v>
       </c>
       <c r="M18" t="n">
-        <v>8.017270736902599</v>
+        <v>0.1925184621613945</v>
       </c>
       <c r="N18" t="n">
-        <v>7.958177899947811</v>
+        <v>0.2242862996193263</v>
       </c>
       <c r="O18" t="n">
-        <v>7.93328792444624</v>
+        <v>0.2573425638025986</v>
       </c>
       <c r="P18" t="n">
-        <v>7.925037516858879</v>
+        <v>0.2860618279210103</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.91543635057458</v>
+        <v>0.3135677057503517</v>
       </c>
       <c r="R18" t="n">
-        <v>7.903432153248199</v>
+        <v>0.2877687417314114</v>
       </c>
       <c r="S18" t="n">
-        <v>7.887078183192769</v>
+        <v>0.2467808219714878</v>
       </c>
       <c r="T18" t="n">
-        <v>7.849144821733139</v>
+        <v>0.2082354135385828</v>
       </c>
       <c r="U18" t="n">
-        <v>7.76379590816561</v>
+        <v>0.1712830516853255</v>
       </c>
       <c r="V18" t="n">
-        <v>7.627592529553021</v>
+        <v>0.1336665867186315</v>
       </c>
       <c r="W18" t="n">
-        <v>7.47039390274105</v>
+        <v>0.09147515471034649</v>
       </c>
       <c r="X18" t="n">
-        <v>7.32553068839875</v>
+        <v>0.05244205331586258</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.206201647395261</v>
+        <v>0.04245753052865821</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.12126428758334</v>
+        <v>0.04197421386463281</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.08165120374062</v>
+        <v>0.04189985285928362</v>
       </c>
       <c r="AB18" t="n">
-        <v>7.081331008457751</v>
+        <v>0.04212754524615248</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.10019631966117</v>
+        <v>0.04248511857592827</v>
       </c>
       <c r="AD18" t="n">
-        <v>7.136523402027541</v>
+        <v>0.04287443528262644</v>
       </c>
       <c r="AE18" t="n">
-        <v>7.21516363545814</v>
+        <v>0.0432635037415238</v>
       </c>
       <c r="AF18" t="n">
-        <v>7.369540552972791</v>
+        <v>0.04310171715490522</v>
       </c>
       <c r="AG18" t="n">
-        <v>7.54393228680232</v>
+        <v>0.04286786825629527</v>
       </c>
       <c r="AH18" t="n">
-        <v>7.7198126988364</v>
+        <v>0.04261083655240331</v>
       </c>
       <c r="AI18" t="n">
-        <v>7.89144732650735</v>
+        <v>0.04231474897598567</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8.05844743535936</v>
+        <v>0.04195700631780824</v>
       </c>
       <c r="AK18" t="n">
-        <v>8.223283493103411</v>
+        <v>0.04152529265179956</v>
       </c>
       <c r="AL18" t="n">
-        <v>8.38942798244301</v>
+        <v>0.04101169152922709</v>
       </c>
     </row>
     <row r="19">
@@ -4688,469 +4806,587 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.72115984116729</v>
+        <v>22.38828474035874</v>
       </c>
       <c r="C19" t="n">
-        <v>21.81289580189764</v>
+        <v>21.88242122559168</v>
       </c>
       <c r="D19" t="n">
-        <v>21.33703678904137</v>
+        <v>21.38599118258856</v>
       </c>
       <c r="E19" t="n">
-        <v>20.86806681041621</v>
+        <v>20.89614045057997</v>
       </c>
       <c r="F19" t="n">
-        <v>20.40284880510433</v>
+        <v>20.40841479035495</v>
       </c>
       <c r="G19" t="n">
-        <v>19.93971565673503</v>
+        <v>19.92031198752711</v>
       </c>
       <c r="H19" t="n">
-        <v>19.47967215267237</v>
+        <v>19.43325843618</v>
       </c>
       <c r="I19" t="n">
-        <v>19.02810614944222</v>
+        <v>18.95696041813434</v>
       </c>
       <c r="J19" t="n">
-        <v>18.60347301771073</v>
+        <v>18.60170801000507</v>
       </c>
       <c r="K19" t="n">
-        <v>18.30398462686055</v>
+        <v>18.30204594636793</v>
       </c>
       <c r="L19" t="n">
-        <v>18.03196766558911</v>
+        <v>18.03002163168689</v>
       </c>
       <c r="M19" t="n">
-        <v>17.79078976780458</v>
+        <v>17.78934660658962</v>
       </c>
       <c r="N19" t="n">
-        <v>17.62252003093646</v>
+        <v>17.62315699491442</v>
       </c>
       <c r="O19" t="n">
-        <v>17.55080044119005</v>
+        <v>17.55428523535409</v>
       </c>
       <c r="P19" t="n">
-        <v>17.57236360511077</v>
+        <v>17.57966969316985</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.67430896453093</v>
+        <v>17.68804005227186</v>
       </c>
       <c r="R19" t="n">
-        <v>17.81920057032667</v>
+        <v>17.83987901215577</v>
       </c>
       <c r="S19" t="n">
-        <v>17.98267421312218</v>
+        <v>18.00935463880175</v>
       </c>
       <c r="T19" t="n">
-        <v>18.15688003872699</v>
+        <v>18.18987920628005</v>
       </c>
       <c r="U19" t="n">
-        <v>18.31664317294548</v>
+        <v>18.35592802600791</v>
       </c>
       <c r="V19" t="n">
-        <v>18.43919058166659</v>
+        <v>18.48521960343147</v>
       </c>
       <c r="W19" t="n">
-        <v>18.52825299332555</v>
+        <v>18.57949228233178</v>
       </c>
       <c r="X19" t="n">
-        <v>18.58481999654846</v>
+        <v>18.6372409150975</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.61752005320687</v>
+        <v>18.66821078819968</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.64443809121219</v>
+        <v>18.69200363492683</v>
       </c>
       <c r="AA19" t="n">
-        <v>18.64753938721886</v>
+        <v>18.68988424078015</v>
       </c>
       <c r="AB19" t="n">
-        <v>18.62173317051957</v>
+        <v>18.65724111414149</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.57508266230732</v>
+        <v>18.6042183854359</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.54317226786188</v>
+        <v>18.56656136627576</v>
       </c>
       <c r="AE19" t="n">
-        <v>18.54138657870084</v>
+        <v>18.55925971007614</v>
       </c>
       <c r="AF19" t="n">
-        <v>18.60195156643908</v>
+        <v>18.61592767388196</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.6626114925928</v>
+        <v>18.67294555195469</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.72359596464694</v>
+        <v>18.73052873511103</v>
       </c>
       <c r="AI19" t="n">
-        <v>18.78685248644932</v>
+        <v>18.7905780409813</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18.85308925139378</v>
+        <v>18.85376904608153</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.92221789464155</v>
+        <v>18.91999336984615</v>
       </c>
       <c r="AL19" t="n">
-        <v>18.9932352484084</v>
+        <v>18.98822989611451</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0.38.3</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.08739546042457</v>
+        <v>9.399550578826007</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0389594195666</v>
+        <v>9.310790180609315</v>
       </c>
       <c r="D20" t="n">
-        <v>0.03906500170734</v>
+        <v>9.211649211726252</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03916581358131</v>
+        <v>9.100234240516283</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03925364829266</v>
+        <v>8.976082533074178</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03932800778687</v>
+        <v>8.84513050358562</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03939001832537</v>
+        <v>8.711917343686149</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03945862270167</v>
+        <v>8.576645124458787</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0396008510322</v>
+        <v>8.418034679390708</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03961961445991</v>
+        <v>8.266659724412147</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03971070628713</v>
+        <v>8.137994693946093</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03998471058406</v>
+        <v>8.03537228573115</v>
       </c>
       <c r="N20" t="n">
-        <v>0.04039693060821</v>
+        <v>7.970268194895501</v>
       </c>
       <c r="O20" t="n">
-        <v>0.04086797358919</v>
+        <v>7.943267699856527</v>
       </c>
       <c r="P20" t="n">
-        <v>0.04136097852215</v>
+        <v>7.934438551041984</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.0417955721475</v>
+        <v>7.927215825129023</v>
       </c>
       <c r="R20" t="n">
-        <v>0.04216295407378</v>
+        <v>7.918663959881771</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04250546393267</v>
+        <v>7.903925339951018</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04290331529183</v>
+        <v>7.862677596781137</v>
       </c>
       <c r="U20" t="n">
-        <v>0.04329178817601</v>
+        <v>7.770147134373026</v>
       </c>
       <c r="V20" t="n">
-        <v>0.04338030627480999</v>
+        <v>7.625444944745335</v>
       </c>
       <c r="W20" t="n">
-        <v>0.04301065466109</v>
+        <v>7.45980085208491</v>
       </c>
       <c r="X20" t="n">
-        <v>0.04236450963045</v>
+        <v>7.307363123185991</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.04167986961887001</v>
+        <v>7.181945088066029</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04123495685739</v>
+        <v>7.093547779506736</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.04103375933679</v>
+        <v>7.051682373189426</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.04093226383366</v>
+        <v>7.051628235621033</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.04088081623243</v>
+        <v>7.075584659046691</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.04083868509141</v>
+        <v>7.119627665330548</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.0406133835203</v>
+        <v>7.206376337441724</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.03994158250358</v>
+        <v>7.363707328119566</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.03916569547471</v>
+        <v>7.540554613947191</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.03841756570208</v>
+        <v>7.718270290367101</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.03766464160909</v>
+        <v>7.891152146455625</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.03686140718297</v>
+        <v>8.058861781087504</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.03599088853756</v>
+        <v>8.223951401713533</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.03504710419806</v>
+        <v>8.389977696223026</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.38.3</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.41677839163405</v>
+        <v>0.03878312554224959</v>
       </c>
       <c r="C21" t="n">
-        <v>10.49989288989755</v>
+        <v>0.03888045646987514</v>
       </c>
       <c r="D21" t="n">
-        <v>10.62721500438955</v>
+        <v>0.03899817883156354</v>
       </c>
       <c r="E21" t="n">
-        <v>10.75371558213798</v>
+        <v>0.0391163257670571</v>
       </c>
       <c r="F21" t="n">
-        <v>10.88165863490804</v>
+        <v>0.03922542727759555</v>
       </c>
       <c r="G21" t="n">
-        <v>11.0125838202117</v>
+        <v>0.03932677799776143</v>
       </c>
       <c r="H21" t="n">
-        <v>11.14889588194684</v>
+        <v>0.03942583852234491</v>
       </c>
       <c r="I21" t="n">
-        <v>11.29082650123824</v>
+        <v>0.03956044099731105</v>
       </c>
       <c r="J21" t="n">
-        <v>11.43139298493428</v>
+        <v>0.03961223889860608</v>
       </c>
       <c r="K21" t="n">
-        <v>11.58799686662585</v>
+        <v>0.03962992143932966</v>
       </c>
       <c r="L21" t="n">
-        <v>11.73461229387227</v>
+        <v>0.03972050463565197</v>
       </c>
       <c r="M21" t="n">
-        <v>11.86880833718122</v>
+        <v>0.03999373573984024</v>
       </c>
       <c r="N21" t="n">
-        <v>12.00390057128172</v>
+        <v>0.04040472907960254</v>
       </c>
       <c r="O21" t="n">
-        <v>12.16193773245956</v>
+        <v>0.04087419528080988</v>
       </c>
       <c r="P21" t="n">
-        <v>12.33495940749035</v>
+        <v>0.04136578347264097</v>
       </c>
       <c r="Q21" t="n">
-        <v>12.4868066391524</v>
+        <v>0.04180085088309777</v>
       </c>
       <c r="R21" t="n">
-        <v>12.59104021106149</v>
+        <v>0.04217136562942272</v>
       </c>
       <c r="S21" t="n">
-        <v>12.64703779423143</v>
+        <v>0.04251789380424287</v>
       </c>
       <c r="T21" t="n">
-        <v>12.66275694242431</v>
+        <v>0.04292014457821859</v>
       </c>
       <c r="U21" t="n">
-        <v>12.65611910161433</v>
+        <v>0.04331388725914025</v>
       </c>
       <c r="V21" t="n">
-        <v>12.65567667697276</v>
+        <v>0.04340856871175915</v>
       </c>
       <c r="W21" t="n">
-        <v>12.67191527021179</v>
+        <v>0.04304306044019102</v>
       </c>
       <c r="X21" t="n">
-        <v>12.68887573231013</v>
+        <v>0.04239710240376277</v>
       </c>
       <c r="Y21" t="n">
-        <v>12.706442570746</v>
+        <v>0.04171562565936275</v>
       </c>
       <c r="Z21" t="n">
-        <v>12.72341492250849</v>
+        <v>0.04128532960047193</v>
       </c>
       <c r="AA21" t="n">
-        <v>12.75202910582981</v>
+        <v>0.04110111054931134</v>
       </c>
       <c r="AB21" t="n">
-        <v>12.80440718288365</v>
+        <v>0.04102241697178571</v>
       </c>
       <c r="AC21" t="n">
-        <v>12.87529760018607</v>
+        <v>0.04103110704124712</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.95550478082803</v>
+        <v>0.04110089518993928</v>
       </c>
       <c r="AE21" t="n">
-        <v>13.03225639560133</v>
+        <v>0.04108457751455678</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.13348046764809</v>
+        <v>0.04075541745863209</v>
       </c>
       <c r="AG21" t="n">
-        <v>13.25133314058034</v>
+        <v>0.04025391234902669</v>
       </c>
       <c r="AH21" t="n">
-        <v>13.37342524003249</v>
+        <v>0.03975755065994539</v>
       </c>
       <c r="AI21" t="n">
-        <v>13.49507761185668</v>
+        <v>0.03926174373451469</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13.61552969458212</v>
+        <v>0.0387220169828215</v>
       </c>
       <c r="AK21" t="n">
-        <v>13.73628262826409</v>
+        <v>0.03811262157994798</v>
       </c>
       <c r="AL21" t="n">
-        <v>13.85887292595112</v>
+        <v>0.03741783924743407</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10.89075919456007</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10.9423382234318</v>
+      </c>
+      <c r="D22" t="n">
+        <v>10.99439150322927</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11.04594764615723</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11.09867998283132</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.15549310605534</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11.22417666844015</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11.31779192189344</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11.47579708206038</v>
+      </c>
+      <c r="K22" t="n">
+        <v>11.63664040543313</v>
+      </c>
+      <c r="L22" t="n">
+        <v>11.78392221763655</v>
+      </c>
+      <c r="M22" t="n">
+        <v>11.91639977186579</v>
+      </c>
+      <c r="N22" t="n">
+        <v>12.04914765886429</v>
+      </c>
+      <c r="O22" t="n">
+        <v>12.20640404332115</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12.37842537180212</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>12.52568736382358</v>
+      </c>
+      <c r="R22" t="n">
+        <v>12.62146985107338</v>
+      </c>
+      <c r="S22" t="n">
+        <v>12.66583936334128</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12.66883564300642</v>
+      </c>
+      <c r="U22" t="n">
+        <v>12.65123897734147</v>
+      </c>
+      <c r="V22" t="n">
+        <v>12.64426604648425</v>
+      </c>
+      <c r="W22" t="n">
+        <v>12.65885849598681</v>
+      </c>
+      <c r="X22" t="n">
+        <v>12.6758835246199</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.69494512383917</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>12.71453760666961</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>12.74600828624442</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12.80112760910988</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>12.87437332034181</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>12.95593002479213</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>13.03341583460062</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13.1417056264213</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.26935885113991</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>13.40166728673235</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>13.53363816209377</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>13.6645189431341</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>13.79593839729319</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>13.92974418511979</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
           <t>0.094</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>15.46442256271067</v>
-      </c>
-      <c r="C22" t="n">
-        <v>5.93725923371544</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5.687023214274229</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5.43351143852005</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5.17769895307514</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.9224667701289</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.675005885024619</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.436435086901231</v>
-      </c>
-      <c r="J22" t="n">
-        <v>4.20294575859206</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.04235372825587</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3.8441451557356</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.59648659857274</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.34986961957634</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.20744474531291</v>
-      </c>
-      <c r="P22" t="n">
-        <v>3.02976784349728</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.61566140126465</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.14872896986709</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.7242390262244</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.34797711518935</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.01144388294473</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.70723771280523</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.4458539043360999</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.2505851412568</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.1268610596615</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0.06563651862357001</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.04619930254166</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0.04438922300228</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0.04540412237792</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.04580244119295</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0.04536725220196</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0.04384632685741</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0.04243045835006</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0.04104084139428</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0.03965238903264</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.03825089649378999</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0.03682358461771</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0.03538632589048</v>
+      <c r="B23" t="n">
+        <v>12.16376298492087</v>
+      </c>
+      <c r="C23" t="n">
+        <v>11.03526514588653</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.933719716635233</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8.869085043051165</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7.850452560687772</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.886270792727413</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.98202056862571</v>
+      </c>
+      <c r="I23" t="n">
+        <v>5.132994748243938</v>
+      </c>
+      <c r="J23" t="n">
+        <v>4.769240352136932</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.26000900460514</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3.913914493167813</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.626181949908394</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.377319212883222</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.24406639537833</v>
+      </c>
+      <c r="P23" t="n">
+        <v>3.045646250392202</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.618562960824358</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.148778078398394</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.722912143996325</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.346288019737634</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01011379891579</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.7068330002593689</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.4464566394316656</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.2514648758822344</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.127344314379423</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.06574832161776935</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.04620697120137254</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.04439128472076492</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.04540526753430803</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.04580287168919814</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.0453673513814108</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0.04384638979201162</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.04243048804127023</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.04104084492821634</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.03965237263996822</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.03825086500931587</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.0368235417254675</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0.03538627438486949</v>
       </c>
     </row>
   </sheetData>
